--- a/VerveStacks_ZAF_grids_kan/ReportDefs_vervestacks.xlsx
+++ b/VerveStacks_ZAF_grids_kan/ReportDefs_vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ZAF_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A41DE0F7-1B4A-4B8F-B945-BC438B151E82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6B390E50-145B-487C-8B4A-EF57924035A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4159,7 +4159,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2ED04ADA-17E4-4B9B-8963-E6A1ED519EC0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{841F5866-C6D2-4B33-97E1-2ABDD4225304}">
   <dimension ref="B9:H245"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -27313,7 +27313,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4610E5C5-390D-4D3D-A3C5-BC26EAFCF79E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B587F0BB-ED18-4FEC-909A-60D40EAC4E48}">
   <dimension ref="B9:L245"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_ZAF_grids_kan/ReportDefs_vervestacks.xlsx
+++ b/VerveStacks_ZAF_grids_kan/ReportDefs_vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ZAF_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6B390E50-145B-487C-8B4A-EF57924035A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8C6E5D65-DA8B-456F-885A-8D8E63576E5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4159,7 +4159,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{841F5866-C6D2-4B33-97E1-2ABDD4225304}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46B9F38F-AB21-48D3-873F-3EFACE40E5D2}">
   <dimension ref="B9:H245"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -27313,7 +27313,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B587F0BB-ED18-4FEC-909A-60D40EAC4E48}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B92A12C7-4B74-4AD0-9615-673027657D35}">
   <dimension ref="B9:L245"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_ZAF_grids_kan/ReportDefs_vervestacks.xlsx
+++ b/VerveStacks_ZAF_grids_kan/ReportDefs_vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ZAF_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{798178D7-3CE3-449A-8836-909727B56FA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{68444E5E-7854-47AE-8412-297D662C2BAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4108,7 +4108,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BB149D8-CA8F-4B9C-907D-6FE038F6486A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{725E4E88-7490-4B8F-B4D7-E6AC2C1384AD}">
   <dimension ref="B9:H245"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -27334,7 +27334,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57D878D5-8030-4EFA-BCE4-47E0FBF2CFA6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11909A5F-2A32-4715-AB8B-16AAB5536F1B}">
   <dimension ref="B9:L245"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_ZAF_grids_kan/ReportDefs_vervestacks.xlsx
+++ b/VerveStacks_ZAF_grids_kan/ReportDefs_vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ZAF_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{68444E5E-7854-47AE-8412-297D662C2BAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7C0C1BC3-DEF0-4F99-B1EE-49BCB93704A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4108,7 +4108,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{725E4E88-7490-4B8F-B4D7-E6AC2C1384AD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23C05EA4-DACE-42DA-82C5-F08A3C364498}">
   <dimension ref="B9:H245"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -27334,7 +27334,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11909A5F-2A32-4715-AB8B-16AAB5536F1B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{745583BE-0FD4-4ECF-A666-FBB0A7895B12}">
   <dimension ref="B9:L245"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_ZAF_grids_kan/ReportDefs_vervestacks.xlsx
+++ b/VerveStacks_ZAF_grids_kan/ReportDefs_vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ZAF_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7C0C1BC3-DEF0-4F99-B1EE-49BCB93704A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2ABA65BC-AF1D-4984-B83B-B52A6BC8D425}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4108,7 +4108,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23C05EA4-DACE-42DA-82C5-F08A3C364498}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F175388-9429-4F9E-A362-E0547F7A4832}">
   <dimension ref="B9:H245"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -27334,7 +27334,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{745583BE-0FD4-4ECF-A666-FBB0A7895B12}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2618314-D8B4-48A9-9E94-4DDD757A7306}">
   <dimension ref="B9:L245"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_ZAF_grids_kan/ReportDefs_vervestacks.xlsx
+++ b/VerveStacks_ZAF_grids_kan/ReportDefs_vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ZAF_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2ABA65BC-AF1D-4984-B83B-B52A6BC8D425}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D66D83ED-8E09-4AEA-B331-25E0BAF41FE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4108,7 +4108,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F175388-9429-4F9E-A362-E0547F7A4832}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C03DEF98-214F-4D0C-82DB-72CF530D17C5}">
   <dimension ref="B9:H245"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -27334,7 +27334,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2618314-D8B4-48A9-9E94-4DDD757A7306}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1105066-C8F1-4BEE-A78C-5CAA075F84F5}">
   <dimension ref="B9:L245"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_ZAF_grids_kan/ReportDefs_vervestacks.xlsx
+++ b/VerveStacks_ZAF_grids_kan/ReportDefs_vervestacks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_ZAF_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74633503-E39D-4A0E-BDC9-52411B7B5ABE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61AB18DB-B0A1-4C49-BECB-47C956B02296}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="geolocation" sheetId="72" r:id="rId1"/>
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7378" uniqueCount="1133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7603" uniqueCount="1167">
   <si>
     <t>Unit</t>
   </si>
@@ -3355,123 +3355,24 @@
     <t>coal_flex</t>
   </si>
   <si>
-    <t>~Scenmap</t>
-  </si>
-  <si>
     <t>DEF</t>
   </si>
   <si>
     <t>GAS</t>
   </si>
   <si>
-    <t>Lo.0.CF1.Y.Y</t>
-  </si>
-  <si>
     <t>Lo</t>
   </si>
   <si>
     <t>Y</t>
   </si>
   <si>
-    <t>Hi.0.CF1.Y.Y</t>
-  </si>
-  <si>
     <t>Hi</t>
   </si>
   <si>
-    <t>Lo.95.CF1.Y.Y</t>
-  </si>
-  <si>
-    <t>Hi.95.CF1.Y.Y</t>
-  </si>
-  <si>
-    <t>Lo.0.CF1.N.Y</t>
-  </si>
-  <si>
     <t>N</t>
   </si>
   <si>
-    <t>Hi.0.CF1.N.Y</t>
-  </si>
-  <si>
-    <t>Lo.95.CF1.N.Y</t>
-  </si>
-  <si>
-    <t>Hi.95.CF1.N.Y</t>
-  </si>
-  <si>
-    <t>Lo.0.CF6.Y.Y</t>
-  </si>
-  <si>
-    <t>Hi.0.CF6.Y.Y</t>
-  </si>
-  <si>
-    <t>Lo.95.CF6.Y.Y</t>
-  </si>
-  <si>
-    <t>Hi.95.CF6.Y.Y</t>
-  </si>
-  <si>
-    <t>Lo.0.CF6.N.Y</t>
-  </si>
-  <si>
-    <t>Hi.0.CF6.N.Y</t>
-  </si>
-  <si>
-    <t>Lo.95.CF6.N.Y</t>
-  </si>
-  <si>
-    <t>Hi.95.CF6.N.Y</t>
-  </si>
-  <si>
-    <t>Lo.0.CF1.Y.N</t>
-  </si>
-  <si>
-    <t>Hi.0.CF1.Y.N</t>
-  </si>
-  <si>
-    <t>Lo.95.CF1.Y.N</t>
-  </si>
-  <si>
-    <t>Hi.95.CF1.Y.N</t>
-  </si>
-  <si>
-    <t>Lo.0.CF1.N.N</t>
-  </si>
-  <si>
-    <t>Hi.0.CF1.N.N</t>
-  </si>
-  <si>
-    <t>Lo.95.CF1.N.N</t>
-  </si>
-  <si>
-    <t>Hi.95.CF1.N.N</t>
-  </si>
-  <si>
-    <t>Lo.0.CF6.Y.N</t>
-  </si>
-  <si>
-    <t>Hi.0.CF6.Y.N</t>
-  </si>
-  <si>
-    <t>Lo.95.CF6.Y.N</t>
-  </si>
-  <si>
-    <t>Hi.95.CF6.Y.N</t>
-  </si>
-  <si>
-    <t>Lo.0.CF6.N.N</t>
-  </si>
-  <si>
-    <t>Hi.0.CF6.N.N</t>
-  </si>
-  <si>
-    <t>Lo.95.CF6.N.N</t>
-  </si>
-  <si>
-    <t>Hi.95.CF6.N.N</t>
-  </si>
-  <si>
     <t>dm</t>
   </si>
   <si>
@@ -3482,6 +3383,207 @@
   </si>
   <si>
     <t>ga</t>
+  </si>
+  <si>
+    <t>trancost</t>
+  </si>
+  <si>
+    <t>Lo.0.CF1.Y.Y.Y</t>
+  </si>
+  <si>
+    <t>Hi.0.CF1.Y.Y.Y</t>
+  </si>
+  <si>
+    <t>Lo.95.CF1.Y.Y.Y</t>
+  </si>
+  <si>
+    <t>Hi.95.CF1.Y.Y.Y</t>
+  </si>
+  <si>
+    <t>Lo.0.CF1.N.Y.Y</t>
+  </si>
+  <si>
+    <t>Hi.0.CF1.N.Y.Y</t>
+  </si>
+  <si>
+    <t>Lo.95.CF1.N.Y.Y</t>
+  </si>
+  <si>
+    <t>Hi.95.CF1.N.Y.Y</t>
+  </si>
+  <si>
+    <t>Lo.0.CF6.Y.Y.Y</t>
+  </si>
+  <si>
+    <t>Hi.0.CF6.Y.Y.Y</t>
+  </si>
+  <si>
+    <t>Lo.95.CF6.Y.Y.Y</t>
+  </si>
+  <si>
+    <t>Hi.95.CF6.Y.Y.Y</t>
+  </si>
+  <si>
+    <t>Lo.0.CF6.N.Y.Y</t>
+  </si>
+  <si>
+    <t>Hi.0.CF6.N.Y.Y</t>
+  </si>
+  <si>
+    <t>Lo.95.CF6.N.Y.Y</t>
+  </si>
+  <si>
+    <t>Hi.95.CF6.N.Y.Y</t>
+  </si>
+  <si>
+    <t>Lo.0.CF1.Y.N.Y</t>
+  </si>
+  <si>
+    <t>Hi.0.CF1.Y.N.Y</t>
+  </si>
+  <si>
+    <t>Lo.95.CF1.Y.N.Y</t>
+  </si>
+  <si>
+    <t>Hi.95.CF1.Y.N.Y</t>
+  </si>
+  <si>
+    <t>Lo.0.CF1.N.N.Y</t>
+  </si>
+  <si>
+    <t>Hi.0.CF1.N.N.Y</t>
+  </si>
+  <si>
+    <t>Lo.95.CF1.N.N.Y</t>
+  </si>
+  <si>
+    <t>Hi.95.CF1.N.N.Y</t>
+  </si>
+  <si>
+    <t>Lo.0.CF6.Y.N.Y</t>
+  </si>
+  <si>
+    <t>Hi.0.CF6.Y.N.Y</t>
+  </si>
+  <si>
+    <t>Lo.95.CF6.Y.N.Y</t>
+  </si>
+  <si>
+    <t>Hi.95.CF6.Y.N.Y</t>
+  </si>
+  <si>
+    <t>Lo.0.CF6.N.N.Y</t>
+  </si>
+  <si>
+    <t>Hi.0.CF6.N.N.Y</t>
+  </si>
+  <si>
+    <t>Lo.95.CF6.N.N.Y</t>
+  </si>
+  <si>
+    <t>Hi.95.CF6.N.N.Y</t>
+  </si>
+  <si>
+    <t>Lo.0.CF1.Y.Y.N</t>
+  </si>
+  <si>
+    <t>Hi.0.CF1.Y.Y.N</t>
+  </si>
+  <si>
+    <t>Lo.95.CF1.Y.Y.N</t>
+  </si>
+  <si>
+    <t>Hi.95.CF1.Y.Y.N</t>
+  </si>
+  <si>
+    <t>Lo.0.CF1.N.Y.N</t>
+  </si>
+  <si>
+    <t>Hi.0.CF1.N.Y.N</t>
+  </si>
+  <si>
+    <t>Lo.95.CF1.N.Y.N</t>
+  </si>
+  <si>
+    <t>Hi.95.CF1.N.Y.N</t>
+  </si>
+  <si>
+    <t>Lo.0.CF6.Y.Y.N</t>
+  </si>
+  <si>
+    <t>Hi.0.CF6.Y.Y.N</t>
+  </si>
+  <si>
+    <t>Lo.95.CF6.Y.Y.N</t>
+  </si>
+  <si>
+    <t>Hi.95.CF6.Y.Y.N</t>
+  </si>
+  <si>
+    <t>Lo.0.CF6.N.Y.N</t>
+  </si>
+  <si>
+    <t>Hi.0.CF6.N.Y.N</t>
+  </si>
+  <si>
+    <t>Lo.95.CF6.N.Y.N</t>
+  </si>
+  <si>
+    <t>Hi.95.CF6.N.Y.N</t>
+  </si>
+  <si>
+    <t>Lo.0.CF1.Y.N.N</t>
+  </si>
+  <si>
+    <t>Hi.0.CF1.Y.N.N</t>
+  </si>
+  <si>
+    <t>Lo.95.CF1.Y.N.N</t>
+  </si>
+  <si>
+    <t>Hi.95.CF1.Y.N.N</t>
+  </si>
+  <si>
+    <t>Lo.0.CF1.N.N.N</t>
+  </si>
+  <si>
+    <t>Hi.0.CF1.N.N.N</t>
+  </si>
+  <si>
+    <t>Lo.95.CF1.N.N.N</t>
+  </si>
+  <si>
+    <t>Hi.95.CF1.N.N.N</t>
+  </si>
+  <si>
+    <t>Lo.0.CF6.Y.N.N</t>
+  </si>
+  <si>
+    <t>Hi.0.CF6.Y.N.N</t>
+  </si>
+  <si>
+    <t>Lo.95.CF6.Y.N.N</t>
+  </si>
+  <si>
+    <t>Hi.95.CF6.Y.N.N</t>
+  </si>
+  <si>
+    <t>Lo.0.CF6.N.N.N</t>
+  </si>
+  <si>
+    <t>Hi.0.CF6.N.N.N</t>
+  </si>
+  <si>
+    <t>Lo.95.CF6.N.N.N</t>
+  </si>
+  <si>
+    <t>Hi.95.CF6.N.N.N</t>
+  </si>
+  <si>
+    <t>tc</t>
+  </si>
+  <si>
+    <t>ELE,STG,IRE,grid,aggregators</t>
   </si>
 </sst>
 </file>
@@ -34116,7 +34218,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C50B696F-B355-4FC5-AD3E-AFDC509F717D}">
-  <dimension ref="B1:AC37"/>
+  <dimension ref="B1:AE69"/>
   <sheetFormatPr defaultColWidth="14.73046875" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="2.73046875" bestFit="1" customWidth="1"/>
@@ -34130,40 +34232,43 @@
     <col min="11" max="11" width="9.3984375" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="6.33203125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="6.53125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="6.53125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11.796875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="7.06640625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="7.1328125" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="7.3984375" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="6.796875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="6.33203125" customWidth="1"/>
-    <col min="24" max="24" width="2.73046875" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="5.6640625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="4.1328125" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="3.59765625" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="3.86328125" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="4.1328125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="6.53125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11.796875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="7.06640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="7.1328125" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="7.3984375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="6.796875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="6.33203125" customWidth="1"/>
+    <col min="25" max="25" width="2.73046875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="5.6640625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="4.1328125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="3.59765625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="3.86328125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="4.1328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:29">
+    <row r="1" spans="2:31">
       <c r="I1" t="s">
         <v>35</v>
       </c>
-      <c r="R1" t="s">
-        <v>1129</v>
-      </c>
       <c r="S1" t="s">
-        <v>1130</v>
-      </c>
-      <c r="U1" t="s">
-        <v>1131</v>
+        <v>1096</v>
+      </c>
+      <c r="T1" t="s">
+        <v>1097</v>
       </c>
       <c r="V1" t="s">
-        <v>1132</v>
-      </c>
-    </row>
-    <row r="2" spans="2:29">
+        <v>1098</v>
+      </c>
+      <c r="W1" t="s">
+        <v>1099</v>
+      </c>
+      <c r="X1" t="s">
+        <v>1165</v>
+      </c>
+    </row>
+    <row r="2" spans="2:31">
       <c r="I2" t="s">
         <v>1084</v>
       </c>
@@ -34174,18 +34279,15 @@
         <v>1089</v>
       </c>
     </row>
-    <row r="4" spans="2:29">
+    <row r="4" spans="2:31">
       <c r="B4" t="s">
         <v>57</v>
       </c>
       <c r="H4" t="s">
         <v>58</v>
       </c>
-      <c r="P4" t="s">
-        <v>1090</v>
-      </c>
-    </row>
-    <row r="5" spans="2:29">
+    </row>
+    <row r="5" spans="2:31">
       <c r="B5" t="s">
         <v>19</v>
       </c>
@@ -34202,11 +34304,11 @@
         <v>8</v>
       </c>
       <c r="I5" t="str">
-        <f>"sg_"&amp;R5</f>
+        <f>"sg_"&amp;S5</f>
         <v>sg_demand</v>
       </c>
       <c r="J5" t="str">
-        <f t="shared" ref="J5:M5" si="0">"sg_"&amp;S5</f>
+        <f t="shared" ref="J5:N5" si="0">"sg_"&amp;T5</f>
         <v>sg_co2price</v>
       </c>
       <c r="K5" t="str">
@@ -34221,54 +34323,61 @@
         <f t="shared" si="0"/>
         <v>sg_GAS</v>
       </c>
-      <c r="O5" t="s">
+      <c r="N5" t="str">
+        <f t="shared" si="0"/>
+        <v>sg_trancost</v>
+      </c>
+      <c r="P5" t="s">
         <v>237</v>
       </c>
-      <c r="P5" t="s">
+      <c r="Q5" t="s">
         <v>238</v>
       </c>
-      <c r="Q5" t="s">
+      <c r="R5" t="s">
         <v>239</v>
       </c>
-      <c r="R5" t="s">
+      <c r="S5" t="s">
         <v>1084</v>
       </c>
-      <c r="S5" t="s">
+      <c r="T5" t="s">
         <v>1085</v>
       </c>
-      <c r="T5" t="s">
+      <c r="U5" t="s">
         <v>1086</v>
       </c>
-      <c r="U5" t="s">
+      <c r="V5" t="s">
+        <v>1090</v>
+      </c>
+      <c r="W5" t="s">
         <v>1091</v>
       </c>
-      <c r="V5" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="6" spans="2:29">
+      <c r="X5" t="s">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="6" spans="2:31">
       <c r="B6" t="str">
-        <f>"vs~"&amp;TEXT(Q6,"0000")</f>
+        <f>"vs~"&amp;TEXT(R6,"0000")</f>
         <v>vs~0001</v>
       </c>
       <c r="C6" t="str">
         <f>H6</f>
-        <v>df-Y.ga-Y.dm-Lo.cp-0.CF1</v>
+        <v>tc-Y.df-Y.ga-Y.dm-Lo.cp-0.CF1</v>
       </c>
       <c r="H6" t="str">
-        <f>_xlfn.TEXTJOIN(".",TRUE,AB6:AD6)&amp;"."&amp;_xlfn.TEXTJOIN(".",TRUE,Y6:AA6)</f>
-        <v>df-Y.ga-Y.dm-Lo.cp-0.CF1</v>
+        <f>_xlfn.TEXTJOIN(".",TRUE,AE6,AC6:AD6)&amp;"."&amp;_xlfn.TEXTJOIN(".",TRUE,Z6:AB6)</f>
+        <v>tc-Y.df-Y.ga-Y.dm-Lo.cp-0.CF1</v>
       </c>
       <c r="I6" t="str">
-        <f>R6</f>
+        <f>S6</f>
         <v>Lo</v>
       </c>
       <c r="J6" t="str">
-        <f>TEXT(S6,"00")</f>
+        <f>TEXT(T6,"00")</f>
         <v>00</v>
       </c>
       <c r="K6" t="str">
-        <f t="shared" ref="K6:M6" si="1">T6</f>
+        <f t="shared" ref="K6:N6" si="1">U6</f>
         <v>CF1</v>
       </c>
       <c r="L6" t="str">
@@ -34279,141 +34388,163 @@
         <f t="shared" si="1"/>
         <v>Y</v>
       </c>
-      <c r="O6">
+      <c r="N6" t="str">
+        <f t="shared" si="1"/>
+        <v>Y</v>
+      </c>
+      <c r="P6">
         <v>5</v>
       </c>
-      <c r="P6" t="s">
+      <c r="Q6" t="s">
+        <v>1101</v>
+      </c>
+      <c r="R6">
+        <v>1</v>
+      </c>
+      <c r="S6" t="s">
+        <v>1092</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6" t="s">
+        <v>1087</v>
+      </c>
+      <c r="V6" t="s">
         <v>1093</v>
       </c>
-      <c r="Q6">
-        <v>1</v>
-      </c>
-      <c r="R6" t="s">
-        <v>1094</v>
-      </c>
-      <c r="S6">
-        <v>0</v>
-      </c>
-      <c r="T6" t="s">
-        <v>1087</v>
-      </c>
-      <c r="U6" t="s">
-        <v>1095</v>
-      </c>
-      <c r="V6" t="s">
-        <v>1095</v>
-      </c>
-      <c r="Y6" t="str">
-        <f>R$1&amp;"-"&amp;R6</f>
-        <v>dm-Lo</v>
+      <c r="W6" t="s">
+        <v>1093</v>
+      </c>
+      <c r="X6" t="s">
+        <v>1093</v>
       </c>
       <c r="Z6" t="str">
         <f>S$1&amp;"-"&amp;S6</f>
+        <v>dm-Lo</v>
+      </c>
+      <c r="AA6" t="str">
+        <f>T$1&amp;"-"&amp;T6</f>
         <v>cp-0</v>
       </c>
-      <c r="AA6" t="str">
-        <f>T6</f>
+      <c r="AB6" t="str">
+        <f>U6</f>
         <v>CF1</v>
-      </c>
-      <c r="AB6" t="str">
-        <f>U$1&amp;"-"&amp;U6</f>
-        <v>df-Y</v>
       </c>
       <c r="AC6" t="str">
         <f>V$1&amp;"-"&amp;V6</f>
+        <v>df-Y</v>
+      </c>
+      <c r="AD6" t="str">
+        <f>W$1&amp;"-"&amp;W6</f>
         <v>ga-Y</v>
       </c>
-    </row>
-    <row r="7" spans="2:29">
+      <c r="AE6" t="str">
+        <f>X$1&amp;"-"&amp;X6</f>
+        <v>tc-Y</v>
+      </c>
+    </row>
+    <row r="7" spans="2:31">
       <c r="B7" t="str">
-        <f t="shared" ref="B7:B17" si="2">"vs~"&amp;TEXT(Q7,"0000")</f>
+        <f t="shared" ref="B7:B17" si="2">"vs~"&amp;TEXT(R7,"0000")</f>
         <v>vs~0002</v>
       </c>
       <c r="C7" t="str">
         <f t="shared" ref="C7:C17" si="3">H7</f>
-        <v>df-Y.ga-Y.dm-Hi.cp-0.CF1</v>
+        <v>tc-Y.df-Y.ga-Y.dm-Hi.cp-0.CF1</v>
       </c>
       <c r="H7" t="str">
-        <f t="shared" ref="H7:H37" si="4">_xlfn.TEXTJOIN(".",TRUE,AB7:AD7)&amp;"."&amp;_xlfn.TEXTJOIN(".",TRUE,Y7:AA7)</f>
-        <v>df-Y.ga-Y.dm-Hi.cp-0.CF1</v>
+        <f t="shared" ref="H7:H37" si="4">_xlfn.TEXTJOIN(".",TRUE,AE7,AC7:AD7)&amp;"."&amp;_xlfn.TEXTJOIN(".",TRUE,Z7:AB7)</f>
+        <v>tc-Y.df-Y.ga-Y.dm-Hi.cp-0.CF1</v>
       </c>
       <c r="I7" t="str">
-        <f t="shared" ref="I7:I37" si="5">R7</f>
+        <f t="shared" ref="I7:I37" si="5">S7</f>
         <v>Hi</v>
       </c>
       <c r="J7" t="str">
-        <f t="shared" ref="J7:J37" si="6">TEXT(S7,"00")</f>
+        <f t="shared" ref="J7:J37" si="6">TEXT(T7,"00")</f>
         <v>00</v>
       </c>
       <c r="K7" t="str">
-        <f t="shared" ref="K7:K37" si="7">T7</f>
+        <f t="shared" ref="K7:K37" si="7">U7</f>
         <v>CF1</v>
       </c>
       <c r="L7" t="str">
-        <f t="shared" ref="L7:L37" si="8">U7</f>
+        <f t="shared" ref="L7:L37" si="8">V7</f>
         <v>Y</v>
       </c>
       <c r="M7" t="str">
-        <f t="shared" ref="M7:M37" si="9">V7</f>
+        <f t="shared" ref="M7:N37" si="9">W7</f>
         <v>Y</v>
       </c>
-      <c r="O7">
+      <c r="N7" t="str">
+        <f t="shared" si="9"/>
+        <v>Y</v>
+      </c>
+      <c r="P7">
         <v>5</v>
       </c>
-      <c r="P7" t="s">
-        <v>1096</v>
-      </c>
-      <c r="Q7">
+      <c r="Q7" t="s">
+        <v>1102</v>
+      </c>
+      <c r="R7">
         <v>2</v>
       </c>
-      <c r="R7" t="s">
-        <v>1097</v>
-      </c>
-      <c r="S7">
+      <c r="S7" t="s">
+        <v>1094</v>
+      </c>
+      <c r="T7">
         <v>0</v>
       </c>
-      <c r="T7" t="s">
+      <c r="U7" t="s">
         <v>1087</v>
       </c>
-      <c r="U7" t="s">
-        <v>1095</v>
-      </c>
       <c r="V7" t="s">
-        <v>1095</v>
-      </c>
-      <c r="Y7" t="str">
-        <f t="shared" ref="Y7:Y37" si="10">R$1&amp;"-"&amp;R7</f>
+        <v>1093</v>
+      </c>
+      <c r="W7" t="s">
+        <v>1093</v>
+      </c>
+      <c r="X7" t="s">
+        <v>1093</v>
+      </c>
+      <c r="Z7" t="str">
+        <f t="shared" ref="Z7:Z37" si="10">S$1&amp;"-"&amp;S7</f>
         <v>dm-Hi</v>
       </c>
-      <c r="Z7" t="str">
-        <f t="shared" ref="Z7:Z37" si="11">S$1&amp;"-"&amp;S7</f>
+      <c r="AA7" t="str">
+        <f t="shared" ref="AA7:AA37" si="11">T$1&amp;"-"&amp;T7</f>
         <v>cp-0</v>
       </c>
-      <c r="AA7" t="str">
-        <f t="shared" ref="AA7:AA37" si="12">T7</f>
+      <c r="AB7" t="str">
+        <f t="shared" ref="AB7:AB37" si="12">U7</f>
         <v>CF1</v>
       </c>
-      <c r="AB7" t="str">
-        <f t="shared" ref="AB7:AB37" si="13">U$1&amp;"-"&amp;U7</f>
+      <c r="AC7" t="str">
+        <f t="shared" ref="AC7:AC37" si="13">V$1&amp;"-"&amp;V7</f>
         <v>df-Y</v>
       </c>
-      <c r="AC7" t="str">
-        <f t="shared" ref="AC7:AC37" si="14">V$1&amp;"-"&amp;V7</f>
+      <c r="AD7" t="str">
+        <f t="shared" ref="AD7:AE37" si="14">W$1&amp;"-"&amp;W7</f>
         <v>ga-Y</v>
       </c>
-    </row>
-    <row r="8" spans="2:29">
+      <c r="AE7" t="str">
+        <f t="shared" si="14"/>
+        <v>tc-Y</v>
+      </c>
+    </row>
+    <row r="8" spans="2:31">
       <c r="B8" t="str">
         <f t="shared" si="2"/>
         <v>vs~0003</v>
       </c>
       <c r="C8" t="str">
         <f t="shared" si="3"/>
-        <v>df-Y.ga-Y.dm-Lo.cp-95.CF1</v>
+        <v>tc-Y.df-Y.ga-Y.dm-Lo.cp-95.CF1</v>
       </c>
       <c r="H8" t="str">
         <f t="shared" si="4"/>
-        <v>df-Y.ga-Y.dm-Lo.cp-95.CF1</v>
+        <v>tc-Y.df-Y.ga-Y.dm-Lo.cp-95.CF1</v>
       </c>
       <c r="I8" t="str">
         <f t="shared" si="5"/>
@@ -34435,63 +34566,74 @@
         <f t="shared" si="9"/>
         <v>Y</v>
       </c>
-      <c r="O8">
+      <c r="N8" t="str">
+        <f t="shared" si="9"/>
+        <v>Y</v>
+      </c>
+      <c r="P8">
         <v>5</v>
       </c>
-      <c r="P8" t="s">
-        <v>1098</v>
-      </c>
-      <c r="Q8">
+      <c r="Q8" t="s">
+        <v>1103</v>
+      </c>
+      <c r="R8">
         <v>3</v>
       </c>
-      <c r="R8" t="s">
-        <v>1094</v>
-      </c>
-      <c r="S8">
+      <c r="S8" t="s">
+        <v>1092</v>
+      </c>
+      <c r="T8">
         <v>95</v>
       </c>
-      <c r="T8" t="s">
+      <c r="U8" t="s">
         <v>1087</v>
       </c>
-      <c r="U8" t="s">
-        <v>1095</v>
-      </c>
       <c r="V8" t="s">
-        <v>1095</v>
-      </c>
-      <c r="Y8" t="str">
+        <v>1093</v>
+      </c>
+      <c r="W8" t="s">
+        <v>1093</v>
+      </c>
+      <c r="X8" t="s">
+        <v>1093</v>
+      </c>
+      <c r="Z8" t="str">
         <f t="shared" si="10"/>
         <v>dm-Lo</v>
       </c>
-      <c r="Z8" t="str">
+      <c r="AA8" t="str">
         <f t="shared" si="11"/>
         <v>cp-95</v>
       </c>
-      <c r="AA8" t="str">
+      <c r="AB8" t="str">
         <f t="shared" si="12"/>
         <v>CF1</v>
       </c>
-      <c r="AB8" t="str">
+      <c r="AC8" t="str">
         <f t="shared" si="13"/>
         <v>df-Y</v>
       </c>
-      <c r="AC8" t="str">
+      <c r="AD8" t="str">
         <f t="shared" si="14"/>
         <v>ga-Y</v>
       </c>
-    </row>
-    <row r="9" spans="2:29">
+      <c r="AE8" t="str">
+        <f t="shared" si="14"/>
+        <v>tc-Y</v>
+      </c>
+    </row>
+    <row r="9" spans="2:31">
       <c r="B9" t="str">
         <f t="shared" si="2"/>
         <v>vs~0004</v>
       </c>
       <c r="C9" t="str">
         <f t="shared" si="3"/>
-        <v>df-Y.ga-Y.dm-Hi.cp-95.CF1</v>
+        <v>tc-Y.df-Y.ga-Y.dm-Hi.cp-95.CF1</v>
       </c>
       <c r="H9" t="str">
         <f t="shared" si="4"/>
-        <v>df-Y.ga-Y.dm-Hi.cp-95.CF1</v>
+        <v>tc-Y.df-Y.ga-Y.dm-Hi.cp-95.CF1</v>
       </c>
       <c r="I9" t="str">
         <f t="shared" si="5"/>
@@ -34513,63 +34655,74 @@
         <f t="shared" si="9"/>
         <v>Y</v>
       </c>
-      <c r="O9">
+      <c r="N9" t="str">
+        <f t="shared" si="9"/>
+        <v>Y</v>
+      </c>
+      <c r="P9">
         <v>5</v>
       </c>
-      <c r="P9" t="s">
-        <v>1099</v>
-      </c>
-      <c r="Q9">
+      <c r="Q9" t="s">
+        <v>1104</v>
+      </c>
+      <c r="R9">
         <v>4</v>
       </c>
-      <c r="R9" t="s">
-        <v>1097</v>
-      </c>
-      <c r="S9">
+      <c r="S9" t="s">
+        <v>1094</v>
+      </c>
+      <c r="T9">
         <v>95</v>
       </c>
-      <c r="T9" t="s">
+      <c r="U9" t="s">
         <v>1087</v>
       </c>
-      <c r="U9" t="s">
-        <v>1095</v>
-      </c>
       <c r="V9" t="s">
-        <v>1095</v>
-      </c>
-      <c r="Y9" t="str">
+        <v>1093</v>
+      </c>
+      <c r="W9" t="s">
+        <v>1093</v>
+      </c>
+      <c r="X9" t="s">
+        <v>1093</v>
+      </c>
+      <c r="Z9" t="str">
         <f t="shared" si="10"/>
         <v>dm-Hi</v>
       </c>
-      <c r="Z9" t="str">
+      <c r="AA9" t="str">
         <f t="shared" si="11"/>
         <v>cp-95</v>
       </c>
-      <c r="AA9" t="str">
+      <c r="AB9" t="str">
         <f t="shared" si="12"/>
         <v>CF1</v>
       </c>
-      <c r="AB9" t="str">
+      <c r="AC9" t="str">
         <f t="shared" si="13"/>
         <v>df-Y</v>
       </c>
-      <c r="AC9" t="str">
+      <c r="AD9" t="str">
         <f t="shared" si="14"/>
         <v>ga-Y</v>
       </c>
-    </row>
-    <row r="10" spans="2:29">
+      <c r="AE9" t="str">
+        <f t="shared" si="14"/>
+        <v>tc-Y</v>
+      </c>
+    </row>
+    <row r="10" spans="2:31">
       <c r="B10" t="str">
         <f t="shared" si="2"/>
         <v>vs~0005</v>
       </c>
       <c r="C10" t="str">
         <f t="shared" si="3"/>
-        <v>df-N.ga-Y.dm-Lo.cp-0.CF1</v>
+        <v>tc-Y.df-N.ga-Y.dm-Lo.cp-0.CF1</v>
       </c>
       <c r="H10" t="str">
         <f t="shared" si="4"/>
-        <v>df-N.ga-Y.dm-Lo.cp-0.CF1</v>
+        <v>tc-Y.df-N.ga-Y.dm-Lo.cp-0.CF1</v>
       </c>
       <c r="I10" t="str">
         <f t="shared" si="5"/>
@@ -34591,63 +34744,74 @@
         <f t="shared" si="9"/>
         <v>Y</v>
       </c>
-      <c r="O10">
+      <c r="N10" t="str">
+        <f t="shared" si="9"/>
+        <v>Y</v>
+      </c>
+      <c r="P10">
         <v>5</v>
       </c>
-      <c r="P10" t="s">
-        <v>1100</v>
-      </c>
-      <c r="Q10">
+      <c r="Q10" t="s">
+        <v>1105</v>
+      </c>
+      <c r="R10">
         <v>5</v>
       </c>
-      <c r="R10" t="s">
-        <v>1094</v>
-      </c>
-      <c r="S10">
+      <c r="S10" t="s">
+        <v>1092</v>
+      </c>
+      <c r="T10">
         <v>0</v>
       </c>
-      <c r="T10" t="s">
+      <c r="U10" t="s">
         <v>1087</v>
-      </c>
-      <c r="U10" t="s">
-        <v>1101</v>
       </c>
       <c r="V10" t="s">
         <v>1095</v>
       </c>
-      <c r="Y10" t="str">
+      <c r="W10" t="s">
+        <v>1093</v>
+      </c>
+      <c r="X10" t="s">
+        <v>1093</v>
+      </c>
+      <c r="Z10" t="str">
         <f t="shared" si="10"/>
         <v>dm-Lo</v>
       </c>
-      <c r="Z10" t="str">
+      <c r="AA10" t="str">
         <f t="shared" si="11"/>
         <v>cp-0</v>
       </c>
-      <c r="AA10" t="str">
+      <c r="AB10" t="str">
         <f t="shared" si="12"/>
         <v>CF1</v>
       </c>
-      <c r="AB10" t="str">
+      <c r="AC10" t="str">
         <f t="shared" si="13"/>
         <v>df-N</v>
       </c>
-      <c r="AC10" t="str">
+      <c r="AD10" t="str">
         <f t="shared" si="14"/>
         <v>ga-Y</v>
       </c>
-    </row>
-    <row r="11" spans="2:29">
+      <c r="AE10" t="str">
+        <f t="shared" si="14"/>
+        <v>tc-Y</v>
+      </c>
+    </row>
+    <row r="11" spans="2:31">
       <c r="B11" t="str">
         <f t="shared" si="2"/>
         <v>vs~0006</v>
       </c>
       <c r="C11" t="str">
         <f t="shared" si="3"/>
-        <v>df-N.ga-Y.dm-Hi.cp-0.CF1</v>
+        <v>tc-Y.df-N.ga-Y.dm-Hi.cp-0.CF1</v>
       </c>
       <c r="H11" t="str">
         <f t="shared" si="4"/>
-        <v>df-N.ga-Y.dm-Hi.cp-0.CF1</v>
+        <v>tc-Y.df-N.ga-Y.dm-Hi.cp-0.CF1</v>
       </c>
       <c r="I11" t="str">
         <f t="shared" si="5"/>
@@ -34669,63 +34833,74 @@
         <f t="shared" si="9"/>
         <v>Y</v>
       </c>
-      <c r="O11">
+      <c r="N11" t="str">
+        <f t="shared" si="9"/>
+        <v>Y</v>
+      </c>
+      <c r="P11">
         <v>5</v>
       </c>
-      <c r="P11" t="s">
-        <v>1102</v>
-      </c>
-      <c r="Q11">
+      <c r="Q11" t="s">
+        <v>1106</v>
+      </c>
+      <c r="R11">
         <v>6</v>
       </c>
-      <c r="R11" t="s">
-        <v>1097</v>
-      </c>
-      <c r="S11">
+      <c r="S11" t="s">
+        <v>1094</v>
+      </c>
+      <c r="T11">
         <v>0</v>
       </c>
-      <c r="T11" t="s">
+      <c r="U11" t="s">
         <v>1087</v>
-      </c>
-      <c r="U11" t="s">
-        <v>1101</v>
       </c>
       <c r="V11" t="s">
         <v>1095</v>
       </c>
-      <c r="Y11" t="str">
+      <c r="W11" t="s">
+        <v>1093</v>
+      </c>
+      <c r="X11" t="s">
+        <v>1093</v>
+      </c>
+      <c r="Z11" t="str">
         <f t="shared" si="10"/>
         <v>dm-Hi</v>
       </c>
-      <c r="Z11" t="str">
+      <c r="AA11" t="str">
         <f t="shared" si="11"/>
         <v>cp-0</v>
       </c>
-      <c r="AA11" t="str">
+      <c r="AB11" t="str">
         <f t="shared" si="12"/>
         <v>CF1</v>
       </c>
-      <c r="AB11" t="str">
+      <c r="AC11" t="str">
         <f t="shared" si="13"/>
         <v>df-N</v>
       </c>
-      <c r="AC11" t="str">
+      <c r="AD11" t="str">
         <f t="shared" si="14"/>
         <v>ga-Y</v>
       </c>
-    </row>
-    <row r="12" spans="2:29">
+      <c r="AE11" t="str">
+        <f t="shared" si="14"/>
+        <v>tc-Y</v>
+      </c>
+    </row>
+    <row r="12" spans="2:31">
       <c r="B12" t="str">
         <f t="shared" si="2"/>
         <v>vs~0007</v>
       </c>
       <c r="C12" t="str">
         <f t="shared" si="3"/>
-        <v>df-N.ga-Y.dm-Lo.cp-95.CF1</v>
+        <v>tc-Y.df-N.ga-Y.dm-Lo.cp-95.CF1</v>
       </c>
       <c r="H12" t="str">
         <f t="shared" si="4"/>
-        <v>df-N.ga-Y.dm-Lo.cp-95.CF1</v>
+        <v>tc-Y.df-N.ga-Y.dm-Lo.cp-95.CF1</v>
       </c>
       <c r="I12" t="str">
         <f t="shared" si="5"/>
@@ -34747,63 +34922,74 @@
         <f t="shared" si="9"/>
         <v>Y</v>
       </c>
-      <c r="O12">
+      <c r="N12" t="str">
+        <f t="shared" si="9"/>
+        <v>Y</v>
+      </c>
+      <c r="P12">
         <v>5</v>
       </c>
-      <c r="P12" t="s">
-        <v>1103</v>
-      </c>
-      <c r="Q12">
+      <c r="Q12" t="s">
+        <v>1107</v>
+      </c>
+      <c r="R12">
         <v>7</v>
       </c>
-      <c r="R12" t="s">
-        <v>1094</v>
-      </c>
-      <c r="S12">
+      <c r="S12" t="s">
+        <v>1092</v>
+      </c>
+      <c r="T12">
         <v>95</v>
       </c>
-      <c r="T12" t="s">
+      <c r="U12" t="s">
         <v>1087</v>
-      </c>
-      <c r="U12" t="s">
-        <v>1101</v>
       </c>
       <c r="V12" t="s">
         <v>1095</v>
       </c>
-      <c r="Y12" t="str">
+      <c r="W12" t="s">
+        <v>1093</v>
+      </c>
+      <c r="X12" t="s">
+        <v>1093</v>
+      </c>
+      <c r="Z12" t="str">
         <f t="shared" si="10"/>
         <v>dm-Lo</v>
       </c>
-      <c r="Z12" t="str">
+      <c r="AA12" t="str">
         <f t="shared" si="11"/>
         <v>cp-95</v>
       </c>
-      <c r="AA12" t="str">
+      <c r="AB12" t="str">
         <f t="shared" si="12"/>
         <v>CF1</v>
       </c>
-      <c r="AB12" t="str">
+      <c r="AC12" t="str">
         <f t="shared" si="13"/>
         <v>df-N</v>
       </c>
-      <c r="AC12" t="str">
+      <c r="AD12" t="str">
         <f t="shared" si="14"/>
         <v>ga-Y</v>
       </c>
-    </row>
-    <row r="13" spans="2:29">
+      <c r="AE12" t="str">
+        <f t="shared" si="14"/>
+        <v>tc-Y</v>
+      </c>
+    </row>
+    <row r="13" spans="2:31">
       <c r="B13" t="str">
         <f t="shared" si="2"/>
         <v>vs~0008</v>
       </c>
       <c r="C13" t="str">
         <f t="shared" si="3"/>
-        <v>df-N.ga-Y.dm-Hi.cp-95.CF1</v>
+        <v>tc-Y.df-N.ga-Y.dm-Hi.cp-95.CF1</v>
       </c>
       <c r="H13" t="str">
         <f t="shared" si="4"/>
-        <v>df-N.ga-Y.dm-Hi.cp-95.CF1</v>
+        <v>tc-Y.df-N.ga-Y.dm-Hi.cp-95.CF1</v>
       </c>
       <c r="I13" t="str">
         <f t="shared" si="5"/>
@@ -34825,63 +35011,74 @@
         <f t="shared" si="9"/>
         <v>Y</v>
       </c>
-      <c r="O13">
+      <c r="N13" t="str">
+        <f t="shared" si="9"/>
+        <v>Y</v>
+      </c>
+      <c r="P13">
         <v>5</v>
       </c>
-      <c r="P13" t="s">
-        <v>1104</v>
-      </c>
-      <c r="Q13">
+      <c r="Q13" t="s">
+        <v>1108</v>
+      </c>
+      <c r="R13">
         <v>8</v>
       </c>
-      <c r="R13" t="s">
-        <v>1097</v>
-      </c>
-      <c r="S13">
+      <c r="S13" t="s">
+        <v>1094</v>
+      </c>
+      <c r="T13">
         <v>95</v>
       </c>
-      <c r="T13" t="s">
+      <c r="U13" t="s">
         <v>1087</v>
-      </c>
-      <c r="U13" t="s">
-        <v>1101</v>
       </c>
       <c r="V13" t="s">
         <v>1095</v>
       </c>
-      <c r="Y13" t="str">
+      <c r="W13" t="s">
+        <v>1093</v>
+      </c>
+      <c r="X13" t="s">
+        <v>1093</v>
+      </c>
+      <c r="Z13" t="str">
         <f t="shared" si="10"/>
         <v>dm-Hi</v>
       </c>
-      <c r="Z13" t="str">
+      <c r="AA13" t="str">
         <f t="shared" si="11"/>
         <v>cp-95</v>
       </c>
-      <c r="AA13" t="str">
+      <c r="AB13" t="str">
         <f t="shared" si="12"/>
         <v>CF1</v>
       </c>
-      <c r="AB13" t="str">
+      <c r="AC13" t="str">
         <f t="shared" si="13"/>
         <v>df-N</v>
       </c>
-      <c r="AC13" t="str">
+      <c r="AD13" t="str">
         <f t="shared" si="14"/>
         <v>ga-Y</v>
       </c>
-    </row>
-    <row r="14" spans="2:29">
+      <c r="AE13" t="str">
+        <f t="shared" si="14"/>
+        <v>tc-Y</v>
+      </c>
+    </row>
+    <row r="14" spans="2:31">
       <c r="B14" t="str">
         <f t="shared" si="2"/>
         <v>vs~0009</v>
       </c>
       <c r="C14" t="str">
         <f t="shared" si="3"/>
-        <v>df-Y.ga-Y.dm-Lo.cp-0.CF6</v>
+        <v>tc-Y.df-Y.ga-Y.dm-Lo.cp-0.CF6</v>
       </c>
       <c r="H14" t="str">
         <f t="shared" si="4"/>
-        <v>df-Y.ga-Y.dm-Lo.cp-0.CF6</v>
+        <v>tc-Y.df-Y.ga-Y.dm-Lo.cp-0.CF6</v>
       </c>
       <c r="I14" t="str">
         <f t="shared" si="5"/>
@@ -34903,63 +35100,74 @@
         <f t="shared" si="9"/>
         <v>Y</v>
       </c>
-      <c r="O14">
+      <c r="N14" t="str">
+        <f t="shared" si="9"/>
+        <v>Y</v>
+      </c>
+      <c r="P14">
         <v>5</v>
       </c>
-      <c r="P14" t="s">
-        <v>1105</v>
-      </c>
-      <c r="Q14">
+      <c r="Q14" t="s">
+        <v>1109</v>
+      </c>
+      <c r="R14">
         <v>9</v>
       </c>
-      <c r="R14" t="s">
-        <v>1094</v>
-      </c>
-      <c r="S14">
+      <c r="S14" t="s">
+        <v>1092</v>
+      </c>
+      <c r="T14">
         <v>0</v>
       </c>
-      <c r="T14" t="s">
+      <c r="U14" t="s">
         <v>1088</v>
       </c>
-      <c r="U14" t="s">
-        <v>1095</v>
-      </c>
       <c r="V14" t="s">
-        <v>1095</v>
-      </c>
-      <c r="Y14" t="str">
+        <v>1093</v>
+      </c>
+      <c r="W14" t="s">
+        <v>1093</v>
+      </c>
+      <c r="X14" t="s">
+        <v>1093</v>
+      </c>
+      <c r="Z14" t="str">
         <f t="shared" si="10"/>
         <v>dm-Lo</v>
       </c>
-      <c r="Z14" t="str">
+      <c r="AA14" t="str">
         <f t="shared" si="11"/>
         <v>cp-0</v>
       </c>
-      <c r="AA14" t="str">
+      <c r="AB14" t="str">
         <f t="shared" si="12"/>
         <v>CF6</v>
       </c>
-      <c r="AB14" t="str">
+      <c r="AC14" t="str">
         <f t="shared" si="13"/>
         <v>df-Y</v>
       </c>
-      <c r="AC14" t="str">
+      <c r="AD14" t="str">
         <f t="shared" si="14"/>
         <v>ga-Y</v>
       </c>
-    </row>
-    <row r="15" spans="2:29">
+      <c r="AE14" t="str">
+        <f t="shared" si="14"/>
+        <v>tc-Y</v>
+      </c>
+    </row>
+    <row r="15" spans="2:31">
       <c r="B15" t="str">
         <f t="shared" si="2"/>
         <v>vs~0010</v>
       </c>
       <c r="C15" t="str">
         <f t="shared" si="3"/>
-        <v>df-Y.ga-Y.dm-Hi.cp-0.CF6</v>
+        <v>tc-Y.df-Y.ga-Y.dm-Hi.cp-0.CF6</v>
       </c>
       <c r="H15" t="str">
         <f t="shared" si="4"/>
-        <v>df-Y.ga-Y.dm-Hi.cp-0.CF6</v>
+        <v>tc-Y.df-Y.ga-Y.dm-Hi.cp-0.CF6</v>
       </c>
       <c r="I15" t="str">
         <f t="shared" si="5"/>
@@ -34981,63 +35189,74 @@
         <f t="shared" si="9"/>
         <v>Y</v>
       </c>
-      <c r="O15">
+      <c r="N15" t="str">
+        <f t="shared" si="9"/>
+        <v>Y</v>
+      </c>
+      <c r="P15">
         <v>5</v>
       </c>
-      <c r="P15" t="s">
-        <v>1106</v>
-      </c>
-      <c r="Q15">
+      <c r="Q15" t="s">
+        <v>1110</v>
+      </c>
+      <c r="R15">
         <v>10</v>
       </c>
-      <c r="R15" t="s">
-        <v>1097</v>
-      </c>
-      <c r="S15">
+      <c r="S15" t="s">
+        <v>1094</v>
+      </c>
+      <c r="T15">
         <v>0</v>
       </c>
-      <c r="T15" t="s">
+      <c r="U15" t="s">
         <v>1088</v>
       </c>
-      <c r="U15" t="s">
-        <v>1095</v>
-      </c>
       <c r="V15" t="s">
-        <v>1095</v>
-      </c>
-      <c r="Y15" t="str">
+        <v>1093</v>
+      </c>
+      <c r="W15" t="s">
+        <v>1093</v>
+      </c>
+      <c r="X15" t="s">
+        <v>1093</v>
+      </c>
+      <c r="Z15" t="str">
         <f t="shared" si="10"/>
         <v>dm-Hi</v>
       </c>
-      <c r="Z15" t="str">
+      <c r="AA15" t="str">
         <f t="shared" si="11"/>
         <v>cp-0</v>
       </c>
-      <c r="AA15" t="str">
+      <c r="AB15" t="str">
         <f t="shared" si="12"/>
         <v>CF6</v>
       </c>
-      <c r="AB15" t="str">
+      <c r="AC15" t="str">
         <f t="shared" si="13"/>
         <v>df-Y</v>
       </c>
-      <c r="AC15" t="str">
+      <c r="AD15" t="str">
         <f t="shared" si="14"/>
         <v>ga-Y</v>
       </c>
-    </row>
-    <row r="16" spans="2:29">
+      <c r="AE15" t="str">
+        <f t="shared" si="14"/>
+        <v>tc-Y</v>
+      </c>
+    </row>
+    <row r="16" spans="2:31">
       <c r="B16" t="str">
         <f t="shared" si="2"/>
         <v>vs~0011</v>
       </c>
       <c r="C16" t="str">
         <f t="shared" si="3"/>
-        <v>df-Y.ga-Y.dm-Lo.cp-95.CF6</v>
+        <v>tc-Y.df-Y.ga-Y.dm-Lo.cp-95.CF6</v>
       </c>
       <c r="H16" t="str">
         <f t="shared" si="4"/>
-        <v>df-Y.ga-Y.dm-Lo.cp-95.CF6</v>
+        <v>tc-Y.df-Y.ga-Y.dm-Lo.cp-95.CF6</v>
       </c>
       <c r="I16" t="str">
         <f t="shared" si="5"/>
@@ -35059,63 +35278,74 @@
         <f t="shared" si="9"/>
         <v>Y</v>
       </c>
-      <c r="O16">
+      <c r="N16" t="str">
+        <f t="shared" si="9"/>
+        <v>Y</v>
+      </c>
+      <c r="P16">
         <v>5</v>
       </c>
-      <c r="P16" t="s">
-        <v>1107</v>
-      </c>
-      <c r="Q16">
+      <c r="Q16" t="s">
+        <v>1111</v>
+      </c>
+      <c r="R16">
         <v>11</v>
       </c>
-      <c r="R16" t="s">
-        <v>1094</v>
-      </c>
-      <c r="S16">
+      <c r="S16" t="s">
+        <v>1092</v>
+      </c>
+      <c r="T16">
         <v>95</v>
       </c>
-      <c r="T16" t="s">
+      <c r="U16" t="s">
         <v>1088</v>
       </c>
-      <c r="U16" t="s">
-        <v>1095</v>
-      </c>
       <c r="V16" t="s">
-        <v>1095</v>
-      </c>
-      <c r="Y16" t="str">
+        <v>1093</v>
+      </c>
+      <c r="W16" t="s">
+        <v>1093</v>
+      </c>
+      <c r="X16" t="s">
+        <v>1093</v>
+      </c>
+      <c r="Z16" t="str">
         <f t="shared" si="10"/>
         <v>dm-Lo</v>
       </c>
-      <c r="Z16" t="str">
+      <c r="AA16" t="str">
         <f t="shared" si="11"/>
         <v>cp-95</v>
       </c>
-      <c r="AA16" t="str">
+      <c r="AB16" t="str">
         <f t="shared" si="12"/>
         <v>CF6</v>
       </c>
-      <c r="AB16" t="str">
+      <c r="AC16" t="str">
         <f t="shared" si="13"/>
         <v>df-Y</v>
       </c>
-      <c r="AC16" t="str">
+      <c r="AD16" t="str">
         <f t="shared" si="14"/>
         <v>ga-Y</v>
       </c>
-    </row>
-    <row r="17" spans="2:29">
+      <c r="AE16" t="str">
+        <f t="shared" si="14"/>
+        <v>tc-Y</v>
+      </c>
+    </row>
+    <row r="17" spans="2:31">
       <c r="B17" t="str">
         <f t="shared" si="2"/>
         <v>vs~0012</v>
       </c>
       <c r="C17" t="str">
         <f t="shared" si="3"/>
-        <v>df-Y.ga-Y.dm-Hi.cp-95.CF6</v>
+        <v>tc-Y.df-Y.ga-Y.dm-Hi.cp-95.CF6</v>
       </c>
       <c r="H17" t="str">
         <f t="shared" si="4"/>
-        <v>df-Y.ga-Y.dm-Hi.cp-95.CF6</v>
+        <v>tc-Y.df-Y.ga-Y.dm-Hi.cp-95.CF6</v>
       </c>
       <c r="I17" t="str">
         <f t="shared" si="5"/>
@@ -35137,63 +35367,74 @@
         <f t="shared" si="9"/>
         <v>Y</v>
       </c>
-      <c r="O17">
+      <c r="N17" t="str">
+        <f t="shared" si="9"/>
+        <v>Y</v>
+      </c>
+      <c r="P17">
         <v>5</v>
       </c>
-      <c r="P17" t="s">
-        <v>1108</v>
-      </c>
-      <c r="Q17">
+      <c r="Q17" t="s">
+        <v>1112</v>
+      </c>
+      <c r="R17">
         <v>12</v>
       </c>
-      <c r="R17" t="s">
-        <v>1097</v>
-      </c>
-      <c r="S17">
+      <c r="S17" t="s">
+        <v>1094</v>
+      </c>
+      <c r="T17">
         <v>95</v>
       </c>
-      <c r="T17" t="s">
+      <c r="U17" t="s">
         <v>1088</v>
       </c>
-      <c r="U17" t="s">
-        <v>1095</v>
-      </c>
       <c r="V17" t="s">
-        <v>1095</v>
-      </c>
-      <c r="Y17" t="str">
+        <v>1093</v>
+      </c>
+      <c r="W17" t="s">
+        <v>1093</v>
+      </c>
+      <c r="X17" t="s">
+        <v>1093</v>
+      </c>
+      <c r="Z17" t="str">
         <f t="shared" si="10"/>
         <v>dm-Hi</v>
       </c>
-      <c r="Z17" t="str">
+      <c r="AA17" t="str">
         <f t="shared" si="11"/>
         <v>cp-95</v>
       </c>
-      <c r="AA17" t="str">
+      <c r="AB17" t="str">
         <f t="shared" si="12"/>
         <v>CF6</v>
       </c>
-      <c r="AB17" t="str">
+      <c r="AC17" t="str">
         <f t="shared" si="13"/>
         <v>df-Y</v>
       </c>
-      <c r="AC17" t="str">
+      <c r="AD17" t="str">
         <f t="shared" si="14"/>
         <v>ga-Y</v>
       </c>
-    </row>
-    <row r="18" spans="2:29">
+      <c r="AE17" t="str">
+        <f t="shared" si="14"/>
+        <v>tc-Y</v>
+      </c>
+    </row>
+    <row r="18" spans="2:31">
       <c r="B18" t="str">
-        <f t="shared" ref="B18:B37" si="15">"vs~"&amp;TEXT(Q18,"0000")</f>
+        <f t="shared" ref="B18:B37" si="15">"vs~"&amp;TEXT(R18,"0000")</f>
         <v>vs~0013</v>
       </c>
       <c r="C18" t="str">
         <f t="shared" ref="C18:C37" si="16">H18</f>
-        <v>df-N.ga-Y.dm-Lo.cp-0.CF6</v>
+        <v>tc-Y.df-N.ga-Y.dm-Lo.cp-0.CF6</v>
       </c>
       <c r="H18" t="str">
         <f t="shared" si="4"/>
-        <v>df-N.ga-Y.dm-Lo.cp-0.CF6</v>
+        <v>tc-Y.df-N.ga-Y.dm-Lo.cp-0.CF6</v>
       </c>
       <c r="I18" t="str">
         <f t="shared" si="5"/>
@@ -35215,63 +35456,74 @@
         <f t="shared" si="9"/>
         <v>Y</v>
       </c>
-      <c r="O18">
+      <c r="N18" t="str">
+        <f t="shared" si="9"/>
+        <v>Y</v>
+      </c>
+      <c r="P18">
         <v>5</v>
       </c>
-      <c r="P18" t="s">
-        <v>1109</v>
-      </c>
-      <c r="Q18">
+      <c r="Q18" t="s">
+        <v>1113</v>
+      </c>
+      <c r="R18">
         <v>13</v>
       </c>
-      <c r="R18" t="s">
-        <v>1094</v>
-      </c>
-      <c r="S18">
+      <c r="S18" t="s">
+        <v>1092</v>
+      </c>
+      <c r="T18">
         <v>0</v>
       </c>
-      <c r="T18" t="s">
+      <c r="U18" t="s">
         <v>1088</v>
-      </c>
-      <c r="U18" t="s">
-        <v>1101</v>
       </c>
       <c r="V18" t="s">
         <v>1095</v>
       </c>
-      <c r="Y18" t="str">
+      <c r="W18" t="s">
+        <v>1093</v>
+      </c>
+      <c r="X18" t="s">
+        <v>1093</v>
+      </c>
+      <c r="Z18" t="str">
         <f t="shared" si="10"/>
         <v>dm-Lo</v>
       </c>
-      <c r="Z18" t="str">
+      <c r="AA18" t="str">
         <f t="shared" si="11"/>
         <v>cp-0</v>
       </c>
-      <c r="AA18" t="str">
+      <c r="AB18" t="str">
         <f t="shared" si="12"/>
         <v>CF6</v>
       </c>
-      <c r="AB18" t="str">
+      <c r="AC18" t="str">
         <f t="shared" si="13"/>
         <v>df-N</v>
       </c>
-      <c r="AC18" t="str">
+      <c r="AD18" t="str">
         <f t="shared" si="14"/>
         <v>ga-Y</v>
       </c>
-    </row>
-    <row r="19" spans="2:29">
+      <c r="AE18" t="str">
+        <f t="shared" si="14"/>
+        <v>tc-Y</v>
+      </c>
+    </row>
+    <row r="19" spans="2:31">
       <c r="B19" t="str">
         <f t="shared" si="15"/>
         <v>vs~0014</v>
       </c>
       <c r="C19" t="str">
         <f t="shared" si="16"/>
-        <v>df-N.ga-Y.dm-Hi.cp-0.CF6</v>
+        <v>tc-Y.df-N.ga-Y.dm-Hi.cp-0.CF6</v>
       </c>
       <c r="H19" t="str">
         <f t="shared" si="4"/>
-        <v>df-N.ga-Y.dm-Hi.cp-0.CF6</v>
+        <v>tc-Y.df-N.ga-Y.dm-Hi.cp-0.CF6</v>
       </c>
       <c r="I19" t="str">
         <f t="shared" si="5"/>
@@ -35293,63 +35545,74 @@
         <f t="shared" si="9"/>
         <v>Y</v>
       </c>
-      <c r="O19">
+      <c r="N19" t="str">
+        <f t="shared" si="9"/>
+        <v>Y</v>
+      </c>
+      <c r="P19">
         <v>5</v>
       </c>
-      <c r="P19" t="s">
-        <v>1110</v>
-      </c>
-      <c r="Q19">
+      <c r="Q19" t="s">
+        <v>1114</v>
+      </c>
+      <c r="R19">
         <v>14</v>
       </c>
-      <c r="R19" t="s">
-        <v>1097</v>
-      </c>
-      <c r="S19">
+      <c r="S19" t="s">
+        <v>1094</v>
+      </c>
+      <c r="T19">
         <v>0</v>
       </c>
-      <c r="T19" t="s">
+      <c r="U19" t="s">
         <v>1088</v>
-      </c>
-      <c r="U19" t="s">
-        <v>1101</v>
       </c>
       <c r="V19" t="s">
         <v>1095</v>
       </c>
-      <c r="Y19" t="str">
+      <c r="W19" t="s">
+        <v>1093</v>
+      </c>
+      <c r="X19" t="s">
+        <v>1093</v>
+      </c>
+      <c r="Z19" t="str">
         <f t="shared" si="10"/>
         <v>dm-Hi</v>
       </c>
-      <c r="Z19" t="str">
+      <c r="AA19" t="str">
         <f t="shared" si="11"/>
         <v>cp-0</v>
       </c>
-      <c r="AA19" t="str">
+      <c r="AB19" t="str">
         <f t="shared" si="12"/>
         <v>CF6</v>
       </c>
-      <c r="AB19" t="str">
+      <c r="AC19" t="str">
         <f t="shared" si="13"/>
         <v>df-N</v>
       </c>
-      <c r="AC19" t="str">
+      <c r="AD19" t="str">
         <f t="shared" si="14"/>
         <v>ga-Y</v>
       </c>
-    </row>
-    <row r="20" spans="2:29">
+      <c r="AE19" t="str">
+        <f t="shared" si="14"/>
+        <v>tc-Y</v>
+      </c>
+    </row>
+    <row r="20" spans="2:31">
       <c r="B20" t="str">
         <f t="shared" si="15"/>
         <v>vs~0015</v>
       </c>
       <c r="C20" t="str">
         <f t="shared" si="16"/>
-        <v>df-N.ga-Y.dm-Lo.cp-95.CF6</v>
+        <v>tc-Y.df-N.ga-Y.dm-Lo.cp-95.CF6</v>
       </c>
       <c r="H20" t="str">
         <f t="shared" si="4"/>
-        <v>df-N.ga-Y.dm-Lo.cp-95.CF6</v>
+        <v>tc-Y.df-N.ga-Y.dm-Lo.cp-95.CF6</v>
       </c>
       <c r="I20" t="str">
         <f t="shared" si="5"/>
@@ -35371,63 +35634,74 @@
         <f t="shared" si="9"/>
         <v>Y</v>
       </c>
-      <c r="O20">
+      <c r="N20" t="str">
+        <f t="shared" si="9"/>
+        <v>Y</v>
+      </c>
+      <c r="P20">
         <v>5</v>
       </c>
-      <c r="P20" t="s">
-        <v>1111</v>
-      </c>
-      <c r="Q20">
+      <c r="Q20" t="s">
+        <v>1115</v>
+      </c>
+      <c r="R20">
         <v>15</v>
       </c>
-      <c r="R20" t="s">
-        <v>1094</v>
-      </c>
-      <c r="S20">
+      <c r="S20" t="s">
+        <v>1092</v>
+      </c>
+      <c r="T20">
         <v>95</v>
       </c>
-      <c r="T20" t="s">
+      <c r="U20" t="s">
         <v>1088</v>
-      </c>
-      <c r="U20" t="s">
-        <v>1101</v>
       </c>
       <c r="V20" t="s">
         <v>1095</v>
       </c>
-      <c r="Y20" t="str">
+      <c r="W20" t="s">
+        <v>1093</v>
+      </c>
+      <c r="X20" t="s">
+        <v>1093</v>
+      </c>
+      <c r="Z20" t="str">
         <f t="shared" si="10"/>
         <v>dm-Lo</v>
       </c>
-      <c r="Z20" t="str">
+      <c r="AA20" t="str">
         <f t="shared" si="11"/>
         <v>cp-95</v>
       </c>
-      <c r="AA20" t="str">
+      <c r="AB20" t="str">
         <f t="shared" si="12"/>
         <v>CF6</v>
       </c>
-      <c r="AB20" t="str">
+      <c r="AC20" t="str">
         <f t="shared" si="13"/>
         <v>df-N</v>
       </c>
-      <c r="AC20" t="str">
+      <c r="AD20" t="str">
         <f t="shared" si="14"/>
         <v>ga-Y</v>
       </c>
-    </row>
-    <row r="21" spans="2:29">
+      <c r="AE20" t="str">
+        <f t="shared" si="14"/>
+        <v>tc-Y</v>
+      </c>
+    </row>
+    <row r="21" spans="2:31">
       <c r="B21" t="str">
         <f t="shared" si="15"/>
         <v>vs~0016</v>
       </c>
       <c r="C21" t="str">
         <f t="shared" si="16"/>
-        <v>df-N.ga-Y.dm-Hi.cp-95.CF6</v>
+        <v>tc-Y.df-N.ga-Y.dm-Hi.cp-95.CF6</v>
       </c>
       <c r="H21" t="str">
         <f t="shared" si="4"/>
-        <v>df-N.ga-Y.dm-Hi.cp-95.CF6</v>
+        <v>tc-Y.df-N.ga-Y.dm-Hi.cp-95.CF6</v>
       </c>
       <c r="I21" t="str">
         <f t="shared" si="5"/>
@@ -35449,63 +35723,74 @@
         <f t="shared" si="9"/>
         <v>Y</v>
       </c>
-      <c r="O21">
+      <c r="N21" t="str">
+        <f t="shared" si="9"/>
+        <v>Y</v>
+      </c>
+      <c r="P21">
         <v>5</v>
       </c>
-      <c r="P21" t="s">
-        <v>1112</v>
-      </c>
-      <c r="Q21">
+      <c r="Q21" t="s">
+        <v>1116</v>
+      </c>
+      <c r="R21">
         <v>16</v>
       </c>
-      <c r="R21" t="s">
-        <v>1097</v>
-      </c>
-      <c r="S21">
+      <c r="S21" t="s">
+        <v>1094</v>
+      </c>
+      <c r="T21">
         <v>95</v>
       </c>
-      <c r="T21" t="s">
+      <c r="U21" t="s">
         <v>1088</v>
-      </c>
-      <c r="U21" t="s">
-        <v>1101</v>
       </c>
       <c r="V21" t="s">
         <v>1095</v>
       </c>
-      <c r="Y21" t="str">
+      <c r="W21" t="s">
+        <v>1093</v>
+      </c>
+      <c r="X21" t="s">
+        <v>1093</v>
+      </c>
+      <c r="Z21" t="str">
         <f t="shared" si="10"/>
         <v>dm-Hi</v>
       </c>
-      <c r="Z21" t="str">
+      <c r="AA21" t="str">
         <f t="shared" si="11"/>
         <v>cp-95</v>
       </c>
-      <c r="AA21" t="str">
+      <c r="AB21" t="str">
         <f t="shared" si="12"/>
         <v>CF6</v>
       </c>
-      <c r="AB21" t="str">
+      <c r="AC21" t="str">
         <f t="shared" si="13"/>
         <v>df-N</v>
       </c>
-      <c r="AC21" t="str">
+      <c r="AD21" t="str">
         <f t="shared" si="14"/>
         <v>ga-Y</v>
       </c>
-    </row>
-    <row r="22" spans="2:29">
+      <c r="AE21" t="str">
+        <f t="shared" si="14"/>
+        <v>tc-Y</v>
+      </c>
+    </row>
+    <row r="22" spans="2:31">
       <c r="B22" t="str">
         <f t="shared" si="15"/>
         <v>vs~0017</v>
       </c>
       <c r="C22" t="str">
         <f t="shared" si="16"/>
-        <v>df-Y.ga-N.dm-Lo.cp-0.CF1</v>
+        <v>tc-Y.df-Y.ga-N.dm-Lo.cp-0.CF1</v>
       </c>
       <c r="H22" t="str">
         <f t="shared" si="4"/>
-        <v>df-Y.ga-N.dm-Lo.cp-0.CF1</v>
+        <v>tc-Y.df-Y.ga-N.dm-Lo.cp-0.CF1</v>
       </c>
       <c r="I22" t="str">
         <f t="shared" si="5"/>
@@ -35527,63 +35812,74 @@
         <f t="shared" si="9"/>
         <v>N</v>
       </c>
-      <c r="O22">
+      <c r="N22" t="str">
+        <f t="shared" si="9"/>
+        <v>Y</v>
+      </c>
+      <c r="P22">
         <v>5</v>
       </c>
-      <c r="P22" t="s">
-        <v>1113</v>
-      </c>
-      <c r="Q22">
+      <c r="Q22" t="s">
+        <v>1117</v>
+      </c>
+      <c r="R22">
         <v>17</v>
       </c>
-      <c r="R22" t="s">
-        <v>1094</v>
-      </c>
-      <c r="S22">
+      <c r="S22" t="s">
+        <v>1092</v>
+      </c>
+      <c r="T22">
         <v>0</v>
       </c>
-      <c r="T22" t="s">
+      <c r="U22" t="s">
         <v>1087</v>
       </c>
-      <c r="U22" t="s">
+      <c r="V22" t="s">
+        <v>1093</v>
+      </c>
+      <c r="W22" t="s">
         <v>1095</v>
       </c>
-      <c r="V22" t="s">
-        <v>1101</v>
-      </c>
-      <c r="Y22" t="str">
+      <c r="X22" t="s">
+        <v>1093</v>
+      </c>
+      <c r="Z22" t="str">
         <f t="shared" si="10"/>
         <v>dm-Lo</v>
       </c>
-      <c r="Z22" t="str">
+      <c r="AA22" t="str">
         <f t="shared" si="11"/>
         <v>cp-0</v>
       </c>
-      <c r="AA22" t="str">
+      <c r="AB22" t="str">
         <f t="shared" si="12"/>
         <v>CF1</v>
       </c>
-      <c r="AB22" t="str">
+      <c r="AC22" t="str">
         <f t="shared" si="13"/>
         <v>df-Y</v>
       </c>
-      <c r="AC22" t="str">
+      <c r="AD22" t="str">
         <f t="shared" si="14"/>
         <v>ga-N</v>
       </c>
-    </row>
-    <row r="23" spans="2:29">
+      <c r="AE22" t="str">
+        <f t="shared" si="14"/>
+        <v>tc-Y</v>
+      </c>
+    </row>
+    <row r="23" spans="2:31">
       <c r="B23" t="str">
         <f t="shared" si="15"/>
         <v>vs~0018</v>
       </c>
       <c r="C23" t="str">
         <f t="shared" si="16"/>
-        <v>df-Y.ga-N.dm-Hi.cp-0.CF1</v>
+        <v>tc-Y.df-Y.ga-N.dm-Hi.cp-0.CF1</v>
       </c>
       <c r="H23" t="str">
         <f t="shared" si="4"/>
-        <v>df-Y.ga-N.dm-Hi.cp-0.CF1</v>
+        <v>tc-Y.df-Y.ga-N.dm-Hi.cp-0.CF1</v>
       </c>
       <c r="I23" t="str">
         <f t="shared" si="5"/>
@@ -35605,63 +35901,74 @@
         <f t="shared" si="9"/>
         <v>N</v>
       </c>
-      <c r="O23">
+      <c r="N23" t="str">
+        <f t="shared" si="9"/>
+        <v>Y</v>
+      </c>
+      <c r="P23">
         <v>5</v>
       </c>
-      <c r="P23" t="s">
-        <v>1114</v>
-      </c>
-      <c r="Q23">
+      <c r="Q23" t="s">
+        <v>1118</v>
+      </c>
+      <c r="R23">
         <v>18</v>
       </c>
-      <c r="R23" t="s">
-        <v>1097</v>
-      </c>
-      <c r="S23">
+      <c r="S23" t="s">
+        <v>1094</v>
+      </c>
+      <c r="T23">
         <v>0</v>
       </c>
-      <c r="T23" t="s">
+      <c r="U23" t="s">
         <v>1087</v>
       </c>
-      <c r="U23" t="s">
+      <c r="V23" t="s">
+        <v>1093</v>
+      </c>
+      <c r="W23" t="s">
         <v>1095</v>
       </c>
-      <c r="V23" t="s">
-        <v>1101</v>
-      </c>
-      <c r="Y23" t="str">
+      <c r="X23" t="s">
+        <v>1093</v>
+      </c>
+      <c r="Z23" t="str">
         <f t="shared" si="10"/>
         <v>dm-Hi</v>
       </c>
-      <c r="Z23" t="str">
+      <c r="AA23" t="str">
         <f t="shared" si="11"/>
         <v>cp-0</v>
       </c>
-      <c r="AA23" t="str">
+      <c r="AB23" t="str">
         <f t="shared" si="12"/>
         <v>CF1</v>
       </c>
-      <c r="AB23" t="str">
+      <c r="AC23" t="str">
         <f t="shared" si="13"/>
         <v>df-Y</v>
       </c>
-      <c r="AC23" t="str">
+      <c r="AD23" t="str">
         <f t="shared" si="14"/>
         <v>ga-N</v>
       </c>
-    </row>
-    <row r="24" spans="2:29">
+      <c r="AE23" t="str">
+        <f t="shared" si="14"/>
+        <v>tc-Y</v>
+      </c>
+    </row>
+    <row r="24" spans="2:31">
       <c r="B24" t="str">
         <f t="shared" si="15"/>
         <v>vs~0019</v>
       </c>
       <c r="C24" t="str">
         <f t="shared" si="16"/>
-        <v>df-Y.ga-N.dm-Lo.cp-95.CF1</v>
+        <v>tc-Y.df-Y.ga-N.dm-Lo.cp-95.CF1</v>
       </c>
       <c r="H24" t="str">
         <f t="shared" si="4"/>
-        <v>df-Y.ga-N.dm-Lo.cp-95.CF1</v>
+        <v>tc-Y.df-Y.ga-N.dm-Lo.cp-95.CF1</v>
       </c>
       <c r="I24" t="str">
         <f t="shared" si="5"/>
@@ -35683,63 +35990,74 @@
         <f t="shared" si="9"/>
         <v>N</v>
       </c>
-      <c r="O24">
+      <c r="N24" t="str">
+        <f t="shared" si="9"/>
+        <v>Y</v>
+      </c>
+      <c r="P24">
         <v>5</v>
       </c>
-      <c r="P24" t="s">
-        <v>1115</v>
-      </c>
-      <c r="Q24">
+      <c r="Q24" t="s">
+        <v>1119</v>
+      </c>
+      <c r="R24">
         <v>19</v>
       </c>
-      <c r="R24" t="s">
-        <v>1094</v>
-      </c>
-      <c r="S24">
+      <c r="S24" t="s">
+        <v>1092</v>
+      </c>
+      <c r="T24">
         <v>95</v>
       </c>
-      <c r="T24" t="s">
+      <c r="U24" t="s">
         <v>1087</v>
       </c>
-      <c r="U24" t="s">
+      <c r="V24" t="s">
+        <v>1093</v>
+      </c>
+      <c r="W24" t="s">
         <v>1095</v>
       </c>
-      <c r="V24" t="s">
-        <v>1101</v>
-      </c>
-      <c r="Y24" t="str">
+      <c r="X24" t="s">
+        <v>1093</v>
+      </c>
+      <c r="Z24" t="str">
         <f t="shared" si="10"/>
         <v>dm-Lo</v>
       </c>
-      <c r="Z24" t="str">
+      <c r="AA24" t="str">
         <f t="shared" si="11"/>
         <v>cp-95</v>
       </c>
-      <c r="AA24" t="str">
+      <c r="AB24" t="str">
         <f t="shared" si="12"/>
         <v>CF1</v>
       </c>
-      <c r="AB24" t="str">
+      <c r="AC24" t="str">
         <f t="shared" si="13"/>
         <v>df-Y</v>
       </c>
-      <c r="AC24" t="str">
+      <c r="AD24" t="str">
         <f t="shared" si="14"/>
         <v>ga-N</v>
       </c>
-    </row>
-    <row r="25" spans="2:29">
+      <c r="AE24" t="str">
+        <f t="shared" si="14"/>
+        <v>tc-Y</v>
+      </c>
+    </row>
+    <row r="25" spans="2:31">
       <c r="B25" t="str">
         <f t="shared" si="15"/>
         <v>vs~0020</v>
       </c>
       <c r="C25" t="str">
         <f t="shared" si="16"/>
-        <v>df-Y.ga-N.dm-Hi.cp-95.CF1</v>
+        <v>tc-Y.df-Y.ga-N.dm-Hi.cp-95.CF1</v>
       </c>
       <c r="H25" t="str">
         <f t="shared" si="4"/>
-        <v>df-Y.ga-N.dm-Hi.cp-95.CF1</v>
+        <v>tc-Y.df-Y.ga-N.dm-Hi.cp-95.CF1</v>
       </c>
       <c r="I25" t="str">
         <f t="shared" si="5"/>
@@ -35761,63 +36079,74 @@
         <f t="shared" si="9"/>
         <v>N</v>
       </c>
-      <c r="O25">
+      <c r="N25" t="str">
+        <f t="shared" si="9"/>
+        <v>Y</v>
+      </c>
+      <c r="P25">
         <v>5</v>
       </c>
-      <c r="P25" t="s">
-        <v>1116</v>
-      </c>
-      <c r="Q25">
+      <c r="Q25" t="s">
+        <v>1120</v>
+      </c>
+      <c r="R25">
         <v>20</v>
       </c>
-      <c r="R25" t="s">
-        <v>1097</v>
-      </c>
-      <c r="S25">
+      <c r="S25" t="s">
+        <v>1094</v>
+      </c>
+      <c r="T25">
         <v>95</v>
       </c>
-      <c r="T25" t="s">
+      <c r="U25" t="s">
         <v>1087</v>
       </c>
-      <c r="U25" t="s">
+      <c r="V25" t="s">
+        <v>1093</v>
+      </c>
+      <c r="W25" t="s">
         <v>1095</v>
       </c>
-      <c r="V25" t="s">
-        <v>1101</v>
-      </c>
-      <c r="Y25" t="str">
+      <c r="X25" t="s">
+        <v>1093</v>
+      </c>
+      <c r="Z25" t="str">
         <f t="shared" si="10"/>
         <v>dm-Hi</v>
       </c>
-      <c r="Z25" t="str">
+      <c r="AA25" t="str">
         <f t="shared" si="11"/>
         <v>cp-95</v>
       </c>
-      <c r="AA25" t="str">
+      <c r="AB25" t="str">
         <f t="shared" si="12"/>
         <v>CF1</v>
       </c>
-      <c r="AB25" t="str">
+      <c r="AC25" t="str">
         <f t="shared" si="13"/>
         <v>df-Y</v>
       </c>
-      <c r="AC25" t="str">
+      <c r="AD25" t="str">
         <f t="shared" si="14"/>
         <v>ga-N</v>
       </c>
-    </row>
-    <row r="26" spans="2:29">
+      <c r="AE25" t="str">
+        <f t="shared" si="14"/>
+        <v>tc-Y</v>
+      </c>
+    </row>
+    <row r="26" spans="2:31">
       <c r="B26" t="str">
         <f t="shared" si="15"/>
         <v>vs~0021</v>
       </c>
       <c r="C26" t="str">
         <f t="shared" si="16"/>
-        <v>df-N.ga-N.dm-Lo.cp-0.CF1</v>
+        <v>tc-Y.df-N.ga-N.dm-Lo.cp-0.CF1</v>
       </c>
       <c r="H26" t="str">
         <f t="shared" si="4"/>
-        <v>df-N.ga-N.dm-Lo.cp-0.CF1</v>
+        <v>tc-Y.df-N.ga-N.dm-Lo.cp-0.CF1</v>
       </c>
       <c r="I26" t="str">
         <f t="shared" si="5"/>
@@ -35839,63 +36168,74 @@
         <f t="shared" si="9"/>
         <v>N</v>
       </c>
-      <c r="O26">
+      <c r="N26" t="str">
+        <f t="shared" si="9"/>
+        <v>Y</v>
+      </c>
+      <c r="P26">
         <v>5</v>
       </c>
-      <c r="P26" t="s">
-        <v>1117</v>
-      </c>
-      <c r="Q26">
+      <c r="Q26" t="s">
+        <v>1121</v>
+      </c>
+      <c r="R26">
         <v>21</v>
       </c>
-      <c r="R26" t="s">
-        <v>1094</v>
-      </c>
-      <c r="S26">
+      <c r="S26" t="s">
+        <v>1092</v>
+      </c>
+      <c r="T26">
         <v>0</v>
       </c>
-      <c r="T26" t="s">
+      <c r="U26" t="s">
         <v>1087</v>
       </c>
-      <c r="U26" t="s">
-        <v>1101</v>
-      </c>
       <c r="V26" t="s">
-        <v>1101</v>
-      </c>
-      <c r="Y26" t="str">
+        <v>1095</v>
+      </c>
+      <c r="W26" t="s">
+        <v>1095</v>
+      </c>
+      <c r="X26" t="s">
+        <v>1093</v>
+      </c>
+      <c r="Z26" t="str">
         <f t="shared" si="10"/>
         <v>dm-Lo</v>
       </c>
-      <c r="Z26" t="str">
+      <c r="AA26" t="str">
         <f t="shared" si="11"/>
         <v>cp-0</v>
       </c>
-      <c r="AA26" t="str">
+      <c r="AB26" t="str">
         <f t="shared" si="12"/>
         <v>CF1</v>
       </c>
-      <c r="AB26" t="str">
+      <c r="AC26" t="str">
         <f t="shared" si="13"/>
         <v>df-N</v>
       </c>
-      <c r="AC26" t="str">
+      <c r="AD26" t="str">
         <f t="shared" si="14"/>
         <v>ga-N</v>
       </c>
-    </row>
-    <row r="27" spans="2:29">
+      <c r="AE26" t="str">
+        <f t="shared" si="14"/>
+        <v>tc-Y</v>
+      </c>
+    </row>
+    <row r="27" spans="2:31">
       <c r="B27" t="str">
         <f t="shared" si="15"/>
         <v>vs~0022</v>
       </c>
       <c r="C27" t="str">
         <f t="shared" si="16"/>
-        <v>df-N.ga-N.dm-Hi.cp-0.CF1</v>
+        <v>tc-Y.df-N.ga-N.dm-Hi.cp-0.CF1</v>
       </c>
       <c r="H27" t="str">
         <f t="shared" si="4"/>
-        <v>df-N.ga-N.dm-Hi.cp-0.CF1</v>
+        <v>tc-Y.df-N.ga-N.dm-Hi.cp-0.CF1</v>
       </c>
       <c r="I27" t="str">
         <f t="shared" si="5"/>
@@ -35917,63 +36257,74 @@
         <f t="shared" si="9"/>
         <v>N</v>
       </c>
-      <c r="O27">
+      <c r="N27" t="str">
+        <f t="shared" si="9"/>
+        <v>Y</v>
+      </c>
+      <c r="P27">
         <v>5</v>
       </c>
-      <c r="P27" t="s">
-        <v>1118</v>
-      </c>
-      <c r="Q27">
+      <c r="Q27" t="s">
+        <v>1122</v>
+      </c>
+      <c r="R27">
         <v>22</v>
       </c>
-      <c r="R27" t="s">
-        <v>1097</v>
-      </c>
-      <c r="S27">
+      <c r="S27" t="s">
+        <v>1094</v>
+      </c>
+      <c r="T27">
         <v>0</v>
       </c>
-      <c r="T27" t="s">
+      <c r="U27" t="s">
         <v>1087</v>
       </c>
-      <c r="U27" t="s">
-        <v>1101</v>
-      </c>
       <c r="V27" t="s">
-        <v>1101</v>
-      </c>
-      <c r="Y27" t="str">
+        <v>1095</v>
+      </c>
+      <c r="W27" t="s">
+        <v>1095</v>
+      </c>
+      <c r="X27" t="s">
+        <v>1093</v>
+      </c>
+      <c r="Z27" t="str">
         <f t="shared" si="10"/>
         <v>dm-Hi</v>
       </c>
-      <c r="Z27" t="str">
+      <c r="AA27" t="str">
         <f t="shared" si="11"/>
         <v>cp-0</v>
       </c>
-      <c r="AA27" t="str">
+      <c r="AB27" t="str">
         <f t="shared" si="12"/>
         <v>CF1</v>
       </c>
-      <c r="AB27" t="str">
+      <c r="AC27" t="str">
         <f t="shared" si="13"/>
         <v>df-N</v>
       </c>
-      <c r="AC27" t="str">
+      <c r="AD27" t="str">
         <f t="shared" si="14"/>
         <v>ga-N</v>
       </c>
-    </row>
-    <row r="28" spans="2:29">
+      <c r="AE27" t="str">
+        <f t="shared" si="14"/>
+        <v>tc-Y</v>
+      </c>
+    </row>
+    <row r="28" spans="2:31">
       <c r="B28" t="str">
         <f t="shared" si="15"/>
         <v>vs~0023</v>
       </c>
       <c r="C28" t="str">
         <f t="shared" si="16"/>
-        <v>df-N.ga-N.dm-Lo.cp-95.CF1</v>
+        <v>tc-Y.df-N.ga-N.dm-Lo.cp-95.CF1</v>
       </c>
       <c r="H28" t="str">
         <f t="shared" si="4"/>
-        <v>df-N.ga-N.dm-Lo.cp-95.CF1</v>
+        <v>tc-Y.df-N.ga-N.dm-Lo.cp-95.CF1</v>
       </c>
       <c r="I28" t="str">
         <f t="shared" si="5"/>
@@ -35995,63 +36346,74 @@
         <f t="shared" si="9"/>
         <v>N</v>
       </c>
-      <c r="O28">
+      <c r="N28" t="str">
+        <f t="shared" si="9"/>
+        <v>Y</v>
+      </c>
+      <c r="P28">
         <v>5</v>
       </c>
-      <c r="P28" t="s">
-        <v>1119</v>
-      </c>
-      <c r="Q28">
+      <c r="Q28" t="s">
+        <v>1123</v>
+      </c>
+      <c r="R28">
         <v>23</v>
       </c>
-      <c r="R28" t="s">
-        <v>1094</v>
-      </c>
-      <c r="S28">
+      <c r="S28" t="s">
+        <v>1092</v>
+      </c>
+      <c r="T28">
         <v>95</v>
       </c>
-      <c r="T28" t="s">
+      <c r="U28" t="s">
         <v>1087</v>
       </c>
-      <c r="U28" t="s">
-        <v>1101</v>
-      </c>
       <c r="V28" t="s">
-        <v>1101</v>
-      </c>
-      <c r="Y28" t="str">
+        <v>1095</v>
+      </c>
+      <c r="W28" t="s">
+        <v>1095</v>
+      </c>
+      <c r="X28" t="s">
+        <v>1093</v>
+      </c>
+      <c r="Z28" t="str">
         <f t="shared" si="10"/>
         <v>dm-Lo</v>
       </c>
-      <c r="Z28" t="str">
+      <c r="AA28" t="str">
         <f t="shared" si="11"/>
         <v>cp-95</v>
       </c>
-      <c r="AA28" t="str">
+      <c r="AB28" t="str">
         <f t="shared" si="12"/>
         <v>CF1</v>
       </c>
-      <c r="AB28" t="str">
+      <c r="AC28" t="str">
         <f t="shared" si="13"/>
         <v>df-N</v>
       </c>
-      <c r="AC28" t="str">
+      <c r="AD28" t="str">
         <f t="shared" si="14"/>
         <v>ga-N</v>
       </c>
-    </row>
-    <row r="29" spans="2:29">
+      <c r="AE28" t="str">
+        <f t="shared" si="14"/>
+        <v>tc-Y</v>
+      </c>
+    </row>
+    <row r="29" spans="2:31">
       <c r="B29" t="str">
         <f t="shared" si="15"/>
         <v>vs~0024</v>
       </c>
       <c r="C29" t="str">
         <f t="shared" si="16"/>
-        <v>df-N.ga-N.dm-Hi.cp-95.CF1</v>
+        <v>tc-Y.df-N.ga-N.dm-Hi.cp-95.CF1</v>
       </c>
       <c r="H29" t="str">
         <f t="shared" si="4"/>
-        <v>df-N.ga-N.dm-Hi.cp-95.CF1</v>
+        <v>tc-Y.df-N.ga-N.dm-Hi.cp-95.CF1</v>
       </c>
       <c r="I29" t="str">
         <f t="shared" si="5"/>
@@ -36073,63 +36435,74 @@
         <f t="shared" si="9"/>
         <v>N</v>
       </c>
-      <c r="O29">
+      <c r="N29" t="str">
+        <f t="shared" si="9"/>
+        <v>Y</v>
+      </c>
+      <c r="P29">
         <v>5</v>
       </c>
-      <c r="P29" t="s">
-        <v>1120</v>
-      </c>
-      <c r="Q29">
+      <c r="Q29" t="s">
+        <v>1124</v>
+      </c>
+      <c r="R29">
         <v>24</v>
       </c>
-      <c r="R29" t="s">
-        <v>1097</v>
-      </c>
-      <c r="S29">
+      <c r="S29" t="s">
+        <v>1094</v>
+      </c>
+      <c r="T29">
         <v>95</v>
       </c>
-      <c r="T29" t="s">
+      <c r="U29" t="s">
         <v>1087</v>
       </c>
-      <c r="U29" t="s">
-        <v>1101</v>
-      </c>
       <c r="V29" t="s">
-        <v>1101</v>
-      </c>
-      <c r="Y29" t="str">
+        <v>1095</v>
+      </c>
+      <c r="W29" t="s">
+        <v>1095</v>
+      </c>
+      <c r="X29" t="s">
+        <v>1093</v>
+      </c>
+      <c r="Z29" t="str">
         <f t="shared" si="10"/>
         <v>dm-Hi</v>
       </c>
-      <c r="Z29" t="str">
+      <c r="AA29" t="str">
         <f t="shared" si="11"/>
         <v>cp-95</v>
       </c>
-      <c r="AA29" t="str">
+      <c r="AB29" t="str">
         <f t="shared" si="12"/>
         <v>CF1</v>
       </c>
-      <c r="AB29" t="str">
+      <c r="AC29" t="str">
         <f t="shared" si="13"/>
         <v>df-N</v>
       </c>
-      <c r="AC29" t="str">
+      <c r="AD29" t="str">
         <f t="shared" si="14"/>
         <v>ga-N</v>
       </c>
-    </row>
-    <row r="30" spans="2:29">
+      <c r="AE29" t="str">
+        <f t="shared" si="14"/>
+        <v>tc-Y</v>
+      </c>
+    </row>
+    <row r="30" spans="2:31">
       <c r="B30" t="str">
         <f t="shared" si="15"/>
         <v>vs~0025</v>
       </c>
       <c r="C30" t="str">
         <f t="shared" si="16"/>
-        <v>df-Y.ga-N.dm-Lo.cp-0.CF6</v>
+        <v>tc-Y.df-Y.ga-N.dm-Lo.cp-0.CF6</v>
       </c>
       <c r="H30" t="str">
         <f t="shared" si="4"/>
-        <v>df-Y.ga-N.dm-Lo.cp-0.CF6</v>
+        <v>tc-Y.df-Y.ga-N.dm-Lo.cp-0.CF6</v>
       </c>
       <c r="I30" t="str">
         <f t="shared" si="5"/>
@@ -36151,63 +36524,74 @@
         <f t="shared" si="9"/>
         <v>N</v>
       </c>
-      <c r="O30">
+      <c r="N30" t="str">
+        <f t="shared" si="9"/>
+        <v>Y</v>
+      </c>
+      <c r="P30">
         <v>5</v>
       </c>
-      <c r="P30" t="s">
-        <v>1121</v>
-      </c>
-      <c r="Q30">
+      <c r="Q30" t="s">
+        <v>1125</v>
+      </c>
+      <c r="R30">
         <v>25</v>
       </c>
-      <c r="R30" t="s">
-        <v>1094</v>
-      </c>
-      <c r="S30">
+      <c r="S30" t="s">
+        <v>1092</v>
+      </c>
+      <c r="T30">
         <v>0</v>
       </c>
-      <c r="T30" t="s">
+      <c r="U30" t="s">
         <v>1088</v>
       </c>
-      <c r="U30" t="s">
+      <c r="V30" t="s">
+        <v>1093</v>
+      </c>
+      <c r="W30" t="s">
         <v>1095</v>
       </c>
-      <c r="V30" t="s">
-        <v>1101</v>
-      </c>
-      <c r="Y30" t="str">
+      <c r="X30" t="s">
+        <v>1093</v>
+      </c>
+      <c r="Z30" t="str">
         <f t="shared" si="10"/>
         <v>dm-Lo</v>
       </c>
-      <c r="Z30" t="str">
+      <c r="AA30" t="str">
         <f t="shared" si="11"/>
         <v>cp-0</v>
       </c>
-      <c r="AA30" t="str">
+      <c r="AB30" t="str">
         <f t="shared" si="12"/>
         <v>CF6</v>
       </c>
-      <c r="AB30" t="str">
+      <c r="AC30" t="str">
         <f t="shared" si="13"/>
         <v>df-Y</v>
       </c>
-      <c r="AC30" t="str">
+      <c r="AD30" t="str">
         <f t="shared" si="14"/>
         <v>ga-N</v>
       </c>
-    </row>
-    <row r="31" spans="2:29">
+      <c r="AE30" t="str">
+        <f t="shared" si="14"/>
+        <v>tc-Y</v>
+      </c>
+    </row>
+    <row r="31" spans="2:31">
       <c r="B31" t="str">
         <f t="shared" si="15"/>
         <v>vs~0026</v>
       </c>
       <c r="C31" t="str">
         <f t="shared" si="16"/>
-        <v>df-Y.ga-N.dm-Hi.cp-0.CF6</v>
+        <v>tc-Y.df-Y.ga-N.dm-Hi.cp-0.CF6</v>
       </c>
       <c r="H31" t="str">
         <f t="shared" si="4"/>
-        <v>df-Y.ga-N.dm-Hi.cp-0.CF6</v>
+        <v>tc-Y.df-Y.ga-N.dm-Hi.cp-0.CF6</v>
       </c>
       <c r="I31" t="str">
         <f t="shared" si="5"/>
@@ -36229,63 +36613,74 @@
         <f t="shared" si="9"/>
         <v>N</v>
       </c>
-      <c r="O31">
+      <c r="N31" t="str">
+        <f t="shared" si="9"/>
+        <v>Y</v>
+      </c>
+      <c r="P31">
         <v>5</v>
       </c>
-      <c r="P31" t="s">
-        <v>1122</v>
-      </c>
-      <c r="Q31">
+      <c r="Q31" t="s">
+        <v>1126</v>
+      </c>
+      <c r="R31">
         <v>26</v>
       </c>
-      <c r="R31" t="s">
-        <v>1097</v>
-      </c>
-      <c r="S31">
+      <c r="S31" t="s">
+        <v>1094</v>
+      </c>
+      <c r="T31">
         <v>0</v>
       </c>
-      <c r="T31" t="s">
+      <c r="U31" t="s">
         <v>1088</v>
       </c>
-      <c r="U31" t="s">
+      <c r="V31" t="s">
+        <v>1093</v>
+      </c>
+      <c r="W31" t="s">
         <v>1095</v>
       </c>
-      <c r="V31" t="s">
-        <v>1101</v>
-      </c>
-      <c r="Y31" t="str">
+      <c r="X31" t="s">
+        <v>1093</v>
+      </c>
+      <c r="Z31" t="str">
         <f t="shared" si="10"/>
         <v>dm-Hi</v>
       </c>
-      <c r="Z31" t="str">
+      <c r="AA31" t="str">
         <f t="shared" si="11"/>
         <v>cp-0</v>
       </c>
-      <c r="AA31" t="str">
+      <c r="AB31" t="str">
         <f t="shared" si="12"/>
         <v>CF6</v>
       </c>
-      <c r="AB31" t="str">
+      <c r="AC31" t="str">
         <f t="shared" si="13"/>
         <v>df-Y</v>
       </c>
-      <c r="AC31" t="str">
+      <c r="AD31" t="str">
         <f t="shared" si="14"/>
         <v>ga-N</v>
       </c>
-    </row>
-    <row r="32" spans="2:29">
+      <c r="AE31" t="str">
+        <f t="shared" si="14"/>
+        <v>tc-Y</v>
+      </c>
+    </row>
+    <row r="32" spans="2:31">
       <c r="B32" t="str">
         <f t="shared" si="15"/>
         <v>vs~0027</v>
       </c>
       <c r="C32" t="str">
         <f t="shared" si="16"/>
-        <v>df-Y.ga-N.dm-Lo.cp-95.CF6</v>
+        <v>tc-Y.df-Y.ga-N.dm-Lo.cp-95.CF6</v>
       </c>
       <c r="H32" t="str">
         <f t="shared" si="4"/>
-        <v>df-Y.ga-N.dm-Lo.cp-95.CF6</v>
+        <v>tc-Y.df-Y.ga-N.dm-Lo.cp-95.CF6</v>
       </c>
       <c r="I32" t="str">
         <f t="shared" si="5"/>
@@ -36307,63 +36702,74 @@
         <f t="shared" si="9"/>
         <v>N</v>
       </c>
-      <c r="O32">
+      <c r="N32" t="str">
+        <f t="shared" si="9"/>
+        <v>Y</v>
+      </c>
+      <c r="P32">
         <v>5</v>
       </c>
-      <c r="P32" t="s">
-        <v>1123</v>
-      </c>
-      <c r="Q32">
+      <c r="Q32" t="s">
+        <v>1127</v>
+      </c>
+      <c r="R32">
         <v>27</v>
       </c>
-      <c r="R32" t="s">
-        <v>1094</v>
-      </c>
-      <c r="S32">
+      <c r="S32" t="s">
+        <v>1092</v>
+      </c>
+      <c r="T32">
         <v>95</v>
       </c>
-      <c r="T32" t="s">
+      <c r="U32" t="s">
         <v>1088</v>
       </c>
-      <c r="U32" t="s">
+      <c r="V32" t="s">
+        <v>1093</v>
+      </c>
+      <c r="W32" t="s">
         <v>1095</v>
       </c>
-      <c r="V32" t="s">
-        <v>1101</v>
-      </c>
-      <c r="Y32" t="str">
+      <c r="X32" t="s">
+        <v>1093</v>
+      </c>
+      <c r="Z32" t="str">
         <f t="shared" si="10"/>
         <v>dm-Lo</v>
       </c>
-      <c r="Z32" t="str">
+      <c r="AA32" t="str">
         <f t="shared" si="11"/>
         <v>cp-95</v>
       </c>
-      <c r="AA32" t="str">
+      <c r="AB32" t="str">
         <f t="shared" si="12"/>
         <v>CF6</v>
       </c>
-      <c r="AB32" t="str">
+      <c r="AC32" t="str">
         <f t="shared" si="13"/>
         <v>df-Y</v>
       </c>
-      <c r="AC32" t="str">
+      <c r="AD32" t="str">
         <f t="shared" si="14"/>
         <v>ga-N</v>
       </c>
-    </row>
-    <row r="33" spans="2:29">
+      <c r="AE32" t="str">
+        <f t="shared" si="14"/>
+        <v>tc-Y</v>
+      </c>
+    </row>
+    <row r="33" spans="2:31">
       <c r="B33" t="str">
         <f t="shared" si="15"/>
         <v>vs~0028</v>
       </c>
       <c r="C33" t="str">
         <f t="shared" si="16"/>
-        <v>df-Y.ga-N.dm-Hi.cp-95.CF6</v>
+        <v>tc-Y.df-Y.ga-N.dm-Hi.cp-95.CF6</v>
       </c>
       <c r="H33" t="str">
         <f t="shared" si="4"/>
-        <v>df-Y.ga-N.dm-Hi.cp-95.CF6</v>
+        <v>tc-Y.df-Y.ga-N.dm-Hi.cp-95.CF6</v>
       </c>
       <c r="I33" t="str">
         <f t="shared" si="5"/>
@@ -36385,63 +36791,74 @@
         <f t="shared" si="9"/>
         <v>N</v>
       </c>
-      <c r="O33">
+      <c r="N33" t="str">
+        <f t="shared" si="9"/>
+        <v>Y</v>
+      </c>
+      <c r="P33">
         <v>5</v>
       </c>
-      <c r="P33" t="s">
-        <v>1124</v>
-      </c>
-      <c r="Q33">
+      <c r="Q33" t="s">
+        <v>1128</v>
+      </c>
+      <c r="R33">
         <v>28</v>
       </c>
-      <c r="R33" t="s">
-        <v>1097</v>
-      </c>
-      <c r="S33">
+      <c r="S33" t="s">
+        <v>1094</v>
+      </c>
+      <c r="T33">
         <v>95</v>
       </c>
-      <c r="T33" t="s">
+      <c r="U33" t="s">
         <v>1088</v>
       </c>
-      <c r="U33" t="s">
+      <c r="V33" t="s">
+        <v>1093</v>
+      </c>
+      <c r="W33" t="s">
         <v>1095</v>
       </c>
-      <c r="V33" t="s">
-        <v>1101</v>
-      </c>
-      <c r="Y33" t="str">
+      <c r="X33" t="s">
+        <v>1093</v>
+      </c>
+      <c r="Z33" t="str">
         <f t="shared" si="10"/>
         <v>dm-Hi</v>
       </c>
-      <c r="Z33" t="str">
+      <c r="AA33" t="str">
         <f t="shared" si="11"/>
         <v>cp-95</v>
       </c>
-      <c r="AA33" t="str">
+      <c r="AB33" t="str">
         <f t="shared" si="12"/>
         <v>CF6</v>
       </c>
-      <c r="AB33" t="str">
+      <c r="AC33" t="str">
         <f t="shared" si="13"/>
         <v>df-Y</v>
       </c>
-      <c r="AC33" t="str">
+      <c r="AD33" t="str">
         <f t="shared" si="14"/>
         <v>ga-N</v>
       </c>
-    </row>
-    <row r="34" spans="2:29">
+      <c r="AE33" t="str">
+        <f t="shared" si="14"/>
+        <v>tc-Y</v>
+      </c>
+    </row>
+    <row r="34" spans="2:31">
       <c r="B34" t="str">
         <f t="shared" si="15"/>
         <v>vs~0029</v>
       </c>
       <c r="C34" t="str">
         <f t="shared" si="16"/>
-        <v>df-N.ga-N.dm-Lo.cp-0.CF6</v>
+        <v>tc-Y.df-N.ga-N.dm-Lo.cp-0.CF6</v>
       </c>
       <c r="H34" t="str">
         <f t="shared" si="4"/>
-        <v>df-N.ga-N.dm-Lo.cp-0.CF6</v>
+        <v>tc-Y.df-N.ga-N.dm-Lo.cp-0.CF6</v>
       </c>
       <c r="I34" t="str">
         <f t="shared" si="5"/>
@@ -36463,63 +36880,74 @@
         <f t="shared" si="9"/>
         <v>N</v>
       </c>
-      <c r="O34">
+      <c r="N34" t="str">
+        <f t="shared" si="9"/>
+        <v>Y</v>
+      </c>
+      <c r="P34">
         <v>5</v>
       </c>
-      <c r="P34" t="s">
-        <v>1125</v>
-      </c>
-      <c r="Q34">
+      <c r="Q34" t="s">
+        <v>1129</v>
+      </c>
+      <c r="R34">
         <v>29</v>
       </c>
-      <c r="R34" t="s">
-        <v>1094</v>
-      </c>
-      <c r="S34">
+      <c r="S34" t="s">
+        <v>1092</v>
+      </c>
+      <c r="T34">
         <v>0</v>
       </c>
-      <c r="T34" t="s">
+      <c r="U34" t="s">
         <v>1088</v>
       </c>
-      <c r="U34" t="s">
-        <v>1101</v>
-      </c>
       <c r="V34" t="s">
-        <v>1101</v>
-      </c>
-      <c r="Y34" t="str">
+        <v>1095</v>
+      </c>
+      <c r="W34" t="s">
+        <v>1095</v>
+      </c>
+      <c r="X34" t="s">
+        <v>1093</v>
+      </c>
+      <c r="Z34" t="str">
         <f t="shared" si="10"/>
         <v>dm-Lo</v>
       </c>
-      <c r="Z34" t="str">
+      <c r="AA34" t="str">
         <f t="shared" si="11"/>
         <v>cp-0</v>
       </c>
-      <c r="AA34" t="str">
+      <c r="AB34" t="str">
         <f t="shared" si="12"/>
         <v>CF6</v>
       </c>
-      <c r="AB34" t="str">
+      <c r="AC34" t="str">
         <f t="shared" si="13"/>
         <v>df-N</v>
       </c>
-      <c r="AC34" t="str">
+      <c r="AD34" t="str">
         <f t="shared" si="14"/>
         <v>ga-N</v>
       </c>
-    </row>
-    <row r="35" spans="2:29">
+      <c r="AE34" t="str">
+        <f t="shared" si="14"/>
+        <v>tc-Y</v>
+      </c>
+    </row>
+    <row r="35" spans="2:31">
       <c r="B35" t="str">
         <f t="shared" si="15"/>
         <v>vs~0030</v>
       </c>
       <c r="C35" t="str">
         <f t="shared" si="16"/>
-        <v>df-N.ga-N.dm-Hi.cp-0.CF6</v>
+        <v>tc-Y.df-N.ga-N.dm-Hi.cp-0.CF6</v>
       </c>
       <c r="H35" t="str">
         <f t="shared" si="4"/>
-        <v>df-N.ga-N.dm-Hi.cp-0.CF6</v>
+        <v>tc-Y.df-N.ga-N.dm-Hi.cp-0.CF6</v>
       </c>
       <c r="I35" t="str">
         <f t="shared" si="5"/>
@@ -36541,63 +36969,74 @@
         <f t="shared" si="9"/>
         <v>N</v>
       </c>
-      <c r="O35">
+      <c r="N35" t="str">
+        <f t="shared" si="9"/>
+        <v>Y</v>
+      </c>
+      <c r="P35">
         <v>5</v>
       </c>
-      <c r="P35" t="s">
-        <v>1126</v>
-      </c>
-      <c r="Q35">
+      <c r="Q35" t="s">
+        <v>1130</v>
+      </c>
+      <c r="R35">
         <v>30</v>
       </c>
-      <c r="R35" t="s">
-        <v>1097</v>
-      </c>
-      <c r="S35">
+      <c r="S35" t="s">
+        <v>1094</v>
+      </c>
+      <c r="T35">
         <v>0</v>
       </c>
-      <c r="T35" t="s">
+      <c r="U35" t="s">
         <v>1088</v>
       </c>
-      <c r="U35" t="s">
-        <v>1101</v>
-      </c>
       <c r="V35" t="s">
-        <v>1101</v>
-      </c>
-      <c r="Y35" t="str">
+        <v>1095</v>
+      </c>
+      <c r="W35" t="s">
+        <v>1095</v>
+      </c>
+      <c r="X35" t="s">
+        <v>1093</v>
+      </c>
+      <c r="Z35" t="str">
         <f t="shared" si="10"/>
         <v>dm-Hi</v>
       </c>
-      <c r="Z35" t="str">
+      <c r="AA35" t="str">
         <f t="shared" si="11"/>
         <v>cp-0</v>
       </c>
-      <c r="AA35" t="str">
+      <c r="AB35" t="str">
         <f t="shared" si="12"/>
         <v>CF6</v>
       </c>
-      <c r="AB35" t="str">
+      <c r="AC35" t="str">
         <f t="shared" si="13"/>
         <v>df-N</v>
       </c>
-      <c r="AC35" t="str">
+      <c r="AD35" t="str">
         <f t="shared" si="14"/>
         <v>ga-N</v>
       </c>
-    </row>
-    <row r="36" spans="2:29">
+      <c r="AE35" t="str">
+        <f t="shared" si="14"/>
+        <v>tc-Y</v>
+      </c>
+    </row>
+    <row r="36" spans="2:31">
       <c r="B36" t="str">
         <f t="shared" si="15"/>
         <v>vs~0031</v>
       </c>
       <c r="C36" t="str">
         <f t="shared" si="16"/>
-        <v>df-N.ga-N.dm-Lo.cp-95.CF6</v>
+        <v>tc-Y.df-N.ga-N.dm-Lo.cp-95.CF6</v>
       </c>
       <c r="H36" t="str">
         <f t="shared" si="4"/>
-        <v>df-N.ga-N.dm-Lo.cp-95.CF6</v>
+        <v>tc-Y.df-N.ga-N.dm-Lo.cp-95.CF6</v>
       </c>
       <c r="I36" t="str">
         <f t="shared" si="5"/>
@@ -36619,63 +37058,74 @@
         <f t="shared" si="9"/>
         <v>N</v>
       </c>
-      <c r="O36">
+      <c r="N36" t="str">
+        <f t="shared" si="9"/>
+        <v>Y</v>
+      </c>
+      <c r="P36">
         <v>5</v>
       </c>
-      <c r="P36" t="s">
-        <v>1127</v>
-      </c>
-      <c r="Q36">
+      <c r="Q36" t="s">
+        <v>1131</v>
+      </c>
+      <c r="R36">
         <v>31</v>
       </c>
-      <c r="R36" t="s">
-        <v>1094</v>
-      </c>
-      <c r="S36">
+      <c r="S36" t="s">
+        <v>1092</v>
+      </c>
+      <c r="T36">
         <v>95</v>
       </c>
-      <c r="T36" t="s">
+      <c r="U36" t="s">
         <v>1088</v>
       </c>
-      <c r="U36" t="s">
-        <v>1101</v>
-      </c>
       <c r="V36" t="s">
-        <v>1101</v>
-      </c>
-      <c r="Y36" t="str">
+        <v>1095</v>
+      </c>
+      <c r="W36" t="s">
+        <v>1095</v>
+      </c>
+      <c r="X36" t="s">
+        <v>1093</v>
+      </c>
+      <c r="Z36" t="str">
         <f t="shared" si="10"/>
         <v>dm-Lo</v>
       </c>
-      <c r="Z36" t="str">
+      <c r="AA36" t="str">
         <f t="shared" si="11"/>
         <v>cp-95</v>
       </c>
-      <c r="AA36" t="str">
+      <c r="AB36" t="str">
         <f t="shared" si="12"/>
         <v>CF6</v>
       </c>
-      <c r="AB36" t="str">
+      <c r="AC36" t="str">
         <f t="shared" si="13"/>
         <v>df-N</v>
       </c>
-      <c r="AC36" t="str">
+      <c r="AD36" t="str">
         <f t="shared" si="14"/>
         <v>ga-N</v>
       </c>
-    </row>
-    <row r="37" spans="2:29">
+      <c r="AE36" t="str">
+        <f t="shared" si="14"/>
+        <v>tc-Y</v>
+      </c>
+    </row>
+    <row r="37" spans="2:31">
       <c r="B37" t="str">
         <f t="shared" si="15"/>
         <v>vs~0032</v>
       </c>
       <c r="C37" t="str">
         <f t="shared" si="16"/>
-        <v>df-N.ga-N.dm-Hi.cp-95.CF6</v>
+        <v>tc-Y.df-N.ga-N.dm-Hi.cp-95.CF6</v>
       </c>
       <c r="H37" t="str">
         <f t="shared" si="4"/>
-        <v>df-N.ga-N.dm-Hi.cp-95.CF6</v>
+        <v>tc-Y.df-N.ga-N.dm-Hi.cp-95.CF6</v>
       </c>
       <c r="I37" t="str">
         <f t="shared" si="5"/>
@@ -36697,49 +37147,2908 @@
         <f t="shared" si="9"/>
         <v>N</v>
       </c>
-      <c r="O37">
+      <c r="N37" t="str">
+        <f t="shared" si="9"/>
+        <v>Y</v>
+      </c>
+      <c r="P37">
         <v>5</v>
       </c>
-      <c r="P37" t="s">
-        <v>1128</v>
-      </c>
-      <c r="Q37">
+      <c r="Q37" t="s">
+        <v>1132</v>
+      </c>
+      <c r="R37">
         <v>32</v>
       </c>
-      <c r="R37" t="s">
-        <v>1097</v>
-      </c>
-      <c r="S37">
+      <c r="S37" t="s">
+        <v>1094</v>
+      </c>
+      <c r="T37">
         <v>95</v>
       </c>
-      <c r="T37" t="s">
+      <c r="U37" t="s">
         <v>1088</v>
       </c>
-      <c r="U37" t="s">
-        <v>1101</v>
-      </c>
       <c r="V37" t="s">
-        <v>1101</v>
-      </c>
-      <c r="Y37" t="str">
+        <v>1095</v>
+      </c>
+      <c r="W37" t="s">
+        <v>1095</v>
+      </c>
+      <c r="X37" t="s">
+        <v>1093</v>
+      </c>
+      <c r="Z37" t="str">
         <f t="shared" si="10"/>
         <v>dm-Hi</v>
       </c>
-      <c r="Z37" t="str">
+      <c r="AA37" t="str">
         <f t="shared" si="11"/>
         <v>cp-95</v>
       </c>
-      <c r="AA37" t="str">
+      <c r="AB37" t="str">
         <f t="shared" si="12"/>
         <v>CF6</v>
       </c>
-      <c r="AB37" t="str">
+      <c r="AC37" t="str">
         <f t="shared" si="13"/>
         <v>df-N</v>
       </c>
-      <c r="AC37" t="str">
+      <c r="AD37" t="str">
         <f t="shared" si="14"/>
         <v>ga-N</v>
+      </c>
+      <c r="AE37" t="str">
+        <f t="shared" si="14"/>
+        <v>tc-Y</v>
+      </c>
+    </row>
+    <row r="38" spans="2:31">
+      <c r="B38" t="str">
+        <f t="shared" ref="B38:B69" si="17">"vs~"&amp;TEXT(R38,"0000")</f>
+        <v>vs~0033</v>
+      </c>
+      <c r="C38" t="str">
+        <f t="shared" ref="C38:C69" si="18">H38</f>
+        <v>tc-N.df-Y.ga-Y.dm-Lo.cp-0.CF1</v>
+      </c>
+      <c r="H38" t="str">
+        <f t="shared" ref="H38:H69" si="19">_xlfn.TEXTJOIN(".",TRUE,AE38,AC38:AD38)&amp;"."&amp;_xlfn.TEXTJOIN(".",TRUE,Z38:AB38)</f>
+        <v>tc-N.df-Y.ga-Y.dm-Lo.cp-0.CF1</v>
+      </c>
+      <c r="I38" t="str">
+        <f t="shared" ref="I38:I69" si="20">S38</f>
+        <v>Lo</v>
+      </c>
+      <c r="J38" t="str">
+        <f t="shared" ref="J38:J69" si="21">TEXT(T38,"00")</f>
+        <v>00</v>
+      </c>
+      <c r="K38" t="str">
+        <f t="shared" ref="K38:K69" si="22">U38</f>
+        <v>CF1</v>
+      </c>
+      <c r="L38" t="str">
+        <f t="shared" ref="L38:L69" si="23">V38</f>
+        <v>Y</v>
+      </c>
+      <c r="M38" t="str">
+        <f t="shared" ref="M38:M69" si="24">W38</f>
+        <v>Y</v>
+      </c>
+      <c r="N38" t="str">
+        <f t="shared" ref="N38:N69" si="25">X38</f>
+        <v>N</v>
+      </c>
+      <c r="P38">
+        <v>5</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>1133</v>
+      </c>
+      <c r="R38">
+        <v>33</v>
+      </c>
+      <c r="S38" t="s">
+        <v>1092</v>
+      </c>
+      <c r="T38">
+        <v>0</v>
+      </c>
+      <c r="U38" t="s">
+        <v>1087</v>
+      </c>
+      <c r="V38" t="s">
+        <v>1093</v>
+      </c>
+      <c r="W38" t="s">
+        <v>1093</v>
+      </c>
+      <c r="X38" t="s">
+        <v>1095</v>
+      </c>
+      <c r="Z38" t="str">
+        <f t="shared" ref="Z38:Z69" si="26">S$1&amp;"-"&amp;S38</f>
+        <v>dm-Lo</v>
+      </c>
+      <c r="AA38" t="str">
+        <f t="shared" ref="AA38:AA69" si="27">T$1&amp;"-"&amp;T38</f>
+        <v>cp-0</v>
+      </c>
+      <c r="AB38" t="str">
+        <f t="shared" ref="AB38:AB69" si="28">U38</f>
+        <v>CF1</v>
+      </c>
+      <c r="AC38" t="str">
+        <f t="shared" ref="AC38:AC69" si="29">V$1&amp;"-"&amp;V38</f>
+        <v>df-Y</v>
+      </c>
+      <c r="AD38" t="str">
+        <f t="shared" ref="AD38:AD69" si="30">W$1&amp;"-"&amp;W38</f>
+        <v>ga-Y</v>
+      </c>
+      <c r="AE38" t="str">
+        <f t="shared" ref="AE38:AE69" si="31">X$1&amp;"-"&amp;X38</f>
+        <v>tc-N</v>
+      </c>
+    </row>
+    <row r="39" spans="2:31">
+      <c r="B39" t="str">
+        <f t="shared" si="17"/>
+        <v>vs~0034</v>
+      </c>
+      <c r="C39" t="str">
+        <f t="shared" si="18"/>
+        <v>tc-N.df-Y.ga-Y.dm-Hi.cp-0.CF1</v>
+      </c>
+      <c r="H39" t="str">
+        <f t="shared" si="19"/>
+        <v>tc-N.df-Y.ga-Y.dm-Hi.cp-0.CF1</v>
+      </c>
+      <c r="I39" t="str">
+        <f t="shared" si="20"/>
+        <v>Hi</v>
+      </c>
+      <c r="J39" t="str">
+        <f t="shared" si="21"/>
+        <v>00</v>
+      </c>
+      <c r="K39" t="str">
+        <f t="shared" si="22"/>
+        <v>CF1</v>
+      </c>
+      <c r="L39" t="str">
+        <f t="shared" si="23"/>
+        <v>Y</v>
+      </c>
+      <c r="M39" t="str">
+        <f t="shared" si="24"/>
+        <v>Y</v>
+      </c>
+      <c r="N39" t="str">
+        <f t="shared" si="25"/>
+        <v>N</v>
+      </c>
+      <c r="P39">
+        <v>5</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>1134</v>
+      </c>
+      <c r="R39">
+        <v>34</v>
+      </c>
+      <c r="S39" t="s">
+        <v>1094</v>
+      </c>
+      <c r="T39">
+        <v>0</v>
+      </c>
+      <c r="U39" t="s">
+        <v>1087</v>
+      </c>
+      <c r="V39" t="s">
+        <v>1093</v>
+      </c>
+      <c r="W39" t="s">
+        <v>1093</v>
+      </c>
+      <c r="X39" t="s">
+        <v>1095</v>
+      </c>
+      <c r="Z39" t="str">
+        <f t="shared" si="26"/>
+        <v>dm-Hi</v>
+      </c>
+      <c r="AA39" t="str">
+        <f t="shared" si="27"/>
+        <v>cp-0</v>
+      </c>
+      <c r="AB39" t="str">
+        <f t="shared" si="28"/>
+        <v>CF1</v>
+      </c>
+      <c r="AC39" t="str">
+        <f t="shared" si="29"/>
+        <v>df-Y</v>
+      </c>
+      <c r="AD39" t="str">
+        <f t="shared" si="30"/>
+        <v>ga-Y</v>
+      </c>
+      <c r="AE39" t="str">
+        <f t="shared" si="31"/>
+        <v>tc-N</v>
+      </c>
+    </row>
+    <row r="40" spans="2:31">
+      <c r="B40" t="str">
+        <f t="shared" si="17"/>
+        <v>vs~0035</v>
+      </c>
+      <c r="C40" t="str">
+        <f t="shared" si="18"/>
+        <v>tc-N.df-Y.ga-Y.dm-Lo.cp-95.CF1</v>
+      </c>
+      <c r="H40" t="str">
+        <f t="shared" si="19"/>
+        <v>tc-N.df-Y.ga-Y.dm-Lo.cp-95.CF1</v>
+      </c>
+      <c r="I40" t="str">
+        <f t="shared" si="20"/>
+        <v>Lo</v>
+      </c>
+      <c r="J40" t="str">
+        <f t="shared" si="21"/>
+        <v>95</v>
+      </c>
+      <c r="K40" t="str">
+        <f t="shared" si="22"/>
+        <v>CF1</v>
+      </c>
+      <c r="L40" t="str">
+        <f t="shared" si="23"/>
+        <v>Y</v>
+      </c>
+      <c r="M40" t="str">
+        <f t="shared" si="24"/>
+        <v>Y</v>
+      </c>
+      <c r="N40" t="str">
+        <f t="shared" si="25"/>
+        <v>N</v>
+      </c>
+      <c r="P40">
+        <v>5</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>1135</v>
+      </c>
+      <c r="R40">
+        <v>35</v>
+      </c>
+      <c r="S40" t="s">
+        <v>1092</v>
+      </c>
+      <c r="T40">
+        <v>95</v>
+      </c>
+      <c r="U40" t="s">
+        <v>1087</v>
+      </c>
+      <c r="V40" t="s">
+        <v>1093</v>
+      </c>
+      <c r="W40" t="s">
+        <v>1093</v>
+      </c>
+      <c r="X40" t="s">
+        <v>1095</v>
+      </c>
+      <c r="Z40" t="str">
+        <f t="shared" si="26"/>
+        <v>dm-Lo</v>
+      </c>
+      <c r="AA40" t="str">
+        <f t="shared" si="27"/>
+        <v>cp-95</v>
+      </c>
+      <c r="AB40" t="str">
+        <f t="shared" si="28"/>
+        <v>CF1</v>
+      </c>
+      <c r="AC40" t="str">
+        <f t="shared" si="29"/>
+        <v>df-Y</v>
+      </c>
+      <c r="AD40" t="str">
+        <f t="shared" si="30"/>
+        <v>ga-Y</v>
+      </c>
+      <c r="AE40" t="str">
+        <f t="shared" si="31"/>
+        <v>tc-N</v>
+      </c>
+    </row>
+    <row r="41" spans="2:31">
+      <c r="B41" t="str">
+        <f t="shared" si="17"/>
+        <v>vs~0036</v>
+      </c>
+      <c r="C41" t="str">
+        <f t="shared" si="18"/>
+        <v>tc-N.df-Y.ga-Y.dm-Hi.cp-95.CF1</v>
+      </c>
+      <c r="H41" t="str">
+        <f t="shared" si="19"/>
+        <v>tc-N.df-Y.ga-Y.dm-Hi.cp-95.CF1</v>
+      </c>
+      <c r="I41" t="str">
+        <f t="shared" si="20"/>
+        <v>Hi</v>
+      </c>
+      <c r="J41" t="str">
+        <f t="shared" si="21"/>
+        <v>95</v>
+      </c>
+      <c r="K41" t="str">
+        <f t="shared" si="22"/>
+        <v>CF1</v>
+      </c>
+      <c r="L41" t="str">
+        <f t="shared" si="23"/>
+        <v>Y</v>
+      </c>
+      <c r="M41" t="str">
+        <f t="shared" si="24"/>
+        <v>Y</v>
+      </c>
+      <c r="N41" t="str">
+        <f t="shared" si="25"/>
+        <v>N</v>
+      </c>
+      <c r="P41">
+        <v>5</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>1136</v>
+      </c>
+      <c r="R41">
+        <v>36</v>
+      </c>
+      <c r="S41" t="s">
+        <v>1094</v>
+      </c>
+      <c r="T41">
+        <v>95</v>
+      </c>
+      <c r="U41" t="s">
+        <v>1087</v>
+      </c>
+      <c r="V41" t="s">
+        <v>1093</v>
+      </c>
+      <c r="W41" t="s">
+        <v>1093</v>
+      </c>
+      <c r="X41" t="s">
+        <v>1095</v>
+      </c>
+      <c r="Z41" t="str">
+        <f t="shared" si="26"/>
+        <v>dm-Hi</v>
+      </c>
+      <c r="AA41" t="str">
+        <f t="shared" si="27"/>
+        <v>cp-95</v>
+      </c>
+      <c r="AB41" t="str">
+        <f t="shared" si="28"/>
+        <v>CF1</v>
+      </c>
+      <c r="AC41" t="str">
+        <f t="shared" si="29"/>
+        <v>df-Y</v>
+      </c>
+      <c r="AD41" t="str">
+        <f t="shared" si="30"/>
+        <v>ga-Y</v>
+      </c>
+      <c r="AE41" t="str">
+        <f t="shared" si="31"/>
+        <v>tc-N</v>
+      </c>
+    </row>
+    <row r="42" spans="2:31">
+      <c r="B42" t="str">
+        <f t="shared" si="17"/>
+        <v>vs~0037</v>
+      </c>
+      <c r="C42" t="str">
+        <f t="shared" si="18"/>
+        <v>tc-N.df-N.ga-Y.dm-Lo.cp-0.CF1</v>
+      </c>
+      <c r="H42" t="str">
+        <f t="shared" si="19"/>
+        <v>tc-N.df-N.ga-Y.dm-Lo.cp-0.CF1</v>
+      </c>
+      <c r="I42" t="str">
+        <f t="shared" si="20"/>
+        <v>Lo</v>
+      </c>
+      <c r="J42" t="str">
+        <f t="shared" si="21"/>
+        <v>00</v>
+      </c>
+      <c r="K42" t="str">
+        <f t="shared" si="22"/>
+        <v>CF1</v>
+      </c>
+      <c r="L42" t="str">
+        <f t="shared" si="23"/>
+        <v>N</v>
+      </c>
+      <c r="M42" t="str">
+        <f t="shared" si="24"/>
+        <v>Y</v>
+      </c>
+      <c r="N42" t="str">
+        <f t="shared" si="25"/>
+        <v>N</v>
+      </c>
+      <c r="P42">
+        <v>5</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>1137</v>
+      </c>
+      <c r="R42">
+        <v>37</v>
+      </c>
+      <c r="S42" t="s">
+        <v>1092</v>
+      </c>
+      <c r="T42">
+        <v>0</v>
+      </c>
+      <c r="U42" t="s">
+        <v>1087</v>
+      </c>
+      <c r="V42" t="s">
+        <v>1095</v>
+      </c>
+      <c r="W42" t="s">
+        <v>1093</v>
+      </c>
+      <c r="X42" t="s">
+        <v>1095</v>
+      </c>
+      <c r="Z42" t="str">
+        <f t="shared" si="26"/>
+        <v>dm-Lo</v>
+      </c>
+      <c r="AA42" t="str">
+        <f t="shared" si="27"/>
+        <v>cp-0</v>
+      </c>
+      <c r="AB42" t="str">
+        <f t="shared" si="28"/>
+        <v>CF1</v>
+      </c>
+      <c r="AC42" t="str">
+        <f t="shared" si="29"/>
+        <v>df-N</v>
+      </c>
+      <c r="AD42" t="str">
+        <f t="shared" si="30"/>
+        <v>ga-Y</v>
+      </c>
+      <c r="AE42" t="str">
+        <f t="shared" si="31"/>
+        <v>tc-N</v>
+      </c>
+    </row>
+    <row r="43" spans="2:31">
+      <c r="B43" t="str">
+        <f t="shared" si="17"/>
+        <v>vs~0038</v>
+      </c>
+      <c r="C43" t="str">
+        <f t="shared" si="18"/>
+        <v>tc-N.df-N.ga-Y.dm-Hi.cp-0.CF1</v>
+      </c>
+      <c r="H43" t="str">
+        <f t="shared" si="19"/>
+        <v>tc-N.df-N.ga-Y.dm-Hi.cp-0.CF1</v>
+      </c>
+      <c r="I43" t="str">
+        <f t="shared" si="20"/>
+        <v>Hi</v>
+      </c>
+      <c r="J43" t="str">
+        <f t="shared" si="21"/>
+        <v>00</v>
+      </c>
+      <c r="K43" t="str">
+        <f t="shared" si="22"/>
+        <v>CF1</v>
+      </c>
+      <c r="L43" t="str">
+        <f t="shared" si="23"/>
+        <v>N</v>
+      </c>
+      <c r="M43" t="str">
+        <f t="shared" si="24"/>
+        <v>Y</v>
+      </c>
+      <c r="N43" t="str">
+        <f t="shared" si="25"/>
+        <v>N</v>
+      </c>
+      <c r="P43">
+        <v>5</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>1138</v>
+      </c>
+      <c r="R43">
+        <v>38</v>
+      </c>
+      <c r="S43" t="s">
+        <v>1094</v>
+      </c>
+      <c r="T43">
+        <v>0</v>
+      </c>
+      <c r="U43" t="s">
+        <v>1087</v>
+      </c>
+      <c r="V43" t="s">
+        <v>1095</v>
+      </c>
+      <c r="W43" t="s">
+        <v>1093</v>
+      </c>
+      <c r="X43" t="s">
+        <v>1095</v>
+      </c>
+      <c r="Z43" t="str">
+        <f t="shared" si="26"/>
+        <v>dm-Hi</v>
+      </c>
+      <c r="AA43" t="str">
+        <f t="shared" si="27"/>
+        <v>cp-0</v>
+      </c>
+      <c r="AB43" t="str">
+        <f t="shared" si="28"/>
+        <v>CF1</v>
+      </c>
+      <c r="AC43" t="str">
+        <f t="shared" si="29"/>
+        <v>df-N</v>
+      </c>
+      <c r="AD43" t="str">
+        <f t="shared" si="30"/>
+        <v>ga-Y</v>
+      </c>
+      <c r="AE43" t="str">
+        <f t="shared" si="31"/>
+        <v>tc-N</v>
+      </c>
+    </row>
+    <row r="44" spans="2:31">
+      <c r="B44" t="str">
+        <f t="shared" si="17"/>
+        <v>vs~0039</v>
+      </c>
+      <c r="C44" t="str">
+        <f t="shared" si="18"/>
+        <v>tc-N.df-N.ga-Y.dm-Lo.cp-95.CF1</v>
+      </c>
+      <c r="H44" t="str">
+        <f t="shared" si="19"/>
+        <v>tc-N.df-N.ga-Y.dm-Lo.cp-95.CF1</v>
+      </c>
+      <c r="I44" t="str">
+        <f t="shared" si="20"/>
+        <v>Lo</v>
+      </c>
+      <c r="J44" t="str">
+        <f t="shared" si="21"/>
+        <v>95</v>
+      </c>
+      <c r="K44" t="str">
+        <f t="shared" si="22"/>
+        <v>CF1</v>
+      </c>
+      <c r="L44" t="str">
+        <f t="shared" si="23"/>
+        <v>N</v>
+      </c>
+      <c r="M44" t="str">
+        <f t="shared" si="24"/>
+        <v>Y</v>
+      </c>
+      <c r="N44" t="str">
+        <f t="shared" si="25"/>
+        <v>N</v>
+      </c>
+      <c r="P44">
+        <v>5</v>
+      </c>
+      <c r="Q44" t="s">
+        <v>1139</v>
+      </c>
+      <c r="R44">
+        <v>39</v>
+      </c>
+      <c r="S44" t="s">
+        <v>1092</v>
+      </c>
+      <c r="T44">
+        <v>95</v>
+      </c>
+      <c r="U44" t="s">
+        <v>1087</v>
+      </c>
+      <c r="V44" t="s">
+        <v>1095</v>
+      </c>
+      <c r="W44" t="s">
+        <v>1093</v>
+      </c>
+      <c r="X44" t="s">
+        <v>1095</v>
+      </c>
+      <c r="Z44" t="str">
+        <f t="shared" si="26"/>
+        <v>dm-Lo</v>
+      </c>
+      <c r="AA44" t="str">
+        <f t="shared" si="27"/>
+        <v>cp-95</v>
+      </c>
+      <c r="AB44" t="str">
+        <f t="shared" si="28"/>
+        <v>CF1</v>
+      </c>
+      <c r="AC44" t="str">
+        <f t="shared" si="29"/>
+        <v>df-N</v>
+      </c>
+      <c r="AD44" t="str">
+        <f t="shared" si="30"/>
+        <v>ga-Y</v>
+      </c>
+      <c r="AE44" t="str">
+        <f t="shared" si="31"/>
+        <v>tc-N</v>
+      </c>
+    </row>
+    <row r="45" spans="2:31">
+      <c r="B45" t="str">
+        <f t="shared" si="17"/>
+        <v>vs~0040</v>
+      </c>
+      <c r="C45" t="str">
+        <f t="shared" si="18"/>
+        <v>tc-N.df-N.ga-Y.dm-Hi.cp-95.CF1</v>
+      </c>
+      <c r="H45" t="str">
+        <f t="shared" si="19"/>
+        <v>tc-N.df-N.ga-Y.dm-Hi.cp-95.CF1</v>
+      </c>
+      <c r="I45" t="str">
+        <f t="shared" si="20"/>
+        <v>Hi</v>
+      </c>
+      <c r="J45" t="str">
+        <f t="shared" si="21"/>
+        <v>95</v>
+      </c>
+      <c r="K45" t="str">
+        <f t="shared" si="22"/>
+        <v>CF1</v>
+      </c>
+      <c r="L45" t="str">
+        <f t="shared" si="23"/>
+        <v>N</v>
+      </c>
+      <c r="M45" t="str">
+        <f t="shared" si="24"/>
+        <v>Y</v>
+      </c>
+      <c r="N45" t="str">
+        <f t="shared" si="25"/>
+        <v>N</v>
+      </c>
+      <c r="P45">
+        <v>5</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>1140</v>
+      </c>
+      <c r="R45">
+        <v>40</v>
+      </c>
+      <c r="S45" t="s">
+        <v>1094</v>
+      </c>
+      <c r="T45">
+        <v>95</v>
+      </c>
+      <c r="U45" t="s">
+        <v>1087</v>
+      </c>
+      <c r="V45" t="s">
+        <v>1095</v>
+      </c>
+      <c r="W45" t="s">
+        <v>1093</v>
+      </c>
+      <c r="X45" t="s">
+        <v>1095</v>
+      </c>
+      <c r="Z45" t="str">
+        <f t="shared" si="26"/>
+        <v>dm-Hi</v>
+      </c>
+      <c r="AA45" t="str">
+        <f t="shared" si="27"/>
+        <v>cp-95</v>
+      </c>
+      <c r="AB45" t="str">
+        <f t="shared" si="28"/>
+        <v>CF1</v>
+      </c>
+      <c r="AC45" t="str">
+        <f t="shared" si="29"/>
+        <v>df-N</v>
+      </c>
+      <c r="AD45" t="str">
+        <f t="shared" si="30"/>
+        <v>ga-Y</v>
+      </c>
+      <c r="AE45" t="str">
+        <f t="shared" si="31"/>
+        <v>tc-N</v>
+      </c>
+    </row>
+    <row r="46" spans="2:31">
+      <c r="B46" t="str">
+        <f t="shared" si="17"/>
+        <v>vs~0041</v>
+      </c>
+      <c r="C46" t="str">
+        <f t="shared" si="18"/>
+        <v>tc-N.df-Y.ga-Y.dm-Lo.cp-0.CF6</v>
+      </c>
+      <c r="H46" t="str">
+        <f t="shared" si="19"/>
+        <v>tc-N.df-Y.ga-Y.dm-Lo.cp-0.CF6</v>
+      </c>
+      <c r="I46" t="str">
+        <f t="shared" si="20"/>
+        <v>Lo</v>
+      </c>
+      <c r="J46" t="str">
+        <f t="shared" si="21"/>
+        <v>00</v>
+      </c>
+      <c r="K46" t="str">
+        <f t="shared" si="22"/>
+        <v>CF6</v>
+      </c>
+      <c r="L46" t="str">
+        <f t="shared" si="23"/>
+        <v>Y</v>
+      </c>
+      <c r="M46" t="str">
+        <f t="shared" si="24"/>
+        <v>Y</v>
+      </c>
+      <c r="N46" t="str">
+        <f t="shared" si="25"/>
+        <v>N</v>
+      </c>
+      <c r="P46">
+        <v>5</v>
+      </c>
+      <c r="Q46" t="s">
+        <v>1141</v>
+      </c>
+      <c r="R46">
+        <v>41</v>
+      </c>
+      <c r="S46" t="s">
+        <v>1092</v>
+      </c>
+      <c r="T46">
+        <v>0</v>
+      </c>
+      <c r="U46" t="s">
+        <v>1088</v>
+      </c>
+      <c r="V46" t="s">
+        <v>1093</v>
+      </c>
+      <c r="W46" t="s">
+        <v>1093</v>
+      </c>
+      <c r="X46" t="s">
+        <v>1095</v>
+      </c>
+      <c r="Z46" t="str">
+        <f t="shared" si="26"/>
+        <v>dm-Lo</v>
+      </c>
+      <c r="AA46" t="str">
+        <f t="shared" si="27"/>
+        <v>cp-0</v>
+      </c>
+      <c r="AB46" t="str">
+        <f t="shared" si="28"/>
+        <v>CF6</v>
+      </c>
+      <c r="AC46" t="str">
+        <f t="shared" si="29"/>
+        <v>df-Y</v>
+      </c>
+      <c r="AD46" t="str">
+        <f t="shared" si="30"/>
+        <v>ga-Y</v>
+      </c>
+      <c r="AE46" t="str">
+        <f t="shared" si="31"/>
+        <v>tc-N</v>
+      </c>
+    </row>
+    <row r="47" spans="2:31">
+      <c r="B47" t="str">
+        <f t="shared" si="17"/>
+        <v>vs~0042</v>
+      </c>
+      <c r="C47" t="str">
+        <f t="shared" si="18"/>
+        <v>tc-N.df-Y.ga-Y.dm-Hi.cp-0.CF6</v>
+      </c>
+      <c r="H47" t="str">
+        <f t="shared" si="19"/>
+        <v>tc-N.df-Y.ga-Y.dm-Hi.cp-0.CF6</v>
+      </c>
+      <c r="I47" t="str">
+        <f t="shared" si="20"/>
+        <v>Hi</v>
+      </c>
+      <c r="J47" t="str">
+        <f t="shared" si="21"/>
+        <v>00</v>
+      </c>
+      <c r="K47" t="str">
+        <f t="shared" si="22"/>
+        <v>CF6</v>
+      </c>
+      <c r="L47" t="str">
+        <f t="shared" si="23"/>
+        <v>Y</v>
+      </c>
+      <c r="M47" t="str">
+        <f t="shared" si="24"/>
+        <v>Y</v>
+      </c>
+      <c r="N47" t="str">
+        <f t="shared" si="25"/>
+        <v>N</v>
+      </c>
+      <c r="P47">
+        <v>5</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>1142</v>
+      </c>
+      <c r="R47">
+        <v>42</v>
+      </c>
+      <c r="S47" t="s">
+        <v>1094</v>
+      </c>
+      <c r="T47">
+        <v>0</v>
+      </c>
+      <c r="U47" t="s">
+        <v>1088</v>
+      </c>
+      <c r="V47" t="s">
+        <v>1093</v>
+      </c>
+      <c r="W47" t="s">
+        <v>1093</v>
+      </c>
+      <c r="X47" t="s">
+        <v>1095</v>
+      </c>
+      <c r="Z47" t="str">
+        <f t="shared" si="26"/>
+        <v>dm-Hi</v>
+      </c>
+      <c r="AA47" t="str">
+        <f t="shared" si="27"/>
+        <v>cp-0</v>
+      </c>
+      <c r="AB47" t="str">
+        <f t="shared" si="28"/>
+        <v>CF6</v>
+      </c>
+      <c r="AC47" t="str">
+        <f t="shared" si="29"/>
+        <v>df-Y</v>
+      </c>
+      <c r="AD47" t="str">
+        <f t="shared" si="30"/>
+        <v>ga-Y</v>
+      </c>
+      <c r="AE47" t="str">
+        <f t="shared" si="31"/>
+        <v>tc-N</v>
+      </c>
+    </row>
+    <row r="48" spans="2:31">
+      <c r="B48" t="str">
+        <f t="shared" si="17"/>
+        <v>vs~0043</v>
+      </c>
+      <c r="C48" t="str">
+        <f t="shared" si="18"/>
+        <v>tc-N.df-Y.ga-Y.dm-Lo.cp-95.CF6</v>
+      </c>
+      <c r="H48" t="str">
+        <f t="shared" si="19"/>
+        <v>tc-N.df-Y.ga-Y.dm-Lo.cp-95.CF6</v>
+      </c>
+      <c r="I48" t="str">
+        <f t="shared" si="20"/>
+        <v>Lo</v>
+      </c>
+      <c r="J48" t="str">
+        <f t="shared" si="21"/>
+        <v>95</v>
+      </c>
+      <c r="K48" t="str">
+        <f t="shared" si="22"/>
+        <v>CF6</v>
+      </c>
+      <c r="L48" t="str">
+        <f t="shared" si="23"/>
+        <v>Y</v>
+      </c>
+      <c r="M48" t="str">
+        <f t="shared" si="24"/>
+        <v>Y</v>
+      </c>
+      <c r="N48" t="str">
+        <f t="shared" si="25"/>
+        <v>N</v>
+      </c>
+      <c r="P48">
+        <v>5</v>
+      </c>
+      <c r="Q48" t="s">
+        <v>1143</v>
+      </c>
+      <c r="R48">
+        <v>43</v>
+      </c>
+      <c r="S48" t="s">
+        <v>1092</v>
+      </c>
+      <c r="T48">
+        <v>95</v>
+      </c>
+      <c r="U48" t="s">
+        <v>1088</v>
+      </c>
+      <c r="V48" t="s">
+        <v>1093</v>
+      </c>
+      <c r="W48" t="s">
+        <v>1093</v>
+      </c>
+      <c r="X48" t="s">
+        <v>1095</v>
+      </c>
+      <c r="Z48" t="str">
+        <f t="shared" si="26"/>
+        <v>dm-Lo</v>
+      </c>
+      <c r="AA48" t="str">
+        <f t="shared" si="27"/>
+        <v>cp-95</v>
+      </c>
+      <c r="AB48" t="str">
+        <f t="shared" si="28"/>
+        <v>CF6</v>
+      </c>
+      <c r="AC48" t="str">
+        <f t="shared" si="29"/>
+        <v>df-Y</v>
+      </c>
+      <c r="AD48" t="str">
+        <f t="shared" si="30"/>
+        <v>ga-Y</v>
+      </c>
+      <c r="AE48" t="str">
+        <f t="shared" si="31"/>
+        <v>tc-N</v>
+      </c>
+    </row>
+    <row r="49" spans="2:31">
+      <c r="B49" t="str">
+        <f t="shared" si="17"/>
+        <v>vs~0044</v>
+      </c>
+      <c r="C49" t="str">
+        <f t="shared" si="18"/>
+        <v>tc-N.df-Y.ga-Y.dm-Hi.cp-95.CF6</v>
+      </c>
+      <c r="H49" t="str">
+        <f t="shared" si="19"/>
+        <v>tc-N.df-Y.ga-Y.dm-Hi.cp-95.CF6</v>
+      </c>
+      <c r="I49" t="str">
+        <f t="shared" si="20"/>
+        <v>Hi</v>
+      </c>
+      <c r="J49" t="str">
+        <f t="shared" si="21"/>
+        <v>95</v>
+      </c>
+      <c r="K49" t="str">
+        <f t="shared" si="22"/>
+        <v>CF6</v>
+      </c>
+      <c r="L49" t="str">
+        <f t="shared" si="23"/>
+        <v>Y</v>
+      </c>
+      <c r="M49" t="str">
+        <f t="shared" si="24"/>
+        <v>Y</v>
+      </c>
+      <c r="N49" t="str">
+        <f t="shared" si="25"/>
+        <v>N</v>
+      </c>
+      <c r="P49">
+        <v>5</v>
+      </c>
+      <c r="Q49" t="s">
+        <v>1144</v>
+      </c>
+      <c r="R49">
+        <v>44</v>
+      </c>
+      <c r="S49" t="s">
+        <v>1094</v>
+      </c>
+      <c r="T49">
+        <v>95</v>
+      </c>
+      <c r="U49" t="s">
+        <v>1088</v>
+      </c>
+      <c r="V49" t="s">
+        <v>1093</v>
+      </c>
+      <c r="W49" t="s">
+        <v>1093</v>
+      </c>
+      <c r="X49" t="s">
+        <v>1095</v>
+      </c>
+      <c r="Z49" t="str">
+        <f t="shared" si="26"/>
+        <v>dm-Hi</v>
+      </c>
+      <c r="AA49" t="str">
+        <f t="shared" si="27"/>
+        <v>cp-95</v>
+      </c>
+      <c r="AB49" t="str">
+        <f t="shared" si="28"/>
+        <v>CF6</v>
+      </c>
+      <c r="AC49" t="str">
+        <f t="shared" si="29"/>
+        <v>df-Y</v>
+      </c>
+      <c r="AD49" t="str">
+        <f t="shared" si="30"/>
+        <v>ga-Y</v>
+      </c>
+      <c r="AE49" t="str">
+        <f t="shared" si="31"/>
+        <v>tc-N</v>
+      </c>
+    </row>
+    <row r="50" spans="2:31">
+      <c r="B50" t="str">
+        <f t="shared" si="17"/>
+        <v>vs~0045</v>
+      </c>
+      <c r="C50" t="str">
+        <f t="shared" si="18"/>
+        <v>tc-N.df-N.ga-Y.dm-Lo.cp-0.CF6</v>
+      </c>
+      <c r="H50" t="str">
+        <f t="shared" si="19"/>
+        <v>tc-N.df-N.ga-Y.dm-Lo.cp-0.CF6</v>
+      </c>
+      <c r="I50" t="str">
+        <f t="shared" si="20"/>
+        <v>Lo</v>
+      </c>
+      <c r="J50" t="str">
+        <f t="shared" si="21"/>
+        <v>00</v>
+      </c>
+      <c r="K50" t="str">
+        <f t="shared" si="22"/>
+        <v>CF6</v>
+      </c>
+      <c r="L50" t="str">
+        <f t="shared" si="23"/>
+        <v>N</v>
+      </c>
+      <c r="M50" t="str">
+        <f t="shared" si="24"/>
+        <v>Y</v>
+      </c>
+      <c r="N50" t="str">
+        <f t="shared" si="25"/>
+        <v>N</v>
+      </c>
+      <c r="P50">
+        <v>5</v>
+      </c>
+      <c r="Q50" t="s">
+        <v>1145</v>
+      </c>
+      <c r="R50">
+        <v>45</v>
+      </c>
+      <c r="S50" t="s">
+        <v>1092</v>
+      </c>
+      <c r="T50">
+        <v>0</v>
+      </c>
+      <c r="U50" t="s">
+        <v>1088</v>
+      </c>
+      <c r="V50" t="s">
+        <v>1095</v>
+      </c>
+      <c r="W50" t="s">
+        <v>1093</v>
+      </c>
+      <c r="X50" t="s">
+        <v>1095</v>
+      </c>
+      <c r="Z50" t="str">
+        <f t="shared" si="26"/>
+        <v>dm-Lo</v>
+      </c>
+      <c r="AA50" t="str">
+        <f t="shared" si="27"/>
+        <v>cp-0</v>
+      </c>
+      <c r="AB50" t="str">
+        <f t="shared" si="28"/>
+        <v>CF6</v>
+      </c>
+      <c r="AC50" t="str">
+        <f t="shared" si="29"/>
+        <v>df-N</v>
+      </c>
+      <c r="AD50" t="str">
+        <f t="shared" si="30"/>
+        <v>ga-Y</v>
+      </c>
+      <c r="AE50" t="str">
+        <f t="shared" si="31"/>
+        <v>tc-N</v>
+      </c>
+    </row>
+    <row r="51" spans="2:31">
+      <c r="B51" t="str">
+        <f t="shared" si="17"/>
+        <v>vs~0046</v>
+      </c>
+      <c r="C51" t="str">
+        <f t="shared" si="18"/>
+        <v>tc-N.df-N.ga-Y.dm-Hi.cp-0.CF6</v>
+      </c>
+      <c r="H51" t="str">
+        <f t="shared" si="19"/>
+        <v>tc-N.df-N.ga-Y.dm-Hi.cp-0.CF6</v>
+      </c>
+      <c r="I51" t="str">
+        <f t="shared" si="20"/>
+        <v>Hi</v>
+      </c>
+      <c r="J51" t="str">
+        <f t="shared" si="21"/>
+        <v>00</v>
+      </c>
+      <c r="K51" t="str">
+        <f t="shared" si="22"/>
+        <v>CF6</v>
+      </c>
+      <c r="L51" t="str">
+        <f t="shared" si="23"/>
+        <v>N</v>
+      </c>
+      <c r="M51" t="str">
+        <f t="shared" si="24"/>
+        <v>Y</v>
+      </c>
+      <c r="N51" t="str">
+        <f t="shared" si="25"/>
+        <v>N</v>
+      </c>
+      <c r="P51">
+        <v>5</v>
+      </c>
+      <c r="Q51" t="s">
+        <v>1146</v>
+      </c>
+      <c r="R51">
+        <v>46</v>
+      </c>
+      <c r="S51" t="s">
+        <v>1094</v>
+      </c>
+      <c r="T51">
+        <v>0</v>
+      </c>
+      <c r="U51" t="s">
+        <v>1088</v>
+      </c>
+      <c r="V51" t="s">
+        <v>1095</v>
+      </c>
+      <c r="W51" t="s">
+        <v>1093</v>
+      </c>
+      <c r="X51" t="s">
+        <v>1095</v>
+      </c>
+      <c r="Z51" t="str">
+        <f t="shared" si="26"/>
+        <v>dm-Hi</v>
+      </c>
+      <c r="AA51" t="str">
+        <f t="shared" si="27"/>
+        <v>cp-0</v>
+      </c>
+      <c r="AB51" t="str">
+        <f t="shared" si="28"/>
+        <v>CF6</v>
+      </c>
+      <c r="AC51" t="str">
+        <f t="shared" si="29"/>
+        <v>df-N</v>
+      </c>
+      <c r="AD51" t="str">
+        <f t="shared" si="30"/>
+        <v>ga-Y</v>
+      </c>
+      <c r="AE51" t="str">
+        <f t="shared" si="31"/>
+        <v>tc-N</v>
+      </c>
+    </row>
+    <row r="52" spans="2:31">
+      <c r="B52" t="str">
+        <f t="shared" si="17"/>
+        <v>vs~0047</v>
+      </c>
+      <c r="C52" t="str">
+        <f t="shared" si="18"/>
+        <v>tc-N.df-N.ga-Y.dm-Lo.cp-95.CF6</v>
+      </c>
+      <c r="H52" t="str">
+        <f t="shared" si="19"/>
+        <v>tc-N.df-N.ga-Y.dm-Lo.cp-95.CF6</v>
+      </c>
+      <c r="I52" t="str">
+        <f t="shared" si="20"/>
+        <v>Lo</v>
+      </c>
+      <c r="J52" t="str">
+        <f t="shared" si="21"/>
+        <v>95</v>
+      </c>
+      <c r="K52" t="str">
+        <f t="shared" si="22"/>
+        <v>CF6</v>
+      </c>
+      <c r="L52" t="str">
+        <f t="shared" si="23"/>
+        <v>N</v>
+      </c>
+      <c r="M52" t="str">
+        <f t="shared" si="24"/>
+        <v>Y</v>
+      </c>
+      <c r="N52" t="str">
+        <f t="shared" si="25"/>
+        <v>N</v>
+      </c>
+      <c r="P52">
+        <v>5</v>
+      </c>
+      <c r="Q52" t="s">
+        <v>1147</v>
+      </c>
+      <c r="R52">
+        <v>47</v>
+      </c>
+      <c r="S52" t="s">
+        <v>1092</v>
+      </c>
+      <c r="T52">
+        <v>95</v>
+      </c>
+      <c r="U52" t="s">
+        <v>1088</v>
+      </c>
+      <c r="V52" t="s">
+        <v>1095</v>
+      </c>
+      <c r="W52" t="s">
+        <v>1093</v>
+      </c>
+      <c r="X52" t="s">
+        <v>1095</v>
+      </c>
+      <c r="Z52" t="str">
+        <f t="shared" si="26"/>
+        <v>dm-Lo</v>
+      </c>
+      <c r="AA52" t="str">
+        <f t="shared" si="27"/>
+        <v>cp-95</v>
+      </c>
+      <c r="AB52" t="str">
+        <f t="shared" si="28"/>
+        <v>CF6</v>
+      </c>
+      <c r="AC52" t="str">
+        <f t="shared" si="29"/>
+        <v>df-N</v>
+      </c>
+      <c r="AD52" t="str">
+        <f t="shared" si="30"/>
+        <v>ga-Y</v>
+      </c>
+      <c r="AE52" t="str">
+        <f t="shared" si="31"/>
+        <v>tc-N</v>
+      </c>
+    </row>
+    <row r="53" spans="2:31">
+      <c r="B53" t="str">
+        <f t="shared" si="17"/>
+        <v>vs~0048</v>
+      </c>
+      <c r="C53" t="str">
+        <f t="shared" si="18"/>
+        <v>tc-N.df-N.ga-Y.dm-Hi.cp-95.CF6</v>
+      </c>
+      <c r="H53" t="str">
+        <f t="shared" si="19"/>
+        <v>tc-N.df-N.ga-Y.dm-Hi.cp-95.CF6</v>
+      </c>
+      <c r="I53" t="str">
+        <f t="shared" si="20"/>
+        <v>Hi</v>
+      </c>
+      <c r="J53" t="str">
+        <f t="shared" si="21"/>
+        <v>95</v>
+      </c>
+      <c r="K53" t="str">
+        <f t="shared" si="22"/>
+        <v>CF6</v>
+      </c>
+      <c r="L53" t="str">
+        <f t="shared" si="23"/>
+        <v>N</v>
+      </c>
+      <c r="M53" t="str">
+        <f t="shared" si="24"/>
+        <v>Y</v>
+      </c>
+      <c r="N53" t="str">
+        <f t="shared" si="25"/>
+        <v>N</v>
+      </c>
+      <c r="P53">
+        <v>5</v>
+      </c>
+      <c r="Q53" t="s">
+        <v>1148</v>
+      </c>
+      <c r="R53">
+        <v>48</v>
+      </c>
+      <c r="S53" t="s">
+        <v>1094</v>
+      </c>
+      <c r="T53">
+        <v>95</v>
+      </c>
+      <c r="U53" t="s">
+        <v>1088</v>
+      </c>
+      <c r="V53" t="s">
+        <v>1095</v>
+      </c>
+      <c r="W53" t="s">
+        <v>1093</v>
+      </c>
+      <c r="X53" t="s">
+        <v>1095</v>
+      </c>
+      <c r="Z53" t="str">
+        <f t="shared" si="26"/>
+        <v>dm-Hi</v>
+      </c>
+      <c r="AA53" t="str">
+        <f t="shared" si="27"/>
+        <v>cp-95</v>
+      </c>
+      <c r="AB53" t="str">
+        <f t="shared" si="28"/>
+        <v>CF6</v>
+      </c>
+      <c r="AC53" t="str">
+        <f t="shared" si="29"/>
+        <v>df-N</v>
+      </c>
+      <c r="AD53" t="str">
+        <f t="shared" si="30"/>
+        <v>ga-Y</v>
+      </c>
+      <c r="AE53" t="str">
+        <f t="shared" si="31"/>
+        <v>tc-N</v>
+      </c>
+    </row>
+    <row r="54" spans="2:31">
+      <c r="B54" t="str">
+        <f t="shared" si="17"/>
+        <v>vs~0049</v>
+      </c>
+      <c r="C54" t="str">
+        <f t="shared" si="18"/>
+        <v>tc-N.df-Y.ga-N.dm-Lo.cp-0.CF1</v>
+      </c>
+      <c r="H54" t="str">
+        <f t="shared" si="19"/>
+        <v>tc-N.df-Y.ga-N.dm-Lo.cp-0.CF1</v>
+      </c>
+      <c r="I54" t="str">
+        <f t="shared" si="20"/>
+        <v>Lo</v>
+      </c>
+      <c r="J54" t="str">
+        <f t="shared" si="21"/>
+        <v>00</v>
+      </c>
+      <c r="K54" t="str">
+        <f t="shared" si="22"/>
+        <v>CF1</v>
+      </c>
+      <c r="L54" t="str">
+        <f t="shared" si="23"/>
+        <v>Y</v>
+      </c>
+      <c r="M54" t="str">
+        <f t="shared" si="24"/>
+        <v>N</v>
+      </c>
+      <c r="N54" t="str">
+        <f t="shared" si="25"/>
+        <v>N</v>
+      </c>
+      <c r="P54">
+        <v>5</v>
+      </c>
+      <c r="Q54" t="s">
+        <v>1149</v>
+      </c>
+      <c r="R54">
+        <v>49</v>
+      </c>
+      <c r="S54" t="s">
+        <v>1092</v>
+      </c>
+      <c r="T54">
+        <v>0</v>
+      </c>
+      <c r="U54" t="s">
+        <v>1087</v>
+      </c>
+      <c r="V54" t="s">
+        <v>1093</v>
+      </c>
+      <c r="W54" t="s">
+        <v>1095</v>
+      </c>
+      <c r="X54" t="s">
+        <v>1095</v>
+      </c>
+      <c r="Z54" t="str">
+        <f t="shared" si="26"/>
+        <v>dm-Lo</v>
+      </c>
+      <c r="AA54" t="str">
+        <f t="shared" si="27"/>
+        <v>cp-0</v>
+      </c>
+      <c r="AB54" t="str">
+        <f t="shared" si="28"/>
+        <v>CF1</v>
+      </c>
+      <c r="AC54" t="str">
+        <f t="shared" si="29"/>
+        <v>df-Y</v>
+      </c>
+      <c r="AD54" t="str">
+        <f t="shared" si="30"/>
+        <v>ga-N</v>
+      </c>
+      <c r="AE54" t="str">
+        <f t="shared" si="31"/>
+        <v>tc-N</v>
+      </c>
+    </row>
+    <row r="55" spans="2:31">
+      <c r="B55" t="str">
+        <f t="shared" si="17"/>
+        <v>vs~0050</v>
+      </c>
+      <c r="C55" t="str">
+        <f t="shared" si="18"/>
+        <v>tc-N.df-Y.ga-N.dm-Hi.cp-0.CF1</v>
+      </c>
+      <c r="H55" t="str">
+        <f t="shared" si="19"/>
+        <v>tc-N.df-Y.ga-N.dm-Hi.cp-0.CF1</v>
+      </c>
+      <c r="I55" t="str">
+        <f t="shared" si="20"/>
+        <v>Hi</v>
+      </c>
+      <c r="J55" t="str">
+        <f t="shared" si="21"/>
+        <v>00</v>
+      </c>
+      <c r="K55" t="str">
+        <f t="shared" si="22"/>
+        <v>CF1</v>
+      </c>
+      <c r="L55" t="str">
+        <f t="shared" si="23"/>
+        <v>Y</v>
+      </c>
+      <c r="M55" t="str">
+        <f t="shared" si="24"/>
+        <v>N</v>
+      </c>
+      <c r="N55" t="str">
+        <f t="shared" si="25"/>
+        <v>N</v>
+      </c>
+      <c r="P55">
+        <v>5</v>
+      </c>
+      <c r="Q55" t="s">
+        <v>1150</v>
+      </c>
+      <c r="R55">
+        <v>50</v>
+      </c>
+      <c r="S55" t="s">
+        <v>1094</v>
+      </c>
+      <c r="T55">
+        <v>0</v>
+      </c>
+      <c r="U55" t="s">
+        <v>1087</v>
+      </c>
+      <c r="V55" t="s">
+        <v>1093</v>
+      </c>
+      <c r="W55" t="s">
+        <v>1095</v>
+      </c>
+      <c r="X55" t="s">
+        <v>1095</v>
+      </c>
+      <c r="Z55" t="str">
+        <f t="shared" si="26"/>
+        <v>dm-Hi</v>
+      </c>
+      <c r="AA55" t="str">
+        <f t="shared" si="27"/>
+        <v>cp-0</v>
+      </c>
+      <c r="AB55" t="str">
+        <f t="shared" si="28"/>
+        <v>CF1</v>
+      </c>
+      <c r="AC55" t="str">
+        <f t="shared" si="29"/>
+        <v>df-Y</v>
+      </c>
+      <c r="AD55" t="str">
+        <f t="shared" si="30"/>
+        <v>ga-N</v>
+      </c>
+      <c r="AE55" t="str">
+        <f t="shared" si="31"/>
+        <v>tc-N</v>
+      </c>
+    </row>
+    <row r="56" spans="2:31">
+      <c r="B56" t="str">
+        <f t="shared" si="17"/>
+        <v>vs~0051</v>
+      </c>
+      <c r="C56" t="str">
+        <f t="shared" si="18"/>
+        <v>tc-N.df-Y.ga-N.dm-Lo.cp-95.CF1</v>
+      </c>
+      <c r="H56" t="str">
+        <f t="shared" si="19"/>
+        <v>tc-N.df-Y.ga-N.dm-Lo.cp-95.CF1</v>
+      </c>
+      <c r="I56" t="str">
+        <f t="shared" si="20"/>
+        <v>Lo</v>
+      </c>
+      <c r="J56" t="str">
+        <f t="shared" si="21"/>
+        <v>95</v>
+      </c>
+      <c r="K56" t="str">
+        <f t="shared" si="22"/>
+        <v>CF1</v>
+      </c>
+      <c r="L56" t="str">
+        <f t="shared" si="23"/>
+        <v>Y</v>
+      </c>
+      <c r="M56" t="str">
+        <f t="shared" si="24"/>
+        <v>N</v>
+      </c>
+      <c r="N56" t="str">
+        <f t="shared" si="25"/>
+        <v>N</v>
+      </c>
+      <c r="P56">
+        <v>5</v>
+      </c>
+      <c r="Q56" t="s">
+        <v>1151</v>
+      </c>
+      <c r="R56">
+        <v>51</v>
+      </c>
+      <c r="S56" t="s">
+        <v>1092</v>
+      </c>
+      <c r="T56">
+        <v>95</v>
+      </c>
+      <c r="U56" t="s">
+        <v>1087</v>
+      </c>
+      <c r="V56" t="s">
+        <v>1093</v>
+      </c>
+      <c r="W56" t="s">
+        <v>1095</v>
+      </c>
+      <c r="X56" t="s">
+        <v>1095</v>
+      </c>
+      <c r="Z56" t="str">
+        <f t="shared" si="26"/>
+        <v>dm-Lo</v>
+      </c>
+      <c r="AA56" t="str">
+        <f t="shared" si="27"/>
+        <v>cp-95</v>
+      </c>
+      <c r="AB56" t="str">
+        <f t="shared" si="28"/>
+        <v>CF1</v>
+      </c>
+      <c r="AC56" t="str">
+        <f t="shared" si="29"/>
+        <v>df-Y</v>
+      </c>
+      <c r="AD56" t="str">
+        <f t="shared" si="30"/>
+        <v>ga-N</v>
+      </c>
+      <c r="AE56" t="str">
+        <f t="shared" si="31"/>
+        <v>tc-N</v>
+      </c>
+    </row>
+    <row r="57" spans="2:31">
+      <c r="B57" t="str">
+        <f t="shared" si="17"/>
+        <v>vs~0052</v>
+      </c>
+      <c r="C57" t="str">
+        <f t="shared" si="18"/>
+        <v>tc-N.df-Y.ga-N.dm-Hi.cp-95.CF1</v>
+      </c>
+      <c r="H57" t="str">
+        <f t="shared" si="19"/>
+        <v>tc-N.df-Y.ga-N.dm-Hi.cp-95.CF1</v>
+      </c>
+      <c r="I57" t="str">
+        <f t="shared" si="20"/>
+        <v>Hi</v>
+      </c>
+      <c r="J57" t="str">
+        <f t="shared" si="21"/>
+        <v>95</v>
+      </c>
+      <c r="K57" t="str">
+        <f t="shared" si="22"/>
+        <v>CF1</v>
+      </c>
+      <c r="L57" t="str">
+        <f t="shared" si="23"/>
+        <v>Y</v>
+      </c>
+      <c r="M57" t="str">
+        <f t="shared" si="24"/>
+        <v>N</v>
+      </c>
+      <c r="N57" t="str">
+        <f t="shared" si="25"/>
+        <v>N</v>
+      </c>
+      <c r="P57">
+        <v>5</v>
+      </c>
+      <c r="Q57" t="s">
+        <v>1152</v>
+      </c>
+      <c r="R57">
+        <v>52</v>
+      </c>
+      <c r="S57" t="s">
+        <v>1094</v>
+      </c>
+      <c r="T57">
+        <v>95</v>
+      </c>
+      <c r="U57" t="s">
+        <v>1087</v>
+      </c>
+      <c r="V57" t="s">
+        <v>1093</v>
+      </c>
+      <c r="W57" t="s">
+        <v>1095</v>
+      </c>
+      <c r="X57" t="s">
+        <v>1095</v>
+      </c>
+      <c r="Z57" t="str">
+        <f t="shared" si="26"/>
+        <v>dm-Hi</v>
+      </c>
+      <c r="AA57" t="str">
+        <f t="shared" si="27"/>
+        <v>cp-95</v>
+      </c>
+      <c r="AB57" t="str">
+        <f t="shared" si="28"/>
+        <v>CF1</v>
+      </c>
+      <c r="AC57" t="str">
+        <f t="shared" si="29"/>
+        <v>df-Y</v>
+      </c>
+      <c r="AD57" t="str">
+        <f t="shared" si="30"/>
+        <v>ga-N</v>
+      </c>
+      <c r="AE57" t="str">
+        <f t="shared" si="31"/>
+        <v>tc-N</v>
+      </c>
+    </row>
+    <row r="58" spans="2:31">
+      <c r="B58" t="str">
+        <f t="shared" si="17"/>
+        <v>vs~0053</v>
+      </c>
+      <c r="C58" t="str">
+        <f t="shared" si="18"/>
+        <v>tc-N.df-N.ga-N.dm-Lo.cp-0.CF1</v>
+      </c>
+      <c r="H58" t="str">
+        <f t="shared" si="19"/>
+        <v>tc-N.df-N.ga-N.dm-Lo.cp-0.CF1</v>
+      </c>
+      <c r="I58" t="str">
+        <f t="shared" si="20"/>
+        <v>Lo</v>
+      </c>
+      <c r="J58" t="str">
+        <f t="shared" si="21"/>
+        <v>00</v>
+      </c>
+      <c r="K58" t="str">
+        <f t="shared" si="22"/>
+        <v>CF1</v>
+      </c>
+      <c r="L58" t="str">
+        <f t="shared" si="23"/>
+        <v>N</v>
+      </c>
+      <c r="M58" t="str">
+        <f t="shared" si="24"/>
+        <v>N</v>
+      </c>
+      <c r="N58" t="str">
+        <f t="shared" si="25"/>
+        <v>N</v>
+      </c>
+      <c r="P58">
+        <v>5</v>
+      </c>
+      <c r="Q58" t="s">
+        <v>1153</v>
+      </c>
+      <c r="R58">
+        <v>53</v>
+      </c>
+      <c r="S58" t="s">
+        <v>1092</v>
+      </c>
+      <c r="T58">
+        <v>0</v>
+      </c>
+      <c r="U58" t="s">
+        <v>1087</v>
+      </c>
+      <c r="V58" t="s">
+        <v>1095</v>
+      </c>
+      <c r="W58" t="s">
+        <v>1095</v>
+      </c>
+      <c r="X58" t="s">
+        <v>1095</v>
+      </c>
+      <c r="Z58" t="str">
+        <f t="shared" si="26"/>
+        <v>dm-Lo</v>
+      </c>
+      <c r="AA58" t="str">
+        <f t="shared" si="27"/>
+        <v>cp-0</v>
+      </c>
+      <c r="AB58" t="str">
+        <f t="shared" si="28"/>
+        <v>CF1</v>
+      </c>
+      <c r="AC58" t="str">
+        <f t="shared" si="29"/>
+        <v>df-N</v>
+      </c>
+      <c r="AD58" t="str">
+        <f t="shared" si="30"/>
+        <v>ga-N</v>
+      </c>
+      <c r="AE58" t="str">
+        <f t="shared" si="31"/>
+        <v>tc-N</v>
+      </c>
+    </row>
+    <row r="59" spans="2:31">
+      <c r="B59" t="str">
+        <f t="shared" si="17"/>
+        <v>vs~0054</v>
+      </c>
+      <c r="C59" t="str">
+        <f t="shared" si="18"/>
+        <v>tc-N.df-N.ga-N.dm-Hi.cp-0.CF1</v>
+      </c>
+      <c r="H59" t="str">
+        <f t="shared" si="19"/>
+        <v>tc-N.df-N.ga-N.dm-Hi.cp-0.CF1</v>
+      </c>
+      <c r="I59" t="str">
+        <f t="shared" si="20"/>
+        <v>Hi</v>
+      </c>
+      <c r="J59" t="str">
+        <f t="shared" si="21"/>
+        <v>00</v>
+      </c>
+      <c r="K59" t="str">
+        <f t="shared" si="22"/>
+        <v>CF1</v>
+      </c>
+      <c r="L59" t="str">
+        <f t="shared" si="23"/>
+        <v>N</v>
+      </c>
+      <c r="M59" t="str">
+        <f t="shared" si="24"/>
+        <v>N</v>
+      </c>
+      <c r="N59" t="str">
+        <f t="shared" si="25"/>
+        <v>N</v>
+      </c>
+      <c r="P59">
+        <v>5</v>
+      </c>
+      <c r="Q59" t="s">
+        <v>1154</v>
+      </c>
+      <c r="R59">
+        <v>54</v>
+      </c>
+      <c r="S59" t="s">
+        <v>1094</v>
+      </c>
+      <c r="T59">
+        <v>0</v>
+      </c>
+      <c r="U59" t="s">
+        <v>1087</v>
+      </c>
+      <c r="V59" t="s">
+        <v>1095</v>
+      </c>
+      <c r="W59" t="s">
+        <v>1095</v>
+      </c>
+      <c r="X59" t="s">
+        <v>1095</v>
+      </c>
+      <c r="Z59" t="str">
+        <f t="shared" si="26"/>
+        <v>dm-Hi</v>
+      </c>
+      <c r="AA59" t="str">
+        <f t="shared" si="27"/>
+        <v>cp-0</v>
+      </c>
+      <c r="AB59" t="str">
+        <f t="shared" si="28"/>
+        <v>CF1</v>
+      </c>
+      <c r="AC59" t="str">
+        <f t="shared" si="29"/>
+        <v>df-N</v>
+      </c>
+      <c r="AD59" t="str">
+        <f t="shared" si="30"/>
+        <v>ga-N</v>
+      </c>
+      <c r="AE59" t="str">
+        <f t="shared" si="31"/>
+        <v>tc-N</v>
+      </c>
+    </row>
+    <row r="60" spans="2:31">
+      <c r="B60" t="str">
+        <f t="shared" si="17"/>
+        <v>vs~0055</v>
+      </c>
+      <c r="C60" t="str">
+        <f t="shared" si="18"/>
+        <v>tc-N.df-N.ga-N.dm-Lo.cp-95.CF1</v>
+      </c>
+      <c r="H60" t="str">
+        <f t="shared" si="19"/>
+        <v>tc-N.df-N.ga-N.dm-Lo.cp-95.CF1</v>
+      </c>
+      <c r="I60" t="str">
+        <f t="shared" si="20"/>
+        <v>Lo</v>
+      </c>
+      <c r="J60" t="str">
+        <f t="shared" si="21"/>
+        <v>95</v>
+      </c>
+      <c r="K60" t="str">
+        <f t="shared" si="22"/>
+        <v>CF1</v>
+      </c>
+      <c r="L60" t="str">
+        <f t="shared" si="23"/>
+        <v>N</v>
+      </c>
+      <c r="M60" t="str">
+        <f t="shared" si="24"/>
+        <v>N</v>
+      </c>
+      <c r="N60" t="str">
+        <f t="shared" si="25"/>
+        <v>N</v>
+      </c>
+      <c r="P60">
+        <v>5</v>
+      </c>
+      <c r="Q60" t="s">
+        <v>1155</v>
+      </c>
+      <c r="R60">
+        <v>55</v>
+      </c>
+      <c r="S60" t="s">
+        <v>1092</v>
+      </c>
+      <c r="T60">
+        <v>95</v>
+      </c>
+      <c r="U60" t="s">
+        <v>1087</v>
+      </c>
+      <c r="V60" t="s">
+        <v>1095</v>
+      </c>
+      <c r="W60" t="s">
+        <v>1095</v>
+      </c>
+      <c r="X60" t="s">
+        <v>1095</v>
+      </c>
+      <c r="Z60" t="str">
+        <f t="shared" si="26"/>
+        <v>dm-Lo</v>
+      </c>
+      <c r="AA60" t="str">
+        <f t="shared" si="27"/>
+        <v>cp-95</v>
+      </c>
+      <c r="AB60" t="str">
+        <f t="shared" si="28"/>
+        <v>CF1</v>
+      </c>
+      <c r="AC60" t="str">
+        <f t="shared" si="29"/>
+        <v>df-N</v>
+      </c>
+      <c r="AD60" t="str">
+        <f t="shared" si="30"/>
+        <v>ga-N</v>
+      </c>
+      <c r="AE60" t="str">
+        <f t="shared" si="31"/>
+        <v>tc-N</v>
+      </c>
+    </row>
+    <row r="61" spans="2:31">
+      <c r="B61" t="str">
+        <f t="shared" si="17"/>
+        <v>vs~0056</v>
+      </c>
+      <c r="C61" t="str">
+        <f t="shared" si="18"/>
+        <v>tc-N.df-N.ga-N.dm-Hi.cp-95.CF1</v>
+      </c>
+      <c r="H61" t="str">
+        <f t="shared" si="19"/>
+        <v>tc-N.df-N.ga-N.dm-Hi.cp-95.CF1</v>
+      </c>
+      <c r="I61" t="str">
+        <f t="shared" si="20"/>
+        <v>Hi</v>
+      </c>
+      <c r="J61" t="str">
+        <f t="shared" si="21"/>
+        <v>95</v>
+      </c>
+      <c r="K61" t="str">
+        <f t="shared" si="22"/>
+        <v>CF1</v>
+      </c>
+      <c r="L61" t="str">
+        <f t="shared" si="23"/>
+        <v>N</v>
+      </c>
+      <c r="M61" t="str">
+        <f t="shared" si="24"/>
+        <v>N</v>
+      </c>
+      <c r="N61" t="str">
+        <f t="shared" si="25"/>
+        <v>N</v>
+      </c>
+      <c r="P61">
+        <v>5</v>
+      </c>
+      <c r="Q61" t="s">
+        <v>1156</v>
+      </c>
+      <c r="R61">
+        <v>56</v>
+      </c>
+      <c r="S61" t="s">
+        <v>1094</v>
+      </c>
+      <c r="T61">
+        <v>95</v>
+      </c>
+      <c r="U61" t="s">
+        <v>1087</v>
+      </c>
+      <c r="V61" t="s">
+        <v>1095</v>
+      </c>
+      <c r="W61" t="s">
+        <v>1095</v>
+      </c>
+      <c r="X61" t="s">
+        <v>1095</v>
+      </c>
+      <c r="Z61" t="str">
+        <f t="shared" si="26"/>
+        <v>dm-Hi</v>
+      </c>
+      <c r="AA61" t="str">
+        <f t="shared" si="27"/>
+        <v>cp-95</v>
+      </c>
+      <c r="AB61" t="str">
+        <f t="shared" si="28"/>
+        <v>CF1</v>
+      </c>
+      <c r="AC61" t="str">
+        <f t="shared" si="29"/>
+        <v>df-N</v>
+      </c>
+      <c r="AD61" t="str">
+        <f t="shared" si="30"/>
+        <v>ga-N</v>
+      </c>
+      <c r="AE61" t="str">
+        <f t="shared" si="31"/>
+        <v>tc-N</v>
+      </c>
+    </row>
+    <row r="62" spans="2:31">
+      <c r="B62" t="str">
+        <f t="shared" si="17"/>
+        <v>vs~0057</v>
+      </c>
+      <c r="C62" t="str">
+        <f t="shared" si="18"/>
+        <v>tc-N.df-Y.ga-N.dm-Lo.cp-0.CF6</v>
+      </c>
+      <c r="H62" t="str">
+        <f t="shared" si="19"/>
+        <v>tc-N.df-Y.ga-N.dm-Lo.cp-0.CF6</v>
+      </c>
+      <c r="I62" t="str">
+        <f t="shared" si="20"/>
+        <v>Lo</v>
+      </c>
+      <c r="J62" t="str">
+        <f t="shared" si="21"/>
+        <v>00</v>
+      </c>
+      <c r="K62" t="str">
+        <f t="shared" si="22"/>
+        <v>CF6</v>
+      </c>
+      <c r="L62" t="str">
+        <f t="shared" si="23"/>
+        <v>Y</v>
+      </c>
+      <c r="M62" t="str">
+        <f t="shared" si="24"/>
+        <v>N</v>
+      </c>
+      <c r="N62" t="str">
+        <f t="shared" si="25"/>
+        <v>N</v>
+      </c>
+      <c r="P62">
+        <v>5</v>
+      </c>
+      <c r="Q62" t="s">
+        <v>1157</v>
+      </c>
+      <c r="R62">
+        <v>57</v>
+      </c>
+      <c r="S62" t="s">
+        <v>1092</v>
+      </c>
+      <c r="T62">
+        <v>0</v>
+      </c>
+      <c r="U62" t="s">
+        <v>1088</v>
+      </c>
+      <c r="V62" t="s">
+        <v>1093</v>
+      </c>
+      <c r="W62" t="s">
+        <v>1095</v>
+      </c>
+      <c r="X62" t="s">
+        <v>1095</v>
+      </c>
+      <c r="Z62" t="str">
+        <f t="shared" si="26"/>
+        <v>dm-Lo</v>
+      </c>
+      <c r="AA62" t="str">
+        <f t="shared" si="27"/>
+        <v>cp-0</v>
+      </c>
+      <c r="AB62" t="str">
+        <f t="shared" si="28"/>
+        <v>CF6</v>
+      </c>
+      <c r="AC62" t="str">
+        <f t="shared" si="29"/>
+        <v>df-Y</v>
+      </c>
+      <c r="AD62" t="str">
+        <f t="shared" si="30"/>
+        <v>ga-N</v>
+      </c>
+      <c r="AE62" t="str">
+        <f t="shared" si="31"/>
+        <v>tc-N</v>
+      </c>
+    </row>
+    <row r="63" spans="2:31">
+      <c r="B63" t="str">
+        <f t="shared" si="17"/>
+        <v>vs~0058</v>
+      </c>
+      <c r="C63" t="str">
+        <f t="shared" si="18"/>
+        <v>tc-N.df-Y.ga-N.dm-Hi.cp-0.CF6</v>
+      </c>
+      <c r="H63" t="str">
+        <f t="shared" si="19"/>
+        <v>tc-N.df-Y.ga-N.dm-Hi.cp-0.CF6</v>
+      </c>
+      <c r="I63" t="str">
+        <f t="shared" si="20"/>
+        <v>Hi</v>
+      </c>
+      <c r="J63" t="str">
+        <f t="shared" si="21"/>
+        <v>00</v>
+      </c>
+      <c r="K63" t="str">
+        <f t="shared" si="22"/>
+        <v>CF6</v>
+      </c>
+      <c r="L63" t="str">
+        <f t="shared" si="23"/>
+        <v>Y</v>
+      </c>
+      <c r="M63" t="str">
+        <f t="shared" si="24"/>
+        <v>N</v>
+      </c>
+      <c r="N63" t="str">
+        <f t="shared" si="25"/>
+        <v>N</v>
+      </c>
+      <c r="P63">
+        <v>5</v>
+      </c>
+      <c r="Q63" t="s">
+        <v>1158</v>
+      </c>
+      <c r="R63">
+        <v>58</v>
+      </c>
+      <c r="S63" t="s">
+        <v>1094</v>
+      </c>
+      <c r="T63">
+        <v>0</v>
+      </c>
+      <c r="U63" t="s">
+        <v>1088</v>
+      </c>
+      <c r="V63" t="s">
+        <v>1093</v>
+      </c>
+      <c r="W63" t="s">
+        <v>1095</v>
+      </c>
+      <c r="X63" t="s">
+        <v>1095</v>
+      </c>
+      <c r="Z63" t="str">
+        <f t="shared" si="26"/>
+        <v>dm-Hi</v>
+      </c>
+      <c r="AA63" t="str">
+        <f t="shared" si="27"/>
+        <v>cp-0</v>
+      </c>
+      <c r="AB63" t="str">
+        <f t="shared" si="28"/>
+        <v>CF6</v>
+      </c>
+      <c r="AC63" t="str">
+        <f t="shared" si="29"/>
+        <v>df-Y</v>
+      </c>
+      <c r="AD63" t="str">
+        <f t="shared" si="30"/>
+        <v>ga-N</v>
+      </c>
+      <c r="AE63" t="str">
+        <f t="shared" si="31"/>
+        <v>tc-N</v>
+      </c>
+    </row>
+    <row r="64" spans="2:31">
+      <c r="B64" t="str">
+        <f t="shared" si="17"/>
+        <v>vs~0059</v>
+      </c>
+      <c r="C64" t="str">
+        <f t="shared" si="18"/>
+        <v>tc-N.df-Y.ga-N.dm-Lo.cp-95.CF6</v>
+      </c>
+      <c r="H64" t="str">
+        <f t="shared" si="19"/>
+        <v>tc-N.df-Y.ga-N.dm-Lo.cp-95.CF6</v>
+      </c>
+      <c r="I64" t="str">
+        <f t="shared" si="20"/>
+        <v>Lo</v>
+      </c>
+      <c r="J64" t="str">
+        <f t="shared" si="21"/>
+        <v>95</v>
+      </c>
+      <c r="K64" t="str">
+        <f t="shared" si="22"/>
+        <v>CF6</v>
+      </c>
+      <c r="L64" t="str">
+        <f t="shared" si="23"/>
+        <v>Y</v>
+      </c>
+      <c r="M64" t="str">
+        <f t="shared" si="24"/>
+        <v>N</v>
+      </c>
+      <c r="N64" t="str">
+        <f t="shared" si="25"/>
+        <v>N</v>
+      </c>
+      <c r="P64">
+        <v>5</v>
+      </c>
+      <c r="Q64" t="s">
+        <v>1159</v>
+      </c>
+      <c r="R64">
+        <v>59</v>
+      </c>
+      <c r="S64" t="s">
+        <v>1092</v>
+      </c>
+      <c r="T64">
+        <v>95</v>
+      </c>
+      <c r="U64" t="s">
+        <v>1088</v>
+      </c>
+      <c r="V64" t="s">
+        <v>1093</v>
+      </c>
+      <c r="W64" t="s">
+        <v>1095</v>
+      </c>
+      <c r="X64" t="s">
+        <v>1095</v>
+      </c>
+      <c r="Z64" t="str">
+        <f t="shared" si="26"/>
+        <v>dm-Lo</v>
+      </c>
+      <c r="AA64" t="str">
+        <f t="shared" si="27"/>
+        <v>cp-95</v>
+      </c>
+      <c r="AB64" t="str">
+        <f t="shared" si="28"/>
+        <v>CF6</v>
+      </c>
+      <c r="AC64" t="str">
+        <f t="shared" si="29"/>
+        <v>df-Y</v>
+      </c>
+      <c r="AD64" t="str">
+        <f t="shared" si="30"/>
+        <v>ga-N</v>
+      </c>
+      <c r="AE64" t="str">
+        <f t="shared" si="31"/>
+        <v>tc-N</v>
+      </c>
+    </row>
+    <row r="65" spans="2:31">
+      <c r="B65" t="str">
+        <f t="shared" si="17"/>
+        <v>vs~0060</v>
+      </c>
+      <c r="C65" t="str">
+        <f t="shared" si="18"/>
+        <v>tc-N.df-Y.ga-N.dm-Hi.cp-95.CF6</v>
+      </c>
+      <c r="H65" t="str">
+        <f t="shared" si="19"/>
+        <v>tc-N.df-Y.ga-N.dm-Hi.cp-95.CF6</v>
+      </c>
+      <c r="I65" t="str">
+        <f t="shared" si="20"/>
+        <v>Hi</v>
+      </c>
+      <c r="J65" t="str">
+        <f t="shared" si="21"/>
+        <v>95</v>
+      </c>
+      <c r="K65" t="str">
+        <f t="shared" si="22"/>
+        <v>CF6</v>
+      </c>
+      <c r="L65" t="str">
+        <f t="shared" si="23"/>
+        <v>Y</v>
+      </c>
+      <c r="M65" t="str">
+        <f t="shared" si="24"/>
+        <v>N</v>
+      </c>
+      <c r="N65" t="str">
+        <f t="shared" si="25"/>
+        <v>N</v>
+      </c>
+      <c r="P65">
+        <v>5</v>
+      </c>
+      <c r="Q65" t="s">
+        <v>1160</v>
+      </c>
+      <c r="R65">
+        <v>60</v>
+      </c>
+      <c r="S65" t="s">
+        <v>1094</v>
+      </c>
+      <c r="T65">
+        <v>95</v>
+      </c>
+      <c r="U65" t="s">
+        <v>1088</v>
+      </c>
+      <c r="V65" t="s">
+        <v>1093</v>
+      </c>
+      <c r="W65" t="s">
+        <v>1095</v>
+      </c>
+      <c r="X65" t="s">
+        <v>1095</v>
+      </c>
+      <c r="Z65" t="str">
+        <f t="shared" si="26"/>
+        <v>dm-Hi</v>
+      </c>
+      <c r="AA65" t="str">
+        <f t="shared" si="27"/>
+        <v>cp-95</v>
+      </c>
+      <c r="AB65" t="str">
+        <f t="shared" si="28"/>
+        <v>CF6</v>
+      </c>
+      <c r="AC65" t="str">
+        <f t="shared" si="29"/>
+        <v>df-Y</v>
+      </c>
+      <c r="AD65" t="str">
+        <f t="shared" si="30"/>
+        <v>ga-N</v>
+      </c>
+      <c r="AE65" t="str">
+        <f t="shared" si="31"/>
+        <v>tc-N</v>
+      </c>
+    </row>
+    <row r="66" spans="2:31">
+      <c r="B66" t="str">
+        <f t="shared" si="17"/>
+        <v>vs~0061</v>
+      </c>
+      <c r="C66" t="str">
+        <f t="shared" si="18"/>
+        <v>tc-N.df-N.ga-N.dm-Lo.cp-0.CF6</v>
+      </c>
+      <c r="H66" t="str">
+        <f t="shared" si="19"/>
+        <v>tc-N.df-N.ga-N.dm-Lo.cp-0.CF6</v>
+      </c>
+      <c r="I66" t="str">
+        <f t="shared" si="20"/>
+        <v>Lo</v>
+      </c>
+      <c r="J66" t="str">
+        <f t="shared" si="21"/>
+        <v>00</v>
+      </c>
+      <c r="K66" t="str">
+        <f t="shared" si="22"/>
+        <v>CF6</v>
+      </c>
+      <c r="L66" t="str">
+        <f t="shared" si="23"/>
+        <v>N</v>
+      </c>
+      <c r="M66" t="str">
+        <f t="shared" si="24"/>
+        <v>N</v>
+      </c>
+      <c r="N66" t="str">
+        <f t="shared" si="25"/>
+        <v>N</v>
+      </c>
+      <c r="P66">
+        <v>5</v>
+      </c>
+      <c r="Q66" t="s">
+        <v>1161</v>
+      </c>
+      <c r="R66">
+        <v>61</v>
+      </c>
+      <c r="S66" t="s">
+        <v>1092</v>
+      </c>
+      <c r="T66">
+        <v>0</v>
+      </c>
+      <c r="U66" t="s">
+        <v>1088</v>
+      </c>
+      <c r="V66" t="s">
+        <v>1095</v>
+      </c>
+      <c r="W66" t="s">
+        <v>1095</v>
+      </c>
+      <c r="X66" t="s">
+        <v>1095</v>
+      </c>
+      <c r="Z66" t="str">
+        <f t="shared" si="26"/>
+        <v>dm-Lo</v>
+      </c>
+      <c r="AA66" t="str">
+        <f t="shared" si="27"/>
+        <v>cp-0</v>
+      </c>
+      <c r="AB66" t="str">
+        <f t="shared" si="28"/>
+        <v>CF6</v>
+      </c>
+      <c r="AC66" t="str">
+        <f t="shared" si="29"/>
+        <v>df-N</v>
+      </c>
+      <c r="AD66" t="str">
+        <f t="shared" si="30"/>
+        <v>ga-N</v>
+      </c>
+      <c r="AE66" t="str">
+        <f t="shared" si="31"/>
+        <v>tc-N</v>
+      </c>
+    </row>
+    <row r="67" spans="2:31">
+      <c r="B67" t="str">
+        <f t="shared" si="17"/>
+        <v>vs~0062</v>
+      </c>
+      <c r="C67" t="str">
+        <f t="shared" si="18"/>
+        <v>tc-N.df-N.ga-N.dm-Hi.cp-0.CF6</v>
+      </c>
+      <c r="H67" t="str">
+        <f t="shared" si="19"/>
+        <v>tc-N.df-N.ga-N.dm-Hi.cp-0.CF6</v>
+      </c>
+      <c r="I67" t="str">
+        <f t="shared" si="20"/>
+        <v>Hi</v>
+      </c>
+      <c r="J67" t="str">
+        <f t="shared" si="21"/>
+        <v>00</v>
+      </c>
+      <c r="K67" t="str">
+        <f t="shared" si="22"/>
+        <v>CF6</v>
+      </c>
+      <c r="L67" t="str">
+        <f t="shared" si="23"/>
+        <v>N</v>
+      </c>
+      <c r="M67" t="str">
+        <f t="shared" si="24"/>
+        <v>N</v>
+      </c>
+      <c r="N67" t="str">
+        <f t="shared" si="25"/>
+        <v>N</v>
+      </c>
+      <c r="P67">
+        <v>5</v>
+      </c>
+      <c r="Q67" t="s">
+        <v>1162</v>
+      </c>
+      <c r="R67">
+        <v>62</v>
+      </c>
+      <c r="S67" t="s">
+        <v>1094</v>
+      </c>
+      <c r="T67">
+        <v>0</v>
+      </c>
+      <c r="U67" t="s">
+        <v>1088</v>
+      </c>
+      <c r="V67" t="s">
+        <v>1095</v>
+      </c>
+      <c r="W67" t="s">
+        <v>1095</v>
+      </c>
+      <c r="X67" t="s">
+        <v>1095</v>
+      </c>
+      <c r="Z67" t="str">
+        <f t="shared" si="26"/>
+        <v>dm-Hi</v>
+      </c>
+      <c r="AA67" t="str">
+        <f t="shared" si="27"/>
+        <v>cp-0</v>
+      </c>
+      <c r="AB67" t="str">
+        <f t="shared" si="28"/>
+        <v>CF6</v>
+      </c>
+      <c r="AC67" t="str">
+        <f t="shared" si="29"/>
+        <v>df-N</v>
+      </c>
+      <c r="AD67" t="str">
+        <f t="shared" si="30"/>
+        <v>ga-N</v>
+      </c>
+      <c r="AE67" t="str">
+        <f t="shared" si="31"/>
+        <v>tc-N</v>
+      </c>
+    </row>
+    <row r="68" spans="2:31">
+      <c r="B68" t="str">
+        <f t="shared" si="17"/>
+        <v>vs~0063</v>
+      </c>
+      <c r="C68" t="str">
+        <f t="shared" si="18"/>
+        <v>tc-N.df-N.ga-N.dm-Lo.cp-95.CF6</v>
+      </c>
+      <c r="H68" t="str">
+        <f t="shared" si="19"/>
+        <v>tc-N.df-N.ga-N.dm-Lo.cp-95.CF6</v>
+      </c>
+      <c r="I68" t="str">
+        <f t="shared" si="20"/>
+        <v>Lo</v>
+      </c>
+      <c r="J68" t="str">
+        <f t="shared" si="21"/>
+        <v>95</v>
+      </c>
+      <c r="K68" t="str">
+        <f t="shared" si="22"/>
+        <v>CF6</v>
+      </c>
+      <c r="L68" t="str">
+        <f t="shared" si="23"/>
+        <v>N</v>
+      </c>
+      <c r="M68" t="str">
+        <f t="shared" si="24"/>
+        <v>N</v>
+      </c>
+      <c r="N68" t="str">
+        <f t="shared" si="25"/>
+        <v>N</v>
+      </c>
+      <c r="P68">
+        <v>5</v>
+      </c>
+      <c r="Q68" t="s">
+        <v>1163</v>
+      </c>
+      <c r="R68">
+        <v>63</v>
+      </c>
+      <c r="S68" t="s">
+        <v>1092</v>
+      </c>
+      <c r="T68">
+        <v>95</v>
+      </c>
+      <c r="U68" t="s">
+        <v>1088</v>
+      </c>
+      <c r="V68" t="s">
+        <v>1095</v>
+      </c>
+      <c r="W68" t="s">
+        <v>1095</v>
+      </c>
+      <c r="X68" t="s">
+        <v>1095</v>
+      </c>
+      <c r="Z68" t="str">
+        <f t="shared" si="26"/>
+        <v>dm-Lo</v>
+      </c>
+      <c r="AA68" t="str">
+        <f t="shared" si="27"/>
+        <v>cp-95</v>
+      </c>
+      <c r="AB68" t="str">
+        <f t="shared" si="28"/>
+        <v>CF6</v>
+      </c>
+      <c r="AC68" t="str">
+        <f t="shared" si="29"/>
+        <v>df-N</v>
+      </c>
+      <c r="AD68" t="str">
+        <f t="shared" si="30"/>
+        <v>ga-N</v>
+      </c>
+      <c r="AE68" t="str">
+        <f t="shared" si="31"/>
+        <v>tc-N</v>
+      </c>
+    </row>
+    <row r="69" spans="2:31">
+      <c r="B69" t="str">
+        <f t="shared" si="17"/>
+        <v>vs~0064</v>
+      </c>
+      <c r="C69" t="str">
+        <f t="shared" si="18"/>
+        <v>tc-N.df-N.ga-N.dm-Hi.cp-95.CF6</v>
+      </c>
+      <c r="H69" t="str">
+        <f t="shared" si="19"/>
+        <v>tc-N.df-N.ga-N.dm-Hi.cp-95.CF6</v>
+      </c>
+      <c r="I69" t="str">
+        <f t="shared" si="20"/>
+        <v>Hi</v>
+      </c>
+      <c r="J69" t="str">
+        <f t="shared" si="21"/>
+        <v>95</v>
+      </c>
+      <c r="K69" t="str">
+        <f t="shared" si="22"/>
+        <v>CF6</v>
+      </c>
+      <c r="L69" t="str">
+        <f t="shared" si="23"/>
+        <v>N</v>
+      </c>
+      <c r="M69" t="str">
+        <f t="shared" si="24"/>
+        <v>N</v>
+      </c>
+      <c r="N69" t="str">
+        <f t="shared" si="25"/>
+        <v>N</v>
+      </c>
+      <c r="P69">
+        <v>5</v>
+      </c>
+      <c r="Q69" t="s">
+        <v>1164</v>
+      </c>
+      <c r="R69">
+        <v>64</v>
+      </c>
+      <c r="S69" t="s">
+        <v>1094</v>
+      </c>
+      <c r="T69">
+        <v>95</v>
+      </c>
+      <c r="U69" t="s">
+        <v>1088</v>
+      </c>
+      <c r="V69" t="s">
+        <v>1095</v>
+      </c>
+      <c r="W69" t="s">
+        <v>1095</v>
+      </c>
+      <c r="X69" t="s">
+        <v>1095</v>
+      </c>
+      <c r="Z69" t="str">
+        <f t="shared" si="26"/>
+        <v>dm-Hi</v>
+      </c>
+      <c r="AA69" t="str">
+        <f t="shared" si="27"/>
+        <v>cp-95</v>
+      </c>
+      <c r="AB69" t="str">
+        <f t="shared" si="28"/>
+        <v>CF6</v>
+      </c>
+      <c r="AC69" t="str">
+        <f t="shared" si="29"/>
+        <v>df-N</v>
+      </c>
+      <c r="AD69" t="str">
+        <f t="shared" si="30"/>
+        <v>ga-N</v>
+      </c>
+      <c r="AE69" t="str">
+        <f t="shared" si="31"/>
+        <v>tc-N</v>
       </c>
     </row>
   </sheetData>
@@ -36966,7 +40275,7 @@
         <v>283</v>
       </c>
       <c r="C9" t="s">
-        <v>108</v>
+        <v>1166</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>110</v>
@@ -36983,7 +40292,7 @@
         <v>286</v>
       </c>
       <c r="C10" t="s">
-        <v>108</v>
+        <v>1166</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>110</v>

--- a/VerveStacks_ZAF_grids_kan/ReportDefs_vervestacks.xlsx
+++ b/VerveStacks_ZAF_grids_kan/ReportDefs_vervestacks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_ZAF_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61AB18DB-B0A1-4C49-BECB-47C956B02296}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CADAF0B8-E87E-4DF4-9332-F1F82095EE02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="geolocation" sheetId="72" r:id="rId1"/>
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7603" uniqueCount="1167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7570" uniqueCount="1172">
   <si>
     <t>Unit</t>
   </si>
@@ -3584,6 +3584,21 @@
   </si>
   <si>
     <t>ELE,STG,IRE,grid,aggregators</t>
+  </si>
+  <si>
+    <t>Grids</t>
+  </si>
+  <si>
+    <t>Grid</t>
+  </si>
+  <si>
+    <t>Cap_New</t>
+  </si>
+  <si>
+    <t>LUMPINV</t>
+  </si>
+  <si>
+    <t>Cost_Inv_lumpsum</t>
   </si>
 </sst>
 </file>
@@ -9205,7 +9220,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10ADB714-E6AA-4E3E-B77B-62B65BA0E218}">
-  <dimension ref="A1:G75"/>
+  <dimension ref="A1:G55"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="14.86328125" bestFit="1" customWidth="1"/>
@@ -9283,7 +9298,7 @@
         <v>64</v>
       </c>
       <c r="C6" t="str">
-        <f t="shared" ref="C6:C49" si="0">D6</f>
+        <f t="shared" ref="C6:C29" si="0">D6</f>
         <v>Int Comb</v>
       </c>
       <c r="D6" t="s">
@@ -9410,7 +9425,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17" spans="1:5">
       <c r="A17" t="s">
         <v>64</v>
       </c>
@@ -9422,7 +9437,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="18" spans="1:4">
+    <row r="18" spans="1:5">
       <c r="A18" t="s">
         <v>64</v>
       </c>
@@ -9434,7 +9449,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="19" spans="1:4">
+    <row r="19" spans="1:5">
       <c r="A19" t="s">
         <v>64</v>
       </c>
@@ -9446,7 +9461,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="20" spans="1:4">
+    <row r="20" spans="1:5">
       <c r="A20" t="s">
         <v>64</v>
       </c>
@@ -9458,7 +9473,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="21" spans="1:4">
+    <row r="21" spans="1:5">
       <c r="A21" t="s">
         <v>64</v>
       </c>
@@ -9470,7 +9485,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="22" spans="1:4">
+    <row r="22" spans="1:5">
       <c r="A22" t="s">
         <v>64</v>
       </c>
@@ -9482,7 +9497,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="23" spans="1:4">
+    <row r="23" spans="1:5">
       <c r="A23" t="s">
         <v>64</v>
       </c>
@@ -9494,7 +9509,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="24" spans="1:4">
+    <row r="24" spans="1:5">
       <c r="A24" t="s">
         <v>64</v>
       </c>
@@ -9506,7 +9521,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="25" spans="1:4">
+    <row r="25" spans="1:5">
       <c r="A25" t="s">
         <v>64</v>
       </c>
@@ -9518,7 +9533,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="26" spans="1:4">
+    <row r="26" spans="1:5">
       <c r="A26" t="s">
         <v>64</v>
       </c>
@@ -9530,586 +9545,345 @@
         <v>210</v>
       </c>
     </row>
-    <row r="27" spans="1:4">
+    <row r="27" spans="1:5">
       <c r="A27" t="s">
         <v>64</v>
       </c>
-      <c r="C27" t="str">
-        <f t="shared" si="0"/>
-        <v>Grid-220V</v>
+      <c r="C27" t="s">
+        <v>1167</v>
       </c>
       <c r="D27" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4">
+        <v>1168</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
       <c r="A28" t="s">
         <v>64</v>
       </c>
       <c r="C28" t="str">
         <f t="shared" si="0"/>
-        <v>Grid-400V</v>
+        <v>Aggregators</v>
       </c>
       <c r="D28" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
       <c r="A29" t="s">
         <v>64</v>
       </c>
       <c r="C29" t="str">
         <f t="shared" si="0"/>
-        <v>Grid-380V</v>
+        <v>DUMMY_IMP</v>
       </c>
       <c r="D29" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
       <c r="A30" t="s">
         <v>64</v>
       </c>
-      <c r="C30" t="str">
-        <f t="shared" si="0"/>
-        <v>Grid-225V</v>
-      </c>
-      <c r="D30" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4">
+      <c r="B30" t="s">
+        <v>347</v>
+      </c>
+      <c r="C30" t="s">
+        <v>123</v>
+      </c>
+      <c r="E30" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
       <c r="A31" t="s">
         <v>64</v>
       </c>
-      <c r="C31" t="str">
-        <f t="shared" si="0"/>
-        <v>Grid-330V</v>
-      </c>
-      <c r="D31" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4">
+      <c r="B31" t="s">
+        <v>347</v>
+      </c>
+      <c r="C31" t="s">
+        <v>124</v>
+      </c>
+      <c r="E31" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
       <c r="A32" t="s">
         <v>64</v>
       </c>
-      <c r="C32" t="str">
-        <f t="shared" si="0"/>
-        <v>Grid-275V</v>
-      </c>
-      <c r="D32" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4">
+      <c r="B32" t="s">
+        <v>348</v>
+      </c>
+      <c r="C32" t="s">
+        <v>125</v>
+      </c>
+      <c r="E32" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
       <c r="A33" t="s">
         <v>64</v>
       </c>
-      <c r="C33" t="str">
-        <f t="shared" si="0"/>
-        <v>Grid-420V</v>
-      </c>
-      <c r="D33" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4">
+      <c r="B33" t="s">
+        <v>348</v>
+      </c>
+      <c r="C33" t="s">
+        <v>126</v>
+      </c>
+      <c r="E33" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
       <c r="A34" t="s">
         <v>64</v>
       </c>
-      <c r="C34" t="str">
-        <f t="shared" si="0"/>
-        <v>Grid-300V</v>
-      </c>
-      <c r="D34" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4">
+      <c r="B34" t="s">
+        <v>93</v>
+      </c>
+      <c r="C34" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
       <c r="A35" t="s">
         <v>64</v>
       </c>
-      <c r="C35" t="str">
-        <f t="shared" si="0"/>
-        <v>Grid-500V</v>
-      </c>
-      <c r="D35" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4">
+      <c r="B35" t="s">
+        <v>94</v>
+      </c>
+      <c r="C35" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
       <c r="A36" t="s">
         <v>64</v>
       </c>
-      <c r="C36" t="str">
-        <f t="shared" si="0"/>
-        <v>Grid-750V</v>
-      </c>
-      <c r="D36" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4">
+      <c r="B36" t="s">
+        <v>106</v>
+      </c>
+      <c r="C36" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
       <c r="A37" t="s">
-        <v>64</v>
-      </c>
-      <c r="C37" t="str">
-        <f t="shared" si="0"/>
-        <v>Grid-450V</v>
-      </c>
-      <c r="D37" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4">
+        <v>245</v>
+      </c>
+      <c r="B37" t="s">
+        <v>246</v>
+      </c>
+      <c r="C37" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
       <c r="A38" t="s">
-        <v>64</v>
-      </c>
-      <c r="C38" t="str">
-        <f t="shared" si="0"/>
-        <v>Grid-515V</v>
-      </c>
-      <c r="D38" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4">
+        <v>245</v>
+      </c>
+      <c r="B38" t="s">
+        <v>248</v>
+      </c>
+      <c r="C38" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
       <c r="A39" t="s">
-        <v>64</v>
-      </c>
-      <c r="C39" t="str">
-        <f t="shared" si="0"/>
-        <v>Grid-525V</v>
-      </c>
-      <c r="D39" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4">
+        <v>245</v>
+      </c>
+      <c r="B39" t="s">
+        <v>249</v>
+      </c>
+      <c r="C39" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
       <c r="A40" t="s">
-        <v>64</v>
-      </c>
-      <c r="C40" t="str">
-        <f t="shared" si="0"/>
-        <v>Grid-320V</v>
-      </c>
-      <c r="D40" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4">
+        <v>255</v>
+      </c>
+      <c r="B40" t="s">
+        <v>113</v>
+      </c>
+      <c r="C40" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
       <c r="A41" t="s">
-        <v>64</v>
-      </c>
-      <c r="C41" t="str">
-        <f t="shared" si="0"/>
-        <v>Grid-150V</v>
-      </c>
-      <c r="D41" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4">
+        <v>255</v>
+      </c>
+      <c r="B41" t="s">
+        <v>256</v>
+      </c>
+      <c r="C41" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
       <c r="A42" t="s">
-        <v>64</v>
-      </c>
-      <c r="C42" t="str">
-        <f t="shared" si="0"/>
-        <v>Grid-270V</v>
-      </c>
-      <c r="D42" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4">
+        <v>255</v>
+      </c>
+      <c r="B42" t="s">
+        <v>258</v>
+      </c>
+      <c r="C42" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
       <c r="A43" t="s">
-        <v>64</v>
-      </c>
-      <c r="C43" t="str">
-        <f t="shared" si="0"/>
-        <v>Grid-350V</v>
-      </c>
-      <c r="D43" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4">
+        <v>255</v>
+      </c>
+      <c r="B43" t="s">
+        <v>260</v>
+      </c>
+      <c r="C43" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
       <c r="A44" t="s">
-        <v>64</v>
-      </c>
-      <c r="C44" t="str">
-        <f t="shared" si="0"/>
-        <v>Grid-250V</v>
-      </c>
-      <c r="D44" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4">
+        <v>255</v>
+      </c>
+      <c r="B44" t="s">
+        <v>262</v>
+      </c>
+      <c r="C44" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
       <c r="A45" t="s">
-        <v>64</v>
-      </c>
-      <c r="C45" t="str">
-        <f t="shared" si="0"/>
-        <v>Grid-200V</v>
-      </c>
-      <c r="D45" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4">
+        <v>255</v>
+      </c>
+      <c r="B45" t="s">
+        <v>264</v>
+      </c>
+      <c r="C45" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
       <c r="A46" t="s">
-        <v>64</v>
-      </c>
-      <c r="C46" t="str">
-        <f t="shared" si="0"/>
-        <v>Grid-236V</v>
-      </c>
-      <c r="D46" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4">
+        <v>255</v>
+      </c>
+      <c r="B46" t="s">
+        <v>266</v>
+      </c>
+      <c r="C46" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
       <c r="A47" t="s">
-        <v>64</v>
+        <v>276</v>
       </c>
       <c r="C47" t="str">
-        <f t="shared" si="0"/>
-        <v>Grid-600V</v>
-      </c>
-      <c r="D47" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4">
+        <f>E47</f>
+        <v>bioenergy</v>
+      </c>
+      <c r="E47" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
       <c r="A48" t="s">
-        <v>64</v>
+        <v>276</v>
       </c>
       <c r="C48" t="str">
-        <f t="shared" si="0"/>
-        <v>Aggregators</v>
-      </c>
-      <c r="D48" t="s">
-        <v>207</v>
+        <f t="shared" ref="C48:C55" si="1">E48</f>
+        <v>coal</v>
+      </c>
+      <c r="E48" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" t="s">
-        <v>64</v>
+        <v>276</v>
       </c>
       <c r="C49" t="str">
-        <f t="shared" si="0"/>
-        <v>DUMMY_IMP</v>
-      </c>
-      <c r="D49" t="s">
-        <v>208</v>
+        <f t="shared" si="1"/>
+        <v>gas</v>
+      </c>
+      <c r="E49" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" t="s">
-        <v>64</v>
-      </c>
-      <c r="B50" t="s">
-        <v>347</v>
-      </c>
-      <c r="C50" t="s">
-        <v>123</v>
+        <v>276</v>
+      </c>
+      <c r="C50" t="str">
+        <f t="shared" si="1"/>
+        <v>hydro</v>
       </c>
       <c r="E50" t="s">
-        <v>127</v>
+        <v>213</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" t="s">
-        <v>64</v>
-      </c>
-      <c r="B51" t="s">
-        <v>347</v>
-      </c>
-      <c r="C51" t="s">
-        <v>124</v>
+        <v>276</v>
+      </c>
+      <c r="C51" t="str">
+        <f t="shared" si="1"/>
+        <v>nuclear</v>
       </c>
       <c r="E51" t="s">
-        <v>128</v>
+        <v>167</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" t="s">
-        <v>64</v>
-      </c>
-      <c r="B52" t="s">
-        <v>348</v>
-      </c>
-      <c r="C52" t="s">
-        <v>125</v>
+        <v>276</v>
+      </c>
+      <c r="C52" t="str">
+        <f t="shared" si="1"/>
+        <v>oil</v>
       </c>
       <c r="E52" t="s">
-        <v>127</v>
+        <v>214</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" t="s">
-        <v>64</v>
-      </c>
-      <c r="B53" t="s">
-        <v>348</v>
-      </c>
-      <c r="C53" t="s">
-        <v>126</v>
+        <v>276</v>
+      </c>
+      <c r="C53" t="str">
+        <f t="shared" si="1"/>
+        <v>solar</v>
       </c>
       <c r="E53" t="s">
-        <v>128</v>
+        <v>215</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" t="s">
-        <v>64</v>
-      </c>
-      <c r="B54" t="s">
-        <v>93</v>
-      </c>
-      <c r="C54" t="s">
-        <v>3</v>
+        <v>276</v>
+      </c>
+      <c r="C54" t="str">
+        <f t="shared" si="1"/>
+        <v>windoff</v>
+      </c>
+      <c r="E54" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" t="s">
-        <v>64</v>
-      </c>
-      <c r="B55" t="s">
-        <v>94</v>
-      </c>
-      <c r="C55" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" t="s">
-        <v>64</v>
-      </c>
-      <c r="B56" t="s">
-        <v>106</v>
-      </c>
-      <c r="C56" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" t="s">
-        <v>245</v>
-      </c>
-      <c r="B57" t="s">
-        <v>246</v>
-      </c>
-      <c r="C57" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" t="s">
-        <v>245</v>
-      </c>
-      <c r="B58" t="s">
-        <v>248</v>
-      </c>
-      <c r="C58" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" t="s">
-        <v>245</v>
-      </c>
-      <c r="B59" t="s">
-        <v>249</v>
-      </c>
-      <c r="C59" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" t="s">
-        <v>255</v>
-      </c>
-      <c r="B60" t="s">
-        <v>113</v>
-      </c>
-      <c r="C60" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" t="s">
-        <v>255</v>
-      </c>
-      <c r="B61" t="s">
-        <v>256</v>
-      </c>
-      <c r="C61" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" t="s">
-        <v>255</v>
-      </c>
-      <c r="B62" t="s">
-        <v>258</v>
-      </c>
-      <c r="C62" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" t="s">
-        <v>255</v>
-      </c>
-      <c r="B63" t="s">
-        <v>260</v>
-      </c>
-      <c r="C63" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" t="s">
-        <v>255</v>
-      </c>
-      <c r="B64" t="s">
-        <v>262</v>
-      </c>
-      <c r="C64" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" t="s">
-        <v>255</v>
-      </c>
-      <c r="B65" t="s">
-        <v>264</v>
-      </c>
-      <c r="C65" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" t="s">
-        <v>255</v>
-      </c>
-      <c r="B66" t="s">
-        <v>266</v>
-      </c>
-      <c r="C66" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" t="s">
         <v>276</v>
       </c>
-      <c r="C67" t="str">
-        <f>E67</f>
-        <v>bioenergy</v>
-      </c>
-      <c r="E67" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" t="s">
-        <v>276</v>
-      </c>
-      <c r="C68" t="str">
-        <f t="shared" ref="C68:C75" si="1">E68</f>
-        <v>coal</v>
-      </c>
-      <c r="E68" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" t="s">
-        <v>276</v>
-      </c>
-      <c r="C69" t="str">
-        <f t="shared" si="1"/>
-        <v>gas</v>
-      </c>
-      <c r="E69" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" t="s">
-        <v>276</v>
-      </c>
-      <c r="C70" t="str">
-        <f t="shared" si="1"/>
-        <v>hydro</v>
-      </c>
-      <c r="E70" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" t="s">
-        <v>276</v>
-      </c>
-      <c r="C71" t="str">
-        <f t="shared" si="1"/>
-        <v>nuclear</v>
-      </c>
-      <c r="E71" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" t="s">
-        <v>276</v>
-      </c>
-      <c r="C72" t="str">
-        <f t="shared" si="1"/>
-        <v>oil</v>
-      </c>
-      <c r="E72" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" t="s">
-        <v>276</v>
-      </c>
-      <c r="C73" t="str">
-        <f t="shared" si="1"/>
-        <v>solar</v>
-      </c>
-      <c r="E73" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" t="s">
-        <v>276</v>
-      </c>
-      <c r="C74" t="str">
-        <f t="shared" si="1"/>
-        <v>windoff</v>
-      </c>
-      <c r="E74" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" t="s">
-        <v>276</v>
-      </c>
-      <c r="C75" t="str">
+      <c r="C55" t="str">
         <f t="shared" si="1"/>
         <v>windon</v>
       </c>
-      <c r="E75" t="s">
+      <c r="E55" t="s">
         <v>216</v>
       </c>
     </row>
@@ -40060,7 +39834,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet19"/>
-  <dimension ref="A1:U27"/>
+  <dimension ref="A1:U28"/>
   <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13.86328125" bestFit="1" customWidth="1"/>
@@ -40272,7 +40046,7 @@
     </row>
     <row r="9" spans="1:21">
       <c r="A9" t="s">
-        <v>283</v>
+        <v>1169</v>
       </c>
       <c r="C9" t="s">
         <v>1166</v>
@@ -40283,13 +40057,18 @@
       <c r="K9" t="s">
         <v>233</v>
       </c>
+      <c r="M9" t="s">
+        <v>1170</v>
+      </c>
       <c r="N9" t="s">
-        <v>76</v>
-      </c>
+        <v>1171</v>
+      </c>
+      <c r="T9" s="3"/>
+      <c r="U9" s="3"/>
     </row>
     <row r="10" spans="1:21">
       <c r="A10" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="C10" t="s">
         <v>1166</v>
@@ -40306,10 +40085,10 @@
     </row>
     <row r="11" spans="1:21">
       <c r="A11" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C11" t="s">
-        <v>108</v>
+        <v>1166</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>110</v>
@@ -40318,12 +40097,12 @@
         <v>233</v>
       </c>
       <c r="N11" t="s">
-        <v>277</v>
+        <v>76</v>
       </c>
     </row>
     <row r="12" spans="1:21">
       <c r="A12" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="C12" t="s">
         <v>108</v>
@@ -40340,7 +40119,7 @@
     </row>
     <row r="13" spans="1:21">
       <c r="A13" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C13" t="s">
         <v>108</v>
@@ -40352,48 +40131,42 @@
         <v>233</v>
       </c>
       <c r="N13" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="14" spans="1:21">
       <c r="A14" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="C14" t="s">
-        <v>280</v>
-      </c>
-      <c r="D14" s="2"/>
-      <c r="I14" t="s">
-        <v>281</v>
+        <v>108</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>110</v>
       </c>
       <c r="K14" t="s">
         <v>233</v>
       </c>
       <c r="N14" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21">
+      <c r="A15" t="s">
+        <v>282</v>
+      </c>
+      <c r="C15" t="s">
+        <v>280</v>
+      </c>
+      <c r="D15" s="2"/>
+      <c r="I15" t="s">
+        <v>281</v>
+      </c>
+      <c r="K15" t="s">
+        <v>233</v>
+      </c>
+      <c r="N15" t="s">
         <v>279</v>
-      </c>
-    </row>
-    <row r="15" spans="1:21">
-      <c r="A15" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="H15" t="s">
-        <v>25</v>
-      </c>
-      <c r="K15" t="s">
-        <v>291</v>
-      </c>
-      <c r="N15" t="s">
-        <v>40</v>
-      </c>
-      <c r="P15" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="16" spans="1:21">
@@ -40403,98 +40176,104 @@
       <c r="B16" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="I16" t="s">
+      <c r="H16" t="s">
+        <v>25</v>
+      </c>
+      <c r="K16" t="s">
+        <v>291</v>
+      </c>
+      <c r="N16" t="s">
+        <v>40</v>
+      </c>
+      <c r="P16" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17">
+      <c r="A17" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="I17" t="s">
         <v>129</v>
       </c>
-      <c r="K16" t="s">
+      <c r="K17" t="s">
         <v>130</v>
       </c>
-      <c r="N16" t="s">
+      <c r="N17" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="17" spans="1:17">
-      <c r="A17" t="s">
+    <row r="18" spans="1:17">
+      <c r="A18" t="s">
         <v>43</v>
       </c>
-      <c r="K17" t="s">
+      <c r="K18" t="s">
         <v>77</v>
       </c>
-      <c r="N17" t="s">
+      <c r="N18" t="s">
         <v>44</v>
       </c>
-      <c r="P17" t="s">
+      <c r="P18" t="s">
         <v>46</v>
       </c>
-      <c r="Q17" t="s">
+      <c r="Q18" t="s">
         <v>45</v>
-      </c>
-    </row>
-    <row r="18" spans="1:17">
-      <c r="A18" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="K18" t="s">
-        <v>291</v>
-      </c>
-      <c r="N18" t="s">
-        <v>56</v>
-      </c>
-      <c r="Q18" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="19" spans="1:17">
       <c r="A19" s="4" t="s">
-        <v>231</v>
+        <v>52</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>34</v>
       </c>
       <c r="K19" t="s">
-        <v>233</v>
+        <v>291</v>
       </c>
       <c r="N19" t="s">
-        <v>234</v>
+        <v>56</v>
       </c>
       <c r="Q19" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20" spans="1:17">
       <c r="A20" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K20" t="s">
         <v>233</v>
       </c>
       <c r="N20" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="Q20" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="21" spans="1:17">
-      <c r="A21" t="s">
-        <v>6</v>
-      </c>
-      <c r="C21" t="s">
-        <v>241</v>
-      </c>
-      <c r="D21" t="s">
-        <v>242</v>
+      <c r="A21" s="4" t="s">
+        <v>232</v>
       </c>
       <c r="K21" t="s">
-        <v>7</v>
+        <v>233</v>
       </c>
       <c r="N21" t="s">
-        <v>243</v>
+        <v>235</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="22" spans="1:17">
       <c r="A22" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="C22" t="s">
         <v>241</v>
@@ -40506,49 +40285,46 @@
         <v>7</v>
       </c>
       <c r="N22" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17">
+      <c r="A23" t="s">
+        <v>34</v>
+      </c>
+      <c r="C23" t="s">
+        <v>241</v>
+      </c>
+      <c r="D23" t="s">
+        <v>242</v>
+      </c>
+      <c r="K23" t="s">
+        <v>7</v>
+      </c>
+      <c r="N23" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="23" spans="1:17">
-      <c r="A23" s="4" t="s">
+    <row r="24" spans="1:17">
+      <c r="A24" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="D23" t="s">
+      <c r="D24" t="s">
         <v>250</v>
       </c>
-      <c r="I23" t="s">
+      <c r="I24" t="s">
         <v>251</v>
-      </c>
-      <c r="K23" t="s">
-        <v>141</v>
-      </c>
-      <c r="N23" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="24" spans="1:17">
-      <c r="A24" t="s">
-        <v>142</v>
-      </c>
-      <c r="I24" t="s">
-        <v>253</v>
       </c>
       <c r="K24" t="s">
         <v>141</v>
       </c>
       <c r="N24" t="s">
-        <v>271</v>
-      </c>
-      <c r="P24" t="s">
-        <v>268</v>
-      </c>
-      <c r="Q24" t="s">
-        <v>252</v>
+        <v>143</v>
       </c>
     </row>
     <row r="25" spans="1:17">
       <c r="A25" t="s">
-        <v>4</v>
+        <v>142</v>
       </c>
       <c r="I25" t="s">
         <v>253</v>
@@ -40557,7 +40333,7 @@
         <v>141</v>
       </c>
       <c r="N25" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="P25" t="s">
         <v>268</v>
@@ -40568,30 +40344,27 @@
     </row>
     <row r="26" spans="1:17">
       <c r="A26" t="s">
-        <v>6</v>
-      </c>
-      <c r="F26" t="s">
-        <v>275</v>
-      </c>
-      <c r="G26" t="s">
-        <v>275</v>
+        <v>4</v>
+      </c>
+      <c r="I26" t="s">
+        <v>253</v>
       </c>
       <c r="K26" t="s">
-        <v>7</v>
+        <v>141</v>
       </c>
       <c r="N26" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="P26" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q26" t="s">
-        <v>39</v>
+        <v>252</v>
       </c>
     </row>
     <row r="27" spans="1:17">
       <c r="A27" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="F27" t="s">
         <v>275</v>
@@ -40603,12 +40376,35 @@
         <v>7</v>
       </c>
       <c r="N27" t="s">
+        <v>273</v>
+      </c>
+      <c r="P27" t="s">
+        <v>269</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17">
+      <c r="A28" t="s">
+        <v>34</v>
+      </c>
+      <c r="F28" t="s">
+        <v>275</v>
+      </c>
+      <c r="G28" t="s">
+        <v>275</v>
+      </c>
+      <c r="K28" t="s">
+        <v>7</v>
+      </c>
+      <c r="N28" t="s">
         <v>274</v>
       </c>
-      <c r="P27" t="s">
+      <c r="P28" t="s">
         <v>270</v>
       </c>
-      <c r="Q27" t="s">
+      <c r="Q28" t="s">
         <v>39</v>
       </c>
     </row>

--- a/VerveStacks_ZAF_grids_kan/ReportDefs_vervestacks.xlsx
+++ b/VerveStacks_ZAF_grids_kan/ReportDefs_vervestacks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_ZAF_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CADAF0B8-E87E-4DF4-9332-F1F82095EE02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77C8488D-BB10-4A28-82A9-29778EDEDB4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="geolocation" sheetId="72" r:id="rId1"/>
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7570" uniqueCount="1172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7426" uniqueCount="1156">
   <si>
     <t>Unit</t>
   </si>
@@ -3388,198 +3388,6 @@
     <t>trancost</t>
   </si>
   <si>
-    <t>Lo.0.CF1.Y.Y.Y</t>
-  </si>
-  <si>
-    <t>Hi.0.CF1.Y.Y.Y</t>
-  </si>
-  <si>
-    <t>Lo.95.CF1.Y.Y.Y</t>
-  </si>
-  <si>
-    <t>Hi.95.CF1.Y.Y.Y</t>
-  </si>
-  <si>
-    <t>Lo.0.CF1.N.Y.Y</t>
-  </si>
-  <si>
-    <t>Hi.0.CF1.N.Y.Y</t>
-  </si>
-  <si>
-    <t>Lo.95.CF1.N.Y.Y</t>
-  </si>
-  <si>
-    <t>Hi.95.CF1.N.Y.Y</t>
-  </si>
-  <si>
-    <t>Lo.0.CF6.Y.Y.Y</t>
-  </si>
-  <si>
-    <t>Hi.0.CF6.Y.Y.Y</t>
-  </si>
-  <si>
-    <t>Lo.95.CF6.Y.Y.Y</t>
-  </si>
-  <si>
-    <t>Hi.95.CF6.Y.Y.Y</t>
-  </si>
-  <si>
-    <t>Lo.0.CF6.N.Y.Y</t>
-  </si>
-  <si>
-    <t>Hi.0.CF6.N.Y.Y</t>
-  </si>
-  <si>
-    <t>Lo.95.CF6.N.Y.Y</t>
-  </si>
-  <si>
-    <t>Hi.95.CF6.N.Y.Y</t>
-  </si>
-  <si>
-    <t>Lo.0.CF1.Y.N.Y</t>
-  </si>
-  <si>
-    <t>Hi.0.CF1.Y.N.Y</t>
-  </si>
-  <si>
-    <t>Lo.95.CF1.Y.N.Y</t>
-  </si>
-  <si>
-    <t>Hi.95.CF1.Y.N.Y</t>
-  </si>
-  <si>
-    <t>Lo.0.CF1.N.N.Y</t>
-  </si>
-  <si>
-    <t>Hi.0.CF1.N.N.Y</t>
-  </si>
-  <si>
-    <t>Lo.95.CF1.N.N.Y</t>
-  </si>
-  <si>
-    <t>Hi.95.CF1.N.N.Y</t>
-  </si>
-  <si>
-    <t>Lo.0.CF6.Y.N.Y</t>
-  </si>
-  <si>
-    <t>Hi.0.CF6.Y.N.Y</t>
-  </si>
-  <si>
-    <t>Lo.95.CF6.Y.N.Y</t>
-  </si>
-  <si>
-    <t>Hi.95.CF6.Y.N.Y</t>
-  </si>
-  <si>
-    <t>Lo.0.CF6.N.N.Y</t>
-  </si>
-  <si>
-    <t>Hi.0.CF6.N.N.Y</t>
-  </si>
-  <si>
-    <t>Lo.95.CF6.N.N.Y</t>
-  </si>
-  <si>
-    <t>Hi.95.CF6.N.N.Y</t>
-  </si>
-  <si>
-    <t>Lo.0.CF1.Y.Y.N</t>
-  </si>
-  <si>
-    <t>Hi.0.CF1.Y.Y.N</t>
-  </si>
-  <si>
-    <t>Lo.95.CF1.Y.Y.N</t>
-  </si>
-  <si>
-    <t>Hi.95.CF1.Y.Y.N</t>
-  </si>
-  <si>
-    <t>Lo.0.CF1.N.Y.N</t>
-  </si>
-  <si>
-    <t>Hi.0.CF1.N.Y.N</t>
-  </si>
-  <si>
-    <t>Lo.95.CF1.N.Y.N</t>
-  </si>
-  <si>
-    <t>Hi.95.CF1.N.Y.N</t>
-  </si>
-  <si>
-    <t>Lo.0.CF6.Y.Y.N</t>
-  </si>
-  <si>
-    <t>Hi.0.CF6.Y.Y.N</t>
-  </si>
-  <si>
-    <t>Lo.95.CF6.Y.Y.N</t>
-  </si>
-  <si>
-    <t>Hi.95.CF6.Y.Y.N</t>
-  </si>
-  <si>
-    <t>Lo.0.CF6.N.Y.N</t>
-  </si>
-  <si>
-    <t>Hi.0.CF6.N.Y.N</t>
-  </si>
-  <si>
-    <t>Lo.95.CF6.N.Y.N</t>
-  </si>
-  <si>
-    <t>Hi.95.CF6.N.Y.N</t>
-  </si>
-  <si>
-    <t>Lo.0.CF1.Y.N.N</t>
-  </si>
-  <si>
-    <t>Hi.0.CF1.Y.N.N</t>
-  </si>
-  <si>
-    <t>Lo.95.CF1.Y.N.N</t>
-  </si>
-  <si>
-    <t>Hi.95.CF1.Y.N.N</t>
-  </si>
-  <si>
-    <t>Lo.0.CF1.N.N.N</t>
-  </si>
-  <si>
-    <t>Hi.0.CF1.N.N.N</t>
-  </si>
-  <si>
-    <t>Lo.95.CF1.N.N.N</t>
-  </si>
-  <si>
-    <t>Hi.95.CF1.N.N.N</t>
-  </si>
-  <si>
-    <t>Lo.0.CF6.Y.N.N</t>
-  </si>
-  <si>
-    <t>Hi.0.CF6.Y.N.N</t>
-  </si>
-  <si>
-    <t>Lo.95.CF6.Y.N.N</t>
-  </si>
-  <si>
-    <t>Hi.95.CF6.Y.N.N</t>
-  </si>
-  <si>
-    <t>Lo.0.CF6.N.N.N</t>
-  </si>
-  <si>
-    <t>Hi.0.CF6.N.N.N</t>
-  </si>
-  <si>
-    <t>Lo.95.CF6.N.N.N</t>
-  </si>
-  <si>
-    <t>Hi.95.CF6.N.N.N</t>
-  </si>
-  <si>
     <t>tc</t>
   </si>
   <si>
@@ -3599,6 +3407,150 @@
   </si>
   <si>
     <t>Cost_Inv_lumpsum</t>
+  </si>
+  <si>
+    <t>Lo.0.CF1.Y.Y.1</t>
+  </si>
+  <si>
+    <t>Hi.0.CF1.Y.Y.1</t>
+  </si>
+  <si>
+    <t>Lo.95.CF1.Y.Y.1</t>
+  </si>
+  <si>
+    <t>Hi.95.CF1.Y.Y.1</t>
+  </si>
+  <si>
+    <t>Lo.0.CF1.N.Y.1</t>
+  </si>
+  <si>
+    <t>Hi.0.CF1.N.Y.1</t>
+  </si>
+  <si>
+    <t>Lo.95.CF1.N.Y.1</t>
+  </si>
+  <si>
+    <t>Hi.95.CF1.N.Y.1</t>
+  </si>
+  <si>
+    <t>Lo.0.CF6.Y.Y.1</t>
+  </si>
+  <si>
+    <t>Hi.0.CF6.Y.Y.1</t>
+  </si>
+  <si>
+    <t>Lo.95.CF6.Y.Y.1</t>
+  </si>
+  <si>
+    <t>Hi.95.CF6.Y.Y.1</t>
+  </si>
+  <si>
+    <t>Lo.0.CF6.N.Y.1</t>
+  </si>
+  <si>
+    <t>Hi.0.CF6.N.Y.1</t>
+  </si>
+  <si>
+    <t>Lo.95.CF6.N.Y.1</t>
+  </si>
+  <si>
+    <t>Hi.95.CF6.N.Y.1</t>
+  </si>
+  <si>
+    <t>Lo.0.CF1.Y.Y.0.25</t>
+  </si>
+  <si>
+    <t>Hi.0.CF1.Y.Y.0.25</t>
+  </si>
+  <si>
+    <t>Lo.95.CF1.Y.Y.0.25</t>
+  </si>
+  <si>
+    <t>Hi.95.CF1.Y.Y.0.25</t>
+  </si>
+  <si>
+    <t>Lo.0.CF1.N.Y.0.25</t>
+  </si>
+  <si>
+    <t>Hi.0.CF1.N.Y.0.25</t>
+  </si>
+  <si>
+    <t>Lo.95.CF1.N.Y.0.25</t>
+  </si>
+  <si>
+    <t>Hi.95.CF1.N.Y.0.25</t>
+  </si>
+  <si>
+    <t>Lo.0.CF6.Y.Y.0.25</t>
+  </si>
+  <si>
+    <t>Hi.0.CF6.Y.Y.0.25</t>
+  </si>
+  <si>
+    <t>Lo.95.CF6.Y.Y.0.25</t>
+  </si>
+  <si>
+    <t>Hi.95.CF6.Y.Y.0.25</t>
+  </si>
+  <si>
+    <t>Lo.0.CF6.N.Y.0.25</t>
+  </si>
+  <si>
+    <t>Hi.0.CF6.N.Y.0.25</t>
+  </si>
+  <si>
+    <t>Lo.95.CF6.N.Y.0.25</t>
+  </si>
+  <si>
+    <t>Hi.95.CF6.N.Y.0.25</t>
+  </si>
+  <si>
+    <t>Lo.0.CF1.Y.Y.2</t>
+  </si>
+  <si>
+    <t>Hi.0.CF1.Y.Y.2</t>
+  </si>
+  <si>
+    <t>Lo.95.CF1.Y.Y.2</t>
+  </si>
+  <si>
+    <t>Hi.95.CF1.Y.Y.2</t>
+  </si>
+  <si>
+    <t>Lo.0.CF1.N.Y.2</t>
+  </si>
+  <si>
+    <t>Hi.0.CF1.N.Y.2</t>
+  </si>
+  <si>
+    <t>Lo.95.CF1.N.Y.2</t>
+  </si>
+  <si>
+    <t>Hi.95.CF1.N.Y.2</t>
+  </si>
+  <si>
+    <t>Lo.0.CF6.Y.Y.2</t>
+  </si>
+  <si>
+    <t>Hi.0.CF6.Y.Y.2</t>
+  </si>
+  <si>
+    <t>Lo.95.CF6.Y.Y.2</t>
+  </si>
+  <si>
+    <t>Hi.95.CF6.Y.Y.2</t>
+  </si>
+  <si>
+    <t>Lo.0.CF6.N.Y.2</t>
+  </si>
+  <si>
+    <t>Hi.0.CF6.N.Y.2</t>
+  </si>
+  <si>
+    <t>Lo.95.CF6.N.Y.2</t>
+  </si>
+  <si>
+    <t>Hi.95.CF6.N.Y.2</t>
   </si>
 </sst>
 </file>
@@ -9550,10 +9502,10 @@
         <v>64</v>
       </c>
       <c r="C27" t="s">
-        <v>1167</v>
+        <v>1103</v>
       </c>
       <c r="D27" t="s">
-        <v>1168</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -33992,7 +33944,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C50B696F-B355-4FC5-AD3E-AFDC509F717D}">
-  <dimension ref="B1:AE69"/>
+  <dimension ref="B1:AC53"/>
   <sheetFormatPr defaultColWidth="14.73046875" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="2.73046875" bestFit="1" customWidth="1"/>
@@ -34000,49 +33952,48 @@
     <col min="3" max="3" width="22.19921875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="4.3984375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="22.19921875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="27.9296875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9.73046875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="10" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.3984375" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="6.53125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="6.53125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="11.796875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="7.06640625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="7.1328125" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="7.3984375" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="6.796875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="6.33203125" customWidth="1"/>
-    <col min="25" max="25" width="2.73046875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="5.6640625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="4.1328125" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="3.59765625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="3.86328125" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="4.1328125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.796875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="6.53125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.796875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.06640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="7.1328125" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="7.3984375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="6.796875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="6.33203125" customWidth="1"/>
+    <col min="24" max="24" width="2.73046875" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="5.6640625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="5.1328125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="3.59765625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="3.86328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:31">
+    <row r="1" spans="2:29">
       <c r="I1" t="s">
         <v>35</v>
       </c>
+      <c r="R1" t="s">
+        <v>1096</v>
+      </c>
       <c r="S1" t="s">
-        <v>1096</v>
-      </c>
-      <c r="T1" t="s">
         <v>1097</v>
       </c>
+      <c r="U1" t="s">
+        <v>1098</v>
+      </c>
       <c r="V1" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="W1" t="s">
-        <v>1099</v>
-      </c>
-      <c r="X1" t="s">
-        <v>1165</v>
-      </c>
-    </row>
-    <row r="2" spans="2:31">
+        <v>1101</v>
+      </c>
+    </row>
+    <row r="2" spans="2:29">
       <c r="I2" t="s">
         <v>1084</v>
       </c>
@@ -34053,7 +34004,7 @@
         <v>1089</v>
       </c>
     </row>
-    <row r="4" spans="2:31">
+    <row r="4" spans="2:29">
       <c r="B4" t="s">
         <v>57</v>
       </c>
@@ -34061,7 +34012,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="5" spans="2:31">
+    <row r="5" spans="2:29">
       <c r="B5" t="s">
         <v>19</v>
       </c>
@@ -34078,5751 +34029,3939 @@
         <v>8</v>
       </c>
       <c r="I5" t="str">
+        <f>"sg_"&amp;R5</f>
+        <v>sg_demand</v>
+      </c>
+      <c r="J5" t="str">
         <f>"sg_"&amp;S5</f>
-        <v>sg_demand</v>
-      </c>
-      <c r="J5" t="str">
-        <f t="shared" ref="J5:N5" si="0">"sg_"&amp;T5</f>
         <v>sg_co2price</v>
       </c>
       <c r="K5" t="str">
-        <f t="shared" si="0"/>
+        <f>"sg_"&amp;T5</f>
         <v>sg_coalflex</v>
       </c>
       <c r="L5" t="str">
-        <f t="shared" si="0"/>
+        <f>"sg_"&amp;U5</f>
         <v>sg_DEF</v>
       </c>
       <c r="M5" t="str">
-        <f t="shared" si="0"/>
-        <v>sg_GAS</v>
-      </c>
-      <c r="N5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="M5" si="0">"sg_"&amp;W5</f>
         <v>sg_trancost</v>
       </c>
+      <c r="O5" t="s">
+        <v>237</v>
+      </c>
       <c r="P5" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q5" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="R5" t="s">
-        <v>239</v>
+        <v>1084</v>
       </c>
       <c r="S5" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="T5" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="U5" t="s">
-        <v>1086</v>
+        <v>1090</v>
       </c>
       <c r="V5" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="W5" t="s">
-        <v>1091</v>
-      </c>
-      <c r="X5" t="s">
         <v>1100</v>
       </c>
     </row>
-    <row r="6" spans="2:31">
+    <row r="6" spans="2:29">
       <c r="B6" t="str">
-        <f>"vs~"&amp;TEXT(R6,"0000")</f>
+        <f>"vs~"&amp;TEXT(Q6,"0000")</f>
         <v>vs~0001</v>
       </c>
       <c r="C6" t="str">
         <f>H6</f>
-        <v>tc-Y.df-Y.ga-Y.dm-Lo.cp-0.CF1</v>
+        <v>tc-1.00.df-Y.dm-Lo.cp-00.CF1</v>
       </c>
       <c r="H6" t="str">
-        <f>_xlfn.TEXTJOIN(".",TRUE,AE6,AC6:AD6)&amp;"."&amp;_xlfn.TEXTJOIN(".",TRUE,Z6:AB6)</f>
-        <v>tc-Y.df-Y.ga-Y.dm-Lo.cp-0.CF1</v>
+        <f>_xlfn.TEXTJOIN(".",TRUE,AC6,AB6:AB6)&amp;"."&amp;_xlfn.TEXTJOIN(".",TRUE,Y6:AA6)</f>
+        <v>tc-1.00.df-Y.dm-Lo.cp-00.CF1</v>
       </c>
       <c r="I6" t="str">
-        <f>S6</f>
+        <f>R6</f>
         <v>Lo</v>
       </c>
       <c r="J6" t="str">
-        <f>TEXT(T6,"00")</f>
+        <f>TEXT(S6,"00")</f>
         <v>00</v>
       </c>
       <c r="K6" t="str">
-        <f t="shared" ref="K6:N6" si="1">U6</f>
+        <f>T6</f>
         <v>CF1</v>
       </c>
       <c r="L6" t="str">
-        <f t="shared" si="1"/>
+        <f>U6</f>
         <v>Y</v>
       </c>
-      <c r="M6" t="str">
-        <f t="shared" si="1"/>
-        <v>Y</v>
-      </c>
-      <c r="N6" t="str">
-        <f t="shared" si="1"/>
-        <v>Y</v>
-      </c>
-      <c r="P6">
+      <c r="M6">
+        <f t="shared" ref="M6" si="1">W6</f>
+        <v>1</v>
+      </c>
+      <c r="O6">
         <v>5</v>
       </c>
-      <c r="Q6" t="s">
-        <v>1101</v>
-      </c>
-      <c r="R6">
+      <c r="P6" t="s">
+        <v>1108</v>
+      </c>
+      <c r="Q6">
         <v>1</v>
       </c>
-      <c r="S6" t="s">
+      <c r="R6" t="s">
         <v>1092</v>
       </c>
-      <c r="T6">
+      <c r="S6">
         <v>0</v>
       </c>
+      <c r="T6" t="s">
+        <v>1087</v>
+      </c>
       <c r="U6" t="s">
-        <v>1087</v>
+        <v>1093</v>
       </c>
       <c r="V6" t="s">
         <v>1093</v>
       </c>
-      <c r="W6" t="s">
-        <v>1093</v>
-      </c>
-      <c r="X6" t="s">
-        <v>1093</v>
+      <c r="W6">
+        <v>1</v>
+      </c>
+      <c r="Y6" t="str">
+        <f>R$1&amp;"-"&amp;R6</f>
+        <v>dm-Lo</v>
       </c>
       <c r="Z6" t="str">
-        <f>S$1&amp;"-"&amp;S6</f>
-        <v>dm-Lo</v>
+        <f>S$1&amp;"-"&amp;TEXT(S6,"00")</f>
+        <v>cp-00</v>
       </c>
       <c r="AA6" t="str">
-        <f>T$1&amp;"-"&amp;T6</f>
-        <v>cp-0</v>
+        <f>T6</f>
+        <v>CF1</v>
       </c>
       <c r="AB6" t="str">
-        <f>U6</f>
-        <v>CF1</v>
+        <f>U$1&amp;"-"&amp;U6</f>
+        <v>df-Y</v>
       </c>
       <c r="AC6" t="str">
-        <f>V$1&amp;"-"&amp;V6</f>
-        <v>df-Y</v>
-      </c>
-      <c r="AD6" t="str">
-        <f>W$1&amp;"-"&amp;W6</f>
-        <v>ga-Y</v>
-      </c>
-      <c r="AE6" t="str">
-        <f>X$1&amp;"-"&amp;X6</f>
-        <v>tc-Y</v>
-      </c>
-    </row>
-    <row r="7" spans="2:31">
+        <f>W$1&amp;"-"&amp;TEXT(W6,"0.00")</f>
+        <v>tc-1.00</v>
+      </c>
+    </row>
+    <row r="7" spans="2:29">
       <c r="B7" t="str">
-        <f t="shared" ref="B7:B17" si="2">"vs~"&amp;TEXT(R7,"0000")</f>
+        <f t="shared" ref="B7:B17" si="2">"vs~"&amp;TEXT(Q7,"0000")</f>
         <v>vs~0002</v>
       </c>
       <c r="C7" t="str">
         <f t="shared" ref="C7:C17" si="3">H7</f>
-        <v>tc-Y.df-Y.ga-Y.dm-Hi.cp-0.CF1</v>
+        <v>tc-1.00.df-Y.dm-Hi.cp-00.CF1</v>
       </c>
       <c r="H7" t="str">
-        <f t="shared" ref="H7:H37" si="4">_xlfn.TEXTJOIN(".",TRUE,AE7,AC7:AD7)&amp;"."&amp;_xlfn.TEXTJOIN(".",TRUE,Z7:AB7)</f>
-        <v>tc-Y.df-Y.ga-Y.dm-Hi.cp-0.CF1</v>
+        <f>_xlfn.TEXTJOIN(".",TRUE,AC7,AB7:AB7)&amp;"."&amp;_xlfn.TEXTJOIN(".",TRUE,Y7:AA7)</f>
+        <v>tc-1.00.df-Y.dm-Hi.cp-00.CF1</v>
       </c>
       <c r="I7" t="str">
-        <f t="shared" ref="I7:I37" si="5">S7</f>
+        <f t="shared" ref="I7:I37" si="4">R7</f>
         <v>Hi</v>
       </c>
       <c r="J7" t="str">
-        <f t="shared" ref="J7:J37" si="6">TEXT(T7,"00")</f>
+        <f t="shared" ref="J7:J37" si="5">TEXT(S7,"00")</f>
         <v>00</v>
       </c>
       <c r="K7" t="str">
-        <f t="shared" ref="K7:K37" si="7">U7</f>
+        <f t="shared" ref="K7:K37" si="6">T7</f>
         <v>CF1</v>
       </c>
       <c r="L7" t="str">
-        <f t="shared" ref="L7:L37" si="8">V7</f>
+        <f t="shared" ref="L7:L37" si="7">U7</f>
         <v>Y</v>
       </c>
-      <c r="M7" t="str">
-        <f t="shared" ref="M7:N37" si="9">W7</f>
-        <v>Y</v>
-      </c>
-      <c r="N7" t="str">
-        <f t="shared" si="9"/>
-        <v>Y</v>
-      </c>
-      <c r="P7">
+      <c r="M7">
+        <f t="shared" ref="M7:M37" si="8">W7</f>
+        <v>1</v>
+      </c>
+      <c r="O7">
         <v>5</v>
       </c>
-      <c r="Q7" t="s">
-        <v>1102</v>
-      </c>
-      <c r="R7">
+      <c r="P7" t="s">
+        <v>1109</v>
+      </c>
+      <c r="Q7">
         <v>2</v>
       </c>
-      <c r="S7" t="s">
+      <c r="R7" t="s">
         <v>1094</v>
       </c>
-      <c r="T7">
+      <c r="S7">
         <v>0</v>
       </c>
+      <c r="T7" t="s">
+        <v>1087</v>
+      </c>
       <c r="U7" t="s">
-        <v>1087</v>
+        <v>1093</v>
       </c>
       <c r="V7" t="s">
         <v>1093</v>
       </c>
-      <c r="W7" t="s">
-        <v>1093</v>
-      </c>
-      <c r="X7" t="s">
-        <v>1093</v>
+      <c r="W7">
+        <v>1</v>
+      </c>
+      <c r="Y7" t="str">
+        <f t="shared" ref="Y7:Y37" si="9">R$1&amp;"-"&amp;R7</f>
+        <v>dm-Hi</v>
       </c>
       <c r="Z7" t="str">
-        <f t="shared" ref="Z7:Z37" si="10">S$1&amp;"-"&amp;S7</f>
-        <v>dm-Hi</v>
+        <f t="shared" ref="Z7:Z53" si="10">S$1&amp;"-"&amp;TEXT(S7,"00")</f>
+        <v>cp-00</v>
       </c>
       <c r="AA7" t="str">
-        <f t="shared" ref="AA7:AA37" si="11">T$1&amp;"-"&amp;T7</f>
-        <v>cp-0</v>
+        <f t="shared" ref="AA7:AA37" si="11">T7</f>
+        <v>CF1</v>
       </c>
       <c r="AB7" t="str">
-        <f t="shared" ref="AB7:AB37" si="12">U7</f>
-        <v>CF1</v>
+        <f t="shared" ref="AB7:AB37" si="12">U$1&amp;"-"&amp;U7</f>
+        <v>df-Y</v>
       </c>
       <c r="AC7" t="str">
-        <f t="shared" ref="AC7:AC37" si="13">V$1&amp;"-"&amp;V7</f>
-        <v>df-Y</v>
-      </c>
-      <c r="AD7" t="str">
-        <f t="shared" ref="AD7:AE37" si="14">W$1&amp;"-"&amp;W7</f>
-        <v>ga-Y</v>
-      </c>
-      <c r="AE7" t="str">
-        <f t="shared" si="14"/>
-        <v>tc-Y</v>
-      </c>
-    </row>
-    <row r="8" spans="2:31">
+        <f t="shared" ref="AC7:AC53" si="13">W$1&amp;"-"&amp;TEXT(W7,"0.00")</f>
+        <v>tc-1.00</v>
+      </c>
+    </row>
+    <row r="8" spans="2:29">
       <c r="B8" t="str">
         <f t="shared" si="2"/>
         <v>vs~0003</v>
       </c>
       <c r="C8" t="str">
         <f t="shared" si="3"/>
-        <v>tc-Y.df-Y.ga-Y.dm-Lo.cp-95.CF1</v>
+        <v>tc-1.00.df-Y.dm-Lo.cp-95.CF1</v>
       </c>
       <c r="H8" t="str">
+        <f>_xlfn.TEXTJOIN(".",TRUE,AC8,AB8:AB8)&amp;"."&amp;_xlfn.TEXTJOIN(".",TRUE,Y8:AA8)</f>
+        <v>tc-1.00.df-Y.dm-Lo.cp-95.CF1</v>
+      </c>
+      <c r="I8" t="str">
         <f t="shared" si="4"/>
-        <v>tc-Y.df-Y.ga-Y.dm-Lo.cp-95.CF1</v>
-      </c>
-      <c r="I8" t="str">
+        <v>Lo</v>
+      </c>
+      <c r="J8" t="str">
         <f t="shared" si="5"/>
-        <v>Lo</v>
-      </c>
-      <c r="J8" t="str">
+        <v>95</v>
+      </c>
+      <c r="K8" t="str">
         <f t="shared" si="6"/>
+        <v>CF1</v>
+      </c>
+      <c r="L8" t="str">
+        <f t="shared" si="7"/>
+        <v>Y</v>
+      </c>
+      <c r="M8">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="O8">
+        <v>5</v>
+      </c>
+      <c r="P8" t="s">
+        <v>1110</v>
+      </c>
+      <c r="Q8">
+        <v>3</v>
+      </c>
+      <c r="R8" t="s">
+        <v>1092</v>
+      </c>
+      <c r="S8">
         <v>95</v>
       </c>
-      <c r="K8" t="str">
-        <f t="shared" si="7"/>
-        <v>CF1</v>
-      </c>
-      <c r="L8" t="str">
-        <f t="shared" si="8"/>
-        <v>Y</v>
-      </c>
-      <c r="M8" t="str">
-        <f t="shared" si="9"/>
-        <v>Y</v>
-      </c>
-      <c r="N8" t="str">
-        <f t="shared" si="9"/>
-        <v>Y</v>
-      </c>
-      <c r="P8">
-        <v>5</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>1103</v>
-      </c>
-      <c r="R8">
-        <v>3</v>
-      </c>
-      <c r="S8" t="s">
-        <v>1092</v>
-      </c>
-      <c r="T8">
-        <v>95</v>
+      <c r="T8" t="s">
+        <v>1087</v>
       </c>
       <c r="U8" t="s">
-        <v>1087</v>
+        <v>1093</v>
       </c>
       <c r="V8" t="s">
         <v>1093</v>
       </c>
-      <c r="W8" t="s">
-        <v>1093</v>
-      </c>
-      <c r="X8" t="s">
-        <v>1093</v>
+      <c r="W8">
+        <v>1</v>
+      </c>
+      <c r="Y8" t="str">
+        <f t="shared" si="9"/>
+        <v>dm-Lo</v>
       </c>
       <c r="Z8" t="str">
         <f t="shared" si="10"/>
-        <v>dm-Lo</v>
+        <v>cp-95</v>
       </c>
       <c r="AA8" t="str">
         <f t="shared" si="11"/>
-        <v>cp-95</v>
+        <v>CF1</v>
       </c>
       <c r="AB8" t="str">
         <f t="shared" si="12"/>
-        <v>CF1</v>
+        <v>df-Y</v>
       </c>
       <c r="AC8" t="str">
         <f t="shared" si="13"/>
-        <v>df-Y</v>
-      </c>
-      <c r="AD8" t="str">
-        <f t="shared" si="14"/>
-        <v>ga-Y</v>
-      </c>
-      <c r="AE8" t="str">
-        <f t="shared" si="14"/>
-        <v>tc-Y</v>
-      </c>
-    </row>
-    <row r="9" spans="2:31">
+        <v>tc-1.00</v>
+      </c>
+    </row>
+    <row r="9" spans="2:29">
       <c r="B9" t="str">
         <f t="shared" si="2"/>
         <v>vs~0004</v>
       </c>
       <c r="C9" t="str">
         <f t="shared" si="3"/>
-        <v>tc-Y.df-Y.ga-Y.dm-Hi.cp-95.CF1</v>
+        <v>tc-1.00.df-Y.dm-Hi.cp-95.CF1</v>
       </c>
       <c r="H9" t="str">
+        <f>_xlfn.TEXTJOIN(".",TRUE,AC9,AB9:AB9)&amp;"."&amp;_xlfn.TEXTJOIN(".",TRUE,Y9:AA9)</f>
+        <v>tc-1.00.df-Y.dm-Hi.cp-95.CF1</v>
+      </c>
+      <c r="I9" t="str">
         <f t="shared" si="4"/>
-        <v>tc-Y.df-Y.ga-Y.dm-Hi.cp-95.CF1</v>
-      </c>
-      <c r="I9" t="str">
+        <v>Hi</v>
+      </c>
+      <c r="J9" t="str">
         <f t="shared" si="5"/>
-        <v>Hi</v>
-      </c>
-      <c r="J9" t="str">
+        <v>95</v>
+      </c>
+      <c r="K9" t="str">
         <f t="shared" si="6"/>
+        <v>CF1</v>
+      </c>
+      <c r="L9" t="str">
+        <f t="shared" si="7"/>
+        <v>Y</v>
+      </c>
+      <c r="M9">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="O9">
+        <v>5</v>
+      </c>
+      <c r="P9" t="s">
+        <v>1111</v>
+      </c>
+      <c r="Q9">
+        <v>4</v>
+      </c>
+      <c r="R9" t="s">
+        <v>1094</v>
+      </c>
+      <c r="S9">
         <v>95</v>
       </c>
-      <c r="K9" t="str">
-        <f t="shared" si="7"/>
-        <v>CF1</v>
-      </c>
-      <c r="L9" t="str">
-        <f t="shared" si="8"/>
-        <v>Y</v>
-      </c>
-      <c r="M9" t="str">
-        <f t="shared" si="9"/>
-        <v>Y</v>
-      </c>
-      <c r="N9" t="str">
-        <f t="shared" si="9"/>
-        <v>Y</v>
-      </c>
-      <c r="P9">
-        <v>5</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>1104</v>
-      </c>
-      <c r="R9">
-        <v>4</v>
-      </c>
-      <c r="S9" t="s">
-        <v>1094</v>
-      </c>
-      <c r="T9">
-        <v>95</v>
+      <c r="T9" t="s">
+        <v>1087</v>
       </c>
       <c r="U9" t="s">
-        <v>1087</v>
+        <v>1093</v>
       </c>
       <c r="V9" t="s">
         <v>1093</v>
       </c>
-      <c r="W9" t="s">
-        <v>1093</v>
-      </c>
-      <c r="X9" t="s">
-        <v>1093</v>
+      <c r="W9">
+        <v>1</v>
+      </c>
+      <c r="Y9" t="str">
+        <f t="shared" si="9"/>
+        <v>dm-Hi</v>
       </c>
       <c r="Z9" t="str">
         <f t="shared" si="10"/>
-        <v>dm-Hi</v>
+        <v>cp-95</v>
       </c>
       <c r="AA9" t="str">
         <f t="shared" si="11"/>
-        <v>cp-95</v>
+        <v>CF1</v>
       </c>
       <c r="AB9" t="str">
         <f t="shared" si="12"/>
-        <v>CF1</v>
+        <v>df-Y</v>
       </c>
       <c r="AC9" t="str">
         <f t="shared" si="13"/>
-        <v>df-Y</v>
-      </c>
-      <c r="AD9" t="str">
-        <f t="shared" si="14"/>
-        <v>ga-Y</v>
-      </c>
-      <c r="AE9" t="str">
-        <f t="shared" si="14"/>
-        <v>tc-Y</v>
-      </c>
-    </row>
-    <row r="10" spans="2:31">
+        <v>tc-1.00</v>
+      </c>
+    </row>
+    <row r="10" spans="2:29">
       <c r="B10" t="str">
         <f t="shared" si="2"/>
         <v>vs~0005</v>
       </c>
       <c r="C10" t="str">
         <f t="shared" si="3"/>
-        <v>tc-Y.df-N.ga-Y.dm-Lo.cp-0.CF1</v>
+        <v>tc-1.00.df-N.dm-Lo.cp-00.CF1</v>
       </c>
       <c r="H10" t="str">
+        <f>_xlfn.TEXTJOIN(".",TRUE,AC10,AB10:AB10)&amp;"."&amp;_xlfn.TEXTJOIN(".",TRUE,Y10:AA10)</f>
+        <v>tc-1.00.df-N.dm-Lo.cp-00.CF1</v>
+      </c>
+      <c r="I10" t="str">
         <f t="shared" si="4"/>
-        <v>tc-Y.df-N.ga-Y.dm-Lo.cp-0.CF1</v>
-      </c>
-      <c r="I10" t="str">
+        <v>Lo</v>
+      </c>
+      <c r="J10" t="str">
         <f t="shared" si="5"/>
-        <v>Lo</v>
-      </c>
-      <c r="J10" t="str">
+        <v>00</v>
+      </c>
+      <c r="K10" t="str">
         <f t="shared" si="6"/>
-        <v>00</v>
-      </c>
-      <c r="K10" t="str">
+        <v>CF1</v>
+      </c>
+      <c r="L10" t="str">
         <f t="shared" si="7"/>
-        <v>CF1</v>
-      </c>
-      <c r="L10" t="str">
+        <v>N</v>
+      </c>
+      <c r="M10">
         <f t="shared" si="8"/>
-        <v>N</v>
-      </c>
-      <c r="M10" t="str">
+        <v>1</v>
+      </c>
+      <c r="O10">
+        <v>5</v>
+      </c>
+      <c r="P10" t="s">
+        <v>1112</v>
+      </c>
+      <c r="Q10">
+        <v>5</v>
+      </c>
+      <c r="R10" t="s">
+        <v>1092</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="T10" t="s">
+        <v>1087</v>
+      </c>
+      <c r="U10" t="s">
+        <v>1095</v>
+      </c>
+      <c r="V10" t="s">
+        <v>1093</v>
+      </c>
+      <c r="W10">
+        <v>1</v>
+      </c>
+      <c r="Y10" t="str">
         <f t="shared" si="9"/>
-        <v>Y</v>
-      </c>
-      <c r="N10" t="str">
-        <f t="shared" si="9"/>
-        <v>Y</v>
-      </c>
-      <c r="P10">
-        <v>5</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>1105</v>
-      </c>
-      <c r="R10">
-        <v>5</v>
-      </c>
-      <c r="S10" t="s">
-        <v>1092</v>
-      </c>
-      <c r="T10">
-        <v>0</v>
-      </c>
-      <c r="U10" t="s">
-        <v>1087</v>
-      </c>
-      <c r="V10" t="s">
-        <v>1095</v>
-      </c>
-      <c r="W10" t="s">
-        <v>1093</v>
-      </c>
-      <c r="X10" t="s">
-        <v>1093</v>
+        <v>dm-Lo</v>
       </c>
       <c r="Z10" t="str">
         <f t="shared" si="10"/>
-        <v>dm-Lo</v>
+        <v>cp-00</v>
       </c>
       <c r="AA10" t="str">
         <f t="shared" si="11"/>
-        <v>cp-0</v>
+        <v>CF1</v>
       </c>
       <c r="AB10" t="str">
         <f t="shared" si="12"/>
-        <v>CF1</v>
+        <v>df-N</v>
       </c>
       <c r="AC10" t="str">
         <f t="shared" si="13"/>
-        <v>df-N</v>
-      </c>
-      <c r="AD10" t="str">
-        <f t="shared" si="14"/>
-        <v>ga-Y</v>
-      </c>
-      <c r="AE10" t="str">
-        <f t="shared" si="14"/>
-        <v>tc-Y</v>
-      </c>
-    </row>
-    <row r="11" spans="2:31">
+        <v>tc-1.00</v>
+      </c>
+    </row>
+    <row r="11" spans="2:29">
       <c r="B11" t="str">
         <f t="shared" si="2"/>
         <v>vs~0006</v>
       </c>
       <c r="C11" t="str">
         <f t="shared" si="3"/>
-        <v>tc-Y.df-N.ga-Y.dm-Hi.cp-0.CF1</v>
+        <v>tc-1.00.df-N.dm-Hi.cp-00.CF1</v>
       </c>
       <c r="H11" t="str">
+        <f>_xlfn.TEXTJOIN(".",TRUE,AC11,AB11:AB11)&amp;"."&amp;_xlfn.TEXTJOIN(".",TRUE,Y11:AA11)</f>
+        <v>tc-1.00.df-N.dm-Hi.cp-00.CF1</v>
+      </c>
+      <c r="I11" t="str">
         <f t="shared" si="4"/>
-        <v>tc-Y.df-N.ga-Y.dm-Hi.cp-0.CF1</v>
-      </c>
-      <c r="I11" t="str">
+        <v>Hi</v>
+      </c>
+      <c r="J11" t="str">
         <f t="shared" si="5"/>
-        <v>Hi</v>
-      </c>
-      <c r="J11" t="str">
+        <v>00</v>
+      </c>
+      <c r="K11" t="str">
         <f t="shared" si="6"/>
-        <v>00</v>
-      </c>
-      <c r="K11" t="str">
+        <v>CF1</v>
+      </c>
+      <c r="L11" t="str">
         <f t="shared" si="7"/>
-        <v>CF1</v>
-      </c>
-      <c r="L11" t="str">
+        <v>N</v>
+      </c>
+      <c r="M11">
         <f t="shared" si="8"/>
-        <v>N</v>
-      </c>
-      <c r="M11" t="str">
+        <v>1</v>
+      </c>
+      <c r="O11">
+        <v>5</v>
+      </c>
+      <c r="P11" t="s">
+        <v>1113</v>
+      </c>
+      <c r="Q11">
+        <v>6</v>
+      </c>
+      <c r="R11" t="s">
+        <v>1094</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="T11" t="s">
+        <v>1087</v>
+      </c>
+      <c r="U11" t="s">
+        <v>1095</v>
+      </c>
+      <c r="V11" t="s">
+        <v>1093</v>
+      </c>
+      <c r="W11">
+        <v>1</v>
+      </c>
+      <c r="Y11" t="str">
         <f t="shared" si="9"/>
-        <v>Y</v>
-      </c>
-      <c r="N11" t="str">
-        <f t="shared" si="9"/>
-        <v>Y</v>
-      </c>
-      <c r="P11">
-        <v>5</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>1106</v>
-      </c>
-      <c r="R11">
-        <v>6</v>
-      </c>
-      <c r="S11" t="s">
-        <v>1094</v>
-      </c>
-      <c r="T11">
-        <v>0</v>
-      </c>
-      <c r="U11" t="s">
-        <v>1087</v>
-      </c>
-      <c r="V11" t="s">
-        <v>1095</v>
-      </c>
-      <c r="W11" t="s">
-        <v>1093</v>
-      </c>
-      <c r="X11" t="s">
-        <v>1093</v>
+        <v>dm-Hi</v>
       </c>
       <c r="Z11" t="str">
         <f t="shared" si="10"/>
-        <v>dm-Hi</v>
+        <v>cp-00</v>
       </c>
       <c r="AA11" t="str">
         <f t="shared" si="11"/>
-        <v>cp-0</v>
+        <v>CF1</v>
       </c>
       <c r="AB11" t="str">
         <f t="shared" si="12"/>
-        <v>CF1</v>
+        <v>df-N</v>
       </c>
       <c r="AC11" t="str">
         <f t="shared" si="13"/>
-        <v>df-N</v>
-      </c>
-      <c r="AD11" t="str">
-        <f t="shared" si="14"/>
-        <v>ga-Y</v>
-      </c>
-      <c r="AE11" t="str">
-        <f t="shared" si="14"/>
-        <v>tc-Y</v>
-      </c>
-    </row>
-    <row r="12" spans="2:31">
+        <v>tc-1.00</v>
+      </c>
+    </row>
+    <row r="12" spans="2:29">
       <c r="B12" t="str">
         <f t="shared" si="2"/>
         <v>vs~0007</v>
       </c>
       <c r="C12" t="str">
         <f t="shared" si="3"/>
-        <v>tc-Y.df-N.ga-Y.dm-Lo.cp-95.CF1</v>
+        <v>tc-1.00.df-N.dm-Lo.cp-95.CF1</v>
       </c>
       <c r="H12" t="str">
+        <f>_xlfn.TEXTJOIN(".",TRUE,AC12,AB12:AB12)&amp;"."&amp;_xlfn.TEXTJOIN(".",TRUE,Y12:AA12)</f>
+        <v>tc-1.00.df-N.dm-Lo.cp-95.CF1</v>
+      </c>
+      <c r="I12" t="str">
         <f t="shared" si="4"/>
-        <v>tc-Y.df-N.ga-Y.dm-Lo.cp-95.CF1</v>
-      </c>
-      <c r="I12" t="str">
+        <v>Lo</v>
+      </c>
+      <c r="J12" t="str">
         <f t="shared" si="5"/>
-        <v>Lo</v>
-      </c>
-      <c r="J12" t="str">
+        <v>95</v>
+      </c>
+      <c r="K12" t="str">
         <f t="shared" si="6"/>
+        <v>CF1</v>
+      </c>
+      <c r="L12" t="str">
+        <f t="shared" si="7"/>
+        <v>N</v>
+      </c>
+      <c r="M12">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="O12">
+        <v>5</v>
+      </c>
+      <c r="P12" t="s">
+        <v>1114</v>
+      </c>
+      <c r="Q12">
+        <v>7</v>
+      </c>
+      <c r="R12" t="s">
+        <v>1092</v>
+      </c>
+      <c r="S12">
         <v>95</v>
       </c>
-      <c r="K12" t="str">
-        <f t="shared" si="7"/>
-        <v>CF1</v>
-      </c>
-      <c r="L12" t="str">
-        <f t="shared" si="8"/>
-        <v>N</v>
-      </c>
-      <c r="M12" t="str">
+      <c r="T12" t="s">
+        <v>1087</v>
+      </c>
+      <c r="U12" t="s">
+        <v>1095</v>
+      </c>
+      <c r="V12" t="s">
+        <v>1093</v>
+      </c>
+      <c r="W12">
+        <v>1</v>
+      </c>
+      <c r="Y12" t="str">
         <f t="shared" si="9"/>
-        <v>Y</v>
-      </c>
-      <c r="N12" t="str">
-        <f t="shared" si="9"/>
-        <v>Y</v>
-      </c>
-      <c r="P12">
-        <v>5</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>1107</v>
-      </c>
-      <c r="R12">
-        <v>7</v>
-      </c>
-      <c r="S12" t="s">
-        <v>1092</v>
-      </c>
-      <c r="T12">
-        <v>95</v>
-      </c>
-      <c r="U12" t="s">
-        <v>1087</v>
-      </c>
-      <c r="V12" t="s">
-        <v>1095</v>
-      </c>
-      <c r="W12" t="s">
-        <v>1093</v>
-      </c>
-      <c r="X12" t="s">
-        <v>1093</v>
+        <v>dm-Lo</v>
       </c>
       <c r="Z12" t="str">
         <f t="shared" si="10"/>
-        <v>dm-Lo</v>
+        <v>cp-95</v>
       </c>
       <c r="AA12" t="str">
         <f t="shared" si="11"/>
-        <v>cp-95</v>
+        <v>CF1</v>
       </c>
       <c r="AB12" t="str">
         <f t="shared" si="12"/>
-        <v>CF1</v>
+        <v>df-N</v>
       </c>
       <c r="AC12" t="str">
         <f t="shared" si="13"/>
-        <v>df-N</v>
-      </c>
-      <c r="AD12" t="str">
-        <f t="shared" si="14"/>
-        <v>ga-Y</v>
-      </c>
-      <c r="AE12" t="str">
-        <f t="shared" si="14"/>
-        <v>tc-Y</v>
-      </c>
-    </row>
-    <row r="13" spans="2:31">
+        <v>tc-1.00</v>
+      </c>
+    </row>
+    <row r="13" spans="2:29">
       <c r="B13" t="str">
         <f t="shared" si="2"/>
         <v>vs~0008</v>
       </c>
       <c r="C13" t="str">
         <f t="shared" si="3"/>
-        <v>tc-Y.df-N.ga-Y.dm-Hi.cp-95.CF1</v>
+        <v>tc-1.00.df-N.dm-Hi.cp-95.CF1</v>
       </c>
       <c r="H13" t="str">
+        <f>_xlfn.TEXTJOIN(".",TRUE,AC13,AB13:AB13)&amp;"."&amp;_xlfn.TEXTJOIN(".",TRUE,Y13:AA13)</f>
+        <v>tc-1.00.df-N.dm-Hi.cp-95.CF1</v>
+      </c>
+      <c r="I13" t="str">
         <f t="shared" si="4"/>
-        <v>tc-Y.df-N.ga-Y.dm-Hi.cp-95.CF1</v>
-      </c>
-      <c r="I13" t="str">
+        <v>Hi</v>
+      </c>
+      <c r="J13" t="str">
         <f t="shared" si="5"/>
-        <v>Hi</v>
-      </c>
-      <c r="J13" t="str">
+        <v>95</v>
+      </c>
+      <c r="K13" t="str">
         <f t="shared" si="6"/>
+        <v>CF1</v>
+      </c>
+      <c r="L13" t="str">
+        <f t="shared" si="7"/>
+        <v>N</v>
+      </c>
+      <c r="M13">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="O13">
+        <v>5</v>
+      </c>
+      <c r="P13" t="s">
+        <v>1115</v>
+      </c>
+      <c r="Q13">
+        <v>8</v>
+      </c>
+      <c r="R13" t="s">
+        <v>1094</v>
+      </c>
+      <c r="S13">
         <v>95</v>
       </c>
-      <c r="K13" t="str">
-        <f t="shared" si="7"/>
-        <v>CF1</v>
-      </c>
-      <c r="L13" t="str">
-        <f t="shared" si="8"/>
-        <v>N</v>
-      </c>
-      <c r="M13" t="str">
+      <c r="T13" t="s">
+        <v>1087</v>
+      </c>
+      <c r="U13" t="s">
+        <v>1095</v>
+      </c>
+      <c r="V13" t="s">
+        <v>1093</v>
+      </c>
+      <c r="W13">
+        <v>1</v>
+      </c>
+      <c r="Y13" t="str">
         <f t="shared" si="9"/>
-        <v>Y</v>
-      </c>
-      <c r="N13" t="str">
-        <f t="shared" si="9"/>
-        <v>Y</v>
-      </c>
-      <c r="P13">
-        <v>5</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>1108</v>
-      </c>
-      <c r="R13">
-        <v>8</v>
-      </c>
-      <c r="S13" t="s">
-        <v>1094</v>
-      </c>
-      <c r="T13">
-        <v>95</v>
-      </c>
-      <c r="U13" t="s">
-        <v>1087</v>
-      </c>
-      <c r="V13" t="s">
-        <v>1095</v>
-      </c>
-      <c r="W13" t="s">
-        <v>1093</v>
-      </c>
-      <c r="X13" t="s">
-        <v>1093</v>
+        <v>dm-Hi</v>
       </c>
       <c r="Z13" t="str">
         <f t="shared" si="10"/>
-        <v>dm-Hi</v>
+        <v>cp-95</v>
       </c>
       <c r="AA13" t="str">
         <f t="shared" si="11"/>
-        <v>cp-95</v>
+        <v>CF1</v>
       </c>
       <c r="AB13" t="str">
         <f t="shared" si="12"/>
-        <v>CF1</v>
+        <v>df-N</v>
       </c>
       <c r="AC13" t="str">
         <f t="shared" si="13"/>
-        <v>df-N</v>
-      </c>
-      <c r="AD13" t="str">
-        <f t="shared" si="14"/>
-        <v>ga-Y</v>
-      </c>
-      <c r="AE13" t="str">
-        <f t="shared" si="14"/>
-        <v>tc-Y</v>
-      </c>
-    </row>
-    <row r="14" spans="2:31">
+        <v>tc-1.00</v>
+      </c>
+    </row>
+    <row r="14" spans="2:29">
       <c r="B14" t="str">
         <f t="shared" si="2"/>
         <v>vs~0009</v>
       </c>
       <c r="C14" t="str">
         <f t="shared" si="3"/>
-        <v>tc-Y.df-Y.ga-Y.dm-Lo.cp-0.CF6</v>
+        <v>tc-1.00.df-Y.dm-Lo.cp-00.CF6</v>
       </c>
       <c r="H14" t="str">
+        <f>_xlfn.TEXTJOIN(".",TRUE,AC14,AB14:AB14)&amp;"."&amp;_xlfn.TEXTJOIN(".",TRUE,Y14:AA14)</f>
+        <v>tc-1.00.df-Y.dm-Lo.cp-00.CF6</v>
+      </c>
+      <c r="I14" t="str">
         <f t="shared" si="4"/>
-        <v>tc-Y.df-Y.ga-Y.dm-Lo.cp-0.CF6</v>
-      </c>
-      <c r="I14" t="str">
+        <v>Lo</v>
+      </c>
+      <c r="J14" t="str">
         <f t="shared" si="5"/>
-        <v>Lo</v>
-      </c>
-      <c r="J14" t="str">
+        <v>00</v>
+      </c>
+      <c r="K14" t="str">
         <f t="shared" si="6"/>
-        <v>00</v>
-      </c>
-      <c r="K14" t="str">
+        <v>CF6</v>
+      </c>
+      <c r="L14" t="str">
         <f t="shared" si="7"/>
-        <v>CF6</v>
-      </c>
-      <c r="L14" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M14">
         <f t="shared" si="8"/>
-        <v>Y</v>
-      </c>
-      <c r="M14" t="str">
-        <f t="shared" si="9"/>
-        <v>Y</v>
-      </c>
-      <c r="N14" t="str">
-        <f t="shared" si="9"/>
-        <v>Y</v>
-      </c>
-      <c r="P14">
+        <v>1</v>
+      </c>
+      <c r="O14">
         <v>5</v>
       </c>
-      <c r="Q14" t="s">
-        <v>1109</v>
-      </c>
-      <c r="R14">
+      <c r="P14" t="s">
+        <v>1116</v>
+      </c>
+      <c r="Q14">
         <v>9</v>
       </c>
-      <c r="S14" t="s">
+      <c r="R14" t="s">
         <v>1092</v>
       </c>
-      <c r="T14">
+      <c r="S14">
         <v>0</v>
       </c>
+      <c r="T14" t="s">
+        <v>1088</v>
+      </c>
       <c r="U14" t="s">
-        <v>1088</v>
+        <v>1093</v>
       </c>
       <c r="V14" t="s">
         <v>1093</v>
       </c>
-      <c r="W14" t="s">
-        <v>1093</v>
-      </c>
-      <c r="X14" t="s">
-        <v>1093</v>
+      <c r="W14">
+        <v>1</v>
+      </c>
+      <c r="Y14" t="str">
+        <f t="shared" si="9"/>
+        <v>dm-Lo</v>
       </c>
       <c r="Z14" t="str">
         <f t="shared" si="10"/>
-        <v>dm-Lo</v>
+        <v>cp-00</v>
       </c>
       <c r="AA14" t="str">
         <f t="shared" si="11"/>
-        <v>cp-0</v>
+        <v>CF6</v>
       </c>
       <c r="AB14" t="str">
         <f t="shared" si="12"/>
-        <v>CF6</v>
+        <v>df-Y</v>
       </c>
       <c r="AC14" t="str">
         <f t="shared" si="13"/>
-        <v>df-Y</v>
-      </c>
-      <c r="AD14" t="str">
-        <f t="shared" si="14"/>
-        <v>ga-Y</v>
-      </c>
-      <c r="AE14" t="str">
-        <f t="shared" si="14"/>
-        <v>tc-Y</v>
-      </c>
-    </row>
-    <row r="15" spans="2:31">
+        <v>tc-1.00</v>
+      </c>
+    </row>
+    <row r="15" spans="2:29">
       <c r="B15" t="str">
         <f t="shared" si="2"/>
         <v>vs~0010</v>
       </c>
       <c r="C15" t="str">
         <f t="shared" si="3"/>
-        <v>tc-Y.df-Y.ga-Y.dm-Hi.cp-0.CF6</v>
+        <v>tc-1.00.df-Y.dm-Hi.cp-00.CF6</v>
       </c>
       <c r="H15" t="str">
+        <f>_xlfn.TEXTJOIN(".",TRUE,AC15,AB15:AB15)&amp;"."&amp;_xlfn.TEXTJOIN(".",TRUE,Y15:AA15)</f>
+        <v>tc-1.00.df-Y.dm-Hi.cp-00.CF6</v>
+      </c>
+      <c r="I15" t="str">
         <f t="shared" si="4"/>
-        <v>tc-Y.df-Y.ga-Y.dm-Hi.cp-0.CF6</v>
-      </c>
-      <c r="I15" t="str">
+        <v>Hi</v>
+      </c>
+      <c r="J15" t="str">
         <f t="shared" si="5"/>
-        <v>Hi</v>
-      </c>
-      <c r="J15" t="str">
+        <v>00</v>
+      </c>
+      <c r="K15" t="str">
         <f t="shared" si="6"/>
-        <v>00</v>
-      </c>
-      <c r="K15" t="str">
+        <v>CF6</v>
+      </c>
+      <c r="L15" t="str">
         <f t="shared" si="7"/>
-        <v>CF6</v>
-      </c>
-      <c r="L15" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M15">
         <f t="shared" si="8"/>
-        <v>Y</v>
-      </c>
-      <c r="M15" t="str">
-        <f t="shared" si="9"/>
-        <v>Y</v>
-      </c>
-      <c r="N15" t="str">
-        <f t="shared" si="9"/>
-        <v>Y</v>
-      </c>
-      <c r="P15">
+        <v>1</v>
+      </c>
+      <c r="O15">
         <v>5</v>
       </c>
-      <c r="Q15" t="s">
-        <v>1110</v>
-      </c>
-      <c r="R15">
+      <c r="P15" t="s">
+        <v>1117</v>
+      </c>
+      <c r="Q15">
         <v>10</v>
       </c>
-      <c r="S15" t="s">
+      <c r="R15" t="s">
         <v>1094</v>
       </c>
-      <c r="T15">
+      <c r="S15">
         <v>0</v>
       </c>
+      <c r="T15" t="s">
+        <v>1088</v>
+      </c>
       <c r="U15" t="s">
-        <v>1088</v>
+        <v>1093</v>
       </c>
       <c r="V15" t="s">
         <v>1093</v>
       </c>
-      <c r="W15" t="s">
-        <v>1093</v>
-      </c>
-      <c r="X15" t="s">
-        <v>1093</v>
+      <c r="W15">
+        <v>1</v>
+      </c>
+      <c r="Y15" t="str">
+        <f t="shared" si="9"/>
+        <v>dm-Hi</v>
       </c>
       <c r="Z15" t="str">
         <f t="shared" si="10"/>
-        <v>dm-Hi</v>
+        <v>cp-00</v>
       </c>
       <c r="AA15" t="str">
         <f t="shared" si="11"/>
-        <v>cp-0</v>
+        <v>CF6</v>
       </c>
       <c r="AB15" t="str">
         <f t="shared" si="12"/>
-        <v>CF6</v>
+        <v>df-Y</v>
       </c>
       <c r="AC15" t="str">
         <f t="shared" si="13"/>
-        <v>df-Y</v>
-      </c>
-      <c r="AD15" t="str">
-        <f t="shared" si="14"/>
-        <v>ga-Y</v>
-      </c>
-      <c r="AE15" t="str">
-        <f t="shared" si="14"/>
-        <v>tc-Y</v>
-      </c>
-    </row>
-    <row r="16" spans="2:31">
+        <v>tc-1.00</v>
+      </c>
+    </row>
+    <row r="16" spans="2:29">
       <c r="B16" t="str">
         <f t="shared" si="2"/>
         <v>vs~0011</v>
       </c>
       <c r="C16" t="str">
         <f t="shared" si="3"/>
-        <v>tc-Y.df-Y.ga-Y.dm-Lo.cp-95.CF6</v>
+        <v>tc-1.00.df-Y.dm-Lo.cp-95.CF6</v>
       </c>
       <c r="H16" t="str">
+        <f>_xlfn.TEXTJOIN(".",TRUE,AC16,AB16:AB16)&amp;"."&amp;_xlfn.TEXTJOIN(".",TRUE,Y16:AA16)</f>
+        <v>tc-1.00.df-Y.dm-Lo.cp-95.CF6</v>
+      </c>
+      <c r="I16" t="str">
         <f t="shared" si="4"/>
-        <v>tc-Y.df-Y.ga-Y.dm-Lo.cp-95.CF6</v>
-      </c>
-      <c r="I16" t="str">
+        <v>Lo</v>
+      </c>
+      <c r="J16" t="str">
         <f t="shared" si="5"/>
-        <v>Lo</v>
-      </c>
-      <c r="J16" t="str">
+        <v>95</v>
+      </c>
+      <c r="K16" t="str">
         <f t="shared" si="6"/>
+        <v>CF6</v>
+      </c>
+      <c r="L16" t="str">
+        <f t="shared" si="7"/>
+        <v>Y</v>
+      </c>
+      <c r="M16">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="O16">
+        <v>5</v>
+      </c>
+      <c r="P16" t="s">
+        <v>1118</v>
+      </c>
+      <c r="Q16">
+        <v>11</v>
+      </c>
+      <c r="R16" t="s">
+        <v>1092</v>
+      </c>
+      <c r="S16">
         <v>95</v>
       </c>
-      <c r="K16" t="str">
-        <f t="shared" si="7"/>
-        <v>CF6</v>
-      </c>
-      <c r="L16" t="str">
-        <f t="shared" si="8"/>
-        <v>Y</v>
-      </c>
-      <c r="M16" t="str">
-        <f t="shared" si="9"/>
-        <v>Y</v>
-      </c>
-      <c r="N16" t="str">
-        <f t="shared" si="9"/>
-        <v>Y</v>
-      </c>
-      <c r="P16">
-        <v>5</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>1111</v>
-      </c>
-      <c r="R16">
-        <v>11</v>
-      </c>
-      <c r="S16" t="s">
-        <v>1092</v>
-      </c>
-      <c r="T16">
-        <v>95</v>
+      <c r="T16" t="s">
+        <v>1088</v>
       </c>
       <c r="U16" t="s">
-        <v>1088</v>
+        <v>1093</v>
       </c>
       <c r="V16" t="s">
         <v>1093</v>
       </c>
-      <c r="W16" t="s">
-        <v>1093</v>
-      </c>
-      <c r="X16" t="s">
-        <v>1093</v>
+      <c r="W16">
+        <v>1</v>
+      </c>
+      <c r="Y16" t="str">
+        <f t="shared" si="9"/>
+        <v>dm-Lo</v>
       </c>
       <c r="Z16" t="str">
         <f t="shared" si="10"/>
-        <v>dm-Lo</v>
+        <v>cp-95</v>
       </c>
       <c r="AA16" t="str">
         <f t="shared" si="11"/>
-        <v>cp-95</v>
+        <v>CF6</v>
       </c>
       <c r="AB16" t="str">
         <f t="shared" si="12"/>
-        <v>CF6</v>
+        <v>df-Y</v>
       </c>
       <c r="AC16" t="str">
         <f t="shared" si="13"/>
-        <v>df-Y</v>
-      </c>
-      <c r="AD16" t="str">
-        <f t="shared" si="14"/>
-        <v>ga-Y</v>
-      </c>
-      <c r="AE16" t="str">
-        <f t="shared" si="14"/>
-        <v>tc-Y</v>
-      </c>
-    </row>
-    <row r="17" spans="2:31">
+        <v>tc-1.00</v>
+      </c>
+    </row>
+    <row r="17" spans="2:29">
       <c r="B17" t="str">
         <f t="shared" si="2"/>
         <v>vs~0012</v>
       </c>
       <c r="C17" t="str">
         <f t="shared" si="3"/>
-        <v>tc-Y.df-Y.ga-Y.dm-Hi.cp-95.CF6</v>
+        <v>tc-1.00.df-Y.dm-Hi.cp-95.CF6</v>
       </c>
       <c r="H17" t="str">
+        <f>_xlfn.TEXTJOIN(".",TRUE,AC17,AB17:AB17)&amp;"."&amp;_xlfn.TEXTJOIN(".",TRUE,Y17:AA17)</f>
+        <v>tc-1.00.df-Y.dm-Hi.cp-95.CF6</v>
+      </c>
+      <c r="I17" t="str">
         <f t="shared" si="4"/>
-        <v>tc-Y.df-Y.ga-Y.dm-Hi.cp-95.CF6</v>
-      </c>
-      <c r="I17" t="str">
+        <v>Hi</v>
+      </c>
+      <c r="J17" t="str">
         <f t="shared" si="5"/>
-        <v>Hi</v>
-      </c>
-      <c r="J17" t="str">
+        <v>95</v>
+      </c>
+      <c r="K17" t="str">
         <f t="shared" si="6"/>
+        <v>CF6</v>
+      </c>
+      <c r="L17" t="str">
+        <f t="shared" si="7"/>
+        <v>Y</v>
+      </c>
+      <c r="M17">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="O17">
+        <v>5</v>
+      </c>
+      <c r="P17" t="s">
+        <v>1119</v>
+      </c>
+      <c r="Q17">
+        <v>12</v>
+      </c>
+      <c r="R17" t="s">
+        <v>1094</v>
+      </c>
+      <c r="S17">
         <v>95</v>
       </c>
-      <c r="K17" t="str">
-        <f t="shared" si="7"/>
-        <v>CF6</v>
-      </c>
-      <c r="L17" t="str">
-        <f t="shared" si="8"/>
-        <v>Y</v>
-      </c>
-      <c r="M17" t="str">
-        <f t="shared" si="9"/>
-        <v>Y</v>
-      </c>
-      <c r="N17" t="str">
-        <f t="shared" si="9"/>
-        <v>Y</v>
-      </c>
-      <c r="P17">
-        <v>5</v>
-      </c>
-      <c r="Q17" t="s">
-        <v>1112</v>
-      </c>
-      <c r="R17">
-        <v>12</v>
-      </c>
-      <c r="S17" t="s">
-        <v>1094</v>
-      </c>
-      <c r="T17">
-        <v>95</v>
+      <c r="T17" t="s">
+        <v>1088</v>
       </c>
       <c r="U17" t="s">
-        <v>1088</v>
+        <v>1093</v>
       </c>
       <c r="V17" t="s">
         <v>1093</v>
       </c>
-      <c r="W17" t="s">
-        <v>1093</v>
-      </c>
-      <c r="X17" t="s">
-        <v>1093</v>
+      <c r="W17">
+        <v>1</v>
+      </c>
+      <c r="Y17" t="str">
+        <f t="shared" si="9"/>
+        <v>dm-Hi</v>
       </c>
       <c r="Z17" t="str">
         <f t="shared" si="10"/>
-        <v>dm-Hi</v>
+        <v>cp-95</v>
       </c>
       <c r="AA17" t="str">
         <f t="shared" si="11"/>
-        <v>cp-95</v>
+        <v>CF6</v>
       </c>
       <c r="AB17" t="str">
         <f t="shared" si="12"/>
-        <v>CF6</v>
+        <v>df-Y</v>
       </c>
       <c r="AC17" t="str">
         <f t="shared" si="13"/>
-        <v>df-Y</v>
-      </c>
-      <c r="AD17" t="str">
-        <f t="shared" si="14"/>
-        <v>ga-Y</v>
-      </c>
-      <c r="AE17" t="str">
-        <f t="shared" si="14"/>
-        <v>tc-Y</v>
-      </c>
-    </row>
-    <row r="18" spans="2:31">
+        <v>tc-1.00</v>
+      </c>
+    </row>
+    <row r="18" spans="2:29">
       <c r="B18" t="str">
-        <f t="shared" ref="B18:B37" si="15">"vs~"&amp;TEXT(R18,"0000")</f>
+        <f t="shared" ref="B18:B37" si="14">"vs~"&amp;TEXT(Q18,"0000")</f>
         <v>vs~0013</v>
       </c>
       <c r="C18" t="str">
-        <f t="shared" ref="C18:C37" si="16">H18</f>
-        <v>tc-Y.df-N.ga-Y.dm-Lo.cp-0.CF6</v>
+        <f t="shared" ref="C18:C37" si="15">H18</f>
+        <v>tc-1.00.df-N.dm-Lo.cp-00.CF6</v>
       </c>
       <c r="H18" t="str">
+        <f>_xlfn.TEXTJOIN(".",TRUE,AC18,AB18:AB18)&amp;"."&amp;_xlfn.TEXTJOIN(".",TRUE,Y18:AA18)</f>
+        <v>tc-1.00.df-N.dm-Lo.cp-00.CF6</v>
+      </c>
+      <c r="I18" t="str">
         <f t="shared" si="4"/>
-        <v>tc-Y.df-N.ga-Y.dm-Lo.cp-0.CF6</v>
-      </c>
-      <c r="I18" t="str">
+        <v>Lo</v>
+      </c>
+      <c r="J18" t="str">
         <f t="shared" si="5"/>
-        <v>Lo</v>
-      </c>
-      <c r="J18" t="str">
+        <v>00</v>
+      </c>
+      <c r="K18" t="str">
         <f t="shared" si="6"/>
-        <v>00</v>
-      </c>
-      <c r="K18" t="str">
+        <v>CF6</v>
+      </c>
+      <c r="L18" t="str">
         <f t="shared" si="7"/>
-        <v>CF6</v>
-      </c>
-      <c r="L18" t="str">
+        <v>N</v>
+      </c>
+      <c r="M18">
         <f t="shared" si="8"/>
-        <v>N</v>
-      </c>
-      <c r="M18" t="str">
+        <v>1</v>
+      </c>
+      <c r="O18">
+        <v>5</v>
+      </c>
+      <c r="P18" t="s">
+        <v>1120</v>
+      </c>
+      <c r="Q18">
+        <v>13</v>
+      </c>
+      <c r="R18" t="s">
+        <v>1092</v>
+      </c>
+      <c r="S18">
+        <v>0</v>
+      </c>
+      <c r="T18" t="s">
+        <v>1088</v>
+      </c>
+      <c r="U18" t="s">
+        <v>1095</v>
+      </c>
+      <c r="V18" t="s">
+        <v>1093</v>
+      </c>
+      <c r="W18">
+        <v>1</v>
+      </c>
+      <c r="Y18" t="str">
         <f t="shared" si="9"/>
-        <v>Y</v>
-      </c>
-      <c r="N18" t="str">
-        <f t="shared" si="9"/>
-        <v>Y</v>
-      </c>
-      <c r="P18">
-        <v>5</v>
-      </c>
-      <c r="Q18" t="s">
-        <v>1113</v>
-      </c>
-      <c r="R18">
-        <v>13</v>
-      </c>
-      <c r="S18" t="s">
-        <v>1092</v>
-      </c>
-      <c r="T18">
-        <v>0</v>
-      </c>
-      <c r="U18" t="s">
-        <v>1088</v>
-      </c>
-      <c r="V18" t="s">
-        <v>1095</v>
-      </c>
-      <c r="W18" t="s">
-        <v>1093</v>
-      </c>
-      <c r="X18" t="s">
-        <v>1093</v>
+        <v>dm-Lo</v>
       </c>
       <c r="Z18" t="str">
         <f t="shared" si="10"/>
-        <v>dm-Lo</v>
+        <v>cp-00</v>
       </c>
       <c r="AA18" t="str">
         <f t="shared" si="11"/>
-        <v>cp-0</v>
+        <v>CF6</v>
       </c>
       <c r="AB18" t="str">
         <f t="shared" si="12"/>
-        <v>CF6</v>
+        <v>df-N</v>
       </c>
       <c r="AC18" t="str">
         <f t="shared" si="13"/>
-        <v>df-N</v>
-      </c>
-      <c r="AD18" t="str">
+        <v>tc-1.00</v>
+      </c>
+    </row>
+    <row r="19" spans="2:29">
+      <c r="B19" t="str">
         <f t="shared" si="14"/>
-        <v>ga-Y</v>
-      </c>
-      <c r="AE18" t="str">
-        <f t="shared" si="14"/>
-        <v>tc-Y</v>
-      </c>
-    </row>
-    <row r="19" spans="2:31">
-      <c r="B19" t="str">
+        <v>vs~0014</v>
+      </c>
+      <c r="C19" t="str">
         <f t="shared" si="15"/>
-        <v>vs~0014</v>
-      </c>
-      <c r="C19" t="str">
-        <f t="shared" si="16"/>
-        <v>tc-Y.df-N.ga-Y.dm-Hi.cp-0.CF6</v>
+        <v>tc-1.00.df-N.dm-Hi.cp-00.CF6</v>
       </c>
       <c r="H19" t="str">
+        <f>_xlfn.TEXTJOIN(".",TRUE,AC19,AB19:AB19)&amp;"."&amp;_xlfn.TEXTJOIN(".",TRUE,Y19:AA19)</f>
+        <v>tc-1.00.df-N.dm-Hi.cp-00.CF6</v>
+      </c>
+      <c r="I19" t="str">
         <f t="shared" si="4"/>
-        <v>tc-Y.df-N.ga-Y.dm-Hi.cp-0.CF6</v>
-      </c>
-      <c r="I19" t="str">
+        <v>Hi</v>
+      </c>
+      <c r="J19" t="str">
         <f t="shared" si="5"/>
-        <v>Hi</v>
-      </c>
-      <c r="J19" t="str">
+        <v>00</v>
+      </c>
+      <c r="K19" t="str">
         <f t="shared" si="6"/>
-        <v>00</v>
-      </c>
-      <c r="K19" t="str">
+        <v>CF6</v>
+      </c>
+      <c r="L19" t="str">
         <f t="shared" si="7"/>
-        <v>CF6</v>
-      </c>
-      <c r="L19" t="str">
+        <v>N</v>
+      </c>
+      <c r="M19">
         <f t="shared" si="8"/>
-        <v>N</v>
-      </c>
-      <c r="M19" t="str">
+        <v>1</v>
+      </c>
+      <c r="O19">
+        <v>5</v>
+      </c>
+      <c r="P19" t="s">
+        <v>1121</v>
+      </c>
+      <c r="Q19">
+        <v>14</v>
+      </c>
+      <c r="R19" t="s">
+        <v>1094</v>
+      </c>
+      <c r="S19">
+        <v>0</v>
+      </c>
+      <c r="T19" t="s">
+        <v>1088</v>
+      </c>
+      <c r="U19" t="s">
+        <v>1095</v>
+      </c>
+      <c r="V19" t="s">
+        <v>1093</v>
+      </c>
+      <c r="W19">
+        <v>1</v>
+      </c>
+      <c r="Y19" t="str">
         <f t="shared" si="9"/>
-        <v>Y</v>
-      </c>
-      <c r="N19" t="str">
-        <f t="shared" si="9"/>
-        <v>Y</v>
-      </c>
-      <c r="P19">
-        <v>5</v>
-      </c>
-      <c r="Q19" t="s">
-        <v>1114</v>
-      </c>
-      <c r="R19">
-        <v>14</v>
-      </c>
-      <c r="S19" t="s">
-        <v>1094</v>
-      </c>
-      <c r="T19">
-        <v>0</v>
-      </c>
-      <c r="U19" t="s">
-        <v>1088</v>
-      </c>
-      <c r="V19" t="s">
-        <v>1095</v>
-      </c>
-      <c r="W19" t="s">
-        <v>1093</v>
-      </c>
-      <c r="X19" t="s">
-        <v>1093</v>
+        <v>dm-Hi</v>
       </c>
       <c r="Z19" t="str">
         <f t="shared" si="10"/>
-        <v>dm-Hi</v>
+        <v>cp-00</v>
       </c>
       <c r="AA19" t="str">
         <f t="shared" si="11"/>
-        <v>cp-0</v>
+        <v>CF6</v>
       </c>
       <c r="AB19" t="str">
         <f t="shared" si="12"/>
-        <v>CF6</v>
+        <v>df-N</v>
       </c>
       <c r="AC19" t="str">
         <f t="shared" si="13"/>
-        <v>df-N</v>
-      </c>
-      <c r="AD19" t="str">
+        <v>tc-1.00</v>
+      </c>
+    </row>
+    <row r="20" spans="2:29">
+      <c r="B20" t="str">
         <f t="shared" si="14"/>
-        <v>ga-Y</v>
-      </c>
-      <c r="AE19" t="str">
-        <f t="shared" si="14"/>
-        <v>tc-Y</v>
-      </c>
-    </row>
-    <row r="20" spans="2:31">
-      <c r="B20" t="str">
+        <v>vs~0015</v>
+      </c>
+      <c r="C20" t="str">
         <f t="shared" si="15"/>
-        <v>vs~0015</v>
-      </c>
-      <c r="C20" t="str">
-        <f t="shared" si="16"/>
-        <v>tc-Y.df-N.ga-Y.dm-Lo.cp-95.CF6</v>
+        <v>tc-1.00.df-N.dm-Lo.cp-95.CF6</v>
       </c>
       <c r="H20" t="str">
+        <f>_xlfn.TEXTJOIN(".",TRUE,AC20,AB20:AB20)&amp;"."&amp;_xlfn.TEXTJOIN(".",TRUE,Y20:AA20)</f>
+        <v>tc-1.00.df-N.dm-Lo.cp-95.CF6</v>
+      </c>
+      <c r="I20" t="str">
         <f t="shared" si="4"/>
-        <v>tc-Y.df-N.ga-Y.dm-Lo.cp-95.CF6</v>
-      </c>
-      <c r="I20" t="str">
+        <v>Lo</v>
+      </c>
+      <c r="J20" t="str">
         <f t="shared" si="5"/>
-        <v>Lo</v>
-      </c>
-      <c r="J20" t="str">
+        <v>95</v>
+      </c>
+      <c r="K20" t="str">
         <f t="shared" si="6"/>
+        <v>CF6</v>
+      </c>
+      <c r="L20" t="str">
+        <f t="shared" si="7"/>
+        <v>N</v>
+      </c>
+      <c r="M20">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="O20">
+        <v>5</v>
+      </c>
+      <c r="P20" t="s">
+        <v>1122</v>
+      </c>
+      <c r="Q20">
+        <v>15</v>
+      </c>
+      <c r="R20" t="s">
+        <v>1092</v>
+      </c>
+      <c r="S20">
         <v>95</v>
       </c>
-      <c r="K20" t="str">
-        <f t="shared" si="7"/>
-        <v>CF6</v>
-      </c>
-      <c r="L20" t="str">
-        <f t="shared" si="8"/>
-        <v>N</v>
-      </c>
-      <c r="M20" t="str">
+      <c r="T20" t="s">
+        <v>1088</v>
+      </c>
+      <c r="U20" t="s">
+        <v>1095</v>
+      </c>
+      <c r="V20" t="s">
+        <v>1093</v>
+      </c>
+      <c r="W20">
+        <v>1</v>
+      </c>
+      <c r="Y20" t="str">
         <f t="shared" si="9"/>
-        <v>Y</v>
-      </c>
-      <c r="N20" t="str">
-        <f t="shared" si="9"/>
-        <v>Y</v>
-      </c>
-      <c r="P20">
-        <v>5</v>
-      </c>
-      <c r="Q20" t="s">
-        <v>1115</v>
-      </c>
-      <c r="R20">
-        <v>15</v>
-      </c>
-      <c r="S20" t="s">
-        <v>1092</v>
-      </c>
-      <c r="T20">
-        <v>95</v>
-      </c>
-      <c r="U20" t="s">
-        <v>1088</v>
-      </c>
-      <c r="V20" t="s">
-        <v>1095</v>
-      </c>
-      <c r="W20" t="s">
-        <v>1093</v>
-      </c>
-      <c r="X20" t="s">
-        <v>1093</v>
+        <v>dm-Lo</v>
       </c>
       <c r="Z20" t="str">
         <f t="shared" si="10"/>
-        <v>dm-Lo</v>
+        <v>cp-95</v>
       </c>
       <c r="AA20" t="str">
         <f t="shared" si="11"/>
-        <v>cp-95</v>
+        <v>CF6</v>
       </c>
       <c r="AB20" t="str">
         <f t="shared" si="12"/>
-        <v>CF6</v>
+        <v>df-N</v>
       </c>
       <c r="AC20" t="str">
         <f t="shared" si="13"/>
-        <v>df-N</v>
-      </c>
-      <c r="AD20" t="str">
+        <v>tc-1.00</v>
+      </c>
+    </row>
+    <row r="21" spans="2:29">
+      <c r="B21" t="str">
         <f t="shared" si="14"/>
-        <v>ga-Y</v>
-      </c>
-      <c r="AE20" t="str">
-        <f t="shared" si="14"/>
-        <v>tc-Y</v>
-      </c>
-    </row>
-    <row r="21" spans="2:31">
-      <c r="B21" t="str">
+        <v>vs~0016</v>
+      </c>
+      <c r="C21" t="str">
         <f t="shared" si="15"/>
-        <v>vs~0016</v>
-      </c>
-      <c r="C21" t="str">
-        <f t="shared" si="16"/>
-        <v>tc-Y.df-N.ga-Y.dm-Hi.cp-95.CF6</v>
+        <v>tc-1.00.df-N.dm-Hi.cp-95.CF6</v>
       </c>
       <c r="H21" t="str">
+        <f>_xlfn.TEXTJOIN(".",TRUE,AC21,AB21:AB21)&amp;"."&amp;_xlfn.TEXTJOIN(".",TRUE,Y21:AA21)</f>
+        <v>tc-1.00.df-N.dm-Hi.cp-95.CF6</v>
+      </c>
+      <c r="I21" t="str">
         <f t="shared" si="4"/>
-        <v>tc-Y.df-N.ga-Y.dm-Hi.cp-95.CF6</v>
-      </c>
-      <c r="I21" t="str">
+        <v>Hi</v>
+      </c>
+      <c r="J21" t="str">
         <f t="shared" si="5"/>
-        <v>Hi</v>
-      </c>
-      <c r="J21" t="str">
+        <v>95</v>
+      </c>
+      <c r="K21" t="str">
         <f t="shared" si="6"/>
+        <v>CF6</v>
+      </c>
+      <c r="L21" t="str">
+        <f t="shared" si="7"/>
+        <v>N</v>
+      </c>
+      <c r="M21">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="O21">
+        <v>5</v>
+      </c>
+      <c r="P21" t="s">
+        <v>1123</v>
+      </c>
+      <c r="Q21">
+        <v>16</v>
+      </c>
+      <c r="R21" t="s">
+        <v>1094</v>
+      </c>
+      <c r="S21">
         <v>95</v>
       </c>
-      <c r="K21" t="str">
-        <f t="shared" si="7"/>
-        <v>CF6</v>
-      </c>
-      <c r="L21" t="str">
-        <f t="shared" si="8"/>
-        <v>N</v>
-      </c>
-      <c r="M21" t="str">
+      <c r="T21" t="s">
+        <v>1088</v>
+      </c>
+      <c r="U21" t="s">
+        <v>1095</v>
+      </c>
+      <c r="V21" t="s">
+        <v>1093</v>
+      </c>
+      <c r="W21">
+        <v>1</v>
+      </c>
+      <c r="Y21" t="str">
         <f t="shared" si="9"/>
-        <v>Y</v>
-      </c>
-      <c r="N21" t="str">
-        <f t="shared" si="9"/>
-        <v>Y</v>
-      </c>
-      <c r="P21">
-        <v>5</v>
-      </c>
-      <c r="Q21" t="s">
-        <v>1116</v>
-      </c>
-      <c r="R21">
-        <v>16</v>
-      </c>
-      <c r="S21" t="s">
-        <v>1094</v>
-      </c>
-      <c r="T21">
-        <v>95</v>
-      </c>
-      <c r="U21" t="s">
-        <v>1088</v>
-      </c>
-      <c r="V21" t="s">
-        <v>1095</v>
-      </c>
-      <c r="W21" t="s">
-        <v>1093</v>
-      </c>
-      <c r="X21" t="s">
-        <v>1093</v>
+        <v>dm-Hi</v>
       </c>
       <c r="Z21" t="str">
         <f t="shared" si="10"/>
-        <v>dm-Hi</v>
+        <v>cp-95</v>
       </c>
       <c r="AA21" t="str">
         <f t="shared" si="11"/>
-        <v>cp-95</v>
+        <v>CF6</v>
       </c>
       <c r="AB21" t="str">
         <f t="shared" si="12"/>
-        <v>CF6</v>
+        <v>df-N</v>
       </c>
       <c r="AC21" t="str">
         <f t="shared" si="13"/>
-        <v>df-N</v>
-      </c>
-      <c r="AD21" t="str">
+        <v>tc-1.00</v>
+      </c>
+    </row>
+    <row r="22" spans="2:29">
+      <c r="B22" t="str">
         <f t="shared" si="14"/>
-        <v>ga-Y</v>
-      </c>
-      <c r="AE21" t="str">
-        <f t="shared" si="14"/>
-        <v>tc-Y</v>
-      </c>
-    </row>
-    <row r="22" spans="2:31">
-      <c r="B22" t="str">
+        <v>vs~0017</v>
+      </c>
+      <c r="C22" t="str">
         <f t="shared" si="15"/>
-        <v>vs~0017</v>
-      </c>
-      <c r="C22" t="str">
-        <f t="shared" si="16"/>
-        <v>tc-Y.df-Y.ga-N.dm-Lo.cp-0.CF1</v>
+        <v>tc-0.25.df-Y.dm-Lo.cp-00.CF1</v>
       </c>
       <c r="H22" t="str">
+        <f>_xlfn.TEXTJOIN(".",TRUE,AC22,AB22:AB22)&amp;"."&amp;_xlfn.TEXTJOIN(".",TRUE,Y22:AA22)</f>
+        <v>tc-0.25.df-Y.dm-Lo.cp-00.CF1</v>
+      </c>
+      <c r="I22" t="str">
         <f t="shared" si="4"/>
-        <v>tc-Y.df-Y.ga-N.dm-Lo.cp-0.CF1</v>
-      </c>
-      <c r="I22" t="str">
+        <v>Lo</v>
+      </c>
+      <c r="J22" t="str">
         <f t="shared" si="5"/>
-        <v>Lo</v>
-      </c>
-      <c r="J22" t="str">
+        <v>00</v>
+      </c>
+      <c r="K22" t="str">
         <f t="shared" si="6"/>
-        <v>00</v>
-      </c>
-      <c r="K22" t="str">
+        <v>CF1</v>
+      </c>
+      <c r="L22" t="str">
         <f t="shared" si="7"/>
-        <v>CF1</v>
-      </c>
-      <c r="L22" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M22">
         <f t="shared" si="8"/>
-        <v>Y</v>
-      </c>
-      <c r="M22" t="str">
-        <f t="shared" si="9"/>
-        <v>N</v>
-      </c>
-      <c r="N22" t="str">
-        <f t="shared" si="9"/>
-        <v>Y</v>
-      </c>
-      <c r="P22">
+        <v>0.25</v>
+      </c>
+      <c r="O22">
         <v>5</v>
       </c>
-      <c r="Q22" t="s">
-        <v>1117</v>
-      </c>
-      <c r="R22">
+      <c r="P22" t="s">
+        <v>1124</v>
+      </c>
+      <c r="Q22">
         <v>17</v>
       </c>
-      <c r="S22" t="s">
+      <c r="R22" t="s">
         <v>1092</v>
       </c>
-      <c r="T22">
+      <c r="S22">
         <v>0</v>
       </c>
+      <c r="T22" t="s">
+        <v>1087</v>
+      </c>
       <c r="U22" t="s">
-        <v>1087</v>
+        <v>1093</v>
       </c>
       <c r="V22" t="s">
         <v>1093</v>
       </c>
-      <c r="W22" t="s">
-        <v>1095</v>
-      </c>
-      <c r="X22" t="s">
-        <v>1093</v>
+      <c r="W22">
+        <v>0.25</v>
+      </c>
+      <c r="Y22" t="str">
+        <f t="shared" si="9"/>
+        <v>dm-Lo</v>
       </c>
       <c r="Z22" t="str">
         <f t="shared" si="10"/>
-        <v>dm-Lo</v>
+        <v>cp-00</v>
       </c>
       <c r="AA22" t="str">
         <f t="shared" si="11"/>
-        <v>cp-0</v>
+        <v>CF1</v>
       </c>
       <c r="AB22" t="str">
         <f t="shared" si="12"/>
-        <v>CF1</v>
+        <v>df-Y</v>
       </c>
       <c r="AC22" t="str">
         <f t="shared" si="13"/>
-        <v>df-Y</v>
-      </c>
-      <c r="AD22" t="str">
+        <v>tc-0.25</v>
+      </c>
+    </row>
+    <row r="23" spans="2:29">
+      <c r="B23" t="str">
         <f t="shared" si="14"/>
-        <v>ga-N</v>
-      </c>
-      <c r="AE22" t="str">
-        <f t="shared" si="14"/>
-        <v>tc-Y</v>
-      </c>
-    </row>
-    <row r="23" spans="2:31">
-      <c r="B23" t="str">
+        <v>vs~0018</v>
+      </c>
+      <c r="C23" t="str">
         <f t="shared" si="15"/>
-        <v>vs~0018</v>
-      </c>
-      <c r="C23" t="str">
-        <f t="shared" si="16"/>
-        <v>tc-Y.df-Y.ga-N.dm-Hi.cp-0.CF1</v>
+        <v>tc-0.25.df-Y.dm-Hi.cp-00.CF1</v>
       </c>
       <c r="H23" t="str">
+        <f>_xlfn.TEXTJOIN(".",TRUE,AC23,AB23:AB23)&amp;"."&amp;_xlfn.TEXTJOIN(".",TRUE,Y23:AA23)</f>
+        <v>tc-0.25.df-Y.dm-Hi.cp-00.CF1</v>
+      </c>
+      <c r="I23" t="str">
         <f t="shared" si="4"/>
-        <v>tc-Y.df-Y.ga-N.dm-Hi.cp-0.CF1</v>
-      </c>
-      <c r="I23" t="str">
+        <v>Hi</v>
+      </c>
+      <c r="J23" t="str">
         <f t="shared" si="5"/>
-        <v>Hi</v>
-      </c>
-      <c r="J23" t="str">
+        <v>00</v>
+      </c>
+      <c r="K23" t="str">
         <f t="shared" si="6"/>
-        <v>00</v>
-      </c>
-      <c r="K23" t="str">
+        <v>CF1</v>
+      </c>
+      <c r="L23" t="str">
         <f t="shared" si="7"/>
-        <v>CF1</v>
-      </c>
-      <c r="L23" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M23">
         <f t="shared" si="8"/>
-        <v>Y</v>
-      </c>
-      <c r="M23" t="str">
-        <f t="shared" si="9"/>
-        <v>N</v>
-      </c>
-      <c r="N23" t="str">
-        <f t="shared" si="9"/>
-        <v>Y</v>
-      </c>
-      <c r="P23">
+        <v>0.25</v>
+      </c>
+      <c r="O23">
         <v>5</v>
       </c>
-      <c r="Q23" t="s">
-        <v>1118</v>
-      </c>
-      <c r="R23">
+      <c r="P23" t="s">
+        <v>1125</v>
+      </c>
+      <c r="Q23">
         <v>18</v>
       </c>
-      <c r="S23" t="s">
+      <c r="R23" t="s">
         <v>1094</v>
       </c>
-      <c r="T23">
+      <c r="S23">
         <v>0</v>
       </c>
+      <c r="T23" t="s">
+        <v>1087</v>
+      </c>
       <c r="U23" t="s">
-        <v>1087</v>
+        <v>1093</v>
       </c>
       <c r="V23" t="s">
         <v>1093</v>
       </c>
-      <c r="W23" t="s">
-        <v>1095</v>
-      </c>
-      <c r="X23" t="s">
-        <v>1093</v>
+      <c r="W23">
+        <v>0.25</v>
+      </c>
+      <c r="Y23" t="str">
+        <f t="shared" si="9"/>
+        <v>dm-Hi</v>
       </c>
       <c r="Z23" t="str">
         <f t="shared" si="10"/>
-        <v>dm-Hi</v>
+        <v>cp-00</v>
       </c>
       <c r="AA23" t="str">
         <f t="shared" si="11"/>
-        <v>cp-0</v>
+        <v>CF1</v>
       </c>
       <c r="AB23" t="str">
         <f t="shared" si="12"/>
-        <v>CF1</v>
+        <v>df-Y</v>
       </c>
       <c r="AC23" t="str">
         <f t="shared" si="13"/>
-        <v>df-Y</v>
-      </c>
-      <c r="AD23" t="str">
+        <v>tc-0.25</v>
+      </c>
+    </row>
+    <row r="24" spans="2:29">
+      <c r="B24" t="str">
         <f t="shared" si="14"/>
-        <v>ga-N</v>
-      </c>
-      <c r="AE23" t="str">
-        <f t="shared" si="14"/>
-        <v>tc-Y</v>
-      </c>
-    </row>
-    <row r="24" spans="2:31">
-      <c r="B24" t="str">
+        <v>vs~0019</v>
+      </c>
+      <c r="C24" t="str">
         <f t="shared" si="15"/>
-        <v>vs~0019</v>
-      </c>
-      <c r="C24" t="str">
-        <f t="shared" si="16"/>
-        <v>tc-Y.df-Y.ga-N.dm-Lo.cp-95.CF1</v>
+        <v>tc-0.25.df-Y.dm-Lo.cp-95.CF1</v>
       </c>
       <c r="H24" t="str">
+        <f>_xlfn.TEXTJOIN(".",TRUE,AC24,AB24:AB24)&amp;"."&amp;_xlfn.TEXTJOIN(".",TRUE,Y24:AA24)</f>
+        <v>tc-0.25.df-Y.dm-Lo.cp-95.CF1</v>
+      </c>
+      <c r="I24" t="str">
         <f t="shared" si="4"/>
-        <v>tc-Y.df-Y.ga-N.dm-Lo.cp-95.CF1</v>
-      </c>
-      <c r="I24" t="str">
+        <v>Lo</v>
+      </c>
+      <c r="J24" t="str">
         <f t="shared" si="5"/>
-        <v>Lo</v>
-      </c>
-      <c r="J24" t="str">
+        <v>95</v>
+      </c>
+      <c r="K24" t="str">
         <f t="shared" si="6"/>
+        <v>CF1</v>
+      </c>
+      <c r="L24" t="str">
+        <f t="shared" si="7"/>
+        <v>Y</v>
+      </c>
+      <c r="M24">
+        <f t="shared" si="8"/>
+        <v>0.25</v>
+      </c>
+      <c r="O24">
+        <v>5</v>
+      </c>
+      <c r="P24" t="s">
+        <v>1126</v>
+      </c>
+      <c r="Q24">
+        <v>19</v>
+      </c>
+      <c r="R24" t="s">
+        <v>1092</v>
+      </c>
+      <c r="S24">
         <v>95</v>
       </c>
-      <c r="K24" t="str">
-        <f t="shared" si="7"/>
-        <v>CF1</v>
-      </c>
-      <c r="L24" t="str">
-        <f t="shared" si="8"/>
-        <v>Y</v>
-      </c>
-      <c r="M24" t="str">
-        <f t="shared" si="9"/>
-        <v>N</v>
-      </c>
-      <c r="N24" t="str">
-        <f t="shared" si="9"/>
-        <v>Y</v>
-      </c>
-      <c r="P24">
-        <v>5</v>
-      </c>
-      <c r="Q24" t="s">
-        <v>1119</v>
-      </c>
-      <c r="R24">
-        <v>19</v>
-      </c>
-      <c r="S24" t="s">
-        <v>1092</v>
-      </c>
-      <c r="T24">
-        <v>95</v>
+      <c r="T24" t="s">
+        <v>1087</v>
       </c>
       <c r="U24" t="s">
-        <v>1087</v>
+        <v>1093</v>
       </c>
       <c r="V24" t="s">
         <v>1093</v>
       </c>
-      <c r="W24" t="s">
-        <v>1095</v>
-      </c>
-      <c r="X24" t="s">
-        <v>1093</v>
+      <c r="W24">
+        <v>0.25</v>
+      </c>
+      <c r="Y24" t="str">
+        <f t="shared" si="9"/>
+        <v>dm-Lo</v>
       </c>
       <c r="Z24" t="str">
         <f t="shared" si="10"/>
-        <v>dm-Lo</v>
+        <v>cp-95</v>
       </c>
       <c r="AA24" t="str">
         <f t="shared" si="11"/>
-        <v>cp-95</v>
+        <v>CF1</v>
       </c>
       <c r="AB24" t="str">
         <f t="shared" si="12"/>
-        <v>CF1</v>
+        <v>df-Y</v>
       </c>
       <c r="AC24" t="str">
         <f t="shared" si="13"/>
-        <v>df-Y</v>
-      </c>
-      <c r="AD24" t="str">
+        <v>tc-0.25</v>
+      </c>
+    </row>
+    <row r="25" spans="2:29">
+      <c r="B25" t="str">
         <f t="shared" si="14"/>
-        <v>ga-N</v>
-      </c>
-      <c r="AE24" t="str">
-        <f t="shared" si="14"/>
-        <v>tc-Y</v>
-      </c>
-    </row>
-    <row r="25" spans="2:31">
-      <c r="B25" t="str">
+        <v>vs~0020</v>
+      </c>
+      <c r="C25" t="str">
         <f t="shared" si="15"/>
-        <v>vs~0020</v>
-      </c>
-      <c r="C25" t="str">
-        <f t="shared" si="16"/>
-        <v>tc-Y.df-Y.ga-N.dm-Hi.cp-95.CF1</v>
+        <v>tc-0.25.df-Y.dm-Hi.cp-95.CF1</v>
       </c>
       <c r="H25" t="str">
+        <f>_xlfn.TEXTJOIN(".",TRUE,AC25,AB25:AB25)&amp;"."&amp;_xlfn.TEXTJOIN(".",TRUE,Y25:AA25)</f>
+        <v>tc-0.25.df-Y.dm-Hi.cp-95.CF1</v>
+      </c>
+      <c r="I25" t="str">
         <f t="shared" si="4"/>
-        <v>tc-Y.df-Y.ga-N.dm-Hi.cp-95.CF1</v>
-      </c>
-      <c r="I25" t="str">
+        <v>Hi</v>
+      </c>
+      <c r="J25" t="str">
         <f t="shared" si="5"/>
-        <v>Hi</v>
-      </c>
-      <c r="J25" t="str">
+        <v>95</v>
+      </c>
+      <c r="K25" t="str">
         <f t="shared" si="6"/>
+        <v>CF1</v>
+      </c>
+      <c r="L25" t="str">
+        <f t="shared" si="7"/>
+        <v>Y</v>
+      </c>
+      <c r="M25">
+        <f t="shared" si="8"/>
+        <v>0.25</v>
+      </c>
+      <c r="O25">
+        <v>5</v>
+      </c>
+      <c r="P25" t="s">
+        <v>1127</v>
+      </c>
+      <c r="Q25">
+        <v>20</v>
+      </c>
+      <c r="R25" t="s">
+        <v>1094</v>
+      </c>
+      <c r="S25">
         <v>95</v>
       </c>
-      <c r="K25" t="str">
-        <f t="shared" si="7"/>
-        <v>CF1</v>
-      </c>
-      <c r="L25" t="str">
-        <f t="shared" si="8"/>
-        <v>Y</v>
-      </c>
-      <c r="M25" t="str">
-        <f t="shared" si="9"/>
-        <v>N</v>
-      </c>
-      <c r="N25" t="str">
-        <f t="shared" si="9"/>
-        <v>Y</v>
-      </c>
-      <c r="P25">
-        <v>5</v>
-      </c>
-      <c r="Q25" t="s">
-        <v>1120</v>
-      </c>
-      <c r="R25">
-        <v>20</v>
-      </c>
-      <c r="S25" t="s">
-        <v>1094</v>
-      </c>
-      <c r="T25">
-        <v>95</v>
+      <c r="T25" t="s">
+        <v>1087</v>
       </c>
       <c r="U25" t="s">
-        <v>1087</v>
+        <v>1093</v>
       </c>
       <c r="V25" t="s">
         <v>1093</v>
       </c>
-      <c r="W25" t="s">
-        <v>1095</v>
-      </c>
-      <c r="X25" t="s">
-        <v>1093</v>
+      <c r="W25">
+        <v>0.25</v>
+      </c>
+      <c r="Y25" t="str">
+        <f t="shared" si="9"/>
+        <v>dm-Hi</v>
       </c>
       <c r="Z25" t="str">
         <f t="shared" si="10"/>
-        <v>dm-Hi</v>
+        <v>cp-95</v>
       </c>
       <c r="AA25" t="str">
         <f t="shared" si="11"/>
-        <v>cp-95</v>
+        <v>CF1</v>
       </c>
       <c r="AB25" t="str">
         <f t="shared" si="12"/>
-        <v>CF1</v>
+        <v>df-Y</v>
       </c>
       <c r="AC25" t="str">
         <f t="shared" si="13"/>
-        <v>df-Y</v>
-      </c>
-      <c r="AD25" t="str">
+        <v>tc-0.25</v>
+      </c>
+    </row>
+    <row r="26" spans="2:29">
+      <c r="B26" t="str">
         <f t="shared" si="14"/>
-        <v>ga-N</v>
-      </c>
-      <c r="AE25" t="str">
-        <f t="shared" si="14"/>
-        <v>tc-Y</v>
-      </c>
-    </row>
-    <row r="26" spans="2:31">
-      <c r="B26" t="str">
+        <v>vs~0021</v>
+      </c>
+      <c r="C26" t="str">
         <f t="shared" si="15"/>
-        <v>vs~0021</v>
-      </c>
-      <c r="C26" t="str">
-        <f t="shared" si="16"/>
-        <v>tc-Y.df-N.ga-N.dm-Lo.cp-0.CF1</v>
+        <v>tc-0.25.df-N.dm-Lo.cp-00.CF1</v>
       </c>
       <c r="H26" t="str">
+        <f>_xlfn.TEXTJOIN(".",TRUE,AC26,AB26:AB26)&amp;"."&amp;_xlfn.TEXTJOIN(".",TRUE,Y26:AA26)</f>
+        <v>tc-0.25.df-N.dm-Lo.cp-00.CF1</v>
+      </c>
+      <c r="I26" t="str">
         <f t="shared" si="4"/>
-        <v>tc-Y.df-N.ga-N.dm-Lo.cp-0.CF1</v>
-      </c>
-      <c r="I26" t="str">
+        <v>Lo</v>
+      </c>
+      <c r="J26" t="str">
         <f t="shared" si="5"/>
-        <v>Lo</v>
-      </c>
-      <c r="J26" t="str">
+        <v>00</v>
+      </c>
+      <c r="K26" t="str">
         <f t="shared" si="6"/>
-        <v>00</v>
-      </c>
-      <c r="K26" t="str">
+        <v>CF1</v>
+      </c>
+      <c r="L26" t="str">
         <f t="shared" si="7"/>
-        <v>CF1</v>
-      </c>
-      <c r="L26" t="str">
+        <v>N</v>
+      </c>
+      <c r="M26">
         <f t="shared" si="8"/>
-        <v>N</v>
-      </c>
-      <c r="M26" t="str">
+        <v>0.25</v>
+      </c>
+      <c r="O26">
+        <v>5</v>
+      </c>
+      <c r="P26" t="s">
+        <v>1128</v>
+      </c>
+      <c r="Q26">
+        <v>21</v>
+      </c>
+      <c r="R26" t="s">
+        <v>1092</v>
+      </c>
+      <c r="S26">
+        <v>0</v>
+      </c>
+      <c r="T26" t="s">
+        <v>1087</v>
+      </c>
+      <c r="U26" t="s">
+        <v>1095</v>
+      </c>
+      <c r="V26" t="s">
+        <v>1093</v>
+      </c>
+      <c r="W26">
+        <v>0.25</v>
+      </c>
+      <c r="Y26" t="str">
         <f t="shared" si="9"/>
-        <v>N</v>
-      </c>
-      <c r="N26" t="str">
-        <f t="shared" si="9"/>
-        <v>Y</v>
-      </c>
-      <c r="P26">
-        <v>5</v>
-      </c>
-      <c r="Q26" t="s">
-        <v>1121</v>
-      </c>
-      <c r="R26">
-        <v>21</v>
-      </c>
-      <c r="S26" t="s">
-        <v>1092</v>
-      </c>
-      <c r="T26">
-        <v>0</v>
-      </c>
-      <c r="U26" t="s">
-        <v>1087</v>
-      </c>
-      <c r="V26" t="s">
-        <v>1095</v>
-      </c>
-      <c r="W26" t="s">
-        <v>1095</v>
-      </c>
-      <c r="X26" t="s">
-        <v>1093</v>
+        <v>dm-Lo</v>
       </c>
       <c r="Z26" t="str">
         <f t="shared" si="10"/>
-        <v>dm-Lo</v>
+        <v>cp-00</v>
       </c>
       <c r="AA26" t="str">
         <f t="shared" si="11"/>
-        <v>cp-0</v>
+        <v>CF1</v>
       </c>
       <c r="AB26" t="str">
         <f t="shared" si="12"/>
-        <v>CF1</v>
+        <v>df-N</v>
       </c>
       <c r="AC26" t="str">
         <f t="shared" si="13"/>
-        <v>df-N</v>
-      </c>
-      <c r="AD26" t="str">
+        <v>tc-0.25</v>
+      </c>
+    </row>
+    <row r="27" spans="2:29">
+      <c r="B27" t="str">
         <f t="shared" si="14"/>
-        <v>ga-N</v>
-      </c>
-      <c r="AE26" t="str">
-        <f t="shared" si="14"/>
-        <v>tc-Y</v>
-      </c>
-    </row>
-    <row r="27" spans="2:31">
-      <c r="B27" t="str">
+        <v>vs~0022</v>
+      </c>
+      <c r="C27" t="str">
         <f t="shared" si="15"/>
-        <v>vs~0022</v>
-      </c>
-      <c r="C27" t="str">
-        <f t="shared" si="16"/>
-        <v>tc-Y.df-N.ga-N.dm-Hi.cp-0.CF1</v>
+        <v>tc-0.25.df-N.dm-Hi.cp-00.CF1</v>
       </c>
       <c r="H27" t="str">
+        <f>_xlfn.TEXTJOIN(".",TRUE,AC27,AB27:AB27)&amp;"."&amp;_xlfn.TEXTJOIN(".",TRUE,Y27:AA27)</f>
+        <v>tc-0.25.df-N.dm-Hi.cp-00.CF1</v>
+      </c>
+      <c r="I27" t="str">
         <f t="shared" si="4"/>
-        <v>tc-Y.df-N.ga-N.dm-Hi.cp-0.CF1</v>
-      </c>
-      <c r="I27" t="str">
+        <v>Hi</v>
+      </c>
+      <c r="J27" t="str">
         <f t="shared" si="5"/>
-        <v>Hi</v>
-      </c>
-      <c r="J27" t="str">
+        <v>00</v>
+      </c>
+      <c r="K27" t="str">
         <f t="shared" si="6"/>
-        <v>00</v>
-      </c>
-      <c r="K27" t="str">
+        <v>CF1</v>
+      </c>
+      <c r="L27" t="str">
         <f t="shared" si="7"/>
-        <v>CF1</v>
-      </c>
-      <c r="L27" t="str">
+        <v>N</v>
+      </c>
+      <c r="M27">
         <f t="shared" si="8"/>
-        <v>N</v>
-      </c>
-      <c r="M27" t="str">
+        <v>0.25</v>
+      </c>
+      <c r="O27">
+        <v>5</v>
+      </c>
+      <c r="P27" t="s">
+        <v>1129</v>
+      </c>
+      <c r="Q27">
+        <v>22</v>
+      </c>
+      <c r="R27" t="s">
+        <v>1094</v>
+      </c>
+      <c r="S27">
+        <v>0</v>
+      </c>
+      <c r="T27" t="s">
+        <v>1087</v>
+      </c>
+      <c r="U27" t="s">
+        <v>1095</v>
+      </c>
+      <c r="V27" t="s">
+        <v>1093</v>
+      </c>
+      <c r="W27">
+        <v>0.25</v>
+      </c>
+      <c r="Y27" t="str">
         <f t="shared" si="9"/>
-        <v>N</v>
-      </c>
-      <c r="N27" t="str">
-        <f t="shared" si="9"/>
-        <v>Y</v>
-      </c>
-      <c r="P27">
-        <v>5</v>
-      </c>
-      <c r="Q27" t="s">
-        <v>1122</v>
-      </c>
-      <c r="R27">
-        <v>22</v>
-      </c>
-      <c r="S27" t="s">
-        <v>1094</v>
-      </c>
-      <c r="T27">
-        <v>0</v>
-      </c>
-      <c r="U27" t="s">
-        <v>1087</v>
-      </c>
-      <c r="V27" t="s">
-        <v>1095</v>
-      </c>
-      <c r="W27" t="s">
-        <v>1095</v>
-      </c>
-      <c r="X27" t="s">
-        <v>1093</v>
+        <v>dm-Hi</v>
       </c>
       <c r="Z27" t="str">
         <f t="shared" si="10"/>
-        <v>dm-Hi</v>
+        <v>cp-00</v>
       </c>
       <c r="AA27" t="str">
         <f t="shared" si="11"/>
-        <v>cp-0</v>
+        <v>CF1</v>
       </c>
       <c r="AB27" t="str">
         <f t="shared" si="12"/>
-        <v>CF1</v>
+        <v>df-N</v>
       </c>
       <c r="AC27" t="str">
         <f t="shared" si="13"/>
-        <v>df-N</v>
-      </c>
-      <c r="AD27" t="str">
+        <v>tc-0.25</v>
+      </c>
+    </row>
+    <row r="28" spans="2:29">
+      <c r="B28" t="str">
         <f t="shared" si="14"/>
-        <v>ga-N</v>
-      </c>
-      <c r="AE27" t="str">
-        <f t="shared" si="14"/>
-        <v>tc-Y</v>
-      </c>
-    </row>
-    <row r="28" spans="2:31">
-      <c r="B28" t="str">
+        <v>vs~0023</v>
+      </c>
+      <c r="C28" t="str">
         <f t="shared" si="15"/>
-        <v>vs~0023</v>
-      </c>
-      <c r="C28" t="str">
-        <f t="shared" si="16"/>
-        <v>tc-Y.df-N.ga-N.dm-Lo.cp-95.CF1</v>
+        <v>tc-0.25.df-N.dm-Lo.cp-95.CF1</v>
       </c>
       <c r="H28" t="str">
+        <f>_xlfn.TEXTJOIN(".",TRUE,AC28,AB28:AB28)&amp;"."&amp;_xlfn.TEXTJOIN(".",TRUE,Y28:AA28)</f>
+        <v>tc-0.25.df-N.dm-Lo.cp-95.CF1</v>
+      </c>
+      <c r="I28" t="str">
         <f t="shared" si="4"/>
-        <v>tc-Y.df-N.ga-N.dm-Lo.cp-95.CF1</v>
-      </c>
-      <c r="I28" t="str">
+        <v>Lo</v>
+      </c>
+      <c r="J28" t="str">
         <f t="shared" si="5"/>
-        <v>Lo</v>
-      </c>
-      <c r="J28" t="str">
+        <v>95</v>
+      </c>
+      <c r="K28" t="str">
         <f t="shared" si="6"/>
+        <v>CF1</v>
+      </c>
+      <c r="L28" t="str">
+        <f t="shared" si="7"/>
+        <v>N</v>
+      </c>
+      <c r="M28">
+        <f t="shared" si="8"/>
+        <v>0.25</v>
+      </c>
+      <c r="O28">
+        <v>5</v>
+      </c>
+      <c r="P28" t="s">
+        <v>1130</v>
+      </c>
+      <c r="Q28">
+        <v>23</v>
+      </c>
+      <c r="R28" t="s">
+        <v>1092</v>
+      </c>
+      <c r="S28">
         <v>95</v>
       </c>
-      <c r="K28" t="str">
-        <f t="shared" si="7"/>
-        <v>CF1</v>
-      </c>
-      <c r="L28" t="str">
-        <f t="shared" si="8"/>
-        <v>N</v>
-      </c>
-      <c r="M28" t="str">
+      <c r="T28" t="s">
+        <v>1087</v>
+      </c>
+      <c r="U28" t="s">
+        <v>1095</v>
+      </c>
+      <c r="V28" t="s">
+        <v>1093</v>
+      </c>
+      <c r="W28">
+        <v>0.25</v>
+      </c>
+      <c r="Y28" t="str">
         <f t="shared" si="9"/>
-        <v>N</v>
-      </c>
-      <c r="N28" t="str">
-        <f t="shared" si="9"/>
-        <v>Y</v>
-      </c>
-      <c r="P28">
-        <v>5</v>
-      </c>
-      <c r="Q28" t="s">
-        <v>1123</v>
-      </c>
-      <c r="R28">
-        <v>23</v>
-      </c>
-      <c r="S28" t="s">
-        <v>1092</v>
-      </c>
-      <c r="T28">
-        <v>95</v>
-      </c>
-      <c r="U28" t="s">
-        <v>1087</v>
-      </c>
-      <c r="V28" t="s">
-        <v>1095</v>
-      </c>
-      <c r="W28" t="s">
-        <v>1095</v>
-      </c>
-      <c r="X28" t="s">
-        <v>1093</v>
+        <v>dm-Lo</v>
       </c>
       <c r="Z28" t="str">
         <f t="shared" si="10"/>
-        <v>dm-Lo</v>
+        <v>cp-95</v>
       </c>
       <c r="AA28" t="str">
         <f t="shared" si="11"/>
-        <v>cp-95</v>
+        <v>CF1</v>
       </c>
       <c r="AB28" t="str">
         <f t="shared" si="12"/>
-        <v>CF1</v>
+        <v>df-N</v>
       </c>
       <c r="AC28" t="str">
         <f t="shared" si="13"/>
-        <v>df-N</v>
-      </c>
-      <c r="AD28" t="str">
+        <v>tc-0.25</v>
+      </c>
+    </row>
+    <row r="29" spans="2:29">
+      <c r="B29" t="str">
         <f t="shared" si="14"/>
-        <v>ga-N</v>
-      </c>
-      <c r="AE28" t="str">
-        <f t="shared" si="14"/>
-        <v>tc-Y</v>
-      </c>
-    </row>
-    <row r="29" spans="2:31">
-      <c r="B29" t="str">
+        <v>vs~0024</v>
+      </c>
+      <c r="C29" t="str">
         <f t="shared" si="15"/>
-        <v>vs~0024</v>
-      </c>
-      <c r="C29" t="str">
-        <f t="shared" si="16"/>
-        <v>tc-Y.df-N.ga-N.dm-Hi.cp-95.CF1</v>
+        <v>tc-0.25.df-N.dm-Hi.cp-95.CF1</v>
       </c>
       <c r="H29" t="str">
+        <f>_xlfn.TEXTJOIN(".",TRUE,AC29,AB29:AB29)&amp;"."&amp;_xlfn.TEXTJOIN(".",TRUE,Y29:AA29)</f>
+        <v>tc-0.25.df-N.dm-Hi.cp-95.CF1</v>
+      </c>
+      <c r="I29" t="str">
         <f t="shared" si="4"/>
-        <v>tc-Y.df-N.ga-N.dm-Hi.cp-95.CF1</v>
-      </c>
-      <c r="I29" t="str">
+        <v>Hi</v>
+      </c>
+      <c r="J29" t="str">
         <f t="shared" si="5"/>
-        <v>Hi</v>
-      </c>
-      <c r="J29" t="str">
+        <v>95</v>
+      </c>
+      <c r="K29" t="str">
         <f t="shared" si="6"/>
+        <v>CF1</v>
+      </c>
+      <c r="L29" t="str">
+        <f t="shared" si="7"/>
+        <v>N</v>
+      </c>
+      <c r="M29">
+        <f t="shared" si="8"/>
+        <v>0.25</v>
+      </c>
+      <c r="O29">
+        <v>5</v>
+      </c>
+      <c r="P29" t="s">
+        <v>1131</v>
+      </c>
+      <c r="Q29">
+        <v>24</v>
+      </c>
+      <c r="R29" t="s">
+        <v>1094</v>
+      </c>
+      <c r="S29">
         <v>95</v>
       </c>
-      <c r="K29" t="str">
-        <f t="shared" si="7"/>
-        <v>CF1</v>
-      </c>
-      <c r="L29" t="str">
-        <f t="shared" si="8"/>
-        <v>N</v>
-      </c>
-      <c r="M29" t="str">
+      <c r="T29" t="s">
+        <v>1087</v>
+      </c>
+      <c r="U29" t="s">
+        <v>1095</v>
+      </c>
+      <c r="V29" t="s">
+        <v>1093</v>
+      </c>
+      <c r="W29">
+        <v>0.25</v>
+      </c>
+      <c r="Y29" t="str">
         <f t="shared" si="9"/>
-        <v>N</v>
-      </c>
-      <c r="N29" t="str">
-        <f t="shared" si="9"/>
-        <v>Y</v>
-      </c>
-      <c r="P29">
-        <v>5</v>
-      </c>
-      <c r="Q29" t="s">
-        <v>1124</v>
-      </c>
-      <c r="R29">
-        <v>24</v>
-      </c>
-      <c r="S29" t="s">
-        <v>1094</v>
-      </c>
-      <c r="T29">
-        <v>95</v>
-      </c>
-      <c r="U29" t="s">
-        <v>1087</v>
-      </c>
-      <c r="V29" t="s">
-        <v>1095</v>
-      </c>
-      <c r="W29" t="s">
-        <v>1095</v>
-      </c>
-      <c r="X29" t="s">
-        <v>1093</v>
+        <v>dm-Hi</v>
       </c>
       <c r="Z29" t="str">
         <f t="shared" si="10"/>
-        <v>dm-Hi</v>
+        <v>cp-95</v>
       </c>
       <c r="AA29" t="str">
         <f t="shared" si="11"/>
-        <v>cp-95</v>
+        <v>CF1</v>
       </c>
       <c r="AB29" t="str">
         <f t="shared" si="12"/>
-        <v>CF1</v>
+        <v>df-N</v>
       </c>
       <c r="AC29" t="str">
         <f t="shared" si="13"/>
-        <v>df-N</v>
-      </c>
-      <c r="AD29" t="str">
+        <v>tc-0.25</v>
+      </c>
+    </row>
+    <row r="30" spans="2:29">
+      <c r="B30" t="str">
         <f t="shared" si="14"/>
-        <v>ga-N</v>
-      </c>
-      <c r="AE29" t="str">
-        <f t="shared" si="14"/>
-        <v>tc-Y</v>
-      </c>
-    </row>
-    <row r="30" spans="2:31">
-      <c r="B30" t="str">
+        <v>vs~0025</v>
+      </c>
+      <c r="C30" t="str">
         <f t="shared" si="15"/>
-        <v>vs~0025</v>
-      </c>
-      <c r="C30" t="str">
-        <f t="shared" si="16"/>
-        <v>tc-Y.df-Y.ga-N.dm-Lo.cp-0.CF6</v>
+        <v>tc-0.25.df-Y.dm-Lo.cp-00.CF6</v>
       </c>
       <c r="H30" t="str">
+        <f>_xlfn.TEXTJOIN(".",TRUE,AC30,AB30:AB30)&amp;"."&amp;_xlfn.TEXTJOIN(".",TRUE,Y30:AA30)</f>
+        <v>tc-0.25.df-Y.dm-Lo.cp-00.CF6</v>
+      </c>
+      <c r="I30" t="str">
         <f t="shared" si="4"/>
-        <v>tc-Y.df-Y.ga-N.dm-Lo.cp-0.CF6</v>
-      </c>
-      <c r="I30" t="str">
+        <v>Lo</v>
+      </c>
+      <c r="J30" t="str">
         <f t="shared" si="5"/>
-        <v>Lo</v>
-      </c>
-      <c r="J30" t="str">
+        <v>00</v>
+      </c>
+      <c r="K30" t="str">
         <f t="shared" si="6"/>
-        <v>00</v>
-      </c>
-      <c r="K30" t="str">
+        <v>CF6</v>
+      </c>
+      <c r="L30" t="str">
         <f t="shared" si="7"/>
-        <v>CF6</v>
-      </c>
-      <c r="L30" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M30">
         <f t="shared" si="8"/>
-        <v>Y</v>
-      </c>
-      <c r="M30" t="str">
-        <f t="shared" si="9"/>
-        <v>N</v>
-      </c>
-      <c r="N30" t="str">
-        <f t="shared" si="9"/>
-        <v>Y</v>
-      </c>
-      <c r="P30">
+        <v>0.25</v>
+      </c>
+      <c r="O30">
         <v>5</v>
       </c>
-      <c r="Q30" t="s">
-        <v>1125</v>
-      </c>
-      <c r="R30">
+      <c r="P30" t="s">
+        <v>1132</v>
+      </c>
+      <c r="Q30">
         <v>25</v>
       </c>
-      <c r="S30" t="s">
+      <c r="R30" t="s">
         <v>1092</v>
       </c>
-      <c r="T30">
+      <c r="S30">
         <v>0</v>
       </c>
+      <c r="T30" t="s">
+        <v>1088</v>
+      </c>
       <c r="U30" t="s">
-        <v>1088</v>
+        <v>1093</v>
       </c>
       <c r="V30" t="s">
         <v>1093</v>
       </c>
-      <c r="W30" t="s">
-        <v>1095</v>
-      </c>
-      <c r="X30" t="s">
-        <v>1093</v>
+      <c r="W30">
+        <v>0.25</v>
+      </c>
+      <c r="Y30" t="str">
+        <f t="shared" si="9"/>
+        <v>dm-Lo</v>
       </c>
       <c r="Z30" t="str">
         <f t="shared" si="10"/>
-        <v>dm-Lo</v>
+        <v>cp-00</v>
       </c>
       <c r="AA30" t="str">
         <f t="shared" si="11"/>
-        <v>cp-0</v>
+        <v>CF6</v>
       </c>
       <c r="AB30" t="str">
         <f t="shared" si="12"/>
-        <v>CF6</v>
+        <v>df-Y</v>
       </c>
       <c r="AC30" t="str">
         <f t="shared" si="13"/>
-        <v>df-Y</v>
-      </c>
-      <c r="AD30" t="str">
+        <v>tc-0.25</v>
+      </c>
+    </row>
+    <row r="31" spans="2:29">
+      <c r="B31" t="str">
         <f t="shared" si="14"/>
-        <v>ga-N</v>
-      </c>
-      <c r="AE30" t="str">
-        <f t="shared" si="14"/>
-        <v>tc-Y</v>
-      </c>
-    </row>
-    <row r="31" spans="2:31">
-      <c r="B31" t="str">
+        <v>vs~0026</v>
+      </c>
+      <c r="C31" t="str">
         <f t="shared" si="15"/>
-        <v>vs~0026</v>
-      </c>
-      <c r="C31" t="str">
-        <f t="shared" si="16"/>
-        <v>tc-Y.df-Y.ga-N.dm-Hi.cp-0.CF6</v>
+        <v>tc-0.25.df-Y.dm-Hi.cp-00.CF6</v>
       </c>
       <c r="H31" t="str">
+        <f>_xlfn.TEXTJOIN(".",TRUE,AC31,AB31:AB31)&amp;"."&amp;_xlfn.TEXTJOIN(".",TRUE,Y31:AA31)</f>
+        <v>tc-0.25.df-Y.dm-Hi.cp-00.CF6</v>
+      </c>
+      <c r="I31" t="str">
         <f t="shared" si="4"/>
-        <v>tc-Y.df-Y.ga-N.dm-Hi.cp-0.CF6</v>
-      </c>
-      <c r="I31" t="str">
+        <v>Hi</v>
+      </c>
+      <c r="J31" t="str">
         <f t="shared" si="5"/>
-        <v>Hi</v>
-      </c>
-      <c r="J31" t="str">
+        <v>00</v>
+      </c>
+      <c r="K31" t="str">
         <f t="shared" si="6"/>
-        <v>00</v>
-      </c>
-      <c r="K31" t="str">
+        <v>CF6</v>
+      </c>
+      <c r="L31" t="str">
         <f t="shared" si="7"/>
-        <v>CF6</v>
-      </c>
-      <c r="L31" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M31">
         <f t="shared" si="8"/>
-        <v>Y</v>
-      </c>
-      <c r="M31" t="str">
-        <f t="shared" si="9"/>
-        <v>N</v>
-      </c>
-      <c r="N31" t="str">
-        <f t="shared" si="9"/>
-        <v>Y</v>
-      </c>
-      <c r="P31">
+        <v>0.25</v>
+      </c>
+      <c r="O31">
         <v>5</v>
       </c>
-      <c r="Q31" t="s">
-        <v>1126</v>
-      </c>
-      <c r="R31">
+      <c r="P31" t="s">
+        <v>1133</v>
+      </c>
+      <c r="Q31">
         <v>26</v>
       </c>
-      <c r="S31" t="s">
+      <c r="R31" t="s">
         <v>1094</v>
       </c>
-      <c r="T31">
+      <c r="S31">
         <v>0</v>
       </c>
+      <c r="T31" t="s">
+        <v>1088</v>
+      </c>
       <c r="U31" t="s">
-        <v>1088</v>
+        <v>1093</v>
       </c>
       <c r="V31" t="s">
         <v>1093</v>
       </c>
-      <c r="W31" t="s">
-        <v>1095</v>
-      </c>
-      <c r="X31" t="s">
-        <v>1093</v>
+      <c r="W31">
+        <v>0.25</v>
+      </c>
+      <c r="Y31" t="str">
+        <f t="shared" si="9"/>
+        <v>dm-Hi</v>
       </c>
       <c r="Z31" t="str">
         <f t="shared" si="10"/>
-        <v>dm-Hi</v>
+        <v>cp-00</v>
       </c>
       <c r="AA31" t="str">
         <f t="shared" si="11"/>
-        <v>cp-0</v>
+        <v>CF6</v>
       </c>
       <c r="AB31" t="str">
         <f t="shared" si="12"/>
-        <v>CF6</v>
+        <v>df-Y</v>
       </c>
       <c r="AC31" t="str">
         <f t="shared" si="13"/>
-        <v>df-Y</v>
-      </c>
-      <c r="AD31" t="str">
+        <v>tc-0.25</v>
+      </c>
+    </row>
+    <row r="32" spans="2:29">
+      <c r="B32" t="str">
         <f t="shared" si="14"/>
-        <v>ga-N</v>
-      </c>
-      <c r="AE31" t="str">
-        <f t="shared" si="14"/>
-        <v>tc-Y</v>
-      </c>
-    </row>
-    <row r="32" spans="2:31">
-      <c r="B32" t="str">
+        <v>vs~0027</v>
+      </c>
+      <c r="C32" t="str">
         <f t="shared" si="15"/>
-        <v>vs~0027</v>
-      </c>
-      <c r="C32" t="str">
-        <f t="shared" si="16"/>
-        <v>tc-Y.df-Y.ga-N.dm-Lo.cp-95.CF6</v>
+        <v>tc-0.25.df-Y.dm-Lo.cp-95.CF6</v>
       </c>
       <c r="H32" t="str">
+        <f>_xlfn.TEXTJOIN(".",TRUE,AC32,AB32:AB32)&amp;"."&amp;_xlfn.TEXTJOIN(".",TRUE,Y32:AA32)</f>
+        <v>tc-0.25.df-Y.dm-Lo.cp-95.CF6</v>
+      </c>
+      <c r="I32" t="str">
         <f t="shared" si="4"/>
-        <v>tc-Y.df-Y.ga-N.dm-Lo.cp-95.CF6</v>
-      </c>
-      <c r="I32" t="str">
+        <v>Lo</v>
+      </c>
+      <c r="J32" t="str">
         <f t="shared" si="5"/>
-        <v>Lo</v>
-      </c>
-      <c r="J32" t="str">
+        <v>95</v>
+      </c>
+      <c r="K32" t="str">
         <f t="shared" si="6"/>
+        <v>CF6</v>
+      </c>
+      <c r="L32" t="str">
+        <f t="shared" si="7"/>
+        <v>Y</v>
+      </c>
+      <c r="M32">
+        <f t="shared" si="8"/>
+        <v>0.25</v>
+      </c>
+      <c r="O32">
+        <v>5</v>
+      </c>
+      <c r="P32" t="s">
+        <v>1134</v>
+      </c>
+      <c r="Q32">
+        <v>27</v>
+      </c>
+      <c r="R32" t="s">
+        <v>1092</v>
+      </c>
+      <c r="S32">
         <v>95</v>
       </c>
-      <c r="K32" t="str">
-        <f t="shared" si="7"/>
-        <v>CF6</v>
-      </c>
-      <c r="L32" t="str">
-        <f t="shared" si="8"/>
-        <v>Y</v>
-      </c>
-      <c r="M32" t="str">
-        <f t="shared" si="9"/>
-        <v>N</v>
-      </c>
-      <c r="N32" t="str">
-        <f t="shared" si="9"/>
-        <v>Y</v>
-      </c>
-      <c r="P32">
-        <v>5</v>
-      </c>
-      <c r="Q32" t="s">
-        <v>1127</v>
-      </c>
-      <c r="R32">
-        <v>27</v>
-      </c>
-      <c r="S32" t="s">
-        <v>1092</v>
-      </c>
-      <c r="T32">
-        <v>95</v>
+      <c r="T32" t="s">
+        <v>1088</v>
       </c>
       <c r="U32" t="s">
-        <v>1088</v>
+        <v>1093</v>
       </c>
       <c r="V32" t="s">
         <v>1093</v>
       </c>
-      <c r="W32" t="s">
-        <v>1095</v>
-      </c>
-      <c r="X32" t="s">
-        <v>1093</v>
+      <c r="W32">
+        <v>0.25</v>
+      </c>
+      <c r="Y32" t="str">
+        <f t="shared" si="9"/>
+        <v>dm-Lo</v>
       </c>
       <c r="Z32" t="str">
         <f t="shared" si="10"/>
-        <v>dm-Lo</v>
+        <v>cp-95</v>
       </c>
       <c r="AA32" t="str">
         <f t="shared" si="11"/>
-        <v>cp-95</v>
+        <v>CF6</v>
       </c>
       <c r="AB32" t="str">
         <f t="shared" si="12"/>
-        <v>CF6</v>
+        <v>df-Y</v>
       </c>
       <c r="AC32" t="str">
         <f t="shared" si="13"/>
-        <v>df-Y</v>
-      </c>
-      <c r="AD32" t="str">
+        <v>tc-0.25</v>
+      </c>
+    </row>
+    <row r="33" spans="2:29">
+      <c r="B33" t="str">
         <f t="shared" si="14"/>
-        <v>ga-N</v>
-      </c>
-      <c r="AE32" t="str">
-        <f t="shared" si="14"/>
-        <v>tc-Y</v>
-      </c>
-    </row>
-    <row r="33" spans="2:31">
-      <c r="B33" t="str">
+        <v>vs~0028</v>
+      </c>
+      <c r="C33" t="str">
         <f t="shared" si="15"/>
-        <v>vs~0028</v>
-      </c>
-      <c r="C33" t="str">
-        <f t="shared" si="16"/>
-        <v>tc-Y.df-Y.ga-N.dm-Hi.cp-95.CF6</v>
+        <v>tc-0.25.df-Y.dm-Hi.cp-95.CF6</v>
       </c>
       <c r="H33" t="str">
+        <f>_xlfn.TEXTJOIN(".",TRUE,AC33,AB33:AB33)&amp;"."&amp;_xlfn.TEXTJOIN(".",TRUE,Y33:AA33)</f>
+        <v>tc-0.25.df-Y.dm-Hi.cp-95.CF6</v>
+      </c>
+      <c r="I33" t="str">
         <f t="shared" si="4"/>
-        <v>tc-Y.df-Y.ga-N.dm-Hi.cp-95.CF6</v>
-      </c>
-      <c r="I33" t="str">
+        <v>Hi</v>
+      </c>
+      <c r="J33" t="str">
         <f t="shared" si="5"/>
-        <v>Hi</v>
-      </c>
-      <c r="J33" t="str">
+        <v>95</v>
+      </c>
+      <c r="K33" t="str">
         <f t="shared" si="6"/>
+        <v>CF6</v>
+      </c>
+      <c r="L33" t="str">
+        <f t="shared" si="7"/>
+        <v>Y</v>
+      </c>
+      <c r="M33">
+        <f t="shared" si="8"/>
+        <v>0.25</v>
+      </c>
+      <c r="O33">
+        <v>5</v>
+      </c>
+      <c r="P33" t="s">
+        <v>1135</v>
+      </c>
+      <c r="Q33">
+        <v>28</v>
+      </c>
+      <c r="R33" t="s">
+        <v>1094</v>
+      </c>
+      <c r="S33">
         <v>95</v>
       </c>
-      <c r="K33" t="str">
-        <f t="shared" si="7"/>
-        <v>CF6</v>
-      </c>
-      <c r="L33" t="str">
-        <f t="shared" si="8"/>
-        <v>Y</v>
-      </c>
-      <c r="M33" t="str">
-        <f t="shared" si="9"/>
-        <v>N</v>
-      </c>
-      <c r="N33" t="str">
-        <f t="shared" si="9"/>
-        <v>Y</v>
-      </c>
-      <c r="P33">
-        <v>5</v>
-      </c>
-      <c r="Q33" t="s">
-        <v>1128</v>
-      </c>
-      <c r="R33">
-        <v>28</v>
-      </c>
-      <c r="S33" t="s">
-        <v>1094</v>
-      </c>
-      <c r="T33">
-        <v>95</v>
+      <c r="T33" t="s">
+        <v>1088</v>
       </c>
       <c r="U33" t="s">
-        <v>1088</v>
+        <v>1093</v>
       </c>
       <c r="V33" t="s">
         <v>1093</v>
       </c>
-      <c r="W33" t="s">
-        <v>1095</v>
-      </c>
-      <c r="X33" t="s">
-        <v>1093</v>
+      <c r="W33">
+        <v>0.25</v>
+      </c>
+      <c r="Y33" t="str">
+        <f t="shared" si="9"/>
+        <v>dm-Hi</v>
       </c>
       <c r="Z33" t="str">
         <f t="shared" si="10"/>
-        <v>dm-Hi</v>
+        <v>cp-95</v>
       </c>
       <c r="AA33" t="str">
         <f t="shared" si="11"/>
-        <v>cp-95</v>
+        <v>CF6</v>
       </c>
       <c r="AB33" t="str">
         <f t="shared" si="12"/>
-        <v>CF6</v>
+        <v>df-Y</v>
       </c>
       <c r="AC33" t="str">
         <f t="shared" si="13"/>
-        <v>df-Y</v>
-      </c>
-      <c r="AD33" t="str">
+        <v>tc-0.25</v>
+      </c>
+    </row>
+    <row r="34" spans="2:29">
+      <c r="B34" t="str">
         <f t="shared" si="14"/>
-        <v>ga-N</v>
-      </c>
-      <c r="AE33" t="str">
-        <f t="shared" si="14"/>
-        <v>tc-Y</v>
-      </c>
-    </row>
-    <row r="34" spans="2:31">
-      <c r="B34" t="str">
+        <v>vs~0029</v>
+      </c>
+      <c r="C34" t="str">
         <f t="shared" si="15"/>
-        <v>vs~0029</v>
-      </c>
-      <c r="C34" t="str">
-        <f t="shared" si="16"/>
-        <v>tc-Y.df-N.ga-N.dm-Lo.cp-0.CF6</v>
+        <v>tc-0.25.df-N.dm-Lo.cp-00.CF6</v>
       </c>
       <c r="H34" t="str">
+        <f>_xlfn.TEXTJOIN(".",TRUE,AC34,AB34:AB34)&amp;"."&amp;_xlfn.TEXTJOIN(".",TRUE,Y34:AA34)</f>
+        <v>tc-0.25.df-N.dm-Lo.cp-00.CF6</v>
+      </c>
+      <c r="I34" t="str">
         <f t="shared" si="4"/>
-        <v>tc-Y.df-N.ga-N.dm-Lo.cp-0.CF6</v>
-      </c>
-      <c r="I34" t="str">
+        <v>Lo</v>
+      </c>
+      <c r="J34" t="str">
         <f t="shared" si="5"/>
-        <v>Lo</v>
-      </c>
-      <c r="J34" t="str">
+        <v>00</v>
+      </c>
+      <c r="K34" t="str">
         <f t="shared" si="6"/>
-        <v>00</v>
-      </c>
-      <c r="K34" t="str">
+        <v>CF6</v>
+      </c>
+      <c r="L34" t="str">
         <f t="shared" si="7"/>
-        <v>CF6</v>
-      </c>
-      <c r="L34" t="str">
+        <v>N</v>
+      </c>
+      <c r="M34">
         <f t="shared" si="8"/>
-        <v>N</v>
-      </c>
-      <c r="M34" t="str">
+        <v>0.25</v>
+      </c>
+      <c r="O34">
+        <v>5</v>
+      </c>
+      <c r="P34" t="s">
+        <v>1136</v>
+      </c>
+      <c r="Q34">
+        <v>29</v>
+      </c>
+      <c r="R34" t="s">
+        <v>1092</v>
+      </c>
+      <c r="S34">
+        <v>0</v>
+      </c>
+      <c r="T34" t="s">
+        <v>1088</v>
+      </c>
+      <c r="U34" t="s">
+        <v>1095</v>
+      </c>
+      <c r="V34" t="s">
+        <v>1093</v>
+      </c>
+      <c r="W34">
+        <v>0.25</v>
+      </c>
+      <c r="Y34" t="str">
         <f t="shared" si="9"/>
-        <v>N</v>
-      </c>
-      <c r="N34" t="str">
-        <f t="shared" si="9"/>
-        <v>Y</v>
-      </c>
-      <c r="P34">
-        <v>5</v>
-      </c>
-      <c r="Q34" t="s">
-        <v>1129</v>
-      </c>
-      <c r="R34">
-        <v>29</v>
-      </c>
-      <c r="S34" t="s">
-        <v>1092</v>
-      </c>
-      <c r="T34">
-        <v>0</v>
-      </c>
-      <c r="U34" t="s">
-        <v>1088</v>
-      </c>
-      <c r="V34" t="s">
-        <v>1095</v>
-      </c>
-      <c r="W34" t="s">
-        <v>1095</v>
-      </c>
-      <c r="X34" t="s">
-        <v>1093</v>
+        <v>dm-Lo</v>
       </c>
       <c r="Z34" t="str">
         <f t="shared" si="10"/>
-        <v>dm-Lo</v>
+        <v>cp-00</v>
       </c>
       <c r="AA34" t="str">
         <f t="shared" si="11"/>
-        <v>cp-0</v>
+        <v>CF6</v>
       </c>
       <c r="AB34" t="str">
         <f t="shared" si="12"/>
-        <v>CF6</v>
+        <v>df-N</v>
       </c>
       <c r="AC34" t="str">
         <f t="shared" si="13"/>
-        <v>df-N</v>
-      </c>
-      <c r="AD34" t="str">
+        <v>tc-0.25</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29">
+      <c r="B35" t="str">
         <f t="shared" si="14"/>
-        <v>ga-N</v>
-      </c>
-      <c r="AE34" t="str">
-        <f t="shared" si="14"/>
-        <v>tc-Y</v>
-      </c>
-    </row>
-    <row r="35" spans="2:31">
-      <c r="B35" t="str">
+        <v>vs~0030</v>
+      </c>
+      <c r="C35" t="str">
         <f t="shared" si="15"/>
-        <v>vs~0030</v>
-      </c>
-      <c r="C35" t="str">
-        <f t="shared" si="16"/>
-        <v>tc-Y.df-N.ga-N.dm-Hi.cp-0.CF6</v>
+        <v>tc-0.25.df-N.dm-Hi.cp-00.CF6</v>
       </c>
       <c r="H35" t="str">
+        <f>_xlfn.TEXTJOIN(".",TRUE,AC35,AB35:AB35)&amp;"."&amp;_xlfn.TEXTJOIN(".",TRUE,Y35:AA35)</f>
+        <v>tc-0.25.df-N.dm-Hi.cp-00.CF6</v>
+      </c>
+      <c r="I35" t="str">
         <f t="shared" si="4"/>
-        <v>tc-Y.df-N.ga-N.dm-Hi.cp-0.CF6</v>
-      </c>
-      <c r="I35" t="str">
+        <v>Hi</v>
+      </c>
+      <c r="J35" t="str">
         <f t="shared" si="5"/>
-        <v>Hi</v>
-      </c>
-      <c r="J35" t="str">
+        <v>00</v>
+      </c>
+      <c r="K35" t="str">
         <f t="shared" si="6"/>
-        <v>00</v>
-      </c>
-      <c r="K35" t="str">
+        <v>CF6</v>
+      </c>
+      <c r="L35" t="str">
         <f t="shared" si="7"/>
-        <v>CF6</v>
-      </c>
-      <c r="L35" t="str">
+        <v>N</v>
+      </c>
+      <c r="M35">
         <f t="shared" si="8"/>
-        <v>N</v>
-      </c>
-      <c r="M35" t="str">
+        <v>0.25</v>
+      </c>
+      <c r="O35">
+        <v>5</v>
+      </c>
+      <c r="P35" t="s">
+        <v>1137</v>
+      </c>
+      <c r="Q35">
+        <v>30</v>
+      </c>
+      <c r="R35" t="s">
+        <v>1094</v>
+      </c>
+      <c r="S35">
+        <v>0</v>
+      </c>
+      <c r="T35" t="s">
+        <v>1088</v>
+      </c>
+      <c r="U35" t="s">
+        <v>1095</v>
+      </c>
+      <c r="V35" t="s">
+        <v>1093</v>
+      </c>
+      <c r="W35">
+        <v>0.25</v>
+      </c>
+      <c r="Y35" t="str">
         <f t="shared" si="9"/>
-        <v>N</v>
-      </c>
-      <c r="N35" t="str">
-        <f t="shared" si="9"/>
-        <v>Y</v>
-      </c>
-      <c r="P35">
-        <v>5</v>
-      </c>
-      <c r="Q35" t="s">
-        <v>1130</v>
-      </c>
-      <c r="R35">
-        <v>30</v>
-      </c>
-      <c r="S35" t="s">
-        <v>1094</v>
-      </c>
-      <c r="T35">
-        <v>0</v>
-      </c>
-      <c r="U35" t="s">
-        <v>1088</v>
-      </c>
-      <c r="V35" t="s">
-        <v>1095</v>
-      </c>
-      <c r="W35" t="s">
-        <v>1095</v>
-      </c>
-      <c r="X35" t="s">
-        <v>1093</v>
+        <v>dm-Hi</v>
       </c>
       <c r="Z35" t="str">
         <f t="shared" si="10"/>
-        <v>dm-Hi</v>
+        <v>cp-00</v>
       </c>
       <c r="AA35" t="str">
         <f t="shared" si="11"/>
-        <v>cp-0</v>
+        <v>CF6</v>
       </c>
       <c r="AB35" t="str">
         <f t="shared" si="12"/>
-        <v>CF6</v>
+        <v>df-N</v>
       </c>
       <c r="AC35" t="str">
         <f t="shared" si="13"/>
-        <v>df-N</v>
-      </c>
-      <c r="AD35" t="str">
+        <v>tc-0.25</v>
+      </c>
+    </row>
+    <row r="36" spans="2:29">
+      <c r="B36" t="str">
         <f t="shared" si="14"/>
-        <v>ga-N</v>
-      </c>
-      <c r="AE35" t="str">
-        <f t="shared" si="14"/>
-        <v>tc-Y</v>
-      </c>
-    </row>
-    <row r="36" spans="2:31">
-      <c r="B36" t="str">
+        <v>vs~0031</v>
+      </c>
+      <c r="C36" t="str">
         <f t="shared" si="15"/>
-        <v>vs~0031</v>
-      </c>
-      <c r="C36" t="str">
-        <f t="shared" si="16"/>
-        <v>tc-Y.df-N.ga-N.dm-Lo.cp-95.CF6</v>
+        <v>tc-0.25.df-N.dm-Lo.cp-95.CF6</v>
       </c>
       <c r="H36" t="str">
+        <f>_xlfn.TEXTJOIN(".",TRUE,AC36,AB36:AB36)&amp;"."&amp;_xlfn.TEXTJOIN(".",TRUE,Y36:AA36)</f>
+        <v>tc-0.25.df-N.dm-Lo.cp-95.CF6</v>
+      </c>
+      <c r="I36" t="str">
         <f t="shared" si="4"/>
-        <v>tc-Y.df-N.ga-N.dm-Lo.cp-95.CF6</v>
-      </c>
-      <c r="I36" t="str">
+        <v>Lo</v>
+      </c>
+      <c r="J36" t="str">
         <f t="shared" si="5"/>
-        <v>Lo</v>
-      </c>
-      <c r="J36" t="str">
+        <v>95</v>
+      </c>
+      <c r="K36" t="str">
         <f t="shared" si="6"/>
+        <v>CF6</v>
+      </c>
+      <c r="L36" t="str">
+        <f t="shared" si="7"/>
+        <v>N</v>
+      </c>
+      <c r="M36">
+        <f t="shared" si="8"/>
+        <v>0.25</v>
+      </c>
+      <c r="O36">
+        <v>5</v>
+      </c>
+      <c r="P36" t="s">
+        <v>1138</v>
+      </c>
+      <c r="Q36">
+        <v>31</v>
+      </c>
+      <c r="R36" t="s">
+        <v>1092</v>
+      </c>
+      <c r="S36">
         <v>95</v>
       </c>
-      <c r="K36" t="str">
-        <f t="shared" si="7"/>
-        <v>CF6</v>
-      </c>
-      <c r="L36" t="str">
-        <f t="shared" si="8"/>
-        <v>N</v>
-      </c>
-      <c r="M36" t="str">
+      <c r="T36" t="s">
+        <v>1088</v>
+      </c>
+      <c r="U36" t="s">
+        <v>1095</v>
+      </c>
+      <c r="V36" t="s">
+        <v>1093</v>
+      </c>
+      <c r="W36">
+        <v>0.25</v>
+      </c>
+      <c r="Y36" t="str">
         <f t="shared" si="9"/>
-        <v>N</v>
-      </c>
-      <c r="N36" t="str">
-        <f t="shared" si="9"/>
-        <v>Y</v>
-      </c>
-      <c r="P36">
-        <v>5</v>
-      </c>
-      <c r="Q36" t="s">
-        <v>1131</v>
-      </c>
-      <c r="R36">
-        <v>31</v>
-      </c>
-      <c r="S36" t="s">
-        <v>1092</v>
-      </c>
-      <c r="T36">
-        <v>95</v>
-      </c>
-      <c r="U36" t="s">
-        <v>1088</v>
-      </c>
-      <c r="V36" t="s">
-        <v>1095</v>
-      </c>
-      <c r="W36" t="s">
-        <v>1095</v>
-      </c>
-      <c r="X36" t="s">
-        <v>1093</v>
+        <v>dm-Lo</v>
       </c>
       <c r="Z36" t="str">
         <f t="shared" si="10"/>
-        <v>dm-Lo</v>
+        <v>cp-95</v>
       </c>
       <c r="AA36" t="str">
         <f t="shared" si="11"/>
-        <v>cp-95</v>
+        <v>CF6</v>
       </c>
       <c r="AB36" t="str">
         <f t="shared" si="12"/>
-        <v>CF6</v>
+        <v>df-N</v>
       </c>
       <c r="AC36" t="str">
         <f t="shared" si="13"/>
-        <v>df-N</v>
-      </c>
-      <c r="AD36" t="str">
+        <v>tc-0.25</v>
+      </c>
+    </row>
+    <row r="37" spans="2:29">
+      <c r="B37" t="str">
         <f t="shared" si="14"/>
-        <v>ga-N</v>
-      </c>
-      <c r="AE36" t="str">
-        <f t="shared" si="14"/>
-        <v>tc-Y</v>
-      </c>
-    </row>
-    <row r="37" spans="2:31">
-      <c r="B37" t="str">
+        <v>vs~0032</v>
+      </c>
+      <c r="C37" t="str">
         <f t="shared" si="15"/>
-        <v>vs~0032</v>
-      </c>
-      <c r="C37" t="str">
-        <f t="shared" si="16"/>
-        <v>tc-Y.df-N.ga-N.dm-Hi.cp-95.CF6</v>
+        <v>tc-0.25.df-N.dm-Hi.cp-95.CF6</v>
       </c>
       <c r="H37" t="str">
+        <f>_xlfn.TEXTJOIN(".",TRUE,AC37,AB37:AB37)&amp;"."&amp;_xlfn.TEXTJOIN(".",TRUE,Y37:AA37)</f>
+        <v>tc-0.25.df-N.dm-Hi.cp-95.CF6</v>
+      </c>
+      <c r="I37" t="str">
         <f t="shared" si="4"/>
-        <v>tc-Y.df-N.ga-N.dm-Hi.cp-95.CF6</v>
-      </c>
-      <c r="I37" t="str">
+        <v>Hi</v>
+      </c>
+      <c r="J37" t="str">
         <f t="shared" si="5"/>
-        <v>Hi</v>
-      </c>
-      <c r="J37" t="str">
+        <v>95</v>
+      </c>
+      <c r="K37" t="str">
         <f t="shared" si="6"/>
+        <v>CF6</v>
+      </c>
+      <c r="L37" t="str">
+        <f t="shared" si="7"/>
+        <v>N</v>
+      </c>
+      <c r="M37">
+        <f t="shared" si="8"/>
+        <v>0.25</v>
+      </c>
+      <c r="O37">
+        <v>5</v>
+      </c>
+      <c r="P37" t="s">
+        <v>1139</v>
+      </c>
+      <c r="Q37">
+        <v>32</v>
+      </c>
+      <c r="R37" t="s">
+        <v>1094</v>
+      </c>
+      <c r="S37">
         <v>95</v>
       </c>
-      <c r="K37" t="str">
-        <f t="shared" si="7"/>
-        <v>CF6</v>
-      </c>
-      <c r="L37" t="str">
-        <f t="shared" si="8"/>
-        <v>N</v>
-      </c>
-      <c r="M37" t="str">
+      <c r="T37" t="s">
+        <v>1088</v>
+      </c>
+      <c r="U37" t="s">
+        <v>1095</v>
+      </c>
+      <c r="V37" t="s">
+        <v>1093</v>
+      </c>
+      <c r="W37">
+        <v>0.25</v>
+      </c>
+      <c r="Y37" t="str">
         <f t="shared" si="9"/>
-        <v>N</v>
-      </c>
-      <c r="N37" t="str">
-        <f t="shared" si="9"/>
-        <v>Y</v>
-      </c>
-      <c r="P37">
-        <v>5</v>
-      </c>
-      <c r="Q37" t="s">
-        <v>1132</v>
-      </c>
-      <c r="R37">
-        <v>32</v>
-      </c>
-      <c r="S37" t="s">
-        <v>1094</v>
-      </c>
-      <c r="T37">
-        <v>95</v>
-      </c>
-      <c r="U37" t="s">
-        <v>1088</v>
-      </c>
-      <c r="V37" t="s">
-        <v>1095</v>
-      </c>
-      <c r="W37" t="s">
-        <v>1095</v>
-      </c>
-      <c r="X37" t="s">
-        <v>1093</v>
+        <v>dm-Hi</v>
       </c>
       <c r="Z37" t="str">
         <f t="shared" si="10"/>
-        <v>dm-Hi</v>
+        <v>cp-95</v>
       </c>
       <c r="AA37" t="str">
         <f t="shared" si="11"/>
-        <v>cp-95</v>
+        <v>CF6</v>
       </c>
       <c r="AB37" t="str">
         <f t="shared" si="12"/>
-        <v>CF6</v>
+        <v>df-N</v>
       </c>
       <c r="AC37" t="str">
         <f t="shared" si="13"/>
-        <v>df-N</v>
-      </c>
-      <c r="AD37" t="str">
-        <f t="shared" si="14"/>
-        <v>ga-N</v>
-      </c>
-      <c r="AE37" t="str">
-        <f t="shared" si="14"/>
-        <v>tc-Y</v>
-      </c>
-    </row>
-    <row r="38" spans="2:31">
+        <v>tc-0.25</v>
+      </c>
+    </row>
+    <row r="38" spans="2:29">
       <c r="B38" t="str">
-        <f t="shared" ref="B38:B69" si="17">"vs~"&amp;TEXT(R38,"0000")</f>
+        <f t="shared" ref="B38:B53" si="16">"vs~"&amp;TEXT(Q38,"0000")</f>
         <v>vs~0033</v>
       </c>
       <c r="C38" t="str">
-        <f t="shared" ref="C38:C69" si="18">H38</f>
-        <v>tc-N.df-Y.ga-Y.dm-Lo.cp-0.CF1</v>
+        <f t="shared" ref="C38:C53" si="17">H38</f>
+        <v>tc-2.00.df-Y.dm-Lo.cp-00.CF1</v>
       </c>
       <c r="H38" t="str">
-        <f t="shared" ref="H38:H69" si="19">_xlfn.TEXTJOIN(".",TRUE,AE38,AC38:AD38)&amp;"."&amp;_xlfn.TEXTJOIN(".",TRUE,Z38:AB38)</f>
-        <v>tc-N.df-Y.ga-Y.dm-Lo.cp-0.CF1</v>
+        <f>_xlfn.TEXTJOIN(".",TRUE,AC38,AB38:AB38)&amp;"."&amp;_xlfn.TEXTJOIN(".",TRUE,Y38:AA38)</f>
+        <v>tc-2.00.df-Y.dm-Lo.cp-00.CF1</v>
       </c>
       <c r="I38" t="str">
-        <f t="shared" ref="I38:I69" si="20">S38</f>
+        <f t="shared" ref="I38:I53" si="18">R38</f>
         <v>Lo</v>
       </c>
       <c r="J38" t="str">
-        <f t="shared" ref="J38:J69" si="21">TEXT(T38,"00")</f>
+        <f t="shared" ref="J38:J53" si="19">TEXT(S38,"00")</f>
         <v>00</v>
       </c>
       <c r="K38" t="str">
-        <f t="shared" ref="K38:K69" si="22">U38</f>
+        <f t="shared" ref="K38:K53" si="20">T38</f>
         <v>CF1</v>
       </c>
       <c r="L38" t="str">
-        <f t="shared" ref="L38:L69" si="23">V38</f>
+        <f t="shared" ref="L38:L53" si="21">U38</f>
         <v>Y</v>
       </c>
-      <c r="M38" t="str">
-        <f t="shared" ref="M38:M69" si="24">W38</f>
-        <v>Y</v>
-      </c>
-      <c r="N38" t="str">
-        <f t="shared" ref="N38:N69" si="25">X38</f>
-        <v>N</v>
-      </c>
-      <c r="P38">
+      <c r="M38">
+        <f t="shared" ref="M38:M53" si="22">W38</f>
+        <v>2</v>
+      </c>
+      <c r="O38">
         <v>5</v>
       </c>
-      <c r="Q38" t="s">
-        <v>1133</v>
-      </c>
-      <c r="R38">
+      <c r="P38" t="s">
+        <v>1140</v>
+      </c>
+      <c r="Q38">
         <v>33</v>
       </c>
-      <c r="S38" t="s">
+      <c r="R38" t="s">
         <v>1092</v>
       </c>
-      <c r="T38">
+      <c r="S38">
         <v>0</v>
       </c>
+      <c r="T38" t="s">
+        <v>1087</v>
+      </c>
       <c r="U38" t="s">
-        <v>1087</v>
+        <v>1093</v>
       </c>
       <c r="V38" t="s">
         <v>1093</v>
       </c>
-      <c r="W38" t="s">
+      <c r="W38">
+        <v>2</v>
+      </c>
+      <c r="Y38" t="str">
+        <f t="shared" ref="Y38:Y53" si="23">R$1&amp;"-"&amp;R38</f>
+        <v>dm-Lo</v>
+      </c>
+      <c r="Z38" t="str">
+        <f t="shared" si="10"/>
+        <v>cp-00</v>
+      </c>
+      <c r="AA38" t="str">
+        <f t="shared" ref="AA38:AA53" si="24">T38</f>
+        <v>CF1</v>
+      </c>
+      <c r="AB38" t="str">
+        <f t="shared" ref="AB38:AB53" si="25">U$1&amp;"-"&amp;U38</f>
+        <v>df-Y</v>
+      </c>
+      <c r="AC38" t="str">
+        <f t="shared" si="13"/>
+        <v>tc-2.00</v>
+      </c>
+    </row>
+    <row r="39" spans="2:29">
+      <c r="B39" t="str">
+        <f t="shared" si="16"/>
+        <v>vs~0034</v>
+      </c>
+      <c r="C39" t="str">
+        <f t="shared" si="17"/>
+        <v>tc-2.00.df-Y.dm-Hi.cp-00.CF1</v>
+      </c>
+      <c r="H39" t="str">
+        <f>_xlfn.TEXTJOIN(".",TRUE,AC39,AB39:AB39)&amp;"."&amp;_xlfn.TEXTJOIN(".",TRUE,Y39:AA39)</f>
+        <v>tc-2.00.df-Y.dm-Hi.cp-00.CF1</v>
+      </c>
+      <c r="I39" t="str">
+        <f t="shared" si="18"/>
+        <v>Hi</v>
+      </c>
+      <c r="J39" t="str">
+        <f t="shared" si="19"/>
+        <v>00</v>
+      </c>
+      <c r="K39" t="str">
+        <f t="shared" si="20"/>
+        <v>CF1</v>
+      </c>
+      <c r="L39" t="str">
+        <f t="shared" si="21"/>
+        <v>Y</v>
+      </c>
+      <c r="M39">
+        <f t="shared" si="22"/>
+        <v>2</v>
+      </c>
+      <c r="O39">
+        <v>5</v>
+      </c>
+      <c r="P39" t="s">
+        <v>1141</v>
+      </c>
+      <c r="Q39">
+        <v>34</v>
+      </c>
+      <c r="R39" t="s">
+        <v>1094</v>
+      </c>
+      <c r="S39">
+        <v>0</v>
+      </c>
+      <c r="T39" t="s">
+        <v>1087</v>
+      </c>
+      <c r="U39" t="s">
         <v>1093</v>
-      </c>
-      <c r="X38" t="s">
-        <v>1095</v>
-      </c>
-      <c r="Z38" t="str">
-        <f t="shared" ref="Z38:Z69" si="26">S$1&amp;"-"&amp;S38</f>
-        <v>dm-Lo</v>
-      </c>
-      <c r="AA38" t="str">
-        <f t="shared" ref="AA38:AA69" si="27">T$1&amp;"-"&amp;T38</f>
-        <v>cp-0</v>
-      </c>
-      <c r="AB38" t="str">
-        <f t="shared" ref="AB38:AB69" si="28">U38</f>
-        <v>CF1</v>
-      </c>
-      <c r="AC38" t="str">
-        <f t="shared" ref="AC38:AC69" si="29">V$1&amp;"-"&amp;V38</f>
-        <v>df-Y</v>
-      </c>
-      <c r="AD38" t="str">
-        <f t="shared" ref="AD38:AD69" si="30">W$1&amp;"-"&amp;W38</f>
-        <v>ga-Y</v>
-      </c>
-      <c r="AE38" t="str">
-        <f t="shared" ref="AE38:AE69" si="31">X$1&amp;"-"&amp;X38</f>
-        <v>tc-N</v>
-      </c>
-    </row>
-    <row r="39" spans="2:31">
-      <c r="B39" t="str">
-        <f t="shared" si="17"/>
-        <v>vs~0034</v>
-      </c>
-      <c r="C39" t="str">
-        <f t="shared" si="18"/>
-        <v>tc-N.df-Y.ga-Y.dm-Hi.cp-0.CF1</v>
-      </c>
-      <c r="H39" t="str">
-        <f t="shared" si="19"/>
-        <v>tc-N.df-Y.ga-Y.dm-Hi.cp-0.CF1</v>
-      </c>
-      <c r="I39" t="str">
-        <f t="shared" si="20"/>
-        <v>Hi</v>
-      </c>
-      <c r="J39" t="str">
-        <f t="shared" si="21"/>
-        <v>00</v>
-      </c>
-      <c r="K39" t="str">
-        <f t="shared" si="22"/>
-        <v>CF1</v>
-      </c>
-      <c r="L39" t="str">
-        <f t="shared" si="23"/>
-        <v>Y</v>
-      </c>
-      <c r="M39" t="str">
-        <f t="shared" si="24"/>
-        <v>Y</v>
-      </c>
-      <c r="N39" t="str">
-        <f t="shared" si="25"/>
-        <v>N</v>
-      </c>
-      <c r="P39">
-        <v>5</v>
-      </c>
-      <c r="Q39" t="s">
-        <v>1134</v>
-      </c>
-      <c r="R39">
-        <v>34</v>
-      </c>
-      <c r="S39" t="s">
-        <v>1094</v>
-      </c>
-      <c r="T39">
-        <v>0</v>
-      </c>
-      <c r="U39" t="s">
-        <v>1087</v>
       </c>
       <c r="V39" t="s">
         <v>1093</v>
       </c>
-      <c r="W39" t="s">
+      <c r="W39">
+        <v>2</v>
+      </c>
+      <c r="Y39" t="str">
+        <f t="shared" si="23"/>
+        <v>dm-Hi</v>
+      </c>
+      <c r="Z39" t="str">
+        <f t="shared" si="10"/>
+        <v>cp-00</v>
+      </c>
+      <c r="AA39" t="str">
+        <f t="shared" si="24"/>
+        <v>CF1</v>
+      </c>
+      <c r="AB39" t="str">
+        <f t="shared" si="25"/>
+        <v>df-Y</v>
+      </c>
+      <c r="AC39" t="str">
+        <f t="shared" si="13"/>
+        <v>tc-2.00</v>
+      </c>
+    </row>
+    <row r="40" spans="2:29">
+      <c r="B40" t="str">
+        <f t="shared" si="16"/>
+        <v>vs~0035</v>
+      </c>
+      <c r="C40" t="str">
+        <f t="shared" si="17"/>
+        <v>tc-2.00.df-Y.dm-Lo.cp-95.CF1</v>
+      </c>
+      <c r="H40" t="str">
+        <f>_xlfn.TEXTJOIN(".",TRUE,AC40,AB40:AB40)&amp;"."&amp;_xlfn.TEXTJOIN(".",TRUE,Y40:AA40)</f>
+        <v>tc-2.00.df-Y.dm-Lo.cp-95.CF1</v>
+      </c>
+      <c r="I40" t="str">
+        <f t="shared" si="18"/>
+        <v>Lo</v>
+      </c>
+      <c r="J40" t="str">
+        <f t="shared" si="19"/>
+        <v>95</v>
+      </c>
+      <c r="K40" t="str">
+        <f t="shared" si="20"/>
+        <v>CF1</v>
+      </c>
+      <c r="L40" t="str">
+        <f t="shared" si="21"/>
+        <v>Y</v>
+      </c>
+      <c r="M40">
+        <f t="shared" si="22"/>
+        <v>2</v>
+      </c>
+      <c r="O40">
+        <v>5</v>
+      </c>
+      <c r="P40" t="s">
+        <v>1142</v>
+      </c>
+      <c r="Q40">
+        <v>35</v>
+      </c>
+      <c r="R40" t="s">
+        <v>1092</v>
+      </c>
+      <c r="S40">
+        <v>95</v>
+      </c>
+      <c r="T40" t="s">
+        <v>1087</v>
+      </c>
+      <c r="U40" t="s">
         <v>1093</v>
-      </c>
-      <c r="X39" t="s">
-        <v>1095</v>
-      </c>
-      <c r="Z39" t="str">
-        <f t="shared" si="26"/>
-        <v>dm-Hi</v>
-      </c>
-      <c r="AA39" t="str">
-        <f t="shared" si="27"/>
-        <v>cp-0</v>
-      </c>
-      <c r="AB39" t="str">
-        <f t="shared" si="28"/>
-        <v>CF1</v>
-      </c>
-      <c r="AC39" t="str">
-        <f t="shared" si="29"/>
-        <v>df-Y</v>
-      </c>
-      <c r="AD39" t="str">
-        <f t="shared" si="30"/>
-        <v>ga-Y</v>
-      </c>
-      <c r="AE39" t="str">
-        <f t="shared" si="31"/>
-        <v>tc-N</v>
-      </c>
-    </row>
-    <row r="40" spans="2:31">
-      <c r="B40" t="str">
-        <f t="shared" si="17"/>
-        <v>vs~0035</v>
-      </c>
-      <c r="C40" t="str">
-        <f t="shared" si="18"/>
-        <v>tc-N.df-Y.ga-Y.dm-Lo.cp-95.CF1</v>
-      </c>
-      <c r="H40" t="str">
-        <f t="shared" si="19"/>
-        <v>tc-N.df-Y.ga-Y.dm-Lo.cp-95.CF1</v>
-      </c>
-      <c r="I40" t="str">
-        <f t="shared" si="20"/>
-        <v>Lo</v>
-      </c>
-      <c r="J40" t="str">
-        <f t="shared" si="21"/>
-        <v>95</v>
-      </c>
-      <c r="K40" t="str">
-        <f t="shared" si="22"/>
-        <v>CF1</v>
-      </c>
-      <c r="L40" t="str">
-        <f t="shared" si="23"/>
-        <v>Y</v>
-      </c>
-      <c r="M40" t="str">
-        <f t="shared" si="24"/>
-        <v>Y</v>
-      </c>
-      <c r="N40" t="str">
-        <f t="shared" si="25"/>
-        <v>N</v>
-      </c>
-      <c r="P40">
-        <v>5</v>
-      </c>
-      <c r="Q40" t="s">
-        <v>1135</v>
-      </c>
-      <c r="R40">
-        <v>35</v>
-      </c>
-      <c r="S40" t="s">
-        <v>1092</v>
-      </c>
-      <c r="T40">
-        <v>95</v>
-      </c>
-      <c r="U40" t="s">
-        <v>1087</v>
       </c>
       <c r="V40" t="s">
         <v>1093</v>
       </c>
-      <c r="W40" t="s">
+      <c r="W40">
+        <v>2</v>
+      </c>
+      <c r="Y40" t="str">
+        <f t="shared" si="23"/>
+        <v>dm-Lo</v>
+      </c>
+      <c r="Z40" t="str">
+        <f t="shared" si="10"/>
+        <v>cp-95</v>
+      </c>
+      <c r="AA40" t="str">
+        <f t="shared" si="24"/>
+        <v>CF1</v>
+      </c>
+      <c r="AB40" t="str">
+        <f t="shared" si="25"/>
+        <v>df-Y</v>
+      </c>
+      <c r="AC40" t="str">
+        <f t="shared" si="13"/>
+        <v>tc-2.00</v>
+      </c>
+    </row>
+    <row r="41" spans="2:29">
+      <c r="B41" t="str">
+        <f t="shared" si="16"/>
+        <v>vs~0036</v>
+      </c>
+      <c r="C41" t="str">
+        <f t="shared" si="17"/>
+        <v>tc-2.00.df-Y.dm-Hi.cp-95.CF1</v>
+      </c>
+      <c r="H41" t="str">
+        <f>_xlfn.TEXTJOIN(".",TRUE,AC41,AB41:AB41)&amp;"."&amp;_xlfn.TEXTJOIN(".",TRUE,Y41:AA41)</f>
+        <v>tc-2.00.df-Y.dm-Hi.cp-95.CF1</v>
+      </c>
+      <c r="I41" t="str">
+        <f t="shared" si="18"/>
+        <v>Hi</v>
+      </c>
+      <c r="J41" t="str">
+        <f t="shared" si="19"/>
+        <v>95</v>
+      </c>
+      <c r="K41" t="str">
+        <f t="shared" si="20"/>
+        <v>CF1</v>
+      </c>
+      <c r="L41" t="str">
+        <f t="shared" si="21"/>
+        <v>Y</v>
+      </c>
+      <c r="M41">
+        <f t="shared" si="22"/>
+        <v>2</v>
+      </c>
+      <c r="O41">
+        <v>5</v>
+      </c>
+      <c r="P41" t="s">
+        <v>1143</v>
+      </c>
+      <c r="Q41">
+        <v>36</v>
+      </c>
+      <c r="R41" t="s">
+        <v>1094</v>
+      </c>
+      <c r="S41">
+        <v>95</v>
+      </c>
+      <c r="T41" t="s">
+        <v>1087</v>
+      </c>
+      <c r="U41" t="s">
         <v>1093</v>
-      </c>
-      <c r="X40" t="s">
-        <v>1095</v>
-      </c>
-      <c r="Z40" t="str">
-        <f t="shared" si="26"/>
-        <v>dm-Lo</v>
-      </c>
-      <c r="AA40" t="str">
-        <f t="shared" si="27"/>
-        <v>cp-95</v>
-      </c>
-      <c r="AB40" t="str">
-        <f t="shared" si="28"/>
-        <v>CF1</v>
-      </c>
-      <c r="AC40" t="str">
-        <f t="shared" si="29"/>
-        <v>df-Y</v>
-      </c>
-      <c r="AD40" t="str">
-        <f t="shared" si="30"/>
-        <v>ga-Y</v>
-      </c>
-      <c r="AE40" t="str">
-        <f t="shared" si="31"/>
-        <v>tc-N</v>
-      </c>
-    </row>
-    <row r="41" spans="2:31">
-      <c r="B41" t="str">
-        <f t="shared" si="17"/>
-        <v>vs~0036</v>
-      </c>
-      <c r="C41" t="str">
-        <f t="shared" si="18"/>
-        <v>tc-N.df-Y.ga-Y.dm-Hi.cp-95.CF1</v>
-      </c>
-      <c r="H41" t="str">
-        <f t="shared" si="19"/>
-        <v>tc-N.df-Y.ga-Y.dm-Hi.cp-95.CF1</v>
-      </c>
-      <c r="I41" t="str">
-        <f t="shared" si="20"/>
-        <v>Hi</v>
-      </c>
-      <c r="J41" t="str">
-        <f t="shared" si="21"/>
-        <v>95</v>
-      </c>
-      <c r="K41" t="str">
-        <f t="shared" si="22"/>
-        <v>CF1</v>
-      </c>
-      <c r="L41" t="str">
-        <f t="shared" si="23"/>
-        <v>Y</v>
-      </c>
-      <c r="M41" t="str">
-        <f t="shared" si="24"/>
-        <v>Y</v>
-      </c>
-      <c r="N41" t="str">
-        <f t="shared" si="25"/>
-        <v>N</v>
-      </c>
-      <c r="P41">
-        <v>5</v>
-      </c>
-      <c r="Q41" t="s">
-        <v>1136</v>
-      </c>
-      <c r="R41">
-        <v>36</v>
-      </c>
-      <c r="S41" t="s">
-        <v>1094</v>
-      </c>
-      <c r="T41">
-        <v>95</v>
-      </c>
-      <c r="U41" t="s">
-        <v>1087</v>
       </c>
       <c r="V41" t="s">
         <v>1093</v>
       </c>
-      <c r="W41" t="s">
+      <c r="W41">
+        <v>2</v>
+      </c>
+      <c r="Y41" t="str">
+        <f t="shared" si="23"/>
+        <v>dm-Hi</v>
+      </c>
+      <c r="Z41" t="str">
+        <f t="shared" si="10"/>
+        <v>cp-95</v>
+      </c>
+      <c r="AA41" t="str">
+        <f t="shared" si="24"/>
+        <v>CF1</v>
+      </c>
+      <c r="AB41" t="str">
+        <f t="shared" si="25"/>
+        <v>df-Y</v>
+      </c>
+      <c r="AC41" t="str">
+        <f t="shared" si="13"/>
+        <v>tc-2.00</v>
+      </c>
+    </row>
+    <row r="42" spans="2:29">
+      <c r="B42" t="str">
+        <f t="shared" si="16"/>
+        <v>vs~0037</v>
+      </c>
+      <c r="C42" t="str">
+        <f t="shared" si="17"/>
+        <v>tc-2.00.df-N.dm-Lo.cp-00.CF1</v>
+      </c>
+      <c r="H42" t="str">
+        <f>_xlfn.TEXTJOIN(".",TRUE,AC42,AB42:AB42)&amp;"."&amp;_xlfn.TEXTJOIN(".",TRUE,Y42:AA42)</f>
+        <v>tc-2.00.df-N.dm-Lo.cp-00.CF1</v>
+      </c>
+      <c r="I42" t="str">
+        <f t="shared" si="18"/>
+        <v>Lo</v>
+      </c>
+      <c r="J42" t="str">
+        <f t="shared" si="19"/>
+        <v>00</v>
+      </c>
+      <c r="K42" t="str">
+        <f t="shared" si="20"/>
+        <v>CF1</v>
+      </c>
+      <c r="L42" t="str">
+        <f t="shared" si="21"/>
+        <v>N</v>
+      </c>
+      <c r="M42">
+        <f t="shared" si="22"/>
+        <v>2</v>
+      </c>
+      <c r="O42">
+        <v>5</v>
+      </c>
+      <c r="P42" t="s">
+        <v>1144</v>
+      </c>
+      <c r="Q42">
+        <v>37</v>
+      </c>
+      <c r="R42" t="s">
+        <v>1092</v>
+      </c>
+      <c r="S42">
+        <v>0</v>
+      </c>
+      <c r="T42" t="s">
+        <v>1087</v>
+      </c>
+      <c r="U42" t="s">
+        <v>1095</v>
+      </c>
+      <c r="V42" t="s">
         <v>1093</v>
       </c>
-      <c r="X41" t="s">
+      <c r="W42">
+        <v>2</v>
+      </c>
+      <c r="Y42" t="str">
+        <f t="shared" si="23"/>
+        <v>dm-Lo</v>
+      </c>
+      <c r="Z42" t="str">
+        <f t="shared" si="10"/>
+        <v>cp-00</v>
+      </c>
+      <c r="AA42" t="str">
+        <f t="shared" si="24"/>
+        <v>CF1</v>
+      </c>
+      <c r="AB42" t="str">
+        <f t="shared" si="25"/>
+        <v>df-N</v>
+      </c>
+      <c r="AC42" t="str">
+        <f t="shared" si="13"/>
+        <v>tc-2.00</v>
+      </c>
+    </row>
+    <row r="43" spans="2:29">
+      <c r="B43" t="str">
+        <f t="shared" si="16"/>
+        <v>vs~0038</v>
+      </c>
+      <c r="C43" t="str">
+        <f t="shared" si="17"/>
+        <v>tc-2.00.df-N.dm-Hi.cp-00.CF1</v>
+      </c>
+      <c r="H43" t="str">
+        <f>_xlfn.TEXTJOIN(".",TRUE,AC43,AB43:AB43)&amp;"."&amp;_xlfn.TEXTJOIN(".",TRUE,Y43:AA43)</f>
+        <v>tc-2.00.df-N.dm-Hi.cp-00.CF1</v>
+      </c>
+      <c r="I43" t="str">
+        <f t="shared" si="18"/>
+        <v>Hi</v>
+      </c>
+      <c r="J43" t="str">
+        <f t="shared" si="19"/>
+        <v>00</v>
+      </c>
+      <c r="K43" t="str">
+        <f t="shared" si="20"/>
+        <v>CF1</v>
+      </c>
+      <c r="L43" t="str">
+        <f t="shared" si="21"/>
+        <v>N</v>
+      </c>
+      <c r="M43">
+        <f t="shared" si="22"/>
+        <v>2</v>
+      </c>
+      <c r="O43">
+        <v>5</v>
+      </c>
+      <c r="P43" t="s">
+        <v>1145</v>
+      </c>
+      <c r="Q43">
+        <v>38</v>
+      </c>
+      <c r="R43" t="s">
+        <v>1094</v>
+      </c>
+      <c r="S43">
+        <v>0</v>
+      </c>
+      <c r="T43" t="s">
+        <v>1087</v>
+      </c>
+      <c r="U43" t="s">
         <v>1095</v>
       </c>
-      <c r="Z41" t="str">
-        <f t="shared" si="26"/>
+      <c r="V43" t="s">
+        <v>1093</v>
+      </c>
+      <c r="W43">
+        <v>2</v>
+      </c>
+      <c r="Y43" t="str">
+        <f t="shared" si="23"/>
         <v>dm-Hi</v>
       </c>
-      <c r="AA41" t="str">
-        <f t="shared" si="27"/>
+      <c r="Z43" t="str">
+        <f t="shared" si="10"/>
+        <v>cp-00</v>
+      </c>
+      <c r="AA43" t="str">
+        <f t="shared" si="24"/>
+        <v>CF1</v>
+      </c>
+      <c r="AB43" t="str">
+        <f t="shared" si="25"/>
+        <v>df-N</v>
+      </c>
+      <c r="AC43" t="str">
+        <f t="shared" si="13"/>
+        <v>tc-2.00</v>
+      </c>
+    </row>
+    <row r="44" spans="2:29">
+      <c r="B44" t="str">
+        <f t="shared" si="16"/>
+        <v>vs~0039</v>
+      </c>
+      <c r="C44" t="str">
+        <f t="shared" si="17"/>
+        <v>tc-2.00.df-N.dm-Lo.cp-95.CF1</v>
+      </c>
+      <c r="H44" t="str">
+        <f>_xlfn.TEXTJOIN(".",TRUE,AC44,AB44:AB44)&amp;"."&amp;_xlfn.TEXTJOIN(".",TRUE,Y44:AA44)</f>
+        <v>tc-2.00.df-N.dm-Lo.cp-95.CF1</v>
+      </c>
+      <c r="I44" t="str">
+        <f t="shared" si="18"/>
+        <v>Lo</v>
+      </c>
+      <c r="J44" t="str">
+        <f t="shared" si="19"/>
+        <v>95</v>
+      </c>
+      <c r="K44" t="str">
+        <f t="shared" si="20"/>
+        <v>CF1</v>
+      </c>
+      <c r="L44" t="str">
+        <f t="shared" si="21"/>
+        <v>N</v>
+      </c>
+      <c r="M44">
+        <f t="shared" si="22"/>
+        <v>2</v>
+      </c>
+      <c r="O44">
+        <v>5</v>
+      </c>
+      <c r="P44" t="s">
+        <v>1146</v>
+      </c>
+      <c r="Q44">
+        <v>39</v>
+      </c>
+      <c r="R44" t="s">
+        <v>1092</v>
+      </c>
+      <c r="S44">
+        <v>95</v>
+      </c>
+      <c r="T44" t="s">
+        <v>1087</v>
+      </c>
+      <c r="U44" t="s">
+        <v>1095</v>
+      </c>
+      <c r="V44" t="s">
+        <v>1093</v>
+      </c>
+      <c r="W44">
+        <v>2</v>
+      </c>
+      <c r="Y44" t="str">
+        <f t="shared" si="23"/>
+        <v>dm-Lo</v>
+      </c>
+      <c r="Z44" t="str">
+        <f t="shared" si="10"/>
         <v>cp-95</v>
       </c>
-      <c r="AB41" t="str">
-        <f t="shared" si="28"/>
+      <c r="AA44" t="str">
+        <f t="shared" si="24"/>
         <v>CF1</v>
       </c>
-      <c r="AC41" t="str">
-        <f t="shared" si="29"/>
-        <v>df-Y</v>
-      </c>
-      <c r="AD41" t="str">
-        <f t="shared" si="30"/>
-        <v>ga-Y</v>
-      </c>
-      <c r="AE41" t="str">
-        <f t="shared" si="31"/>
-        <v>tc-N</v>
-      </c>
-    </row>
-    <row r="42" spans="2:31">
-      <c r="B42" t="str">
+      <c r="AB44" t="str">
+        <f t="shared" si="25"/>
+        <v>df-N</v>
+      </c>
+      <c r="AC44" t="str">
+        <f t="shared" si="13"/>
+        <v>tc-2.00</v>
+      </c>
+    </row>
+    <row r="45" spans="2:29">
+      <c r="B45" t="str">
+        <f t="shared" si="16"/>
+        <v>vs~0040</v>
+      </c>
+      <c r="C45" t="str">
         <f t="shared" si="17"/>
-        <v>vs~0037</v>
-      </c>
-      <c r="C42" t="str">
+        <v>tc-2.00.df-N.dm-Hi.cp-95.CF1</v>
+      </c>
+      <c r="H45" t="str">
+        <f>_xlfn.TEXTJOIN(".",TRUE,AC45,AB45:AB45)&amp;"."&amp;_xlfn.TEXTJOIN(".",TRUE,Y45:AA45)</f>
+        <v>tc-2.00.df-N.dm-Hi.cp-95.CF1</v>
+      </c>
+      <c r="I45" t="str">
         <f t="shared" si="18"/>
-        <v>tc-N.df-N.ga-Y.dm-Lo.cp-0.CF1</v>
-      </c>
-      <c r="H42" t="str">
+        <v>Hi</v>
+      </c>
+      <c r="J45" t="str">
         <f t="shared" si="19"/>
-        <v>tc-N.df-N.ga-Y.dm-Lo.cp-0.CF1</v>
-      </c>
-      <c r="I42" t="str">
+        <v>95</v>
+      </c>
+      <c r="K45" t="str">
         <f t="shared" si="20"/>
+        <v>CF1</v>
+      </c>
+      <c r="L45" t="str">
+        <f t="shared" si="21"/>
+        <v>N</v>
+      </c>
+      <c r="M45">
+        <f t="shared" si="22"/>
+        <v>2</v>
+      </c>
+      <c r="O45">
+        <v>5</v>
+      </c>
+      <c r="P45" t="s">
+        <v>1147</v>
+      </c>
+      <c r="Q45">
+        <v>40</v>
+      </c>
+      <c r="R45" t="s">
+        <v>1094</v>
+      </c>
+      <c r="S45">
+        <v>95</v>
+      </c>
+      <c r="T45" t="s">
+        <v>1087</v>
+      </c>
+      <c r="U45" t="s">
+        <v>1095</v>
+      </c>
+      <c r="V45" t="s">
+        <v>1093</v>
+      </c>
+      <c r="W45">
+        <v>2</v>
+      </c>
+      <c r="Y45" t="str">
+        <f t="shared" si="23"/>
+        <v>dm-Hi</v>
+      </c>
+      <c r="Z45" t="str">
+        <f t="shared" si="10"/>
+        <v>cp-95</v>
+      </c>
+      <c r="AA45" t="str">
+        <f t="shared" si="24"/>
+        <v>CF1</v>
+      </c>
+      <c r="AB45" t="str">
+        <f t="shared" si="25"/>
+        <v>df-N</v>
+      </c>
+      <c r="AC45" t="str">
+        <f t="shared" si="13"/>
+        <v>tc-2.00</v>
+      </c>
+    </row>
+    <row r="46" spans="2:29">
+      <c r="B46" t="str">
+        <f t="shared" si="16"/>
+        <v>vs~0041</v>
+      </c>
+      <c r="C46" t="str">
+        <f t="shared" si="17"/>
+        <v>tc-2.00.df-Y.dm-Lo.cp-00.CF6</v>
+      </c>
+      <c r="H46" t="str">
+        <f>_xlfn.TEXTJOIN(".",TRUE,AC46,AB46:AB46)&amp;"."&amp;_xlfn.TEXTJOIN(".",TRUE,Y46:AA46)</f>
+        <v>tc-2.00.df-Y.dm-Lo.cp-00.CF6</v>
+      </c>
+      <c r="I46" t="str">
+        <f t="shared" si="18"/>
         <v>Lo</v>
       </c>
-      <c r="J42" t="str">
+      <c r="J46" t="str">
+        <f t="shared" si="19"/>
+        <v>00</v>
+      </c>
+      <c r="K46" t="str">
+        <f t="shared" si="20"/>
+        <v>CF6</v>
+      </c>
+      <c r="L46" t="str">
         <f t="shared" si="21"/>
-        <v>00</v>
-      </c>
-      <c r="K42" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M46">
         <f t="shared" si="22"/>
-        <v>CF1</v>
-      </c>
-      <c r="L42" t="str">
-        <f t="shared" si="23"/>
-        <v>N</v>
-      </c>
-      <c r="M42" t="str">
-        <f t="shared" si="24"/>
-        <v>Y</v>
-      </c>
-      <c r="N42" t="str">
-        <f t="shared" si="25"/>
-        <v>N</v>
-      </c>
-      <c r="P42">
+        <v>2</v>
+      </c>
+      <c r="O46">
         <v>5</v>
       </c>
-      <c r="Q42" t="s">
-        <v>1137</v>
-      </c>
-      <c r="R42">
-        <v>37</v>
-      </c>
-      <c r="S42" t="s">
+      <c r="P46" t="s">
+        <v>1148</v>
+      </c>
+      <c r="Q46">
+        <v>41</v>
+      </c>
+      <c r="R46" t="s">
         <v>1092</v>
       </c>
-      <c r="T42">
+      <c r="S46">
         <v>0</v>
       </c>
-      <c r="U42" t="s">
-        <v>1087</v>
-      </c>
-      <c r="V42" t="s">
-        <v>1095</v>
-      </c>
-      <c r="W42" t="s">
+      <c r="T46" t="s">
+        <v>1088</v>
+      </c>
+      <c r="U46" t="s">
         <v>1093</v>
-      </c>
-      <c r="X42" t="s">
-        <v>1095</v>
-      </c>
-      <c r="Z42" t="str">
-        <f t="shared" si="26"/>
-        <v>dm-Lo</v>
-      </c>
-      <c r="AA42" t="str">
-        <f t="shared" si="27"/>
-        <v>cp-0</v>
-      </c>
-      <c r="AB42" t="str">
-        <f t="shared" si="28"/>
-        <v>CF1</v>
-      </c>
-      <c r="AC42" t="str">
-        <f t="shared" si="29"/>
-        <v>df-N</v>
-      </c>
-      <c r="AD42" t="str">
-        <f t="shared" si="30"/>
-        <v>ga-Y</v>
-      </c>
-      <c r="AE42" t="str">
-        <f t="shared" si="31"/>
-        <v>tc-N</v>
-      </c>
-    </row>
-    <row r="43" spans="2:31">
-      <c r="B43" t="str">
-        <f t="shared" si="17"/>
-        <v>vs~0038</v>
-      </c>
-      <c r="C43" t="str">
-        <f t="shared" si="18"/>
-        <v>tc-N.df-N.ga-Y.dm-Hi.cp-0.CF1</v>
-      </c>
-      <c r="H43" t="str">
-        <f t="shared" si="19"/>
-        <v>tc-N.df-N.ga-Y.dm-Hi.cp-0.CF1</v>
-      </c>
-      <c r="I43" t="str">
-        <f t="shared" si="20"/>
-        <v>Hi</v>
-      </c>
-      <c r="J43" t="str">
-        <f t="shared" si="21"/>
-        <v>00</v>
-      </c>
-      <c r="K43" t="str">
-        <f t="shared" si="22"/>
-        <v>CF1</v>
-      </c>
-      <c r="L43" t="str">
-        <f t="shared" si="23"/>
-        <v>N</v>
-      </c>
-      <c r="M43" t="str">
-        <f t="shared" si="24"/>
-        <v>Y</v>
-      </c>
-      <c r="N43" t="str">
-        <f t="shared" si="25"/>
-        <v>N</v>
-      </c>
-      <c r="P43">
-        <v>5</v>
-      </c>
-      <c r="Q43" t="s">
-        <v>1138</v>
-      </c>
-      <c r="R43">
-        <v>38</v>
-      </c>
-      <c r="S43" t="s">
-        <v>1094</v>
-      </c>
-      <c r="T43">
-        <v>0</v>
-      </c>
-      <c r="U43" t="s">
-        <v>1087</v>
-      </c>
-      <c r="V43" t="s">
-        <v>1095</v>
-      </c>
-      <c r="W43" t="s">
-        <v>1093</v>
-      </c>
-      <c r="X43" t="s">
-        <v>1095</v>
-      </c>
-      <c r="Z43" t="str">
-        <f t="shared" si="26"/>
-        <v>dm-Hi</v>
-      </c>
-      <c r="AA43" t="str">
-        <f t="shared" si="27"/>
-        <v>cp-0</v>
-      </c>
-      <c r="AB43" t="str">
-        <f t="shared" si="28"/>
-        <v>CF1</v>
-      </c>
-      <c r="AC43" t="str">
-        <f t="shared" si="29"/>
-        <v>df-N</v>
-      </c>
-      <c r="AD43" t="str">
-        <f t="shared" si="30"/>
-        <v>ga-Y</v>
-      </c>
-      <c r="AE43" t="str">
-        <f t="shared" si="31"/>
-        <v>tc-N</v>
-      </c>
-    </row>
-    <row r="44" spans="2:31">
-      <c r="B44" t="str">
-        <f t="shared" si="17"/>
-        <v>vs~0039</v>
-      </c>
-      <c r="C44" t="str">
-        <f t="shared" si="18"/>
-        <v>tc-N.df-N.ga-Y.dm-Lo.cp-95.CF1</v>
-      </c>
-      <c r="H44" t="str">
-        <f t="shared" si="19"/>
-        <v>tc-N.df-N.ga-Y.dm-Lo.cp-95.CF1</v>
-      </c>
-      <c r="I44" t="str">
-        <f t="shared" si="20"/>
-        <v>Lo</v>
-      </c>
-      <c r="J44" t="str">
-        <f t="shared" si="21"/>
-        <v>95</v>
-      </c>
-      <c r="K44" t="str">
-        <f t="shared" si="22"/>
-        <v>CF1</v>
-      </c>
-      <c r="L44" t="str">
-        <f t="shared" si="23"/>
-        <v>N</v>
-      </c>
-      <c r="M44" t="str">
-        <f t="shared" si="24"/>
-        <v>Y</v>
-      </c>
-      <c r="N44" t="str">
-        <f t="shared" si="25"/>
-        <v>N</v>
-      </c>
-      <c r="P44">
-        <v>5</v>
-      </c>
-      <c r="Q44" t="s">
-        <v>1139</v>
-      </c>
-      <c r="R44">
-        <v>39</v>
-      </c>
-      <c r="S44" t="s">
-        <v>1092</v>
-      </c>
-      <c r="T44">
-        <v>95</v>
-      </c>
-      <c r="U44" t="s">
-        <v>1087</v>
-      </c>
-      <c r="V44" t="s">
-        <v>1095</v>
-      </c>
-      <c r="W44" t="s">
-        <v>1093</v>
-      </c>
-      <c r="X44" t="s">
-        <v>1095</v>
-      </c>
-      <c r="Z44" t="str">
-        <f t="shared" si="26"/>
-        <v>dm-Lo</v>
-      </c>
-      <c r="AA44" t="str">
-        <f t="shared" si="27"/>
-        <v>cp-95</v>
-      </c>
-      <c r="AB44" t="str">
-        <f t="shared" si="28"/>
-        <v>CF1</v>
-      </c>
-      <c r="AC44" t="str">
-        <f t="shared" si="29"/>
-        <v>df-N</v>
-      </c>
-      <c r="AD44" t="str">
-        <f t="shared" si="30"/>
-        <v>ga-Y</v>
-      </c>
-      <c r="AE44" t="str">
-        <f t="shared" si="31"/>
-        <v>tc-N</v>
-      </c>
-    </row>
-    <row r="45" spans="2:31">
-      <c r="B45" t="str">
-        <f t="shared" si="17"/>
-        <v>vs~0040</v>
-      </c>
-      <c r="C45" t="str">
-        <f t="shared" si="18"/>
-        <v>tc-N.df-N.ga-Y.dm-Hi.cp-95.CF1</v>
-      </c>
-      <c r="H45" t="str">
-        <f t="shared" si="19"/>
-        <v>tc-N.df-N.ga-Y.dm-Hi.cp-95.CF1</v>
-      </c>
-      <c r="I45" t="str">
-        <f t="shared" si="20"/>
-        <v>Hi</v>
-      </c>
-      <c r="J45" t="str">
-        <f t="shared" si="21"/>
-        <v>95</v>
-      </c>
-      <c r="K45" t="str">
-        <f t="shared" si="22"/>
-        <v>CF1</v>
-      </c>
-      <c r="L45" t="str">
-        <f t="shared" si="23"/>
-        <v>N</v>
-      </c>
-      <c r="M45" t="str">
-        <f t="shared" si="24"/>
-        <v>Y</v>
-      </c>
-      <c r="N45" t="str">
-        <f t="shared" si="25"/>
-        <v>N</v>
-      </c>
-      <c r="P45">
-        <v>5</v>
-      </c>
-      <c r="Q45" t="s">
-        <v>1140</v>
-      </c>
-      <c r="R45">
-        <v>40</v>
-      </c>
-      <c r="S45" t="s">
-        <v>1094</v>
-      </c>
-      <c r="T45">
-        <v>95</v>
-      </c>
-      <c r="U45" t="s">
-        <v>1087</v>
-      </c>
-      <c r="V45" t="s">
-        <v>1095</v>
-      </c>
-      <c r="W45" t="s">
-        <v>1093</v>
-      </c>
-      <c r="X45" t="s">
-        <v>1095</v>
-      </c>
-      <c r="Z45" t="str">
-        <f t="shared" si="26"/>
-        <v>dm-Hi</v>
-      </c>
-      <c r="AA45" t="str">
-        <f t="shared" si="27"/>
-        <v>cp-95</v>
-      </c>
-      <c r="AB45" t="str">
-        <f t="shared" si="28"/>
-        <v>CF1</v>
-      </c>
-      <c r="AC45" t="str">
-        <f t="shared" si="29"/>
-        <v>df-N</v>
-      </c>
-      <c r="AD45" t="str">
-        <f t="shared" si="30"/>
-        <v>ga-Y</v>
-      </c>
-      <c r="AE45" t="str">
-        <f t="shared" si="31"/>
-        <v>tc-N</v>
-      </c>
-    </row>
-    <row r="46" spans="2:31">
-      <c r="B46" t="str">
-        <f t="shared" si="17"/>
-        <v>vs~0041</v>
-      </c>
-      <c r="C46" t="str">
-        <f t="shared" si="18"/>
-        <v>tc-N.df-Y.ga-Y.dm-Lo.cp-0.CF6</v>
-      </c>
-      <c r="H46" t="str">
-        <f t="shared" si="19"/>
-        <v>tc-N.df-Y.ga-Y.dm-Lo.cp-0.CF6</v>
-      </c>
-      <c r="I46" t="str">
-        <f t="shared" si="20"/>
-        <v>Lo</v>
-      </c>
-      <c r="J46" t="str">
-        <f t="shared" si="21"/>
-        <v>00</v>
-      </c>
-      <c r="K46" t="str">
-        <f t="shared" si="22"/>
-        <v>CF6</v>
-      </c>
-      <c r="L46" t="str">
-        <f t="shared" si="23"/>
-        <v>Y</v>
-      </c>
-      <c r="M46" t="str">
-        <f t="shared" si="24"/>
-        <v>Y</v>
-      </c>
-      <c r="N46" t="str">
-        <f t="shared" si="25"/>
-        <v>N</v>
-      </c>
-      <c r="P46">
-        <v>5</v>
-      </c>
-      <c r="Q46" t="s">
-        <v>1141</v>
-      </c>
-      <c r="R46">
-        <v>41</v>
-      </c>
-      <c r="S46" t="s">
-        <v>1092</v>
-      </c>
-      <c r="T46">
-        <v>0</v>
-      </c>
-      <c r="U46" t="s">
-        <v>1088</v>
       </c>
       <c r="V46" t="s">
         <v>1093</v>
       </c>
-      <c r="W46" t="s">
+      <c r="W46">
+        <v>2</v>
+      </c>
+      <c r="Y46" t="str">
+        <f t="shared" si="23"/>
+        <v>dm-Lo</v>
+      </c>
+      <c r="Z46" t="str">
+        <f t="shared" si="10"/>
+        <v>cp-00</v>
+      </c>
+      <c r="AA46" t="str">
+        <f t="shared" si="24"/>
+        <v>CF6</v>
+      </c>
+      <c r="AB46" t="str">
+        <f t="shared" si="25"/>
+        <v>df-Y</v>
+      </c>
+      <c r="AC46" t="str">
+        <f t="shared" si="13"/>
+        <v>tc-2.00</v>
+      </c>
+    </row>
+    <row r="47" spans="2:29">
+      <c r="B47" t="str">
+        <f t="shared" si="16"/>
+        <v>vs~0042</v>
+      </c>
+      <c r="C47" t="str">
+        <f t="shared" si="17"/>
+        <v>tc-2.00.df-Y.dm-Hi.cp-00.CF6</v>
+      </c>
+      <c r="H47" t="str">
+        <f>_xlfn.TEXTJOIN(".",TRUE,AC47,AB47:AB47)&amp;"."&amp;_xlfn.TEXTJOIN(".",TRUE,Y47:AA47)</f>
+        <v>tc-2.00.df-Y.dm-Hi.cp-00.CF6</v>
+      </c>
+      <c r="I47" t="str">
+        <f t="shared" si="18"/>
+        <v>Hi</v>
+      </c>
+      <c r="J47" t="str">
+        <f t="shared" si="19"/>
+        <v>00</v>
+      </c>
+      <c r="K47" t="str">
+        <f t="shared" si="20"/>
+        <v>CF6</v>
+      </c>
+      <c r="L47" t="str">
+        <f t="shared" si="21"/>
+        <v>Y</v>
+      </c>
+      <c r="M47">
+        <f t="shared" si="22"/>
+        <v>2</v>
+      </c>
+      <c r="O47">
+        <v>5</v>
+      </c>
+      <c r="P47" t="s">
+        <v>1149</v>
+      </c>
+      <c r="Q47">
+        <v>42</v>
+      </c>
+      <c r="R47" t="s">
+        <v>1094</v>
+      </c>
+      <c r="S47">
+        <v>0</v>
+      </c>
+      <c r="T47" t="s">
+        <v>1088</v>
+      </c>
+      <c r="U47" t="s">
         <v>1093</v>
-      </c>
-      <c r="X46" t="s">
-        <v>1095</v>
-      </c>
-      <c r="Z46" t="str">
-        <f t="shared" si="26"/>
-        <v>dm-Lo</v>
-      </c>
-      <c r="AA46" t="str">
-        <f t="shared" si="27"/>
-        <v>cp-0</v>
-      </c>
-      <c r="AB46" t="str">
-        <f t="shared" si="28"/>
-        <v>CF6</v>
-      </c>
-      <c r="AC46" t="str">
-        <f t="shared" si="29"/>
-        <v>df-Y</v>
-      </c>
-      <c r="AD46" t="str">
-        <f t="shared" si="30"/>
-        <v>ga-Y</v>
-      </c>
-      <c r="AE46" t="str">
-        <f t="shared" si="31"/>
-        <v>tc-N</v>
-      </c>
-    </row>
-    <row r="47" spans="2:31">
-      <c r="B47" t="str">
-        <f t="shared" si="17"/>
-        <v>vs~0042</v>
-      </c>
-      <c r="C47" t="str">
-        <f t="shared" si="18"/>
-        <v>tc-N.df-Y.ga-Y.dm-Hi.cp-0.CF6</v>
-      </c>
-      <c r="H47" t="str">
-        <f t="shared" si="19"/>
-        <v>tc-N.df-Y.ga-Y.dm-Hi.cp-0.CF6</v>
-      </c>
-      <c r="I47" t="str">
-        <f t="shared" si="20"/>
-        <v>Hi</v>
-      </c>
-      <c r="J47" t="str">
-        <f t="shared" si="21"/>
-        <v>00</v>
-      </c>
-      <c r="K47" t="str">
-        <f t="shared" si="22"/>
-        <v>CF6</v>
-      </c>
-      <c r="L47" t="str">
-        <f t="shared" si="23"/>
-        <v>Y</v>
-      </c>
-      <c r="M47" t="str">
-        <f t="shared" si="24"/>
-        <v>Y</v>
-      </c>
-      <c r="N47" t="str">
-        <f t="shared" si="25"/>
-        <v>N</v>
-      </c>
-      <c r="P47">
-        <v>5</v>
-      </c>
-      <c r="Q47" t="s">
-        <v>1142</v>
-      </c>
-      <c r="R47">
-        <v>42</v>
-      </c>
-      <c r="S47" t="s">
-        <v>1094</v>
-      </c>
-      <c r="T47">
-        <v>0</v>
-      </c>
-      <c r="U47" t="s">
-        <v>1088</v>
       </c>
       <c r="V47" t="s">
         <v>1093</v>
       </c>
-      <c r="W47" t="s">
+      <c r="W47">
+        <v>2</v>
+      </c>
+      <c r="Y47" t="str">
+        <f t="shared" si="23"/>
+        <v>dm-Hi</v>
+      </c>
+      <c r="Z47" t="str">
+        <f t="shared" si="10"/>
+        <v>cp-00</v>
+      </c>
+      <c r="AA47" t="str">
+        <f t="shared" si="24"/>
+        <v>CF6</v>
+      </c>
+      <c r="AB47" t="str">
+        <f t="shared" si="25"/>
+        <v>df-Y</v>
+      </c>
+      <c r="AC47" t="str">
+        <f t="shared" si="13"/>
+        <v>tc-2.00</v>
+      </c>
+    </row>
+    <row r="48" spans="2:29">
+      <c r="B48" t="str">
+        <f t="shared" si="16"/>
+        <v>vs~0043</v>
+      </c>
+      <c r="C48" t="str">
+        <f t="shared" si="17"/>
+        <v>tc-2.00.df-Y.dm-Lo.cp-95.CF6</v>
+      </c>
+      <c r="H48" t="str">
+        <f>_xlfn.TEXTJOIN(".",TRUE,AC48,AB48:AB48)&amp;"."&amp;_xlfn.TEXTJOIN(".",TRUE,Y48:AA48)</f>
+        <v>tc-2.00.df-Y.dm-Lo.cp-95.CF6</v>
+      </c>
+      <c r="I48" t="str">
+        <f t="shared" si="18"/>
+        <v>Lo</v>
+      </c>
+      <c r="J48" t="str">
+        <f t="shared" si="19"/>
+        <v>95</v>
+      </c>
+      <c r="K48" t="str">
+        <f t="shared" si="20"/>
+        <v>CF6</v>
+      </c>
+      <c r="L48" t="str">
+        <f t="shared" si="21"/>
+        <v>Y</v>
+      </c>
+      <c r="M48">
+        <f t="shared" si="22"/>
+        <v>2</v>
+      </c>
+      <c r="O48">
+        <v>5</v>
+      </c>
+      <c r="P48" t="s">
+        <v>1150</v>
+      </c>
+      <c r="Q48">
+        <v>43</v>
+      </c>
+      <c r="R48" t="s">
+        <v>1092</v>
+      </c>
+      <c r="S48">
+        <v>95</v>
+      </c>
+      <c r="T48" t="s">
+        <v>1088</v>
+      </c>
+      <c r="U48" t="s">
         <v>1093</v>
-      </c>
-      <c r="X47" t="s">
-        <v>1095</v>
-      </c>
-      <c r="Z47" t="str">
-        <f t="shared" si="26"/>
-        <v>dm-Hi</v>
-      </c>
-      <c r="AA47" t="str">
-        <f t="shared" si="27"/>
-        <v>cp-0</v>
-      </c>
-      <c r="AB47" t="str">
-        <f t="shared" si="28"/>
-        <v>CF6</v>
-      </c>
-      <c r="AC47" t="str">
-        <f t="shared" si="29"/>
-        <v>df-Y</v>
-      </c>
-      <c r="AD47" t="str">
-        <f t="shared" si="30"/>
-        <v>ga-Y</v>
-      </c>
-      <c r="AE47" t="str">
-        <f t="shared" si="31"/>
-        <v>tc-N</v>
-      </c>
-    </row>
-    <row r="48" spans="2:31">
-      <c r="B48" t="str">
-        <f t="shared" si="17"/>
-        <v>vs~0043</v>
-      </c>
-      <c r="C48" t="str">
-        <f t="shared" si="18"/>
-        <v>tc-N.df-Y.ga-Y.dm-Lo.cp-95.CF6</v>
-      </c>
-      <c r="H48" t="str">
-        <f t="shared" si="19"/>
-        <v>tc-N.df-Y.ga-Y.dm-Lo.cp-95.CF6</v>
-      </c>
-      <c r="I48" t="str">
-        <f t="shared" si="20"/>
-        <v>Lo</v>
-      </c>
-      <c r="J48" t="str">
-        <f t="shared" si="21"/>
-        <v>95</v>
-      </c>
-      <c r="K48" t="str">
-        <f t="shared" si="22"/>
-        <v>CF6</v>
-      </c>
-      <c r="L48" t="str">
-        <f t="shared" si="23"/>
-        <v>Y</v>
-      </c>
-      <c r="M48" t="str">
-        <f t="shared" si="24"/>
-        <v>Y</v>
-      </c>
-      <c r="N48" t="str">
-        <f t="shared" si="25"/>
-        <v>N</v>
-      </c>
-      <c r="P48">
-        <v>5</v>
-      </c>
-      <c r="Q48" t="s">
-        <v>1143</v>
-      </c>
-      <c r="R48">
-        <v>43</v>
-      </c>
-      <c r="S48" t="s">
-        <v>1092</v>
-      </c>
-      <c r="T48">
-        <v>95</v>
-      </c>
-      <c r="U48" t="s">
-        <v>1088</v>
       </c>
       <c r="V48" t="s">
         <v>1093</v>
       </c>
-      <c r="W48" t="s">
+      <c r="W48">
+        <v>2</v>
+      </c>
+      <c r="Y48" t="str">
+        <f t="shared" si="23"/>
+        <v>dm-Lo</v>
+      </c>
+      <c r="Z48" t="str">
+        <f t="shared" si="10"/>
+        <v>cp-95</v>
+      </c>
+      <c r="AA48" t="str">
+        <f t="shared" si="24"/>
+        <v>CF6</v>
+      </c>
+      <c r="AB48" t="str">
+        <f t="shared" si="25"/>
+        <v>df-Y</v>
+      </c>
+      <c r="AC48" t="str">
+        <f t="shared" si="13"/>
+        <v>tc-2.00</v>
+      </c>
+    </row>
+    <row r="49" spans="2:29">
+      <c r="B49" t="str">
+        <f t="shared" si="16"/>
+        <v>vs~0044</v>
+      </c>
+      <c r="C49" t="str">
+        <f t="shared" si="17"/>
+        <v>tc-2.00.df-Y.dm-Hi.cp-95.CF6</v>
+      </c>
+      <c r="H49" t="str">
+        <f>_xlfn.TEXTJOIN(".",TRUE,AC49,AB49:AB49)&amp;"."&amp;_xlfn.TEXTJOIN(".",TRUE,Y49:AA49)</f>
+        <v>tc-2.00.df-Y.dm-Hi.cp-95.CF6</v>
+      </c>
+      <c r="I49" t="str">
+        <f t="shared" si="18"/>
+        <v>Hi</v>
+      </c>
+      <c r="J49" t="str">
+        <f t="shared" si="19"/>
+        <v>95</v>
+      </c>
+      <c r="K49" t="str">
+        <f t="shared" si="20"/>
+        <v>CF6</v>
+      </c>
+      <c r="L49" t="str">
+        <f t="shared" si="21"/>
+        <v>Y</v>
+      </c>
+      <c r="M49">
+        <f t="shared" si="22"/>
+        <v>2</v>
+      </c>
+      <c r="O49">
+        <v>5</v>
+      </c>
+      <c r="P49" t="s">
+        <v>1151</v>
+      </c>
+      <c r="Q49">
+        <v>44</v>
+      </c>
+      <c r="R49" t="s">
+        <v>1094</v>
+      </c>
+      <c r="S49">
+        <v>95</v>
+      </c>
+      <c r="T49" t="s">
+        <v>1088</v>
+      </c>
+      <c r="U49" t="s">
         <v>1093</v>
-      </c>
-      <c r="X48" t="s">
-        <v>1095</v>
-      </c>
-      <c r="Z48" t="str">
-        <f t="shared" si="26"/>
-        <v>dm-Lo</v>
-      </c>
-      <c r="AA48" t="str">
-        <f t="shared" si="27"/>
-        <v>cp-95</v>
-      </c>
-      <c r="AB48" t="str">
-        <f t="shared" si="28"/>
-        <v>CF6</v>
-      </c>
-      <c r="AC48" t="str">
-        <f t="shared" si="29"/>
-        <v>df-Y</v>
-      </c>
-      <c r="AD48" t="str">
-        <f t="shared" si="30"/>
-        <v>ga-Y</v>
-      </c>
-      <c r="AE48" t="str">
-        <f t="shared" si="31"/>
-        <v>tc-N</v>
-      </c>
-    </row>
-    <row r="49" spans="2:31">
-      <c r="B49" t="str">
-        <f t="shared" si="17"/>
-        <v>vs~0044</v>
-      </c>
-      <c r="C49" t="str">
-        <f t="shared" si="18"/>
-        <v>tc-N.df-Y.ga-Y.dm-Hi.cp-95.CF6</v>
-      </c>
-      <c r="H49" t="str">
-        <f t="shared" si="19"/>
-        <v>tc-N.df-Y.ga-Y.dm-Hi.cp-95.CF6</v>
-      </c>
-      <c r="I49" t="str">
-        <f t="shared" si="20"/>
-        <v>Hi</v>
-      </c>
-      <c r="J49" t="str">
-        <f t="shared" si="21"/>
-        <v>95</v>
-      </c>
-      <c r="K49" t="str">
-        <f t="shared" si="22"/>
-        <v>CF6</v>
-      </c>
-      <c r="L49" t="str">
-        <f t="shared" si="23"/>
-        <v>Y</v>
-      </c>
-      <c r="M49" t="str">
-        <f t="shared" si="24"/>
-        <v>Y</v>
-      </c>
-      <c r="N49" t="str">
-        <f t="shared" si="25"/>
-        <v>N</v>
-      </c>
-      <c r="P49">
-        <v>5</v>
-      </c>
-      <c r="Q49" t="s">
-        <v>1144</v>
-      </c>
-      <c r="R49">
-        <v>44</v>
-      </c>
-      <c r="S49" t="s">
-        <v>1094</v>
-      </c>
-      <c r="T49">
-        <v>95</v>
-      </c>
-      <c r="U49" t="s">
-        <v>1088</v>
       </c>
       <c r="V49" t="s">
         <v>1093</v>
       </c>
-      <c r="W49" t="s">
+      <c r="W49">
+        <v>2</v>
+      </c>
+      <c r="Y49" t="str">
+        <f t="shared" si="23"/>
+        <v>dm-Hi</v>
+      </c>
+      <c r="Z49" t="str">
+        <f t="shared" si="10"/>
+        <v>cp-95</v>
+      </c>
+      <c r="AA49" t="str">
+        <f t="shared" si="24"/>
+        <v>CF6</v>
+      </c>
+      <c r="AB49" t="str">
+        <f t="shared" si="25"/>
+        <v>df-Y</v>
+      </c>
+      <c r="AC49" t="str">
+        <f t="shared" si="13"/>
+        <v>tc-2.00</v>
+      </c>
+    </row>
+    <row r="50" spans="2:29">
+      <c r="B50" t="str">
+        <f t="shared" si="16"/>
+        <v>vs~0045</v>
+      </c>
+      <c r="C50" t="str">
+        <f t="shared" si="17"/>
+        <v>tc-2.00.df-N.dm-Lo.cp-00.CF6</v>
+      </c>
+      <c r="H50" t="str">
+        <f>_xlfn.TEXTJOIN(".",TRUE,AC50,AB50:AB50)&amp;"."&amp;_xlfn.TEXTJOIN(".",TRUE,Y50:AA50)</f>
+        <v>tc-2.00.df-N.dm-Lo.cp-00.CF6</v>
+      </c>
+      <c r="I50" t="str">
+        <f t="shared" si="18"/>
+        <v>Lo</v>
+      </c>
+      <c r="J50" t="str">
+        <f t="shared" si="19"/>
+        <v>00</v>
+      </c>
+      <c r="K50" t="str">
+        <f t="shared" si="20"/>
+        <v>CF6</v>
+      </c>
+      <c r="L50" t="str">
+        <f t="shared" si="21"/>
+        <v>N</v>
+      </c>
+      <c r="M50">
+        <f t="shared" si="22"/>
+        <v>2</v>
+      </c>
+      <c r="O50">
+        <v>5</v>
+      </c>
+      <c r="P50" t="s">
+        <v>1152</v>
+      </c>
+      <c r="Q50">
+        <v>45</v>
+      </c>
+      <c r="R50" t="s">
+        <v>1092</v>
+      </c>
+      <c r="S50">
+        <v>0</v>
+      </c>
+      <c r="T50" t="s">
+        <v>1088</v>
+      </c>
+      <c r="U50" t="s">
+        <v>1095</v>
+      </c>
+      <c r="V50" t="s">
         <v>1093</v>
       </c>
-      <c r="X49" t="s">
+      <c r="W50">
+        <v>2</v>
+      </c>
+      <c r="Y50" t="str">
+        <f t="shared" si="23"/>
+        <v>dm-Lo</v>
+      </c>
+      <c r="Z50" t="str">
+        <f t="shared" si="10"/>
+        <v>cp-00</v>
+      </c>
+      <c r="AA50" t="str">
+        <f t="shared" si="24"/>
+        <v>CF6</v>
+      </c>
+      <c r="AB50" t="str">
+        <f t="shared" si="25"/>
+        <v>df-N</v>
+      </c>
+      <c r="AC50" t="str">
+        <f t="shared" si="13"/>
+        <v>tc-2.00</v>
+      </c>
+    </row>
+    <row r="51" spans="2:29">
+      <c r="B51" t="str">
+        <f t="shared" si="16"/>
+        <v>vs~0046</v>
+      </c>
+      <c r="C51" t="str">
+        <f t="shared" si="17"/>
+        <v>tc-2.00.df-N.dm-Hi.cp-00.CF6</v>
+      </c>
+      <c r="H51" t="str">
+        <f>_xlfn.TEXTJOIN(".",TRUE,AC51,AB51:AB51)&amp;"."&amp;_xlfn.TEXTJOIN(".",TRUE,Y51:AA51)</f>
+        <v>tc-2.00.df-N.dm-Hi.cp-00.CF6</v>
+      </c>
+      <c r="I51" t="str">
+        <f t="shared" si="18"/>
+        <v>Hi</v>
+      </c>
+      <c r="J51" t="str">
+        <f t="shared" si="19"/>
+        <v>00</v>
+      </c>
+      <c r="K51" t="str">
+        <f t="shared" si="20"/>
+        <v>CF6</v>
+      </c>
+      <c r="L51" t="str">
+        <f t="shared" si="21"/>
+        <v>N</v>
+      </c>
+      <c r="M51">
+        <f t="shared" si="22"/>
+        <v>2</v>
+      </c>
+      <c r="O51">
+        <v>5</v>
+      </c>
+      <c r="P51" t="s">
+        <v>1153</v>
+      </c>
+      <c r="Q51">
+        <v>46</v>
+      </c>
+      <c r="R51" t="s">
+        <v>1094</v>
+      </c>
+      <c r="S51">
+        <v>0</v>
+      </c>
+      <c r="T51" t="s">
+        <v>1088</v>
+      </c>
+      <c r="U51" t="s">
         <v>1095</v>
       </c>
-      <c r="Z49" t="str">
-        <f t="shared" si="26"/>
+      <c r="V51" t="s">
+        <v>1093</v>
+      </c>
+      <c r="W51">
+        <v>2</v>
+      </c>
+      <c r="Y51" t="str">
+        <f t="shared" si="23"/>
         <v>dm-Hi</v>
       </c>
-      <c r="AA49" t="str">
-        <f t="shared" si="27"/>
+      <c r="Z51" t="str">
+        <f t="shared" si="10"/>
+        <v>cp-00</v>
+      </c>
+      <c r="AA51" t="str">
+        <f t="shared" si="24"/>
+        <v>CF6</v>
+      </c>
+      <c r="AB51" t="str">
+        <f t="shared" si="25"/>
+        <v>df-N</v>
+      </c>
+      <c r="AC51" t="str">
+        <f t="shared" si="13"/>
+        <v>tc-2.00</v>
+      </c>
+    </row>
+    <row r="52" spans="2:29">
+      <c r="B52" t="str">
+        <f t="shared" si="16"/>
+        <v>vs~0047</v>
+      </c>
+      <c r="C52" t="str">
+        <f t="shared" si="17"/>
+        <v>tc-2.00.df-N.dm-Lo.cp-95.CF6</v>
+      </c>
+      <c r="H52" t="str">
+        <f>_xlfn.TEXTJOIN(".",TRUE,AC52,AB52:AB52)&amp;"."&amp;_xlfn.TEXTJOIN(".",TRUE,Y52:AA52)</f>
+        <v>tc-2.00.df-N.dm-Lo.cp-95.CF6</v>
+      </c>
+      <c r="I52" t="str">
+        <f t="shared" si="18"/>
+        <v>Lo</v>
+      </c>
+      <c r="J52" t="str">
+        <f t="shared" si="19"/>
+        <v>95</v>
+      </c>
+      <c r="K52" t="str">
+        <f t="shared" si="20"/>
+        <v>CF6</v>
+      </c>
+      <c r="L52" t="str">
+        <f t="shared" si="21"/>
+        <v>N</v>
+      </c>
+      <c r="M52">
+        <f t="shared" si="22"/>
+        <v>2</v>
+      </c>
+      <c r="O52">
+        <v>5</v>
+      </c>
+      <c r="P52" t="s">
+        <v>1154</v>
+      </c>
+      <c r="Q52">
+        <v>47</v>
+      </c>
+      <c r="R52" t="s">
+        <v>1092</v>
+      </c>
+      <c r="S52">
+        <v>95</v>
+      </c>
+      <c r="T52" t="s">
+        <v>1088</v>
+      </c>
+      <c r="U52" t="s">
+        <v>1095</v>
+      </c>
+      <c r="V52" t="s">
+        <v>1093</v>
+      </c>
+      <c r="W52">
+        <v>2</v>
+      </c>
+      <c r="Y52" t="str">
+        <f t="shared" si="23"/>
+        <v>dm-Lo</v>
+      </c>
+      <c r="Z52" t="str">
+        <f t="shared" si="10"/>
         <v>cp-95</v>
       </c>
-      <c r="AB49" t="str">
-        <f t="shared" si="28"/>
+      <c r="AA52" t="str">
+        <f t="shared" si="24"/>
         <v>CF6</v>
       </c>
-      <c r="AC49" t="str">
-        <f t="shared" si="29"/>
-        <v>df-Y</v>
-      </c>
-      <c r="AD49" t="str">
-        <f t="shared" si="30"/>
-        <v>ga-Y</v>
-      </c>
-      <c r="AE49" t="str">
-        <f t="shared" si="31"/>
-        <v>tc-N</v>
-      </c>
-    </row>
-    <row r="50" spans="2:31">
-      <c r="B50" t="str">
+      <c r="AB52" t="str">
+        <f t="shared" si="25"/>
+        <v>df-N</v>
+      </c>
+      <c r="AC52" t="str">
+        <f t="shared" si="13"/>
+        <v>tc-2.00</v>
+      </c>
+    </row>
+    <row r="53" spans="2:29">
+      <c r="B53" t="str">
+        <f t="shared" si="16"/>
+        <v>vs~0048</v>
+      </c>
+      <c r="C53" t="str">
         <f t="shared" si="17"/>
-        <v>vs~0045</v>
-      </c>
-      <c r="C50" t="str">
+        <v>tc-2.00.df-N.dm-Hi.cp-95.CF6</v>
+      </c>
+      <c r="H53" t="str">
+        <f>_xlfn.TEXTJOIN(".",TRUE,AC53,AB53:AB53)&amp;"."&amp;_xlfn.TEXTJOIN(".",TRUE,Y53:AA53)</f>
+        <v>tc-2.00.df-N.dm-Hi.cp-95.CF6</v>
+      </c>
+      <c r="I53" t="str">
         <f t="shared" si="18"/>
-        <v>tc-N.df-N.ga-Y.dm-Lo.cp-0.CF6</v>
-      </c>
-      <c r="H50" t="str">
+        <v>Hi</v>
+      </c>
+      <c r="J53" t="str">
         <f t="shared" si="19"/>
-        <v>tc-N.df-N.ga-Y.dm-Lo.cp-0.CF6</v>
-      </c>
-      <c r="I50" t="str">
+        <v>95</v>
+      </c>
+      <c r="K53" t="str">
         <f t="shared" si="20"/>
-        <v>Lo</v>
-      </c>
-      <c r="J50" t="str">
+        <v>CF6</v>
+      </c>
+      <c r="L53" t="str">
         <f t="shared" si="21"/>
-        <v>00</v>
-      </c>
-      <c r="K50" t="str">
+        <v>N</v>
+      </c>
+      <c r="M53">
         <f t="shared" si="22"/>
+        <v>2</v>
+      </c>
+      <c r="O53">
+        <v>5</v>
+      </c>
+      <c r="P53" t="s">
+        <v>1155</v>
+      </c>
+      <c r="Q53">
+        <v>48</v>
+      </c>
+      <c r="R53" t="s">
+        <v>1094</v>
+      </c>
+      <c r="S53">
+        <v>95</v>
+      </c>
+      <c r="T53" t="s">
+        <v>1088</v>
+      </c>
+      <c r="U53" t="s">
+        <v>1095</v>
+      </c>
+      <c r="V53" t="s">
+        <v>1093</v>
+      </c>
+      <c r="W53">
+        <v>2</v>
+      </c>
+      <c r="Y53" t="str">
+        <f t="shared" si="23"/>
+        <v>dm-Hi</v>
+      </c>
+      <c r="Z53" t="str">
+        <f t="shared" si="10"/>
+        <v>cp-95</v>
+      </c>
+      <c r="AA53" t="str">
+        <f t="shared" si="24"/>
         <v>CF6</v>
       </c>
-      <c r="L50" t="str">
-        <f t="shared" si="23"/>
-        <v>N</v>
-      </c>
-      <c r="M50" t="str">
-        <f t="shared" si="24"/>
-        <v>Y</v>
-      </c>
-      <c r="N50" t="str">
+      <c r="AB53" t="str">
         <f t="shared" si="25"/>
-        <v>N</v>
-      </c>
-      <c r="P50">
-        <v>5</v>
-      </c>
-      <c r="Q50" t="s">
-        <v>1145</v>
-      </c>
-      <c r="R50">
-        <v>45</v>
-      </c>
-      <c r="S50" t="s">
-        <v>1092</v>
-      </c>
-      <c r="T50">
-        <v>0</v>
-      </c>
-      <c r="U50" t="s">
-        <v>1088</v>
-      </c>
-      <c r="V50" t="s">
-        <v>1095</v>
-      </c>
-      <c r="W50" t="s">
-        <v>1093</v>
-      </c>
-      <c r="X50" t="s">
-        <v>1095</v>
-      </c>
-      <c r="Z50" t="str">
-        <f t="shared" si="26"/>
-        <v>dm-Lo</v>
-      </c>
-      <c r="AA50" t="str">
-        <f t="shared" si="27"/>
-        <v>cp-0</v>
-      </c>
-      <c r="AB50" t="str">
-        <f t="shared" si="28"/>
-        <v>CF6</v>
-      </c>
-      <c r="AC50" t="str">
-        <f t="shared" si="29"/>
         <v>df-N</v>
       </c>
-      <c r="AD50" t="str">
-        <f t="shared" si="30"/>
-        <v>ga-Y</v>
-      </c>
-      <c r="AE50" t="str">
-        <f t="shared" si="31"/>
-        <v>tc-N</v>
-      </c>
-    </row>
-    <row r="51" spans="2:31">
-      <c r="B51" t="str">
-        <f t="shared" si="17"/>
-        <v>vs~0046</v>
-      </c>
-      <c r="C51" t="str">
-        <f t="shared" si="18"/>
-        <v>tc-N.df-N.ga-Y.dm-Hi.cp-0.CF6</v>
-      </c>
-      <c r="H51" t="str">
-        <f t="shared" si="19"/>
-        <v>tc-N.df-N.ga-Y.dm-Hi.cp-0.CF6</v>
-      </c>
-      <c r="I51" t="str">
-        <f t="shared" si="20"/>
-        <v>Hi</v>
-      </c>
-      <c r="J51" t="str">
-        <f t="shared" si="21"/>
-        <v>00</v>
-      </c>
-      <c r="K51" t="str">
-        <f t="shared" si="22"/>
-        <v>CF6</v>
-      </c>
-      <c r="L51" t="str">
-        <f t="shared" si="23"/>
-        <v>N</v>
-      </c>
-      <c r="M51" t="str">
-        <f t="shared" si="24"/>
-        <v>Y</v>
-      </c>
-      <c r="N51" t="str">
-        <f t="shared" si="25"/>
-        <v>N</v>
-      </c>
-      <c r="P51">
-        <v>5</v>
-      </c>
-      <c r="Q51" t="s">
-        <v>1146</v>
-      </c>
-      <c r="R51">
-        <v>46</v>
-      </c>
-      <c r="S51" t="s">
-        <v>1094</v>
-      </c>
-      <c r="T51">
-        <v>0</v>
-      </c>
-      <c r="U51" t="s">
-        <v>1088</v>
-      </c>
-      <c r="V51" t="s">
-        <v>1095</v>
-      </c>
-      <c r="W51" t="s">
-        <v>1093</v>
-      </c>
-      <c r="X51" t="s">
-        <v>1095</v>
-      </c>
-      <c r="Z51" t="str">
-        <f t="shared" si="26"/>
-        <v>dm-Hi</v>
-      </c>
-      <c r="AA51" t="str">
-        <f t="shared" si="27"/>
-        <v>cp-0</v>
-      </c>
-      <c r="AB51" t="str">
-        <f t="shared" si="28"/>
-        <v>CF6</v>
-      </c>
-      <c r="AC51" t="str">
-        <f t="shared" si="29"/>
-        <v>df-N</v>
-      </c>
-      <c r="AD51" t="str">
-        <f t="shared" si="30"/>
-        <v>ga-Y</v>
-      </c>
-      <c r="AE51" t="str">
-        <f t="shared" si="31"/>
-        <v>tc-N</v>
-      </c>
-    </row>
-    <row r="52" spans="2:31">
-      <c r="B52" t="str">
-        <f t="shared" si="17"/>
-        <v>vs~0047</v>
-      </c>
-      <c r="C52" t="str">
-        <f t="shared" si="18"/>
-        <v>tc-N.df-N.ga-Y.dm-Lo.cp-95.CF6</v>
-      </c>
-      <c r="H52" t="str">
-        <f t="shared" si="19"/>
-        <v>tc-N.df-N.ga-Y.dm-Lo.cp-95.CF6</v>
-      </c>
-      <c r="I52" t="str">
-        <f t="shared" si="20"/>
-        <v>Lo</v>
-      </c>
-      <c r="J52" t="str">
-        <f t="shared" si="21"/>
-        <v>95</v>
-      </c>
-      <c r="K52" t="str">
-        <f t="shared" si="22"/>
-        <v>CF6</v>
-      </c>
-      <c r="L52" t="str">
-        <f t="shared" si="23"/>
-        <v>N</v>
-      </c>
-      <c r="M52" t="str">
-        <f t="shared" si="24"/>
-        <v>Y</v>
-      </c>
-      <c r="N52" t="str">
-        <f t="shared" si="25"/>
-        <v>N</v>
-      </c>
-      <c r="P52">
-        <v>5</v>
-      </c>
-      <c r="Q52" t="s">
-        <v>1147</v>
-      </c>
-      <c r="R52">
-        <v>47</v>
-      </c>
-      <c r="S52" t="s">
-        <v>1092</v>
-      </c>
-      <c r="T52">
-        <v>95</v>
-      </c>
-      <c r="U52" t="s">
-        <v>1088</v>
-      </c>
-      <c r="V52" t="s">
-        <v>1095</v>
-      </c>
-      <c r="W52" t="s">
-        <v>1093</v>
-      </c>
-      <c r="X52" t="s">
-        <v>1095</v>
-      </c>
-      <c r="Z52" t="str">
-        <f t="shared" si="26"/>
-        <v>dm-Lo</v>
-      </c>
-      <c r="AA52" t="str">
-        <f t="shared" si="27"/>
-        <v>cp-95</v>
-      </c>
-      <c r="AB52" t="str">
-        <f t="shared" si="28"/>
-        <v>CF6</v>
-      </c>
-      <c r="AC52" t="str">
-        <f t="shared" si="29"/>
-        <v>df-N</v>
-      </c>
-      <c r="AD52" t="str">
-        <f t="shared" si="30"/>
-        <v>ga-Y</v>
-      </c>
-      <c r="AE52" t="str">
-        <f t="shared" si="31"/>
-        <v>tc-N</v>
-      </c>
-    </row>
-    <row r="53" spans="2:31">
-      <c r="B53" t="str">
-        <f t="shared" si="17"/>
-        <v>vs~0048</v>
-      </c>
-      <c r="C53" t="str">
-        <f t="shared" si="18"/>
-        <v>tc-N.df-N.ga-Y.dm-Hi.cp-95.CF6</v>
-      </c>
-      <c r="H53" t="str">
-        <f t="shared" si="19"/>
-        <v>tc-N.df-N.ga-Y.dm-Hi.cp-95.CF6</v>
-      </c>
-      <c r="I53" t="str">
-        <f t="shared" si="20"/>
-        <v>Hi</v>
-      </c>
-      <c r="J53" t="str">
-        <f t="shared" si="21"/>
-        <v>95</v>
-      </c>
-      <c r="K53" t="str">
-        <f t="shared" si="22"/>
-        <v>CF6</v>
-      </c>
-      <c r="L53" t="str">
-        <f t="shared" si="23"/>
-        <v>N</v>
-      </c>
-      <c r="M53" t="str">
-        <f t="shared" si="24"/>
-        <v>Y</v>
-      </c>
-      <c r="N53" t="str">
-        <f t="shared" si="25"/>
-        <v>N</v>
-      </c>
-      <c r="P53">
-        <v>5</v>
-      </c>
-      <c r="Q53" t="s">
-        <v>1148</v>
-      </c>
-      <c r="R53">
-        <v>48</v>
-      </c>
-      <c r="S53" t="s">
-        <v>1094</v>
-      </c>
-      <c r="T53">
-        <v>95</v>
-      </c>
-      <c r="U53" t="s">
-        <v>1088</v>
-      </c>
-      <c r="V53" t="s">
-        <v>1095</v>
-      </c>
-      <c r="W53" t="s">
-        <v>1093</v>
-      </c>
-      <c r="X53" t="s">
-        <v>1095</v>
-      </c>
-      <c r="Z53" t="str">
-        <f t="shared" si="26"/>
-        <v>dm-Hi</v>
-      </c>
-      <c r="AA53" t="str">
-        <f t="shared" si="27"/>
-        <v>cp-95</v>
-      </c>
-      <c r="AB53" t="str">
-        <f t="shared" si="28"/>
-        <v>CF6</v>
-      </c>
       <c r="AC53" t="str">
-        <f t="shared" si="29"/>
-        <v>df-N</v>
-      </c>
-      <c r="AD53" t="str">
-        <f t="shared" si="30"/>
-        <v>ga-Y</v>
-      </c>
-      <c r="AE53" t="str">
-        <f t="shared" si="31"/>
-        <v>tc-N</v>
-      </c>
-    </row>
-    <row r="54" spans="2:31">
-      <c r="B54" t="str">
-        <f t="shared" si="17"/>
-        <v>vs~0049</v>
-      </c>
-      <c r="C54" t="str">
-        <f t="shared" si="18"/>
-        <v>tc-N.df-Y.ga-N.dm-Lo.cp-0.CF1</v>
-      </c>
-      <c r="H54" t="str">
-        <f t="shared" si="19"/>
-        <v>tc-N.df-Y.ga-N.dm-Lo.cp-0.CF1</v>
-      </c>
-      <c r="I54" t="str">
-        <f t="shared" si="20"/>
-        <v>Lo</v>
-      </c>
-      <c r="J54" t="str">
-        <f t="shared" si="21"/>
-        <v>00</v>
-      </c>
-      <c r="K54" t="str">
-        <f t="shared" si="22"/>
-        <v>CF1</v>
-      </c>
-      <c r="L54" t="str">
-        <f t="shared" si="23"/>
-        <v>Y</v>
-      </c>
-      <c r="M54" t="str">
-        <f t="shared" si="24"/>
-        <v>N</v>
-      </c>
-      <c r="N54" t="str">
-        <f t="shared" si="25"/>
-        <v>N</v>
-      </c>
-      <c r="P54">
-        <v>5</v>
-      </c>
-      <c r="Q54" t="s">
-        <v>1149</v>
-      </c>
-      <c r="R54">
-        <v>49</v>
-      </c>
-      <c r="S54" t="s">
-        <v>1092</v>
-      </c>
-      <c r="T54">
-        <v>0</v>
-      </c>
-      <c r="U54" t="s">
-        <v>1087</v>
-      </c>
-      <c r="V54" t="s">
-        <v>1093</v>
-      </c>
-      <c r="W54" t="s">
-        <v>1095</v>
-      </c>
-      <c r="X54" t="s">
-        <v>1095</v>
-      </c>
-      <c r="Z54" t="str">
-        <f t="shared" si="26"/>
-        <v>dm-Lo</v>
-      </c>
-      <c r="AA54" t="str">
-        <f t="shared" si="27"/>
-        <v>cp-0</v>
-      </c>
-      <c r="AB54" t="str">
-        <f t="shared" si="28"/>
-        <v>CF1</v>
-      </c>
-      <c r="AC54" t="str">
-        <f t="shared" si="29"/>
-        <v>df-Y</v>
-      </c>
-      <c r="AD54" t="str">
-        <f t="shared" si="30"/>
-        <v>ga-N</v>
-      </c>
-      <c r="AE54" t="str">
-        <f t="shared" si="31"/>
-        <v>tc-N</v>
-      </c>
-    </row>
-    <row r="55" spans="2:31">
-      <c r="B55" t="str">
-        <f t="shared" si="17"/>
-        <v>vs~0050</v>
-      </c>
-      <c r="C55" t="str">
-        <f t="shared" si="18"/>
-        <v>tc-N.df-Y.ga-N.dm-Hi.cp-0.CF1</v>
-      </c>
-      <c r="H55" t="str">
-        <f t="shared" si="19"/>
-        <v>tc-N.df-Y.ga-N.dm-Hi.cp-0.CF1</v>
-      </c>
-      <c r="I55" t="str">
-        <f t="shared" si="20"/>
-        <v>Hi</v>
-      </c>
-      <c r="J55" t="str">
-        <f t="shared" si="21"/>
-        <v>00</v>
-      </c>
-      <c r="K55" t="str">
-        <f t="shared" si="22"/>
-        <v>CF1</v>
-      </c>
-      <c r="L55" t="str">
-        <f t="shared" si="23"/>
-        <v>Y</v>
-      </c>
-      <c r="M55" t="str">
-        <f t="shared" si="24"/>
-        <v>N</v>
-      </c>
-      <c r="N55" t="str">
-        <f t="shared" si="25"/>
-        <v>N</v>
-      </c>
-      <c r="P55">
-        <v>5</v>
-      </c>
-      <c r="Q55" t="s">
-        <v>1150</v>
-      </c>
-      <c r="R55">
-        <v>50</v>
-      </c>
-      <c r="S55" t="s">
-        <v>1094</v>
-      </c>
-      <c r="T55">
-        <v>0</v>
-      </c>
-      <c r="U55" t="s">
-        <v>1087</v>
-      </c>
-      <c r="V55" t="s">
-        <v>1093</v>
-      </c>
-      <c r="W55" t="s">
-        <v>1095</v>
-      </c>
-      <c r="X55" t="s">
-        <v>1095</v>
-      </c>
-      <c r="Z55" t="str">
-        <f t="shared" si="26"/>
-        <v>dm-Hi</v>
-      </c>
-      <c r="AA55" t="str">
-        <f t="shared" si="27"/>
-        <v>cp-0</v>
-      </c>
-      <c r="AB55" t="str">
-        <f t="shared" si="28"/>
-        <v>CF1</v>
-      </c>
-      <c r="AC55" t="str">
-        <f t="shared" si="29"/>
-        <v>df-Y</v>
-      </c>
-      <c r="AD55" t="str">
-        <f t="shared" si="30"/>
-        <v>ga-N</v>
-      </c>
-      <c r="AE55" t="str">
-        <f t="shared" si="31"/>
-        <v>tc-N</v>
-      </c>
-    </row>
-    <row r="56" spans="2:31">
-      <c r="B56" t="str">
-        <f t="shared" si="17"/>
-        <v>vs~0051</v>
-      </c>
-      <c r="C56" t="str">
-        <f t="shared" si="18"/>
-        <v>tc-N.df-Y.ga-N.dm-Lo.cp-95.CF1</v>
-      </c>
-      <c r="H56" t="str">
-        <f t="shared" si="19"/>
-        <v>tc-N.df-Y.ga-N.dm-Lo.cp-95.CF1</v>
-      </c>
-      <c r="I56" t="str">
-        <f t="shared" si="20"/>
-        <v>Lo</v>
-      </c>
-      <c r="J56" t="str">
-        <f t="shared" si="21"/>
-        <v>95</v>
-      </c>
-      <c r="K56" t="str">
-        <f t="shared" si="22"/>
-        <v>CF1</v>
-      </c>
-      <c r="L56" t="str">
-        <f t="shared" si="23"/>
-        <v>Y</v>
-      </c>
-      <c r="M56" t="str">
-        <f t="shared" si="24"/>
-        <v>N</v>
-      </c>
-      <c r="N56" t="str">
-        <f t="shared" si="25"/>
-        <v>N</v>
-      </c>
-      <c r="P56">
-        <v>5</v>
-      </c>
-      <c r="Q56" t="s">
-        <v>1151</v>
-      </c>
-      <c r="R56">
-        <v>51</v>
-      </c>
-      <c r="S56" t="s">
-        <v>1092</v>
-      </c>
-      <c r="T56">
-        <v>95</v>
-      </c>
-      <c r="U56" t="s">
-        <v>1087</v>
-      </c>
-      <c r="V56" t="s">
-        <v>1093</v>
-      </c>
-      <c r="W56" t="s">
-        <v>1095</v>
-      </c>
-      <c r="X56" t="s">
-        <v>1095</v>
-      </c>
-      <c r="Z56" t="str">
-        <f t="shared" si="26"/>
-        <v>dm-Lo</v>
-      </c>
-      <c r="AA56" t="str">
-        <f t="shared" si="27"/>
-        <v>cp-95</v>
-      </c>
-      <c r="AB56" t="str">
-        <f t="shared" si="28"/>
-        <v>CF1</v>
-      </c>
-      <c r="AC56" t="str">
-        <f t="shared" si="29"/>
-        <v>df-Y</v>
-      </c>
-      <c r="AD56" t="str">
-        <f t="shared" si="30"/>
-        <v>ga-N</v>
-      </c>
-      <c r="AE56" t="str">
-        <f t="shared" si="31"/>
-        <v>tc-N</v>
-      </c>
-    </row>
-    <row r="57" spans="2:31">
-      <c r="B57" t="str">
-        <f t="shared" si="17"/>
-        <v>vs~0052</v>
-      </c>
-      <c r="C57" t="str">
-        <f t="shared" si="18"/>
-        <v>tc-N.df-Y.ga-N.dm-Hi.cp-95.CF1</v>
-      </c>
-      <c r="H57" t="str">
-        <f t="shared" si="19"/>
-        <v>tc-N.df-Y.ga-N.dm-Hi.cp-95.CF1</v>
-      </c>
-      <c r="I57" t="str">
-        <f t="shared" si="20"/>
-        <v>Hi</v>
-      </c>
-      <c r="J57" t="str">
-        <f t="shared" si="21"/>
-        <v>95</v>
-      </c>
-      <c r="K57" t="str">
-        <f t="shared" si="22"/>
-        <v>CF1</v>
-      </c>
-      <c r="L57" t="str">
-        <f t="shared" si="23"/>
-        <v>Y</v>
-      </c>
-      <c r="M57" t="str">
-        <f t="shared" si="24"/>
-        <v>N</v>
-      </c>
-      <c r="N57" t="str">
-        <f t="shared" si="25"/>
-        <v>N</v>
-      </c>
-      <c r="P57">
-        <v>5</v>
-      </c>
-      <c r="Q57" t="s">
-        <v>1152</v>
-      </c>
-      <c r="R57">
-        <v>52</v>
-      </c>
-      <c r="S57" t="s">
-        <v>1094</v>
-      </c>
-      <c r="T57">
-        <v>95</v>
-      </c>
-      <c r="U57" t="s">
-        <v>1087</v>
-      </c>
-      <c r="V57" t="s">
-        <v>1093</v>
-      </c>
-      <c r="W57" t="s">
-        <v>1095</v>
-      </c>
-      <c r="X57" t="s">
-        <v>1095</v>
-      </c>
-      <c r="Z57" t="str">
-        <f t="shared" si="26"/>
-        <v>dm-Hi</v>
-      </c>
-      <c r="AA57" t="str">
-        <f t="shared" si="27"/>
-        <v>cp-95</v>
-      </c>
-      <c r="AB57" t="str">
-        <f t="shared" si="28"/>
-        <v>CF1</v>
-      </c>
-      <c r="AC57" t="str">
-        <f t="shared" si="29"/>
-        <v>df-Y</v>
-      </c>
-      <c r="AD57" t="str">
-        <f t="shared" si="30"/>
-        <v>ga-N</v>
-      </c>
-      <c r="AE57" t="str">
-        <f t="shared" si="31"/>
-        <v>tc-N</v>
-      </c>
-    </row>
-    <row r="58" spans="2:31">
-      <c r="B58" t="str">
-        <f t="shared" si="17"/>
-        <v>vs~0053</v>
-      </c>
-      <c r="C58" t="str">
-        <f t="shared" si="18"/>
-        <v>tc-N.df-N.ga-N.dm-Lo.cp-0.CF1</v>
-      </c>
-      <c r="H58" t="str">
-        <f t="shared" si="19"/>
-        <v>tc-N.df-N.ga-N.dm-Lo.cp-0.CF1</v>
-      </c>
-      <c r="I58" t="str">
-        <f t="shared" si="20"/>
-        <v>Lo</v>
-      </c>
-      <c r="J58" t="str">
-        <f t="shared" si="21"/>
-        <v>00</v>
-      </c>
-      <c r="K58" t="str">
-        <f t="shared" si="22"/>
-        <v>CF1</v>
-      </c>
-      <c r="L58" t="str">
-        <f t="shared" si="23"/>
-        <v>N</v>
-      </c>
-      <c r="M58" t="str">
-        <f t="shared" si="24"/>
-        <v>N</v>
-      </c>
-      <c r="N58" t="str">
-        <f t="shared" si="25"/>
-        <v>N</v>
-      </c>
-      <c r="P58">
-        <v>5</v>
-      </c>
-      <c r="Q58" t="s">
-        <v>1153</v>
-      </c>
-      <c r="R58">
-        <v>53</v>
-      </c>
-      <c r="S58" t="s">
-        <v>1092</v>
-      </c>
-      <c r="T58">
-        <v>0</v>
-      </c>
-      <c r="U58" t="s">
-        <v>1087</v>
-      </c>
-      <c r="V58" t="s">
-        <v>1095</v>
-      </c>
-      <c r="W58" t="s">
-        <v>1095</v>
-      </c>
-      <c r="X58" t="s">
-        <v>1095</v>
-      </c>
-      <c r="Z58" t="str">
-        <f t="shared" si="26"/>
-        <v>dm-Lo</v>
-      </c>
-      <c r="AA58" t="str">
-        <f t="shared" si="27"/>
-        <v>cp-0</v>
-      </c>
-      <c r="AB58" t="str">
-        <f t="shared" si="28"/>
-        <v>CF1</v>
-      </c>
-      <c r="AC58" t="str">
-        <f t="shared" si="29"/>
-        <v>df-N</v>
-      </c>
-      <c r="AD58" t="str">
-        <f t="shared" si="30"/>
-        <v>ga-N</v>
-      </c>
-      <c r="AE58" t="str">
-        <f t="shared" si="31"/>
-        <v>tc-N</v>
-      </c>
-    </row>
-    <row r="59" spans="2:31">
-      <c r="B59" t="str">
-        <f t="shared" si="17"/>
-        <v>vs~0054</v>
-      </c>
-      <c r="C59" t="str">
-        <f t="shared" si="18"/>
-        <v>tc-N.df-N.ga-N.dm-Hi.cp-0.CF1</v>
-      </c>
-      <c r="H59" t="str">
-        <f t="shared" si="19"/>
-        <v>tc-N.df-N.ga-N.dm-Hi.cp-0.CF1</v>
-      </c>
-      <c r="I59" t="str">
-        <f t="shared" si="20"/>
-        <v>Hi</v>
-      </c>
-      <c r="J59" t="str">
-        <f t="shared" si="21"/>
-        <v>00</v>
-      </c>
-      <c r="K59" t="str">
-        <f t="shared" si="22"/>
-        <v>CF1</v>
-      </c>
-      <c r="L59" t="str">
-        <f t="shared" si="23"/>
-        <v>N</v>
-      </c>
-      <c r="M59" t="str">
-        <f t="shared" si="24"/>
-        <v>N</v>
-      </c>
-      <c r="N59" t="str">
-        <f t="shared" si="25"/>
-        <v>N</v>
-      </c>
-      <c r="P59">
-        <v>5</v>
-      </c>
-      <c r="Q59" t="s">
-        <v>1154</v>
-      </c>
-      <c r="R59">
-        <v>54</v>
-      </c>
-      <c r="S59" t="s">
-        <v>1094</v>
-      </c>
-      <c r="T59">
-        <v>0</v>
-      </c>
-      <c r="U59" t="s">
-        <v>1087</v>
-      </c>
-      <c r="V59" t="s">
-        <v>1095</v>
-      </c>
-      <c r="W59" t="s">
-        <v>1095</v>
-      </c>
-      <c r="X59" t="s">
-        <v>1095</v>
-      </c>
-      <c r="Z59" t="str">
-        <f t="shared" si="26"/>
-        <v>dm-Hi</v>
-      </c>
-      <c r="AA59" t="str">
-        <f t="shared" si="27"/>
-        <v>cp-0</v>
-      </c>
-      <c r="AB59" t="str">
-        <f t="shared" si="28"/>
-        <v>CF1</v>
-      </c>
-      <c r="AC59" t="str">
-        <f t="shared" si="29"/>
-        <v>df-N</v>
-      </c>
-      <c r="AD59" t="str">
-        <f t="shared" si="30"/>
-        <v>ga-N</v>
-      </c>
-      <c r="AE59" t="str">
-        <f t="shared" si="31"/>
-        <v>tc-N</v>
-      </c>
-    </row>
-    <row r="60" spans="2:31">
-      <c r="B60" t="str">
-        <f t="shared" si="17"/>
-        <v>vs~0055</v>
-      </c>
-      <c r="C60" t="str">
-        <f t="shared" si="18"/>
-        <v>tc-N.df-N.ga-N.dm-Lo.cp-95.CF1</v>
-      </c>
-      <c r="H60" t="str">
-        <f t="shared" si="19"/>
-        <v>tc-N.df-N.ga-N.dm-Lo.cp-95.CF1</v>
-      </c>
-      <c r="I60" t="str">
-        <f t="shared" si="20"/>
-        <v>Lo</v>
-      </c>
-      <c r="J60" t="str">
-        <f t="shared" si="21"/>
-        <v>95</v>
-      </c>
-      <c r="K60" t="str">
-        <f t="shared" si="22"/>
-        <v>CF1</v>
-      </c>
-      <c r="L60" t="str">
-        <f t="shared" si="23"/>
-        <v>N</v>
-      </c>
-      <c r="M60" t="str">
-        <f t="shared" si="24"/>
-        <v>N</v>
-      </c>
-      <c r="N60" t="str">
-        <f t="shared" si="25"/>
-        <v>N</v>
-      </c>
-      <c r="P60">
-        <v>5</v>
-      </c>
-      <c r="Q60" t="s">
-        <v>1155</v>
-      </c>
-      <c r="R60">
-        <v>55</v>
-      </c>
-      <c r="S60" t="s">
-        <v>1092</v>
-      </c>
-      <c r="T60">
-        <v>95</v>
-      </c>
-      <c r="U60" t="s">
-        <v>1087</v>
-      </c>
-      <c r="V60" t="s">
-        <v>1095</v>
-      </c>
-      <c r="W60" t="s">
-        <v>1095</v>
-      </c>
-      <c r="X60" t="s">
-        <v>1095</v>
-      </c>
-      <c r="Z60" t="str">
-        <f t="shared" si="26"/>
-        <v>dm-Lo</v>
-      </c>
-      <c r="AA60" t="str">
-        <f t="shared" si="27"/>
-        <v>cp-95</v>
-      </c>
-      <c r="AB60" t="str">
-        <f t="shared" si="28"/>
-        <v>CF1</v>
-      </c>
-      <c r="AC60" t="str">
-        <f t="shared" si="29"/>
-        <v>df-N</v>
-      </c>
-      <c r="AD60" t="str">
-        <f t="shared" si="30"/>
-        <v>ga-N</v>
-      </c>
-      <c r="AE60" t="str">
-        <f t="shared" si="31"/>
-        <v>tc-N</v>
-      </c>
-    </row>
-    <row r="61" spans="2:31">
-      <c r="B61" t="str">
-        <f t="shared" si="17"/>
-        <v>vs~0056</v>
-      </c>
-      <c r="C61" t="str">
-        <f t="shared" si="18"/>
-        <v>tc-N.df-N.ga-N.dm-Hi.cp-95.CF1</v>
-      </c>
-      <c r="H61" t="str">
-        <f t="shared" si="19"/>
-        <v>tc-N.df-N.ga-N.dm-Hi.cp-95.CF1</v>
-      </c>
-      <c r="I61" t="str">
-        <f t="shared" si="20"/>
-        <v>Hi</v>
-      </c>
-      <c r="J61" t="str">
-        <f t="shared" si="21"/>
-        <v>95</v>
-      </c>
-      <c r="K61" t="str">
-        <f t="shared" si="22"/>
-        <v>CF1</v>
-      </c>
-      <c r="L61" t="str">
-        <f t="shared" si="23"/>
-        <v>N</v>
-      </c>
-      <c r="M61" t="str">
-        <f t="shared" si="24"/>
-        <v>N</v>
-      </c>
-      <c r="N61" t="str">
-        <f t="shared" si="25"/>
-        <v>N</v>
-      </c>
-      <c r="P61">
-        <v>5</v>
-      </c>
-      <c r="Q61" t="s">
-        <v>1156</v>
-      </c>
-      <c r="R61">
-        <v>56</v>
-      </c>
-      <c r="S61" t="s">
-        <v>1094</v>
-      </c>
-      <c r="T61">
-        <v>95</v>
-      </c>
-      <c r="U61" t="s">
-        <v>1087</v>
-      </c>
-      <c r="V61" t="s">
-        <v>1095</v>
-      </c>
-      <c r="W61" t="s">
-        <v>1095</v>
-      </c>
-      <c r="X61" t="s">
-        <v>1095</v>
-      </c>
-      <c r="Z61" t="str">
-        <f t="shared" si="26"/>
-        <v>dm-Hi</v>
-      </c>
-      <c r="AA61" t="str">
-        <f t="shared" si="27"/>
-        <v>cp-95</v>
-      </c>
-      <c r="AB61" t="str">
-        <f t="shared" si="28"/>
-        <v>CF1</v>
-      </c>
-      <c r="AC61" t="str">
-        <f t="shared" si="29"/>
-        <v>df-N</v>
-      </c>
-      <c r="AD61" t="str">
-        <f t="shared" si="30"/>
-        <v>ga-N</v>
-      </c>
-      <c r="AE61" t="str">
-        <f t="shared" si="31"/>
-        <v>tc-N</v>
-      </c>
-    </row>
-    <row r="62" spans="2:31">
-      <c r="B62" t="str">
-        <f t="shared" si="17"/>
-        <v>vs~0057</v>
-      </c>
-      <c r="C62" t="str">
-        <f t="shared" si="18"/>
-        <v>tc-N.df-Y.ga-N.dm-Lo.cp-0.CF6</v>
-      </c>
-      <c r="H62" t="str">
-        <f t="shared" si="19"/>
-        <v>tc-N.df-Y.ga-N.dm-Lo.cp-0.CF6</v>
-      </c>
-      <c r="I62" t="str">
-        <f t="shared" si="20"/>
-        <v>Lo</v>
-      </c>
-      <c r="J62" t="str">
-        <f t="shared" si="21"/>
-        <v>00</v>
-      </c>
-      <c r="K62" t="str">
-        <f t="shared" si="22"/>
-        <v>CF6</v>
-      </c>
-      <c r="L62" t="str">
-        <f t="shared" si="23"/>
-        <v>Y</v>
-      </c>
-      <c r="M62" t="str">
-        <f t="shared" si="24"/>
-        <v>N</v>
-      </c>
-      <c r="N62" t="str">
-        <f t="shared" si="25"/>
-        <v>N</v>
-      </c>
-      <c r="P62">
-        <v>5</v>
-      </c>
-      <c r="Q62" t="s">
-        <v>1157</v>
-      </c>
-      <c r="R62">
-        <v>57</v>
-      </c>
-      <c r="S62" t="s">
-        <v>1092</v>
-      </c>
-      <c r="T62">
-        <v>0</v>
-      </c>
-      <c r="U62" t="s">
-        <v>1088</v>
-      </c>
-      <c r="V62" t="s">
-        <v>1093</v>
-      </c>
-      <c r="W62" t="s">
-        <v>1095</v>
-      </c>
-      <c r="X62" t="s">
-        <v>1095</v>
-      </c>
-      <c r="Z62" t="str">
-        <f t="shared" si="26"/>
-        <v>dm-Lo</v>
-      </c>
-      <c r="AA62" t="str">
-        <f t="shared" si="27"/>
-        <v>cp-0</v>
-      </c>
-      <c r="AB62" t="str">
-        <f t="shared" si="28"/>
-        <v>CF6</v>
-      </c>
-      <c r="AC62" t="str">
-        <f t="shared" si="29"/>
-        <v>df-Y</v>
-      </c>
-      <c r="AD62" t="str">
-        <f t="shared" si="30"/>
-        <v>ga-N</v>
-      </c>
-      <c r="AE62" t="str">
-        <f t="shared" si="31"/>
-        <v>tc-N</v>
-      </c>
-    </row>
-    <row r="63" spans="2:31">
-      <c r="B63" t="str">
-        <f t="shared" si="17"/>
-        <v>vs~0058</v>
-      </c>
-      <c r="C63" t="str">
-        <f t="shared" si="18"/>
-        <v>tc-N.df-Y.ga-N.dm-Hi.cp-0.CF6</v>
-      </c>
-      <c r="H63" t="str">
-        <f t="shared" si="19"/>
-        <v>tc-N.df-Y.ga-N.dm-Hi.cp-0.CF6</v>
-      </c>
-      <c r="I63" t="str">
-        <f t="shared" si="20"/>
-        <v>Hi</v>
-      </c>
-      <c r="J63" t="str">
-        <f t="shared" si="21"/>
-        <v>00</v>
-      </c>
-      <c r="K63" t="str">
-        <f t="shared" si="22"/>
-        <v>CF6</v>
-      </c>
-      <c r="L63" t="str">
-        <f t="shared" si="23"/>
-        <v>Y</v>
-      </c>
-      <c r="M63" t="str">
-        <f t="shared" si="24"/>
-        <v>N</v>
-      </c>
-      <c r="N63" t="str">
-        <f t="shared" si="25"/>
-        <v>N</v>
-      </c>
-      <c r="P63">
-        <v>5</v>
-      </c>
-      <c r="Q63" t="s">
-        <v>1158</v>
-      </c>
-      <c r="R63">
-        <v>58</v>
-      </c>
-      <c r="S63" t="s">
-        <v>1094</v>
-      </c>
-      <c r="T63">
-        <v>0</v>
-      </c>
-      <c r="U63" t="s">
-        <v>1088</v>
-      </c>
-      <c r="V63" t="s">
-        <v>1093</v>
-      </c>
-      <c r="W63" t="s">
-        <v>1095</v>
-      </c>
-      <c r="X63" t="s">
-        <v>1095</v>
-      </c>
-      <c r="Z63" t="str">
-        <f t="shared" si="26"/>
-        <v>dm-Hi</v>
-      </c>
-      <c r="AA63" t="str">
-        <f t="shared" si="27"/>
-        <v>cp-0</v>
-      </c>
-      <c r="AB63" t="str">
-        <f t="shared" si="28"/>
-        <v>CF6</v>
-      </c>
-      <c r="AC63" t="str">
-        <f t="shared" si="29"/>
-        <v>df-Y</v>
-      </c>
-      <c r="AD63" t="str">
-        <f t="shared" si="30"/>
-        <v>ga-N</v>
-      </c>
-      <c r="AE63" t="str">
-        <f t="shared" si="31"/>
-        <v>tc-N</v>
-      </c>
-    </row>
-    <row r="64" spans="2:31">
-      <c r="B64" t="str">
-        <f t="shared" si="17"/>
-        <v>vs~0059</v>
-      </c>
-      <c r="C64" t="str">
-        <f t="shared" si="18"/>
-        <v>tc-N.df-Y.ga-N.dm-Lo.cp-95.CF6</v>
-      </c>
-      <c r="H64" t="str">
-        <f t="shared" si="19"/>
-        <v>tc-N.df-Y.ga-N.dm-Lo.cp-95.CF6</v>
-      </c>
-      <c r="I64" t="str">
-        <f t="shared" si="20"/>
-        <v>Lo</v>
-      </c>
-      <c r="J64" t="str">
-        <f t="shared" si="21"/>
-        <v>95</v>
-      </c>
-      <c r="K64" t="str">
-        <f t="shared" si="22"/>
-        <v>CF6</v>
-      </c>
-      <c r="L64" t="str">
-        <f t="shared" si="23"/>
-        <v>Y</v>
-      </c>
-      <c r="M64" t="str">
-        <f t="shared" si="24"/>
-        <v>N</v>
-      </c>
-      <c r="N64" t="str">
-        <f t="shared" si="25"/>
-        <v>N</v>
-      </c>
-      <c r="P64">
-        <v>5</v>
-      </c>
-      <c r="Q64" t="s">
-        <v>1159</v>
-      </c>
-      <c r="R64">
-        <v>59</v>
-      </c>
-      <c r="S64" t="s">
-        <v>1092</v>
-      </c>
-      <c r="T64">
-        <v>95</v>
-      </c>
-      <c r="U64" t="s">
-        <v>1088</v>
-      </c>
-      <c r="V64" t="s">
-        <v>1093</v>
-      </c>
-      <c r="W64" t="s">
-        <v>1095</v>
-      </c>
-      <c r="X64" t="s">
-        <v>1095</v>
-      </c>
-      <c r="Z64" t="str">
-        <f t="shared" si="26"/>
-        <v>dm-Lo</v>
-      </c>
-      <c r="AA64" t="str">
-        <f t="shared" si="27"/>
-        <v>cp-95</v>
-      </c>
-      <c r="AB64" t="str">
-        <f t="shared" si="28"/>
-        <v>CF6</v>
-      </c>
-      <c r="AC64" t="str">
-        <f t="shared" si="29"/>
-        <v>df-Y</v>
-      </c>
-      <c r="AD64" t="str">
-        <f t="shared" si="30"/>
-        <v>ga-N</v>
-      </c>
-      <c r="AE64" t="str">
-        <f t="shared" si="31"/>
-        <v>tc-N</v>
-      </c>
-    </row>
-    <row r="65" spans="2:31">
-      <c r="B65" t="str">
-        <f t="shared" si="17"/>
-        <v>vs~0060</v>
-      </c>
-      <c r="C65" t="str">
-        <f t="shared" si="18"/>
-        <v>tc-N.df-Y.ga-N.dm-Hi.cp-95.CF6</v>
-      </c>
-      <c r="H65" t="str">
-        <f t="shared" si="19"/>
-        <v>tc-N.df-Y.ga-N.dm-Hi.cp-95.CF6</v>
-      </c>
-      <c r="I65" t="str">
-        <f t="shared" si="20"/>
-        <v>Hi</v>
-      </c>
-      <c r="J65" t="str">
-        <f t="shared" si="21"/>
-        <v>95</v>
-      </c>
-      <c r="K65" t="str">
-        <f t="shared" si="22"/>
-        <v>CF6</v>
-      </c>
-      <c r="L65" t="str">
-        <f t="shared" si="23"/>
-        <v>Y</v>
-      </c>
-      <c r="M65" t="str">
-        <f t="shared" si="24"/>
-        <v>N</v>
-      </c>
-      <c r="N65" t="str">
-        <f t="shared" si="25"/>
-        <v>N</v>
-      </c>
-      <c r="P65">
-        <v>5</v>
-      </c>
-      <c r="Q65" t="s">
-        <v>1160</v>
-      </c>
-      <c r="R65">
-        <v>60</v>
-      </c>
-      <c r="S65" t="s">
-        <v>1094</v>
-      </c>
-      <c r="T65">
-        <v>95</v>
-      </c>
-      <c r="U65" t="s">
-        <v>1088</v>
-      </c>
-      <c r="V65" t="s">
-        <v>1093</v>
-      </c>
-      <c r="W65" t="s">
-        <v>1095</v>
-      </c>
-      <c r="X65" t="s">
-        <v>1095</v>
-      </c>
-      <c r="Z65" t="str">
-        <f t="shared" si="26"/>
-        <v>dm-Hi</v>
-      </c>
-      <c r="AA65" t="str">
-        <f t="shared" si="27"/>
-        <v>cp-95</v>
-      </c>
-      <c r="AB65" t="str">
-        <f t="shared" si="28"/>
-        <v>CF6</v>
-      </c>
-      <c r="AC65" t="str">
-        <f t="shared" si="29"/>
-        <v>df-Y</v>
-      </c>
-      <c r="AD65" t="str">
-        <f t="shared" si="30"/>
-        <v>ga-N</v>
-      </c>
-      <c r="AE65" t="str">
-        <f t="shared" si="31"/>
-        <v>tc-N</v>
-      </c>
-    </row>
-    <row r="66" spans="2:31">
-      <c r="B66" t="str">
-        <f t="shared" si="17"/>
-        <v>vs~0061</v>
-      </c>
-      <c r="C66" t="str">
-        <f t="shared" si="18"/>
-        <v>tc-N.df-N.ga-N.dm-Lo.cp-0.CF6</v>
-      </c>
-      <c r="H66" t="str">
-        <f t="shared" si="19"/>
-        <v>tc-N.df-N.ga-N.dm-Lo.cp-0.CF6</v>
-      </c>
-      <c r="I66" t="str">
-        <f t="shared" si="20"/>
-        <v>Lo</v>
-      </c>
-      <c r="J66" t="str">
-        <f t="shared" si="21"/>
-        <v>00</v>
-      </c>
-      <c r="K66" t="str">
-        <f t="shared" si="22"/>
-        <v>CF6</v>
-      </c>
-      <c r="L66" t="str">
-        <f t="shared" si="23"/>
-        <v>N</v>
-      </c>
-      <c r="M66" t="str">
-        <f t="shared" si="24"/>
-        <v>N</v>
-      </c>
-      <c r="N66" t="str">
-        <f t="shared" si="25"/>
-        <v>N</v>
-      </c>
-      <c r="P66">
-        <v>5</v>
-      </c>
-      <c r="Q66" t="s">
-        <v>1161</v>
-      </c>
-      <c r="R66">
-        <v>61</v>
-      </c>
-      <c r="S66" t="s">
-        <v>1092</v>
-      </c>
-      <c r="T66">
-        <v>0</v>
-      </c>
-      <c r="U66" t="s">
-        <v>1088</v>
-      </c>
-      <c r="V66" t="s">
-        <v>1095</v>
-      </c>
-      <c r="W66" t="s">
-        <v>1095</v>
-      </c>
-      <c r="X66" t="s">
-        <v>1095</v>
-      </c>
-      <c r="Z66" t="str">
-        <f t="shared" si="26"/>
-        <v>dm-Lo</v>
-      </c>
-      <c r="AA66" t="str">
-        <f t="shared" si="27"/>
-        <v>cp-0</v>
-      </c>
-      <c r="AB66" t="str">
-        <f t="shared" si="28"/>
-        <v>CF6</v>
-      </c>
-      <c r="AC66" t="str">
-        <f t="shared" si="29"/>
-        <v>df-N</v>
-      </c>
-      <c r="AD66" t="str">
-        <f t="shared" si="30"/>
-        <v>ga-N</v>
-      </c>
-      <c r="AE66" t="str">
-        <f t="shared" si="31"/>
-        <v>tc-N</v>
-      </c>
-    </row>
-    <row r="67" spans="2:31">
-      <c r="B67" t="str">
-        <f t="shared" si="17"/>
-        <v>vs~0062</v>
-      </c>
-      <c r="C67" t="str">
-        <f t="shared" si="18"/>
-        <v>tc-N.df-N.ga-N.dm-Hi.cp-0.CF6</v>
-      </c>
-      <c r="H67" t="str">
-        <f t="shared" si="19"/>
-        <v>tc-N.df-N.ga-N.dm-Hi.cp-0.CF6</v>
-      </c>
-      <c r="I67" t="str">
-        <f t="shared" si="20"/>
-        <v>Hi</v>
-      </c>
-      <c r="J67" t="str">
-        <f t="shared" si="21"/>
-        <v>00</v>
-      </c>
-      <c r="K67" t="str">
-        <f t="shared" si="22"/>
-        <v>CF6</v>
-      </c>
-      <c r="L67" t="str">
-        <f t="shared" si="23"/>
-        <v>N</v>
-      </c>
-      <c r="M67" t="str">
-        <f t="shared" si="24"/>
-        <v>N</v>
-      </c>
-      <c r="N67" t="str">
-        <f t="shared" si="25"/>
-        <v>N</v>
-      </c>
-      <c r="P67">
-        <v>5</v>
-      </c>
-      <c r="Q67" t="s">
-        <v>1162</v>
-      </c>
-      <c r="R67">
-        <v>62</v>
-      </c>
-      <c r="S67" t="s">
-        <v>1094</v>
-      </c>
-      <c r="T67">
-        <v>0</v>
-      </c>
-      <c r="U67" t="s">
-        <v>1088</v>
-      </c>
-      <c r="V67" t="s">
-        <v>1095</v>
-      </c>
-      <c r="W67" t="s">
-        <v>1095</v>
-      </c>
-      <c r="X67" t="s">
-        <v>1095</v>
-      </c>
-      <c r="Z67" t="str">
-        <f t="shared" si="26"/>
-        <v>dm-Hi</v>
-      </c>
-      <c r="AA67" t="str">
-        <f t="shared" si="27"/>
-        <v>cp-0</v>
-      </c>
-      <c r="AB67" t="str">
-        <f t="shared" si="28"/>
-        <v>CF6</v>
-      </c>
-      <c r="AC67" t="str">
-        <f t="shared" si="29"/>
-        <v>df-N</v>
-      </c>
-      <c r="AD67" t="str">
-        <f t="shared" si="30"/>
-        <v>ga-N</v>
-      </c>
-      <c r="AE67" t="str">
-        <f t="shared" si="31"/>
-        <v>tc-N</v>
-      </c>
-    </row>
-    <row r="68" spans="2:31">
-      <c r="B68" t="str">
-        <f t="shared" si="17"/>
-        <v>vs~0063</v>
-      </c>
-      <c r="C68" t="str">
-        <f t="shared" si="18"/>
-        <v>tc-N.df-N.ga-N.dm-Lo.cp-95.CF6</v>
-      </c>
-      <c r="H68" t="str">
-        <f t="shared" si="19"/>
-        <v>tc-N.df-N.ga-N.dm-Lo.cp-95.CF6</v>
-      </c>
-      <c r="I68" t="str">
-        <f t="shared" si="20"/>
-        <v>Lo</v>
-      </c>
-      <c r="J68" t="str">
-        <f t="shared" si="21"/>
-        <v>95</v>
-      </c>
-      <c r="K68" t="str">
-        <f t="shared" si="22"/>
-        <v>CF6</v>
-      </c>
-      <c r="L68" t="str">
-        <f t="shared" si="23"/>
-        <v>N</v>
-      </c>
-      <c r="M68" t="str">
-        <f t="shared" si="24"/>
-        <v>N</v>
-      </c>
-      <c r="N68" t="str">
-        <f t="shared" si="25"/>
-        <v>N</v>
-      </c>
-      <c r="P68">
-        <v>5</v>
-      </c>
-      <c r="Q68" t="s">
-        <v>1163</v>
-      </c>
-      <c r="R68">
-        <v>63</v>
-      </c>
-      <c r="S68" t="s">
-        <v>1092</v>
-      </c>
-      <c r="T68">
-        <v>95</v>
-      </c>
-      <c r="U68" t="s">
-        <v>1088</v>
-      </c>
-      <c r="V68" t="s">
-        <v>1095</v>
-      </c>
-      <c r="W68" t="s">
-        <v>1095</v>
-      </c>
-      <c r="X68" t="s">
-        <v>1095</v>
-      </c>
-      <c r="Z68" t="str">
-        <f t="shared" si="26"/>
-        <v>dm-Lo</v>
-      </c>
-      <c r="AA68" t="str">
-        <f t="shared" si="27"/>
-        <v>cp-95</v>
-      </c>
-      <c r="AB68" t="str">
-        <f t="shared" si="28"/>
-        <v>CF6</v>
-      </c>
-      <c r="AC68" t="str">
-        <f t="shared" si="29"/>
-        <v>df-N</v>
-      </c>
-      <c r="AD68" t="str">
-        <f t="shared" si="30"/>
-        <v>ga-N</v>
-      </c>
-      <c r="AE68" t="str">
-        <f t="shared" si="31"/>
-        <v>tc-N</v>
-      </c>
-    </row>
-    <row r="69" spans="2:31">
-      <c r="B69" t="str">
-        <f t="shared" si="17"/>
-        <v>vs~0064</v>
-      </c>
-      <c r="C69" t="str">
-        <f t="shared" si="18"/>
-        <v>tc-N.df-N.ga-N.dm-Hi.cp-95.CF6</v>
-      </c>
-      <c r="H69" t="str">
-        <f t="shared" si="19"/>
-        <v>tc-N.df-N.ga-N.dm-Hi.cp-95.CF6</v>
-      </c>
-      <c r="I69" t="str">
-        <f t="shared" si="20"/>
-        <v>Hi</v>
-      </c>
-      <c r="J69" t="str">
-        <f t="shared" si="21"/>
-        <v>95</v>
-      </c>
-      <c r="K69" t="str">
-        <f t="shared" si="22"/>
-        <v>CF6</v>
-      </c>
-      <c r="L69" t="str">
-        <f t="shared" si="23"/>
-        <v>N</v>
-      </c>
-      <c r="M69" t="str">
-        <f t="shared" si="24"/>
-        <v>N</v>
-      </c>
-      <c r="N69" t="str">
-        <f t="shared" si="25"/>
-        <v>N</v>
-      </c>
-      <c r="P69">
-        <v>5</v>
-      </c>
-      <c r="Q69" t="s">
-        <v>1164</v>
-      </c>
-      <c r="R69">
-        <v>64</v>
-      </c>
-      <c r="S69" t="s">
-        <v>1094</v>
-      </c>
-      <c r="T69">
-        <v>95</v>
-      </c>
-      <c r="U69" t="s">
-        <v>1088</v>
-      </c>
-      <c r="V69" t="s">
-        <v>1095</v>
-      </c>
-      <c r="W69" t="s">
-        <v>1095</v>
-      </c>
-      <c r="X69" t="s">
-        <v>1095</v>
-      </c>
-      <c r="Z69" t="str">
-        <f t="shared" si="26"/>
-        <v>dm-Hi</v>
-      </c>
-      <c r="AA69" t="str">
-        <f t="shared" si="27"/>
-        <v>cp-95</v>
-      </c>
-      <c r="AB69" t="str">
-        <f t="shared" si="28"/>
-        <v>CF6</v>
-      </c>
-      <c r="AC69" t="str">
-        <f t="shared" si="29"/>
-        <v>df-N</v>
-      </c>
-      <c r="AD69" t="str">
-        <f t="shared" si="30"/>
-        <v>ga-N</v>
-      </c>
-      <c r="AE69" t="str">
-        <f t="shared" si="31"/>
-        <v>tc-N</v>
+        <f t="shared" si="13"/>
+        <v>tc-2.00</v>
       </c>
     </row>
   </sheetData>
@@ -40046,10 +38185,10 @@
     </row>
     <row r="9" spans="1:21">
       <c r="A9" t="s">
-        <v>1169</v>
+        <v>1105</v>
       </c>
       <c r="C9" t="s">
-        <v>1166</v>
+        <v>1102</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>110</v>
@@ -40058,10 +38197,10 @@
         <v>233</v>
       </c>
       <c r="M9" t="s">
-        <v>1170</v>
+        <v>1106</v>
       </c>
       <c r="N9" t="s">
-        <v>1171</v>
+        <v>1107</v>
       </c>
       <c r="T9" s="3"/>
       <c r="U9" s="3"/>
@@ -40071,7 +38210,7 @@
         <v>283</v>
       </c>
       <c r="C10" t="s">
-        <v>1166</v>
+        <v>1102</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>110</v>
@@ -40088,7 +38227,7 @@
         <v>286</v>
       </c>
       <c r="C11" t="s">
-        <v>1166</v>
+        <v>1102</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>110</v>

--- a/VerveStacks_ZAF_grids_kan/ReportDefs_vervestacks.xlsx
+++ b/VerveStacks_ZAF_grids_kan/ReportDefs_vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_ZAF_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77C8488D-BB10-4A28-82A9-29778EDEDB4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{112678F8-7CF9-47FA-8C99-B20E600C5408}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7426" uniqueCount="1156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7506" uniqueCount="1172">
   <si>
     <t>Unit</t>
   </si>
@@ -3551,6 +3551,54 @@
   </si>
   <si>
     <t>Hi.95.CF6.N.Y.2</t>
+  </si>
+  <si>
+    <t>Lo.0.CF1.Y.Y.0.1</t>
+  </si>
+  <si>
+    <t>Hi.0.CF1.Y.Y.0.1</t>
+  </si>
+  <si>
+    <t>Lo.95.CF1.Y.Y.0.1</t>
+  </si>
+  <si>
+    <t>Hi.95.CF1.Y.Y.0.1</t>
+  </si>
+  <si>
+    <t>Lo.0.CF1.N.Y.0.1</t>
+  </si>
+  <si>
+    <t>Hi.0.CF1.N.Y.0.1</t>
+  </si>
+  <si>
+    <t>Lo.95.CF1.N.Y.0.1</t>
+  </si>
+  <si>
+    <t>Hi.95.CF1.N.Y.0.1</t>
+  </si>
+  <si>
+    <t>Lo.0.CF6.Y.Y.0.1</t>
+  </si>
+  <si>
+    <t>Hi.0.CF6.Y.Y.0.1</t>
+  </si>
+  <si>
+    <t>Lo.95.CF6.Y.Y.0.1</t>
+  </si>
+  <si>
+    <t>Hi.95.CF6.Y.Y.0.1</t>
+  </si>
+  <si>
+    <t>Lo.0.CF6.N.Y.0.1</t>
+  </si>
+  <si>
+    <t>Hi.0.CF6.N.Y.0.1</t>
+  </si>
+  <si>
+    <t>Lo.95.CF6.N.Y.0.1</t>
+  </si>
+  <si>
+    <t>Hi.95.CF6.N.Y.0.1</t>
   </si>
 </sst>
 </file>
@@ -33944,7 +33992,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C50B696F-B355-4FC5-AD3E-AFDC509F717D}">
-  <dimension ref="B1:AC53"/>
+  <dimension ref="B1:AC69"/>
   <sheetFormatPr defaultColWidth="14.73046875" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="2.73046875" bestFit="1" customWidth="1"/>
@@ -34086,7 +34134,7 @@
         <v>tc-1.00.df-Y.dm-Lo.cp-00.CF1</v>
       </c>
       <c r="H6" t="str">
-        <f>_xlfn.TEXTJOIN(".",TRUE,AC6,AB6:AB6)&amp;"."&amp;_xlfn.TEXTJOIN(".",TRUE,Y6:AA6)</f>
+        <f t="shared" ref="H6:H53" si="1">_xlfn.TEXTJOIN(".",TRUE,AC6,AB6:AB6)&amp;"."&amp;_xlfn.TEXTJOIN(".",TRUE,Y6:AA6)</f>
         <v>tc-1.00.df-Y.dm-Lo.cp-00.CF1</v>
       </c>
       <c r="I6" t="str">
@@ -34105,9 +34153,9 @@
         <f>U6</f>
         <v>Y</v>
       </c>
-      <c r="M6">
-        <f t="shared" ref="M6" si="1">W6</f>
-        <v>1</v>
+      <c r="M6" t="str">
+        <f>TEXT(W6,"0.00")</f>
+        <v>1.00</v>
       </c>
       <c r="O6">
         <v>5</v>
@@ -34167,7 +34215,7 @@
         <v>tc-1.00.df-Y.dm-Hi.cp-00.CF1</v>
       </c>
       <c r="H7" t="str">
-        <f>_xlfn.TEXTJOIN(".",TRUE,AC7,AB7:AB7)&amp;"."&amp;_xlfn.TEXTJOIN(".",TRUE,Y7:AA7)</f>
+        <f t="shared" si="1"/>
         <v>tc-1.00.df-Y.dm-Hi.cp-00.CF1</v>
       </c>
       <c r="I7" t="str">
@@ -34186,9 +34234,9 @@
         <f t="shared" ref="L7:L37" si="7">U7</f>
         <v>Y</v>
       </c>
-      <c r="M7">
-        <f t="shared" ref="M7:M37" si="8">W7</f>
-        <v>1</v>
+      <c r="M7" t="str">
+        <f t="shared" ref="M7:M69" si="8">TEXT(W7,"0.00")</f>
+        <v>1.00</v>
       </c>
       <c r="O7">
         <v>5</v>
@@ -34248,7 +34296,7 @@
         <v>tc-1.00.df-Y.dm-Lo.cp-95.CF1</v>
       </c>
       <c r="H8" t="str">
-        <f>_xlfn.TEXTJOIN(".",TRUE,AC8,AB8:AB8)&amp;"."&amp;_xlfn.TEXTJOIN(".",TRUE,Y8:AA8)</f>
+        <f t="shared" si="1"/>
         <v>tc-1.00.df-Y.dm-Lo.cp-95.CF1</v>
       </c>
       <c r="I8" t="str">
@@ -34267,9 +34315,9 @@
         <f t="shared" si="7"/>
         <v>Y</v>
       </c>
-      <c r="M8">
+      <c r="M8" t="str">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>1.00</v>
       </c>
       <c r="O8">
         <v>5</v>
@@ -34329,7 +34377,7 @@
         <v>tc-1.00.df-Y.dm-Hi.cp-95.CF1</v>
       </c>
       <c r="H9" t="str">
-        <f>_xlfn.TEXTJOIN(".",TRUE,AC9,AB9:AB9)&amp;"."&amp;_xlfn.TEXTJOIN(".",TRUE,Y9:AA9)</f>
+        <f t="shared" si="1"/>
         <v>tc-1.00.df-Y.dm-Hi.cp-95.CF1</v>
       </c>
       <c r="I9" t="str">
@@ -34348,9 +34396,9 @@
         <f t="shared" si="7"/>
         <v>Y</v>
       </c>
-      <c r="M9">
+      <c r="M9" t="str">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>1.00</v>
       </c>
       <c r="O9">
         <v>5</v>
@@ -34410,7 +34458,7 @@
         <v>tc-1.00.df-N.dm-Lo.cp-00.CF1</v>
       </c>
       <c r="H10" t="str">
-        <f>_xlfn.TEXTJOIN(".",TRUE,AC10,AB10:AB10)&amp;"."&amp;_xlfn.TEXTJOIN(".",TRUE,Y10:AA10)</f>
+        <f t="shared" si="1"/>
         <v>tc-1.00.df-N.dm-Lo.cp-00.CF1</v>
       </c>
       <c r="I10" t="str">
@@ -34429,9 +34477,9 @@
         <f t="shared" si="7"/>
         <v>N</v>
       </c>
-      <c r="M10">
+      <c r="M10" t="str">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>1.00</v>
       </c>
       <c r="O10">
         <v>5</v>
@@ -34491,7 +34539,7 @@
         <v>tc-1.00.df-N.dm-Hi.cp-00.CF1</v>
       </c>
       <c r="H11" t="str">
-        <f>_xlfn.TEXTJOIN(".",TRUE,AC11,AB11:AB11)&amp;"."&amp;_xlfn.TEXTJOIN(".",TRUE,Y11:AA11)</f>
+        <f t="shared" si="1"/>
         <v>tc-1.00.df-N.dm-Hi.cp-00.CF1</v>
       </c>
       <c r="I11" t="str">
@@ -34510,9 +34558,9 @@
         <f t="shared" si="7"/>
         <v>N</v>
       </c>
-      <c r="M11">
+      <c r="M11" t="str">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>1.00</v>
       </c>
       <c r="O11">
         <v>5</v>
@@ -34572,7 +34620,7 @@
         <v>tc-1.00.df-N.dm-Lo.cp-95.CF1</v>
       </c>
       <c r="H12" t="str">
-        <f>_xlfn.TEXTJOIN(".",TRUE,AC12,AB12:AB12)&amp;"."&amp;_xlfn.TEXTJOIN(".",TRUE,Y12:AA12)</f>
+        <f t="shared" si="1"/>
         <v>tc-1.00.df-N.dm-Lo.cp-95.CF1</v>
       </c>
       <c r="I12" t="str">
@@ -34591,9 +34639,9 @@
         <f t="shared" si="7"/>
         <v>N</v>
       </c>
-      <c r="M12">
+      <c r="M12" t="str">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>1.00</v>
       </c>
       <c r="O12">
         <v>5</v>
@@ -34653,7 +34701,7 @@
         <v>tc-1.00.df-N.dm-Hi.cp-95.CF1</v>
       </c>
       <c r="H13" t="str">
-        <f>_xlfn.TEXTJOIN(".",TRUE,AC13,AB13:AB13)&amp;"."&amp;_xlfn.TEXTJOIN(".",TRUE,Y13:AA13)</f>
+        <f t="shared" si="1"/>
         <v>tc-1.00.df-N.dm-Hi.cp-95.CF1</v>
       </c>
       <c r="I13" t="str">
@@ -34672,9 +34720,9 @@
         <f t="shared" si="7"/>
         <v>N</v>
       </c>
-      <c r="M13">
+      <c r="M13" t="str">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>1.00</v>
       </c>
       <c r="O13">
         <v>5</v>
@@ -34734,7 +34782,7 @@
         <v>tc-1.00.df-Y.dm-Lo.cp-00.CF6</v>
       </c>
       <c r="H14" t="str">
-        <f>_xlfn.TEXTJOIN(".",TRUE,AC14,AB14:AB14)&amp;"."&amp;_xlfn.TEXTJOIN(".",TRUE,Y14:AA14)</f>
+        <f t="shared" si="1"/>
         <v>tc-1.00.df-Y.dm-Lo.cp-00.CF6</v>
       </c>
       <c r="I14" t="str">
@@ -34753,9 +34801,9 @@
         <f t="shared" si="7"/>
         <v>Y</v>
       </c>
-      <c r="M14">
+      <c r="M14" t="str">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>1.00</v>
       </c>
       <c r="O14">
         <v>5</v>
@@ -34815,7 +34863,7 @@
         <v>tc-1.00.df-Y.dm-Hi.cp-00.CF6</v>
       </c>
       <c r="H15" t="str">
-        <f>_xlfn.TEXTJOIN(".",TRUE,AC15,AB15:AB15)&amp;"."&amp;_xlfn.TEXTJOIN(".",TRUE,Y15:AA15)</f>
+        <f t="shared" si="1"/>
         <v>tc-1.00.df-Y.dm-Hi.cp-00.CF6</v>
       </c>
       <c r="I15" t="str">
@@ -34834,9 +34882,9 @@
         <f t="shared" si="7"/>
         <v>Y</v>
       </c>
-      <c r="M15">
+      <c r="M15" t="str">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>1.00</v>
       </c>
       <c r="O15">
         <v>5</v>
@@ -34896,7 +34944,7 @@
         <v>tc-1.00.df-Y.dm-Lo.cp-95.CF6</v>
       </c>
       <c r="H16" t="str">
-        <f>_xlfn.TEXTJOIN(".",TRUE,AC16,AB16:AB16)&amp;"."&amp;_xlfn.TEXTJOIN(".",TRUE,Y16:AA16)</f>
+        <f t="shared" si="1"/>
         <v>tc-1.00.df-Y.dm-Lo.cp-95.CF6</v>
       </c>
       <c r="I16" t="str">
@@ -34915,9 +34963,9 @@
         <f t="shared" si="7"/>
         <v>Y</v>
       </c>
-      <c r="M16">
+      <c r="M16" t="str">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>1.00</v>
       </c>
       <c r="O16">
         <v>5</v>
@@ -34977,7 +35025,7 @@
         <v>tc-1.00.df-Y.dm-Hi.cp-95.CF6</v>
       </c>
       <c r="H17" t="str">
-        <f>_xlfn.TEXTJOIN(".",TRUE,AC17,AB17:AB17)&amp;"."&amp;_xlfn.TEXTJOIN(".",TRUE,Y17:AA17)</f>
+        <f t="shared" si="1"/>
         <v>tc-1.00.df-Y.dm-Hi.cp-95.CF6</v>
       </c>
       <c r="I17" t="str">
@@ -34996,9 +35044,9 @@
         <f t="shared" si="7"/>
         <v>Y</v>
       </c>
-      <c r="M17">
+      <c r="M17" t="str">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>1.00</v>
       </c>
       <c r="O17">
         <v>5</v>
@@ -35058,7 +35106,7 @@
         <v>tc-1.00.df-N.dm-Lo.cp-00.CF6</v>
       </c>
       <c r="H18" t="str">
-        <f>_xlfn.TEXTJOIN(".",TRUE,AC18,AB18:AB18)&amp;"."&amp;_xlfn.TEXTJOIN(".",TRUE,Y18:AA18)</f>
+        <f t="shared" si="1"/>
         <v>tc-1.00.df-N.dm-Lo.cp-00.CF6</v>
       </c>
       <c r="I18" t="str">
@@ -35077,9 +35125,9 @@
         <f t="shared" si="7"/>
         <v>N</v>
       </c>
-      <c r="M18">
+      <c r="M18" t="str">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>1.00</v>
       </c>
       <c r="O18">
         <v>5</v>
@@ -35139,7 +35187,7 @@
         <v>tc-1.00.df-N.dm-Hi.cp-00.CF6</v>
       </c>
       <c r="H19" t="str">
-        <f>_xlfn.TEXTJOIN(".",TRUE,AC19,AB19:AB19)&amp;"."&amp;_xlfn.TEXTJOIN(".",TRUE,Y19:AA19)</f>
+        <f t="shared" si="1"/>
         <v>tc-1.00.df-N.dm-Hi.cp-00.CF6</v>
       </c>
       <c r="I19" t="str">
@@ -35158,9 +35206,9 @@
         <f t="shared" si="7"/>
         <v>N</v>
       </c>
-      <c r="M19">
+      <c r="M19" t="str">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>1.00</v>
       </c>
       <c r="O19">
         <v>5</v>
@@ -35220,7 +35268,7 @@
         <v>tc-1.00.df-N.dm-Lo.cp-95.CF6</v>
       </c>
       <c r="H20" t="str">
-        <f>_xlfn.TEXTJOIN(".",TRUE,AC20,AB20:AB20)&amp;"."&amp;_xlfn.TEXTJOIN(".",TRUE,Y20:AA20)</f>
+        <f t="shared" si="1"/>
         <v>tc-1.00.df-N.dm-Lo.cp-95.CF6</v>
       </c>
       <c r="I20" t="str">
@@ -35239,9 +35287,9 @@
         <f t="shared" si="7"/>
         <v>N</v>
       </c>
-      <c r="M20">
+      <c r="M20" t="str">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>1.00</v>
       </c>
       <c r="O20">
         <v>5</v>
@@ -35301,7 +35349,7 @@
         <v>tc-1.00.df-N.dm-Hi.cp-95.CF6</v>
       </c>
       <c r="H21" t="str">
-        <f>_xlfn.TEXTJOIN(".",TRUE,AC21,AB21:AB21)&amp;"."&amp;_xlfn.TEXTJOIN(".",TRUE,Y21:AA21)</f>
+        <f t="shared" si="1"/>
         <v>tc-1.00.df-N.dm-Hi.cp-95.CF6</v>
       </c>
       <c r="I21" t="str">
@@ -35320,9 +35368,9 @@
         <f t="shared" si="7"/>
         <v>N</v>
       </c>
-      <c r="M21">
+      <c r="M21" t="str">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>1.00</v>
       </c>
       <c r="O21">
         <v>5</v>
@@ -35382,7 +35430,7 @@
         <v>tc-0.25.df-Y.dm-Lo.cp-00.CF1</v>
       </c>
       <c r="H22" t="str">
-        <f>_xlfn.TEXTJOIN(".",TRUE,AC22,AB22:AB22)&amp;"."&amp;_xlfn.TEXTJOIN(".",TRUE,Y22:AA22)</f>
+        <f t="shared" si="1"/>
         <v>tc-0.25.df-Y.dm-Lo.cp-00.CF1</v>
       </c>
       <c r="I22" t="str">
@@ -35401,7 +35449,7 @@
         <f t="shared" si="7"/>
         <v>Y</v>
       </c>
-      <c r="M22">
+      <c r="M22" t="str">
         <f t="shared" si="8"/>
         <v>0.25</v>
       </c>
@@ -35463,7 +35511,7 @@
         <v>tc-0.25.df-Y.dm-Hi.cp-00.CF1</v>
       </c>
       <c r="H23" t="str">
-        <f>_xlfn.TEXTJOIN(".",TRUE,AC23,AB23:AB23)&amp;"."&amp;_xlfn.TEXTJOIN(".",TRUE,Y23:AA23)</f>
+        <f t="shared" si="1"/>
         <v>tc-0.25.df-Y.dm-Hi.cp-00.CF1</v>
       </c>
       <c r="I23" t="str">
@@ -35482,7 +35530,7 @@
         <f t="shared" si="7"/>
         <v>Y</v>
       </c>
-      <c r="M23">
+      <c r="M23" t="str">
         <f t="shared" si="8"/>
         <v>0.25</v>
       </c>
@@ -35544,7 +35592,7 @@
         <v>tc-0.25.df-Y.dm-Lo.cp-95.CF1</v>
       </c>
       <c r="H24" t="str">
-        <f>_xlfn.TEXTJOIN(".",TRUE,AC24,AB24:AB24)&amp;"."&amp;_xlfn.TEXTJOIN(".",TRUE,Y24:AA24)</f>
+        <f t="shared" si="1"/>
         <v>tc-0.25.df-Y.dm-Lo.cp-95.CF1</v>
       </c>
       <c r="I24" t="str">
@@ -35563,7 +35611,7 @@
         <f t="shared" si="7"/>
         <v>Y</v>
       </c>
-      <c r="M24">
+      <c r="M24" t="str">
         <f t="shared" si="8"/>
         <v>0.25</v>
       </c>
@@ -35625,7 +35673,7 @@
         <v>tc-0.25.df-Y.dm-Hi.cp-95.CF1</v>
       </c>
       <c r="H25" t="str">
-        <f>_xlfn.TEXTJOIN(".",TRUE,AC25,AB25:AB25)&amp;"."&amp;_xlfn.TEXTJOIN(".",TRUE,Y25:AA25)</f>
+        <f t="shared" si="1"/>
         <v>tc-0.25.df-Y.dm-Hi.cp-95.CF1</v>
       </c>
       <c r="I25" t="str">
@@ -35644,7 +35692,7 @@
         <f t="shared" si="7"/>
         <v>Y</v>
       </c>
-      <c r="M25">
+      <c r="M25" t="str">
         <f t="shared" si="8"/>
         <v>0.25</v>
       </c>
@@ -35706,7 +35754,7 @@
         <v>tc-0.25.df-N.dm-Lo.cp-00.CF1</v>
       </c>
       <c r="H26" t="str">
-        <f>_xlfn.TEXTJOIN(".",TRUE,AC26,AB26:AB26)&amp;"."&amp;_xlfn.TEXTJOIN(".",TRUE,Y26:AA26)</f>
+        <f t="shared" si="1"/>
         <v>tc-0.25.df-N.dm-Lo.cp-00.CF1</v>
       </c>
       <c r="I26" t="str">
@@ -35725,7 +35773,7 @@
         <f t="shared" si="7"/>
         <v>N</v>
       </c>
-      <c r="M26">
+      <c r="M26" t="str">
         <f t="shared" si="8"/>
         <v>0.25</v>
       </c>
@@ -35787,7 +35835,7 @@
         <v>tc-0.25.df-N.dm-Hi.cp-00.CF1</v>
       </c>
       <c r="H27" t="str">
-        <f>_xlfn.TEXTJOIN(".",TRUE,AC27,AB27:AB27)&amp;"."&amp;_xlfn.TEXTJOIN(".",TRUE,Y27:AA27)</f>
+        <f t="shared" si="1"/>
         <v>tc-0.25.df-N.dm-Hi.cp-00.CF1</v>
       </c>
       <c r="I27" t="str">
@@ -35806,7 +35854,7 @@
         <f t="shared" si="7"/>
         <v>N</v>
       </c>
-      <c r="M27">
+      <c r="M27" t="str">
         <f t="shared" si="8"/>
         <v>0.25</v>
       </c>
@@ -35868,7 +35916,7 @@
         <v>tc-0.25.df-N.dm-Lo.cp-95.CF1</v>
       </c>
       <c r="H28" t="str">
-        <f>_xlfn.TEXTJOIN(".",TRUE,AC28,AB28:AB28)&amp;"."&amp;_xlfn.TEXTJOIN(".",TRUE,Y28:AA28)</f>
+        <f t="shared" si="1"/>
         <v>tc-0.25.df-N.dm-Lo.cp-95.CF1</v>
       </c>
       <c r="I28" t="str">
@@ -35887,7 +35935,7 @@
         <f t="shared" si="7"/>
         <v>N</v>
       </c>
-      <c r="M28">
+      <c r="M28" t="str">
         <f t="shared" si="8"/>
         <v>0.25</v>
       </c>
@@ -35949,7 +35997,7 @@
         <v>tc-0.25.df-N.dm-Hi.cp-95.CF1</v>
       </c>
       <c r="H29" t="str">
-        <f>_xlfn.TEXTJOIN(".",TRUE,AC29,AB29:AB29)&amp;"."&amp;_xlfn.TEXTJOIN(".",TRUE,Y29:AA29)</f>
+        <f t="shared" si="1"/>
         <v>tc-0.25.df-N.dm-Hi.cp-95.CF1</v>
       </c>
       <c r="I29" t="str">
@@ -35968,7 +36016,7 @@
         <f t="shared" si="7"/>
         <v>N</v>
       </c>
-      <c r="M29">
+      <c r="M29" t="str">
         <f t="shared" si="8"/>
         <v>0.25</v>
       </c>
@@ -36030,7 +36078,7 @@
         <v>tc-0.25.df-Y.dm-Lo.cp-00.CF6</v>
       </c>
       <c r="H30" t="str">
-        <f>_xlfn.TEXTJOIN(".",TRUE,AC30,AB30:AB30)&amp;"."&amp;_xlfn.TEXTJOIN(".",TRUE,Y30:AA30)</f>
+        <f t="shared" si="1"/>
         <v>tc-0.25.df-Y.dm-Lo.cp-00.CF6</v>
       </c>
       <c r="I30" t="str">
@@ -36049,7 +36097,7 @@
         <f t="shared" si="7"/>
         <v>Y</v>
       </c>
-      <c r="M30">
+      <c r="M30" t="str">
         <f t="shared" si="8"/>
         <v>0.25</v>
       </c>
@@ -36111,7 +36159,7 @@
         <v>tc-0.25.df-Y.dm-Hi.cp-00.CF6</v>
       </c>
       <c r="H31" t="str">
-        <f>_xlfn.TEXTJOIN(".",TRUE,AC31,AB31:AB31)&amp;"."&amp;_xlfn.TEXTJOIN(".",TRUE,Y31:AA31)</f>
+        <f t="shared" si="1"/>
         <v>tc-0.25.df-Y.dm-Hi.cp-00.CF6</v>
       </c>
       <c r="I31" t="str">
@@ -36130,7 +36178,7 @@
         <f t="shared" si="7"/>
         <v>Y</v>
       </c>
-      <c r="M31">
+      <c r="M31" t="str">
         <f t="shared" si="8"/>
         <v>0.25</v>
       </c>
@@ -36192,7 +36240,7 @@
         <v>tc-0.25.df-Y.dm-Lo.cp-95.CF6</v>
       </c>
       <c r="H32" t="str">
-        <f>_xlfn.TEXTJOIN(".",TRUE,AC32,AB32:AB32)&amp;"."&amp;_xlfn.TEXTJOIN(".",TRUE,Y32:AA32)</f>
+        <f t="shared" si="1"/>
         <v>tc-0.25.df-Y.dm-Lo.cp-95.CF6</v>
       </c>
       <c r="I32" t="str">
@@ -36211,7 +36259,7 @@
         <f t="shared" si="7"/>
         <v>Y</v>
       </c>
-      <c r="M32">
+      <c r="M32" t="str">
         <f t="shared" si="8"/>
         <v>0.25</v>
       </c>
@@ -36273,7 +36321,7 @@
         <v>tc-0.25.df-Y.dm-Hi.cp-95.CF6</v>
       </c>
       <c r="H33" t="str">
-        <f>_xlfn.TEXTJOIN(".",TRUE,AC33,AB33:AB33)&amp;"."&amp;_xlfn.TEXTJOIN(".",TRUE,Y33:AA33)</f>
+        <f t="shared" si="1"/>
         <v>tc-0.25.df-Y.dm-Hi.cp-95.CF6</v>
       </c>
       <c r="I33" t="str">
@@ -36292,7 +36340,7 @@
         <f t="shared" si="7"/>
         <v>Y</v>
       </c>
-      <c r="M33">
+      <c r="M33" t="str">
         <f t="shared" si="8"/>
         <v>0.25</v>
       </c>
@@ -36354,7 +36402,7 @@
         <v>tc-0.25.df-N.dm-Lo.cp-00.CF6</v>
       </c>
       <c r="H34" t="str">
-        <f>_xlfn.TEXTJOIN(".",TRUE,AC34,AB34:AB34)&amp;"."&amp;_xlfn.TEXTJOIN(".",TRUE,Y34:AA34)</f>
+        <f t="shared" si="1"/>
         <v>tc-0.25.df-N.dm-Lo.cp-00.CF6</v>
       </c>
       <c r="I34" t="str">
@@ -36373,7 +36421,7 @@
         <f t="shared" si="7"/>
         <v>N</v>
       </c>
-      <c r="M34">
+      <c r="M34" t="str">
         <f t="shared" si="8"/>
         <v>0.25</v>
       </c>
@@ -36435,7 +36483,7 @@
         <v>tc-0.25.df-N.dm-Hi.cp-00.CF6</v>
       </c>
       <c r="H35" t="str">
-        <f>_xlfn.TEXTJOIN(".",TRUE,AC35,AB35:AB35)&amp;"."&amp;_xlfn.TEXTJOIN(".",TRUE,Y35:AA35)</f>
+        <f t="shared" si="1"/>
         <v>tc-0.25.df-N.dm-Hi.cp-00.CF6</v>
       </c>
       <c r="I35" t="str">
@@ -36454,7 +36502,7 @@
         <f t="shared" si="7"/>
         <v>N</v>
       </c>
-      <c r="M35">
+      <c r="M35" t="str">
         <f t="shared" si="8"/>
         <v>0.25</v>
       </c>
@@ -36516,7 +36564,7 @@
         <v>tc-0.25.df-N.dm-Lo.cp-95.CF6</v>
       </c>
       <c r="H36" t="str">
-        <f>_xlfn.TEXTJOIN(".",TRUE,AC36,AB36:AB36)&amp;"."&amp;_xlfn.TEXTJOIN(".",TRUE,Y36:AA36)</f>
+        <f t="shared" si="1"/>
         <v>tc-0.25.df-N.dm-Lo.cp-95.CF6</v>
       </c>
       <c r="I36" t="str">
@@ -36535,7 +36583,7 @@
         <f t="shared" si="7"/>
         <v>N</v>
       </c>
-      <c r="M36">
+      <c r="M36" t="str">
         <f t="shared" si="8"/>
         <v>0.25</v>
       </c>
@@ -36597,7 +36645,7 @@
         <v>tc-0.25.df-N.dm-Hi.cp-95.CF6</v>
       </c>
       <c r="H37" t="str">
-        <f>_xlfn.TEXTJOIN(".",TRUE,AC37,AB37:AB37)&amp;"."&amp;_xlfn.TEXTJOIN(".",TRUE,Y37:AA37)</f>
+        <f t="shared" si="1"/>
         <v>tc-0.25.df-N.dm-Hi.cp-95.CF6</v>
       </c>
       <c r="I37" t="str">
@@ -36616,7 +36664,7 @@
         <f t="shared" si="7"/>
         <v>N</v>
       </c>
-      <c r="M37">
+      <c r="M37" t="str">
         <f t="shared" si="8"/>
         <v>0.25</v>
       </c>
@@ -36678,7 +36726,7 @@
         <v>tc-2.00.df-Y.dm-Lo.cp-00.CF1</v>
       </c>
       <c r="H38" t="str">
-        <f>_xlfn.TEXTJOIN(".",TRUE,AC38,AB38:AB38)&amp;"."&amp;_xlfn.TEXTJOIN(".",TRUE,Y38:AA38)</f>
+        <f t="shared" si="1"/>
         <v>tc-2.00.df-Y.dm-Lo.cp-00.CF1</v>
       </c>
       <c r="I38" t="str">
@@ -36697,9 +36745,9 @@
         <f t="shared" ref="L38:L53" si="21">U38</f>
         <v>Y</v>
       </c>
-      <c r="M38">
-        <f t="shared" ref="M38:M53" si="22">W38</f>
-        <v>2</v>
+      <c r="M38" t="str">
+        <f t="shared" si="8"/>
+        <v>2.00</v>
       </c>
       <c r="O38">
         <v>5</v>
@@ -36729,7 +36777,7 @@
         <v>2</v>
       </c>
       <c r="Y38" t="str">
-        <f t="shared" ref="Y38:Y53" si="23">R$1&amp;"-"&amp;R38</f>
+        <f t="shared" ref="Y38:Y53" si="22">R$1&amp;"-"&amp;R38</f>
         <v>dm-Lo</v>
       </c>
       <c r="Z38" t="str">
@@ -36737,11 +36785,11 @@
         <v>cp-00</v>
       </c>
       <c r="AA38" t="str">
-        <f t="shared" ref="AA38:AA53" si="24">T38</f>
+        <f t="shared" ref="AA38:AA53" si="23">T38</f>
         <v>CF1</v>
       </c>
       <c r="AB38" t="str">
-        <f t="shared" ref="AB38:AB53" si="25">U$1&amp;"-"&amp;U38</f>
+        <f t="shared" ref="AB38:AB53" si="24">U$1&amp;"-"&amp;U38</f>
         <v>df-Y</v>
       </c>
       <c r="AC38" t="str">
@@ -36759,7 +36807,7 @@
         <v>tc-2.00.df-Y.dm-Hi.cp-00.CF1</v>
       </c>
       <c r="H39" t="str">
-        <f>_xlfn.TEXTJOIN(".",TRUE,AC39,AB39:AB39)&amp;"."&amp;_xlfn.TEXTJOIN(".",TRUE,Y39:AA39)</f>
+        <f t="shared" si="1"/>
         <v>tc-2.00.df-Y.dm-Hi.cp-00.CF1</v>
       </c>
       <c r="I39" t="str">
@@ -36778,9 +36826,9 @@
         <f t="shared" si="21"/>
         <v>Y</v>
       </c>
-      <c r="M39">
-        <f t="shared" si="22"/>
-        <v>2</v>
+      <c r="M39" t="str">
+        <f t="shared" si="8"/>
+        <v>2.00</v>
       </c>
       <c r="O39">
         <v>5</v>
@@ -36810,7 +36858,7 @@
         <v>2</v>
       </c>
       <c r="Y39" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>dm-Hi</v>
       </c>
       <c r="Z39" t="str">
@@ -36818,11 +36866,11 @@
         <v>cp-00</v>
       </c>
       <c r="AA39" t="str">
+        <f t="shared" si="23"/>
+        <v>CF1</v>
+      </c>
+      <c r="AB39" t="str">
         <f t="shared" si="24"/>
-        <v>CF1</v>
-      </c>
-      <c r="AB39" t="str">
-        <f t="shared" si="25"/>
         <v>df-Y</v>
       </c>
       <c r="AC39" t="str">
@@ -36840,7 +36888,7 @@
         <v>tc-2.00.df-Y.dm-Lo.cp-95.CF1</v>
       </c>
       <c r="H40" t="str">
-        <f>_xlfn.TEXTJOIN(".",TRUE,AC40,AB40:AB40)&amp;"."&amp;_xlfn.TEXTJOIN(".",TRUE,Y40:AA40)</f>
+        <f t="shared" si="1"/>
         <v>tc-2.00.df-Y.dm-Lo.cp-95.CF1</v>
       </c>
       <c r="I40" t="str">
@@ -36859,9 +36907,9 @@
         <f t="shared" si="21"/>
         <v>Y</v>
       </c>
-      <c r="M40">
-        <f t="shared" si="22"/>
-        <v>2</v>
+      <c r="M40" t="str">
+        <f t="shared" si="8"/>
+        <v>2.00</v>
       </c>
       <c r="O40">
         <v>5</v>
@@ -36891,7 +36939,7 @@
         <v>2</v>
       </c>
       <c r="Y40" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>dm-Lo</v>
       </c>
       <c r="Z40" t="str">
@@ -36899,11 +36947,11 @@
         <v>cp-95</v>
       </c>
       <c r="AA40" t="str">
+        <f t="shared" si="23"/>
+        <v>CF1</v>
+      </c>
+      <c r="AB40" t="str">
         <f t="shared" si="24"/>
-        <v>CF1</v>
-      </c>
-      <c r="AB40" t="str">
-        <f t="shared" si="25"/>
         <v>df-Y</v>
       </c>
       <c r="AC40" t="str">
@@ -36921,7 +36969,7 @@
         <v>tc-2.00.df-Y.dm-Hi.cp-95.CF1</v>
       </c>
       <c r="H41" t="str">
-        <f>_xlfn.TEXTJOIN(".",TRUE,AC41,AB41:AB41)&amp;"."&amp;_xlfn.TEXTJOIN(".",TRUE,Y41:AA41)</f>
+        <f t="shared" si="1"/>
         <v>tc-2.00.df-Y.dm-Hi.cp-95.CF1</v>
       </c>
       <c r="I41" t="str">
@@ -36940,9 +36988,9 @@
         <f t="shared" si="21"/>
         <v>Y</v>
       </c>
-      <c r="M41">
-        <f t="shared" si="22"/>
-        <v>2</v>
+      <c r="M41" t="str">
+        <f t="shared" si="8"/>
+        <v>2.00</v>
       </c>
       <c r="O41">
         <v>5</v>
@@ -36972,7 +37020,7 @@
         <v>2</v>
       </c>
       <c r="Y41" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>dm-Hi</v>
       </c>
       <c r="Z41" t="str">
@@ -36980,11 +37028,11 @@
         <v>cp-95</v>
       </c>
       <c r="AA41" t="str">
+        <f t="shared" si="23"/>
+        <v>CF1</v>
+      </c>
+      <c r="AB41" t="str">
         <f t="shared" si="24"/>
-        <v>CF1</v>
-      </c>
-      <c r="AB41" t="str">
-        <f t="shared" si="25"/>
         <v>df-Y</v>
       </c>
       <c r="AC41" t="str">
@@ -37002,7 +37050,7 @@
         <v>tc-2.00.df-N.dm-Lo.cp-00.CF1</v>
       </c>
       <c r="H42" t="str">
-        <f>_xlfn.TEXTJOIN(".",TRUE,AC42,AB42:AB42)&amp;"."&amp;_xlfn.TEXTJOIN(".",TRUE,Y42:AA42)</f>
+        <f t="shared" si="1"/>
         <v>tc-2.00.df-N.dm-Lo.cp-00.CF1</v>
       </c>
       <c r="I42" t="str">
@@ -37021,9 +37069,9 @@
         <f t="shared" si="21"/>
         <v>N</v>
       </c>
-      <c r="M42">
-        <f t="shared" si="22"/>
-        <v>2</v>
+      <c r="M42" t="str">
+        <f t="shared" si="8"/>
+        <v>2.00</v>
       </c>
       <c r="O42">
         <v>5</v>
@@ -37053,7 +37101,7 @@
         <v>2</v>
       </c>
       <c r="Y42" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>dm-Lo</v>
       </c>
       <c r="Z42" t="str">
@@ -37061,11 +37109,11 @@
         <v>cp-00</v>
       </c>
       <c r="AA42" t="str">
+        <f t="shared" si="23"/>
+        <v>CF1</v>
+      </c>
+      <c r="AB42" t="str">
         <f t="shared" si="24"/>
-        <v>CF1</v>
-      </c>
-      <c r="AB42" t="str">
-        <f t="shared" si="25"/>
         <v>df-N</v>
       </c>
       <c r="AC42" t="str">
@@ -37083,7 +37131,7 @@
         <v>tc-2.00.df-N.dm-Hi.cp-00.CF1</v>
       </c>
       <c r="H43" t="str">
-        <f>_xlfn.TEXTJOIN(".",TRUE,AC43,AB43:AB43)&amp;"."&amp;_xlfn.TEXTJOIN(".",TRUE,Y43:AA43)</f>
+        <f t="shared" si="1"/>
         <v>tc-2.00.df-N.dm-Hi.cp-00.CF1</v>
       </c>
       <c r="I43" t="str">
@@ -37102,9 +37150,9 @@
         <f t="shared" si="21"/>
         <v>N</v>
       </c>
-      <c r="M43">
-        <f t="shared" si="22"/>
-        <v>2</v>
+      <c r="M43" t="str">
+        <f t="shared" si="8"/>
+        <v>2.00</v>
       </c>
       <c r="O43">
         <v>5</v>
@@ -37134,7 +37182,7 @@
         <v>2</v>
       </c>
       <c r="Y43" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>dm-Hi</v>
       </c>
       <c r="Z43" t="str">
@@ -37142,11 +37190,11 @@
         <v>cp-00</v>
       </c>
       <c r="AA43" t="str">
+        <f t="shared" si="23"/>
+        <v>CF1</v>
+      </c>
+      <c r="AB43" t="str">
         <f t="shared" si="24"/>
-        <v>CF1</v>
-      </c>
-      <c r="AB43" t="str">
-        <f t="shared" si="25"/>
         <v>df-N</v>
       </c>
       <c r="AC43" t="str">
@@ -37164,7 +37212,7 @@
         <v>tc-2.00.df-N.dm-Lo.cp-95.CF1</v>
       </c>
       <c r="H44" t="str">
-        <f>_xlfn.TEXTJOIN(".",TRUE,AC44,AB44:AB44)&amp;"."&amp;_xlfn.TEXTJOIN(".",TRUE,Y44:AA44)</f>
+        <f t="shared" si="1"/>
         <v>tc-2.00.df-N.dm-Lo.cp-95.CF1</v>
       </c>
       <c r="I44" t="str">
@@ -37183,9 +37231,9 @@
         <f t="shared" si="21"/>
         <v>N</v>
       </c>
-      <c r="M44">
-        <f t="shared" si="22"/>
-        <v>2</v>
+      <c r="M44" t="str">
+        <f t="shared" si="8"/>
+        <v>2.00</v>
       </c>
       <c r="O44">
         <v>5</v>
@@ -37215,7 +37263,7 @@
         <v>2</v>
       </c>
       <c r="Y44" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>dm-Lo</v>
       </c>
       <c r="Z44" t="str">
@@ -37223,11 +37271,11 @@
         <v>cp-95</v>
       </c>
       <c r="AA44" t="str">
+        <f t="shared" si="23"/>
+        <v>CF1</v>
+      </c>
+      <c r="AB44" t="str">
         <f t="shared" si="24"/>
-        <v>CF1</v>
-      </c>
-      <c r="AB44" t="str">
-        <f t="shared" si="25"/>
         <v>df-N</v>
       </c>
       <c r="AC44" t="str">
@@ -37245,7 +37293,7 @@
         <v>tc-2.00.df-N.dm-Hi.cp-95.CF1</v>
       </c>
       <c r="H45" t="str">
-        <f>_xlfn.TEXTJOIN(".",TRUE,AC45,AB45:AB45)&amp;"."&amp;_xlfn.TEXTJOIN(".",TRUE,Y45:AA45)</f>
+        <f t="shared" si="1"/>
         <v>tc-2.00.df-N.dm-Hi.cp-95.CF1</v>
       </c>
       <c r="I45" t="str">
@@ -37264,9 +37312,9 @@
         <f t="shared" si="21"/>
         <v>N</v>
       </c>
-      <c r="M45">
-        <f t="shared" si="22"/>
-        <v>2</v>
+      <c r="M45" t="str">
+        <f t="shared" si="8"/>
+        <v>2.00</v>
       </c>
       <c r="O45">
         <v>5</v>
@@ -37296,7 +37344,7 @@
         <v>2</v>
       </c>
       <c r="Y45" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>dm-Hi</v>
       </c>
       <c r="Z45" t="str">
@@ -37304,11 +37352,11 @@
         <v>cp-95</v>
       </c>
       <c r="AA45" t="str">
+        <f t="shared" si="23"/>
+        <v>CF1</v>
+      </c>
+      <c r="AB45" t="str">
         <f t="shared" si="24"/>
-        <v>CF1</v>
-      </c>
-      <c r="AB45" t="str">
-        <f t="shared" si="25"/>
         <v>df-N</v>
       </c>
       <c r="AC45" t="str">
@@ -37326,7 +37374,7 @@
         <v>tc-2.00.df-Y.dm-Lo.cp-00.CF6</v>
       </c>
       <c r="H46" t="str">
-        <f>_xlfn.TEXTJOIN(".",TRUE,AC46,AB46:AB46)&amp;"."&amp;_xlfn.TEXTJOIN(".",TRUE,Y46:AA46)</f>
+        <f t="shared" si="1"/>
         <v>tc-2.00.df-Y.dm-Lo.cp-00.CF6</v>
       </c>
       <c r="I46" t="str">
@@ -37345,9 +37393,9 @@
         <f t="shared" si="21"/>
         <v>Y</v>
       </c>
-      <c r="M46">
-        <f t="shared" si="22"/>
-        <v>2</v>
+      <c r="M46" t="str">
+        <f t="shared" si="8"/>
+        <v>2.00</v>
       </c>
       <c r="O46">
         <v>5</v>
@@ -37377,7 +37425,7 @@
         <v>2</v>
       </c>
       <c r="Y46" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>dm-Lo</v>
       </c>
       <c r="Z46" t="str">
@@ -37385,11 +37433,11 @@
         <v>cp-00</v>
       </c>
       <c r="AA46" t="str">
+        <f t="shared" si="23"/>
+        <v>CF6</v>
+      </c>
+      <c r="AB46" t="str">
         <f t="shared" si="24"/>
-        <v>CF6</v>
-      </c>
-      <c r="AB46" t="str">
-        <f t="shared" si="25"/>
         <v>df-Y</v>
       </c>
       <c r="AC46" t="str">
@@ -37407,7 +37455,7 @@
         <v>tc-2.00.df-Y.dm-Hi.cp-00.CF6</v>
       </c>
       <c r="H47" t="str">
-        <f>_xlfn.TEXTJOIN(".",TRUE,AC47,AB47:AB47)&amp;"."&amp;_xlfn.TEXTJOIN(".",TRUE,Y47:AA47)</f>
+        <f t="shared" si="1"/>
         <v>tc-2.00.df-Y.dm-Hi.cp-00.CF6</v>
       </c>
       <c r="I47" t="str">
@@ -37426,9 +37474,9 @@
         <f t="shared" si="21"/>
         <v>Y</v>
       </c>
-      <c r="M47">
-        <f t="shared" si="22"/>
-        <v>2</v>
+      <c r="M47" t="str">
+        <f t="shared" si="8"/>
+        <v>2.00</v>
       </c>
       <c r="O47">
         <v>5</v>
@@ -37458,7 +37506,7 @@
         <v>2</v>
       </c>
       <c r="Y47" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>dm-Hi</v>
       </c>
       <c r="Z47" t="str">
@@ -37466,11 +37514,11 @@
         <v>cp-00</v>
       </c>
       <c r="AA47" t="str">
+        <f t="shared" si="23"/>
+        <v>CF6</v>
+      </c>
+      <c r="AB47" t="str">
         <f t="shared" si="24"/>
-        <v>CF6</v>
-      </c>
-      <c r="AB47" t="str">
-        <f t="shared" si="25"/>
         <v>df-Y</v>
       </c>
       <c r="AC47" t="str">
@@ -37488,7 +37536,7 @@
         <v>tc-2.00.df-Y.dm-Lo.cp-95.CF6</v>
       </c>
       <c r="H48" t="str">
-        <f>_xlfn.TEXTJOIN(".",TRUE,AC48,AB48:AB48)&amp;"."&amp;_xlfn.TEXTJOIN(".",TRUE,Y48:AA48)</f>
+        <f t="shared" si="1"/>
         <v>tc-2.00.df-Y.dm-Lo.cp-95.CF6</v>
       </c>
       <c r="I48" t="str">
@@ -37507,9 +37555,9 @@
         <f t="shared" si="21"/>
         <v>Y</v>
       </c>
-      <c r="M48">
-        <f t="shared" si="22"/>
-        <v>2</v>
+      <c r="M48" t="str">
+        <f t="shared" si="8"/>
+        <v>2.00</v>
       </c>
       <c r="O48">
         <v>5</v>
@@ -37539,7 +37587,7 @@
         <v>2</v>
       </c>
       <c r="Y48" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>dm-Lo</v>
       </c>
       <c r="Z48" t="str">
@@ -37547,11 +37595,11 @@
         <v>cp-95</v>
       </c>
       <c r="AA48" t="str">
+        <f t="shared" si="23"/>
+        <v>CF6</v>
+      </c>
+      <c r="AB48" t="str">
         <f t="shared" si="24"/>
-        <v>CF6</v>
-      </c>
-      <c r="AB48" t="str">
-        <f t="shared" si="25"/>
         <v>df-Y</v>
       </c>
       <c r="AC48" t="str">
@@ -37569,7 +37617,7 @@
         <v>tc-2.00.df-Y.dm-Hi.cp-95.CF6</v>
       </c>
       <c r="H49" t="str">
-        <f>_xlfn.TEXTJOIN(".",TRUE,AC49,AB49:AB49)&amp;"."&amp;_xlfn.TEXTJOIN(".",TRUE,Y49:AA49)</f>
+        <f t="shared" si="1"/>
         <v>tc-2.00.df-Y.dm-Hi.cp-95.CF6</v>
       </c>
       <c r="I49" t="str">
@@ -37588,9 +37636,9 @@
         <f t="shared" si="21"/>
         <v>Y</v>
       </c>
-      <c r="M49">
-        <f t="shared" si="22"/>
-        <v>2</v>
+      <c r="M49" t="str">
+        <f t="shared" si="8"/>
+        <v>2.00</v>
       </c>
       <c r="O49">
         <v>5</v>
@@ -37620,7 +37668,7 @@
         <v>2</v>
       </c>
       <c r="Y49" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>dm-Hi</v>
       </c>
       <c r="Z49" t="str">
@@ -37628,11 +37676,11 @@
         <v>cp-95</v>
       </c>
       <c r="AA49" t="str">
+        <f t="shared" si="23"/>
+        <v>CF6</v>
+      </c>
+      <c r="AB49" t="str">
         <f t="shared" si="24"/>
-        <v>CF6</v>
-      </c>
-      <c r="AB49" t="str">
-        <f t="shared" si="25"/>
         <v>df-Y</v>
       </c>
       <c r="AC49" t="str">
@@ -37650,7 +37698,7 @@
         <v>tc-2.00.df-N.dm-Lo.cp-00.CF6</v>
       </c>
       <c r="H50" t="str">
-        <f>_xlfn.TEXTJOIN(".",TRUE,AC50,AB50:AB50)&amp;"."&amp;_xlfn.TEXTJOIN(".",TRUE,Y50:AA50)</f>
+        <f t="shared" si="1"/>
         <v>tc-2.00.df-N.dm-Lo.cp-00.CF6</v>
       </c>
       <c r="I50" t="str">
@@ -37669,9 +37717,9 @@
         <f t="shared" si="21"/>
         <v>N</v>
       </c>
-      <c r="M50">
-        <f t="shared" si="22"/>
-        <v>2</v>
+      <c r="M50" t="str">
+        <f t="shared" si="8"/>
+        <v>2.00</v>
       </c>
       <c r="O50">
         <v>5</v>
@@ -37701,7 +37749,7 @@
         <v>2</v>
       </c>
       <c r="Y50" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>dm-Lo</v>
       </c>
       <c r="Z50" t="str">
@@ -37709,11 +37757,11 @@
         <v>cp-00</v>
       </c>
       <c r="AA50" t="str">
+        <f t="shared" si="23"/>
+        <v>CF6</v>
+      </c>
+      <c r="AB50" t="str">
         <f t="shared" si="24"/>
-        <v>CF6</v>
-      </c>
-      <c r="AB50" t="str">
-        <f t="shared" si="25"/>
         <v>df-N</v>
       </c>
       <c r="AC50" t="str">
@@ -37731,7 +37779,7 @@
         <v>tc-2.00.df-N.dm-Hi.cp-00.CF6</v>
       </c>
       <c r="H51" t="str">
-        <f>_xlfn.TEXTJOIN(".",TRUE,AC51,AB51:AB51)&amp;"."&amp;_xlfn.TEXTJOIN(".",TRUE,Y51:AA51)</f>
+        <f t="shared" si="1"/>
         <v>tc-2.00.df-N.dm-Hi.cp-00.CF6</v>
       </c>
       <c r="I51" t="str">
@@ -37750,9 +37798,9 @@
         <f t="shared" si="21"/>
         <v>N</v>
       </c>
-      <c r="M51">
-        <f t="shared" si="22"/>
-        <v>2</v>
+      <c r="M51" t="str">
+        <f t="shared" si="8"/>
+        <v>2.00</v>
       </c>
       <c r="O51">
         <v>5</v>
@@ -37782,7 +37830,7 @@
         <v>2</v>
       </c>
       <c r="Y51" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>dm-Hi</v>
       </c>
       <c r="Z51" t="str">
@@ -37790,11 +37838,11 @@
         <v>cp-00</v>
       </c>
       <c r="AA51" t="str">
+        <f t="shared" si="23"/>
+        <v>CF6</v>
+      </c>
+      <c r="AB51" t="str">
         <f t="shared" si="24"/>
-        <v>CF6</v>
-      </c>
-      <c r="AB51" t="str">
-        <f t="shared" si="25"/>
         <v>df-N</v>
       </c>
       <c r="AC51" t="str">
@@ -37812,7 +37860,7 @@
         <v>tc-2.00.df-N.dm-Lo.cp-95.CF6</v>
       </c>
       <c r="H52" t="str">
-        <f>_xlfn.TEXTJOIN(".",TRUE,AC52,AB52:AB52)&amp;"."&amp;_xlfn.TEXTJOIN(".",TRUE,Y52:AA52)</f>
+        <f t="shared" si="1"/>
         <v>tc-2.00.df-N.dm-Lo.cp-95.CF6</v>
       </c>
       <c r="I52" t="str">
@@ -37831,9 +37879,9 @@
         <f t="shared" si="21"/>
         <v>N</v>
       </c>
-      <c r="M52">
-        <f t="shared" si="22"/>
-        <v>2</v>
+      <c r="M52" t="str">
+        <f t="shared" si="8"/>
+        <v>2.00</v>
       </c>
       <c r="O52">
         <v>5</v>
@@ -37863,7 +37911,7 @@
         <v>2</v>
       </c>
       <c r="Y52" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>dm-Lo</v>
       </c>
       <c r="Z52" t="str">
@@ -37871,11 +37919,11 @@
         <v>cp-95</v>
       </c>
       <c r="AA52" t="str">
+        <f t="shared" si="23"/>
+        <v>CF6</v>
+      </c>
+      <c r="AB52" t="str">
         <f t="shared" si="24"/>
-        <v>CF6</v>
-      </c>
-      <c r="AB52" t="str">
-        <f t="shared" si="25"/>
         <v>df-N</v>
       </c>
       <c r="AC52" t="str">
@@ -37893,7 +37941,7 @@
         <v>tc-2.00.df-N.dm-Hi.cp-95.CF6</v>
       </c>
       <c r="H53" t="str">
-        <f>_xlfn.TEXTJOIN(".",TRUE,AC53,AB53:AB53)&amp;"."&amp;_xlfn.TEXTJOIN(".",TRUE,Y53:AA53)</f>
+        <f t="shared" si="1"/>
         <v>tc-2.00.df-N.dm-Hi.cp-95.CF6</v>
       </c>
       <c r="I53" t="str">
@@ -37912,9 +37960,9 @@
         <f t="shared" si="21"/>
         <v>N</v>
       </c>
-      <c r="M53">
-        <f t="shared" si="22"/>
-        <v>2</v>
+      <c r="M53" t="str">
+        <f t="shared" si="8"/>
+        <v>2.00</v>
       </c>
       <c r="O53">
         <v>5</v>
@@ -37944,7 +37992,7 @@
         <v>2</v>
       </c>
       <c r="Y53" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>dm-Hi</v>
       </c>
       <c r="Z53" t="str">
@@ -37952,16 +38000,1312 @@
         <v>cp-95</v>
       </c>
       <c r="AA53" t="str">
+        <f t="shared" si="23"/>
+        <v>CF6</v>
+      </c>
+      <c r="AB53" t="str">
         <f t="shared" si="24"/>
-        <v>CF6</v>
-      </c>
-      <c r="AB53" t="str">
-        <f t="shared" si="25"/>
         <v>df-N</v>
       </c>
       <c r="AC53" t="str">
         <f t="shared" si="13"/>
         <v>tc-2.00</v>
+      </c>
+    </row>
+    <row r="54" spans="2:29">
+      <c r="B54" t="str">
+        <f t="shared" ref="B54:B69" si="25">"vs~"&amp;TEXT(Q54,"0000")</f>
+        <v>vs~0049</v>
+      </c>
+      <c r="C54" t="str">
+        <f t="shared" ref="C54:C69" si="26">H54</f>
+        <v>tc-0.10.df-Y.dm-Lo.cp-00.CF1</v>
+      </c>
+      <c r="H54" t="str">
+        <f t="shared" ref="H54:H69" si="27">_xlfn.TEXTJOIN(".",TRUE,AC54,AB54:AB54)&amp;"."&amp;_xlfn.TEXTJOIN(".",TRUE,Y54:AA54)</f>
+        <v>tc-0.10.df-Y.dm-Lo.cp-00.CF1</v>
+      </c>
+      <c r="I54" t="str">
+        <f t="shared" ref="I54:I69" si="28">R54</f>
+        <v>Lo</v>
+      </c>
+      <c r="J54" t="str">
+        <f t="shared" ref="J54:J69" si="29">TEXT(S54,"00")</f>
+        <v>00</v>
+      </c>
+      <c r="K54" t="str">
+        <f t="shared" ref="K54:K69" si="30">T54</f>
+        <v>CF1</v>
+      </c>
+      <c r="L54" t="str">
+        <f t="shared" ref="L54:L69" si="31">U54</f>
+        <v>Y</v>
+      </c>
+      <c r="M54" t="str">
+        <f t="shared" si="8"/>
+        <v>0.10</v>
+      </c>
+      <c r="O54">
+        <v>5</v>
+      </c>
+      <c r="P54" t="s">
+        <v>1156</v>
+      </c>
+      <c r="Q54">
+        <v>49</v>
+      </c>
+      <c r="R54" t="s">
+        <v>1092</v>
+      </c>
+      <c r="S54">
+        <v>0</v>
+      </c>
+      <c r="T54" t="s">
+        <v>1087</v>
+      </c>
+      <c r="U54" t="s">
+        <v>1093</v>
+      </c>
+      <c r="V54" t="s">
+        <v>1093</v>
+      </c>
+      <c r="W54">
+        <v>0.1</v>
+      </c>
+      <c r="Y54" t="str">
+        <f t="shared" ref="Y54:Y69" si="32">R$1&amp;"-"&amp;R54</f>
+        <v>dm-Lo</v>
+      </c>
+      <c r="Z54" t="str">
+        <f t="shared" ref="Z54:Z69" si="33">S$1&amp;"-"&amp;TEXT(S54,"00")</f>
+        <v>cp-00</v>
+      </c>
+      <c r="AA54" t="str">
+        <f t="shared" ref="AA54:AA69" si="34">T54</f>
+        <v>CF1</v>
+      </c>
+      <c r="AB54" t="str">
+        <f t="shared" ref="AB54:AB69" si="35">U$1&amp;"-"&amp;U54</f>
+        <v>df-Y</v>
+      </c>
+      <c r="AC54" t="str">
+        <f t="shared" ref="AC54:AC69" si="36">W$1&amp;"-"&amp;TEXT(W54,"0.00")</f>
+        <v>tc-0.10</v>
+      </c>
+    </row>
+    <row r="55" spans="2:29">
+      <c r="B55" t="str">
+        <f t="shared" si="25"/>
+        <v>vs~0050</v>
+      </c>
+      <c r="C55" t="str">
+        <f t="shared" si="26"/>
+        <v>tc-0.10.df-Y.dm-Hi.cp-00.CF1</v>
+      </c>
+      <c r="H55" t="str">
+        <f t="shared" si="27"/>
+        <v>tc-0.10.df-Y.dm-Hi.cp-00.CF1</v>
+      </c>
+      <c r="I55" t="str">
+        <f t="shared" si="28"/>
+        <v>Hi</v>
+      </c>
+      <c r="J55" t="str">
+        <f t="shared" si="29"/>
+        <v>00</v>
+      </c>
+      <c r="K55" t="str">
+        <f t="shared" si="30"/>
+        <v>CF1</v>
+      </c>
+      <c r="L55" t="str">
+        <f t="shared" si="31"/>
+        <v>Y</v>
+      </c>
+      <c r="M55" t="str">
+        <f t="shared" si="8"/>
+        <v>0.10</v>
+      </c>
+      <c r="O55">
+        <v>5</v>
+      </c>
+      <c r="P55" t="s">
+        <v>1157</v>
+      </c>
+      <c r="Q55">
+        <v>50</v>
+      </c>
+      <c r="R55" t="s">
+        <v>1094</v>
+      </c>
+      <c r="S55">
+        <v>0</v>
+      </c>
+      <c r="T55" t="s">
+        <v>1087</v>
+      </c>
+      <c r="U55" t="s">
+        <v>1093</v>
+      </c>
+      <c r="V55" t="s">
+        <v>1093</v>
+      </c>
+      <c r="W55">
+        <v>0.1</v>
+      </c>
+      <c r="Y55" t="str">
+        <f t="shared" si="32"/>
+        <v>dm-Hi</v>
+      </c>
+      <c r="Z55" t="str">
+        <f t="shared" si="33"/>
+        <v>cp-00</v>
+      </c>
+      <c r="AA55" t="str">
+        <f t="shared" si="34"/>
+        <v>CF1</v>
+      </c>
+      <c r="AB55" t="str">
+        <f t="shared" si="35"/>
+        <v>df-Y</v>
+      </c>
+      <c r="AC55" t="str">
+        <f t="shared" si="36"/>
+        <v>tc-0.10</v>
+      </c>
+    </row>
+    <row r="56" spans="2:29">
+      <c r="B56" t="str">
+        <f t="shared" si="25"/>
+        <v>vs~0051</v>
+      </c>
+      <c r="C56" t="str">
+        <f t="shared" si="26"/>
+        <v>tc-0.10.df-Y.dm-Lo.cp-95.CF1</v>
+      </c>
+      <c r="H56" t="str">
+        <f t="shared" si="27"/>
+        <v>tc-0.10.df-Y.dm-Lo.cp-95.CF1</v>
+      </c>
+      <c r="I56" t="str">
+        <f t="shared" si="28"/>
+        <v>Lo</v>
+      </c>
+      <c r="J56" t="str">
+        <f t="shared" si="29"/>
+        <v>95</v>
+      </c>
+      <c r="K56" t="str">
+        <f t="shared" si="30"/>
+        <v>CF1</v>
+      </c>
+      <c r="L56" t="str">
+        <f t="shared" si="31"/>
+        <v>Y</v>
+      </c>
+      <c r="M56" t="str">
+        <f t="shared" si="8"/>
+        <v>0.10</v>
+      </c>
+      <c r="O56">
+        <v>5</v>
+      </c>
+      <c r="P56" t="s">
+        <v>1158</v>
+      </c>
+      <c r="Q56">
+        <v>51</v>
+      </c>
+      <c r="R56" t="s">
+        <v>1092</v>
+      </c>
+      <c r="S56">
+        <v>95</v>
+      </c>
+      <c r="T56" t="s">
+        <v>1087</v>
+      </c>
+      <c r="U56" t="s">
+        <v>1093</v>
+      </c>
+      <c r="V56" t="s">
+        <v>1093</v>
+      </c>
+      <c r="W56">
+        <v>0.1</v>
+      </c>
+      <c r="Y56" t="str">
+        <f t="shared" si="32"/>
+        <v>dm-Lo</v>
+      </c>
+      <c r="Z56" t="str">
+        <f t="shared" si="33"/>
+        <v>cp-95</v>
+      </c>
+      <c r="AA56" t="str">
+        <f t="shared" si="34"/>
+        <v>CF1</v>
+      </c>
+      <c r="AB56" t="str">
+        <f t="shared" si="35"/>
+        <v>df-Y</v>
+      </c>
+      <c r="AC56" t="str">
+        <f t="shared" si="36"/>
+        <v>tc-0.10</v>
+      </c>
+    </row>
+    <row r="57" spans="2:29">
+      <c r="B57" t="str">
+        <f t="shared" si="25"/>
+        <v>vs~0052</v>
+      </c>
+      <c r="C57" t="str">
+        <f t="shared" si="26"/>
+        <v>tc-0.10.df-Y.dm-Hi.cp-95.CF1</v>
+      </c>
+      <c r="H57" t="str">
+        <f t="shared" si="27"/>
+        <v>tc-0.10.df-Y.dm-Hi.cp-95.CF1</v>
+      </c>
+      <c r="I57" t="str">
+        <f t="shared" si="28"/>
+        <v>Hi</v>
+      </c>
+      <c r="J57" t="str">
+        <f t="shared" si="29"/>
+        <v>95</v>
+      </c>
+      <c r="K57" t="str">
+        <f t="shared" si="30"/>
+        <v>CF1</v>
+      </c>
+      <c r="L57" t="str">
+        <f t="shared" si="31"/>
+        <v>Y</v>
+      </c>
+      <c r="M57" t="str">
+        <f t="shared" si="8"/>
+        <v>0.10</v>
+      </c>
+      <c r="O57">
+        <v>5</v>
+      </c>
+      <c r="P57" t="s">
+        <v>1159</v>
+      </c>
+      <c r="Q57">
+        <v>52</v>
+      </c>
+      <c r="R57" t="s">
+        <v>1094</v>
+      </c>
+      <c r="S57">
+        <v>95</v>
+      </c>
+      <c r="T57" t="s">
+        <v>1087</v>
+      </c>
+      <c r="U57" t="s">
+        <v>1093</v>
+      </c>
+      <c r="V57" t="s">
+        <v>1093</v>
+      </c>
+      <c r="W57">
+        <v>0.1</v>
+      </c>
+      <c r="Y57" t="str">
+        <f t="shared" si="32"/>
+        <v>dm-Hi</v>
+      </c>
+      <c r="Z57" t="str">
+        <f t="shared" si="33"/>
+        <v>cp-95</v>
+      </c>
+      <c r="AA57" t="str">
+        <f t="shared" si="34"/>
+        <v>CF1</v>
+      </c>
+      <c r="AB57" t="str">
+        <f t="shared" si="35"/>
+        <v>df-Y</v>
+      </c>
+      <c r="AC57" t="str">
+        <f t="shared" si="36"/>
+        <v>tc-0.10</v>
+      </c>
+    </row>
+    <row r="58" spans="2:29">
+      <c r="B58" t="str">
+        <f t="shared" si="25"/>
+        <v>vs~0053</v>
+      </c>
+      <c r="C58" t="str">
+        <f t="shared" si="26"/>
+        <v>tc-0.10.df-N.dm-Lo.cp-00.CF1</v>
+      </c>
+      <c r="H58" t="str">
+        <f t="shared" si="27"/>
+        <v>tc-0.10.df-N.dm-Lo.cp-00.CF1</v>
+      </c>
+      <c r="I58" t="str">
+        <f t="shared" si="28"/>
+        <v>Lo</v>
+      </c>
+      <c r="J58" t="str">
+        <f t="shared" si="29"/>
+        <v>00</v>
+      </c>
+      <c r="K58" t="str">
+        <f t="shared" si="30"/>
+        <v>CF1</v>
+      </c>
+      <c r="L58" t="str">
+        <f t="shared" si="31"/>
+        <v>N</v>
+      </c>
+      <c r="M58" t="str">
+        <f t="shared" si="8"/>
+        <v>0.10</v>
+      </c>
+      <c r="O58">
+        <v>5</v>
+      </c>
+      <c r="P58" t="s">
+        <v>1160</v>
+      </c>
+      <c r="Q58">
+        <v>53</v>
+      </c>
+      <c r="R58" t="s">
+        <v>1092</v>
+      </c>
+      <c r="S58">
+        <v>0</v>
+      </c>
+      <c r="T58" t="s">
+        <v>1087</v>
+      </c>
+      <c r="U58" t="s">
+        <v>1095</v>
+      </c>
+      <c r="V58" t="s">
+        <v>1093</v>
+      </c>
+      <c r="W58">
+        <v>0.1</v>
+      </c>
+      <c r="Y58" t="str">
+        <f t="shared" si="32"/>
+        <v>dm-Lo</v>
+      </c>
+      <c r="Z58" t="str">
+        <f t="shared" si="33"/>
+        <v>cp-00</v>
+      </c>
+      <c r="AA58" t="str">
+        <f t="shared" si="34"/>
+        <v>CF1</v>
+      </c>
+      <c r="AB58" t="str">
+        <f t="shared" si="35"/>
+        <v>df-N</v>
+      </c>
+      <c r="AC58" t="str">
+        <f t="shared" si="36"/>
+        <v>tc-0.10</v>
+      </c>
+    </row>
+    <row r="59" spans="2:29">
+      <c r="B59" t="str">
+        <f t="shared" si="25"/>
+        <v>vs~0054</v>
+      </c>
+      <c r="C59" t="str">
+        <f t="shared" si="26"/>
+        <v>tc-0.10.df-N.dm-Hi.cp-00.CF1</v>
+      </c>
+      <c r="H59" t="str">
+        <f t="shared" si="27"/>
+        <v>tc-0.10.df-N.dm-Hi.cp-00.CF1</v>
+      </c>
+      <c r="I59" t="str">
+        <f t="shared" si="28"/>
+        <v>Hi</v>
+      </c>
+      <c r="J59" t="str">
+        <f t="shared" si="29"/>
+        <v>00</v>
+      </c>
+      <c r="K59" t="str">
+        <f t="shared" si="30"/>
+        <v>CF1</v>
+      </c>
+      <c r="L59" t="str">
+        <f t="shared" si="31"/>
+        <v>N</v>
+      </c>
+      <c r="M59" t="str">
+        <f t="shared" si="8"/>
+        <v>0.10</v>
+      </c>
+      <c r="O59">
+        <v>5</v>
+      </c>
+      <c r="P59" t="s">
+        <v>1161</v>
+      </c>
+      <c r="Q59">
+        <v>54</v>
+      </c>
+      <c r="R59" t="s">
+        <v>1094</v>
+      </c>
+      <c r="S59">
+        <v>0</v>
+      </c>
+      <c r="T59" t="s">
+        <v>1087</v>
+      </c>
+      <c r="U59" t="s">
+        <v>1095</v>
+      </c>
+      <c r="V59" t="s">
+        <v>1093</v>
+      </c>
+      <c r="W59">
+        <v>0.1</v>
+      </c>
+      <c r="Y59" t="str">
+        <f t="shared" si="32"/>
+        <v>dm-Hi</v>
+      </c>
+      <c r="Z59" t="str">
+        <f t="shared" si="33"/>
+        <v>cp-00</v>
+      </c>
+      <c r="AA59" t="str">
+        <f t="shared" si="34"/>
+        <v>CF1</v>
+      </c>
+      <c r="AB59" t="str">
+        <f t="shared" si="35"/>
+        <v>df-N</v>
+      </c>
+      <c r="AC59" t="str">
+        <f t="shared" si="36"/>
+        <v>tc-0.10</v>
+      </c>
+    </row>
+    <row r="60" spans="2:29">
+      <c r="B60" t="str">
+        <f t="shared" si="25"/>
+        <v>vs~0055</v>
+      </c>
+      <c r="C60" t="str">
+        <f t="shared" si="26"/>
+        <v>tc-0.10.df-N.dm-Lo.cp-95.CF1</v>
+      </c>
+      <c r="H60" t="str">
+        <f t="shared" si="27"/>
+        <v>tc-0.10.df-N.dm-Lo.cp-95.CF1</v>
+      </c>
+      <c r="I60" t="str">
+        <f t="shared" si="28"/>
+        <v>Lo</v>
+      </c>
+      <c r="J60" t="str">
+        <f t="shared" si="29"/>
+        <v>95</v>
+      </c>
+      <c r="K60" t="str">
+        <f t="shared" si="30"/>
+        <v>CF1</v>
+      </c>
+      <c r="L60" t="str">
+        <f t="shared" si="31"/>
+        <v>N</v>
+      </c>
+      <c r="M60" t="str">
+        <f t="shared" si="8"/>
+        <v>0.10</v>
+      </c>
+      <c r="O60">
+        <v>5</v>
+      </c>
+      <c r="P60" t="s">
+        <v>1162</v>
+      </c>
+      <c r="Q60">
+        <v>55</v>
+      </c>
+      <c r="R60" t="s">
+        <v>1092</v>
+      </c>
+      <c r="S60">
+        <v>95</v>
+      </c>
+      <c r="T60" t="s">
+        <v>1087</v>
+      </c>
+      <c r="U60" t="s">
+        <v>1095</v>
+      </c>
+      <c r="V60" t="s">
+        <v>1093</v>
+      </c>
+      <c r="W60">
+        <v>0.1</v>
+      </c>
+      <c r="Y60" t="str">
+        <f t="shared" si="32"/>
+        <v>dm-Lo</v>
+      </c>
+      <c r="Z60" t="str">
+        <f t="shared" si="33"/>
+        <v>cp-95</v>
+      </c>
+      <c r="AA60" t="str">
+        <f t="shared" si="34"/>
+        <v>CF1</v>
+      </c>
+      <c r="AB60" t="str">
+        <f t="shared" si="35"/>
+        <v>df-N</v>
+      </c>
+      <c r="AC60" t="str">
+        <f t="shared" si="36"/>
+        <v>tc-0.10</v>
+      </c>
+    </row>
+    <row r="61" spans="2:29">
+      <c r="B61" t="str">
+        <f t="shared" si="25"/>
+        <v>vs~0056</v>
+      </c>
+      <c r="C61" t="str">
+        <f t="shared" si="26"/>
+        <v>tc-0.10.df-N.dm-Hi.cp-95.CF1</v>
+      </c>
+      <c r="H61" t="str">
+        <f t="shared" si="27"/>
+        <v>tc-0.10.df-N.dm-Hi.cp-95.CF1</v>
+      </c>
+      <c r="I61" t="str">
+        <f t="shared" si="28"/>
+        <v>Hi</v>
+      </c>
+      <c r="J61" t="str">
+        <f t="shared" si="29"/>
+        <v>95</v>
+      </c>
+      <c r="K61" t="str">
+        <f t="shared" si="30"/>
+        <v>CF1</v>
+      </c>
+      <c r="L61" t="str">
+        <f t="shared" si="31"/>
+        <v>N</v>
+      </c>
+      <c r="M61" t="str">
+        <f t="shared" si="8"/>
+        <v>0.10</v>
+      </c>
+      <c r="O61">
+        <v>5</v>
+      </c>
+      <c r="P61" t="s">
+        <v>1163</v>
+      </c>
+      <c r="Q61">
+        <v>56</v>
+      </c>
+      <c r="R61" t="s">
+        <v>1094</v>
+      </c>
+      <c r="S61">
+        <v>95</v>
+      </c>
+      <c r="T61" t="s">
+        <v>1087</v>
+      </c>
+      <c r="U61" t="s">
+        <v>1095</v>
+      </c>
+      <c r="V61" t="s">
+        <v>1093</v>
+      </c>
+      <c r="W61">
+        <v>0.1</v>
+      </c>
+      <c r="Y61" t="str">
+        <f t="shared" si="32"/>
+        <v>dm-Hi</v>
+      </c>
+      <c r="Z61" t="str">
+        <f t="shared" si="33"/>
+        <v>cp-95</v>
+      </c>
+      <c r="AA61" t="str">
+        <f t="shared" si="34"/>
+        <v>CF1</v>
+      </c>
+      <c r="AB61" t="str">
+        <f t="shared" si="35"/>
+        <v>df-N</v>
+      </c>
+      <c r="AC61" t="str">
+        <f t="shared" si="36"/>
+        <v>tc-0.10</v>
+      </c>
+    </row>
+    <row r="62" spans="2:29">
+      <c r="B62" t="str">
+        <f t="shared" si="25"/>
+        <v>vs~0057</v>
+      </c>
+      <c r="C62" t="str">
+        <f t="shared" si="26"/>
+        <v>tc-0.10.df-Y.dm-Lo.cp-00.CF6</v>
+      </c>
+      <c r="H62" t="str">
+        <f t="shared" si="27"/>
+        <v>tc-0.10.df-Y.dm-Lo.cp-00.CF6</v>
+      </c>
+      <c r="I62" t="str">
+        <f t="shared" si="28"/>
+        <v>Lo</v>
+      </c>
+      <c r="J62" t="str">
+        <f t="shared" si="29"/>
+        <v>00</v>
+      </c>
+      <c r="K62" t="str">
+        <f t="shared" si="30"/>
+        <v>CF6</v>
+      </c>
+      <c r="L62" t="str">
+        <f t="shared" si="31"/>
+        <v>Y</v>
+      </c>
+      <c r="M62" t="str">
+        <f t="shared" si="8"/>
+        <v>0.10</v>
+      </c>
+      <c r="O62">
+        <v>5</v>
+      </c>
+      <c r="P62" t="s">
+        <v>1164</v>
+      </c>
+      <c r="Q62">
+        <v>57</v>
+      </c>
+      <c r="R62" t="s">
+        <v>1092</v>
+      </c>
+      <c r="S62">
+        <v>0</v>
+      </c>
+      <c r="T62" t="s">
+        <v>1088</v>
+      </c>
+      <c r="U62" t="s">
+        <v>1093</v>
+      </c>
+      <c r="V62" t="s">
+        <v>1093</v>
+      </c>
+      <c r="W62">
+        <v>0.1</v>
+      </c>
+      <c r="Y62" t="str">
+        <f t="shared" si="32"/>
+        <v>dm-Lo</v>
+      </c>
+      <c r="Z62" t="str">
+        <f t="shared" si="33"/>
+        <v>cp-00</v>
+      </c>
+      <c r="AA62" t="str">
+        <f t="shared" si="34"/>
+        <v>CF6</v>
+      </c>
+      <c r="AB62" t="str">
+        <f t="shared" si="35"/>
+        <v>df-Y</v>
+      </c>
+      <c r="AC62" t="str">
+        <f t="shared" si="36"/>
+        <v>tc-0.10</v>
+      </c>
+    </row>
+    <row r="63" spans="2:29">
+      <c r="B63" t="str">
+        <f t="shared" si="25"/>
+        <v>vs~0058</v>
+      </c>
+      <c r="C63" t="str">
+        <f t="shared" si="26"/>
+        <v>tc-0.10.df-Y.dm-Hi.cp-00.CF6</v>
+      </c>
+      <c r="H63" t="str">
+        <f t="shared" si="27"/>
+        <v>tc-0.10.df-Y.dm-Hi.cp-00.CF6</v>
+      </c>
+      <c r="I63" t="str">
+        <f t="shared" si="28"/>
+        <v>Hi</v>
+      </c>
+      <c r="J63" t="str">
+        <f t="shared" si="29"/>
+        <v>00</v>
+      </c>
+      <c r="K63" t="str">
+        <f t="shared" si="30"/>
+        <v>CF6</v>
+      </c>
+      <c r="L63" t="str">
+        <f t="shared" si="31"/>
+        <v>Y</v>
+      </c>
+      <c r="M63" t="str">
+        <f t="shared" si="8"/>
+        <v>0.10</v>
+      </c>
+      <c r="O63">
+        <v>5</v>
+      </c>
+      <c r="P63" t="s">
+        <v>1165</v>
+      </c>
+      <c r="Q63">
+        <v>58</v>
+      </c>
+      <c r="R63" t="s">
+        <v>1094</v>
+      </c>
+      <c r="S63">
+        <v>0</v>
+      </c>
+      <c r="T63" t="s">
+        <v>1088</v>
+      </c>
+      <c r="U63" t="s">
+        <v>1093</v>
+      </c>
+      <c r="V63" t="s">
+        <v>1093</v>
+      </c>
+      <c r="W63">
+        <v>0.1</v>
+      </c>
+      <c r="Y63" t="str">
+        <f t="shared" si="32"/>
+        <v>dm-Hi</v>
+      </c>
+      <c r="Z63" t="str">
+        <f t="shared" si="33"/>
+        <v>cp-00</v>
+      </c>
+      <c r="AA63" t="str">
+        <f t="shared" si="34"/>
+        <v>CF6</v>
+      </c>
+      <c r="AB63" t="str">
+        <f t="shared" si="35"/>
+        <v>df-Y</v>
+      </c>
+      <c r="AC63" t="str">
+        <f t="shared" si="36"/>
+        <v>tc-0.10</v>
+      </c>
+    </row>
+    <row r="64" spans="2:29">
+      <c r="B64" t="str">
+        <f t="shared" si="25"/>
+        <v>vs~0059</v>
+      </c>
+      <c r="C64" t="str">
+        <f t="shared" si="26"/>
+        <v>tc-0.10.df-Y.dm-Lo.cp-95.CF6</v>
+      </c>
+      <c r="H64" t="str">
+        <f t="shared" si="27"/>
+        <v>tc-0.10.df-Y.dm-Lo.cp-95.CF6</v>
+      </c>
+      <c r="I64" t="str">
+        <f t="shared" si="28"/>
+        <v>Lo</v>
+      </c>
+      <c r="J64" t="str">
+        <f t="shared" si="29"/>
+        <v>95</v>
+      </c>
+      <c r="K64" t="str">
+        <f t="shared" si="30"/>
+        <v>CF6</v>
+      </c>
+      <c r="L64" t="str">
+        <f t="shared" si="31"/>
+        <v>Y</v>
+      </c>
+      <c r="M64" t="str">
+        <f t="shared" si="8"/>
+        <v>0.10</v>
+      </c>
+      <c r="O64">
+        <v>5</v>
+      </c>
+      <c r="P64" t="s">
+        <v>1166</v>
+      </c>
+      <c r="Q64">
+        <v>59</v>
+      </c>
+      <c r="R64" t="s">
+        <v>1092</v>
+      </c>
+      <c r="S64">
+        <v>95</v>
+      </c>
+      <c r="T64" t="s">
+        <v>1088</v>
+      </c>
+      <c r="U64" t="s">
+        <v>1093</v>
+      </c>
+      <c r="V64" t="s">
+        <v>1093</v>
+      </c>
+      <c r="W64">
+        <v>0.1</v>
+      </c>
+      <c r="Y64" t="str">
+        <f t="shared" si="32"/>
+        <v>dm-Lo</v>
+      </c>
+      <c r="Z64" t="str">
+        <f t="shared" si="33"/>
+        <v>cp-95</v>
+      </c>
+      <c r="AA64" t="str">
+        <f t="shared" si="34"/>
+        <v>CF6</v>
+      </c>
+      <c r="AB64" t="str">
+        <f t="shared" si="35"/>
+        <v>df-Y</v>
+      </c>
+      <c r="AC64" t="str">
+        <f t="shared" si="36"/>
+        <v>tc-0.10</v>
+      </c>
+    </row>
+    <row r="65" spans="2:29">
+      <c r="B65" t="str">
+        <f t="shared" si="25"/>
+        <v>vs~0060</v>
+      </c>
+      <c r="C65" t="str">
+        <f t="shared" si="26"/>
+        <v>tc-0.10.df-Y.dm-Hi.cp-95.CF6</v>
+      </c>
+      <c r="H65" t="str">
+        <f t="shared" si="27"/>
+        <v>tc-0.10.df-Y.dm-Hi.cp-95.CF6</v>
+      </c>
+      <c r="I65" t="str">
+        <f t="shared" si="28"/>
+        <v>Hi</v>
+      </c>
+      <c r="J65" t="str">
+        <f t="shared" si="29"/>
+        <v>95</v>
+      </c>
+      <c r="K65" t="str">
+        <f t="shared" si="30"/>
+        <v>CF6</v>
+      </c>
+      <c r="L65" t="str">
+        <f t="shared" si="31"/>
+        <v>Y</v>
+      </c>
+      <c r="M65" t="str">
+        <f t="shared" si="8"/>
+        <v>0.10</v>
+      </c>
+      <c r="O65">
+        <v>5</v>
+      </c>
+      <c r="P65" t="s">
+        <v>1167</v>
+      </c>
+      <c r="Q65">
+        <v>60</v>
+      </c>
+      <c r="R65" t="s">
+        <v>1094</v>
+      </c>
+      <c r="S65">
+        <v>95</v>
+      </c>
+      <c r="T65" t="s">
+        <v>1088</v>
+      </c>
+      <c r="U65" t="s">
+        <v>1093</v>
+      </c>
+      <c r="V65" t="s">
+        <v>1093</v>
+      </c>
+      <c r="W65">
+        <v>0.1</v>
+      </c>
+      <c r="Y65" t="str">
+        <f t="shared" si="32"/>
+        <v>dm-Hi</v>
+      </c>
+      <c r="Z65" t="str">
+        <f t="shared" si="33"/>
+        <v>cp-95</v>
+      </c>
+      <c r="AA65" t="str">
+        <f t="shared" si="34"/>
+        <v>CF6</v>
+      </c>
+      <c r="AB65" t="str">
+        <f t="shared" si="35"/>
+        <v>df-Y</v>
+      </c>
+      <c r="AC65" t="str">
+        <f t="shared" si="36"/>
+        <v>tc-0.10</v>
+      </c>
+    </row>
+    <row r="66" spans="2:29">
+      <c r="B66" t="str">
+        <f t="shared" si="25"/>
+        <v>vs~0061</v>
+      </c>
+      <c r="C66" t="str">
+        <f t="shared" si="26"/>
+        <v>tc-0.10.df-N.dm-Lo.cp-00.CF6</v>
+      </c>
+      <c r="H66" t="str">
+        <f t="shared" si="27"/>
+        <v>tc-0.10.df-N.dm-Lo.cp-00.CF6</v>
+      </c>
+      <c r="I66" t="str">
+        <f t="shared" si="28"/>
+        <v>Lo</v>
+      </c>
+      <c r="J66" t="str">
+        <f t="shared" si="29"/>
+        <v>00</v>
+      </c>
+      <c r="K66" t="str">
+        <f t="shared" si="30"/>
+        <v>CF6</v>
+      </c>
+      <c r="L66" t="str">
+        <f t="shared" si="31"/>
+        <v>N</v>
+      </c>
+      <c r="M66" t="str">
+        <f t="shared" si="8"/>
+        <v>0.10</v>
+      </c>
+      <c r="O66">
+        <v>5</v>
+      </c>
+      <c r="P66" t="s">
+        <v>1168</v>
+      </c>
+      <c r="Q66">
+        <v>61</v>
+      </c>
+      <c r="R66" t="s">
+        <v>1092</v>
+      </c>
+      <c r="S66">
+        <v>0</v>
+      </c>
+      <c r="T66" t="s">
+        <v>1088</v>
+      </c>
+      <c r="U66" t="s">
+        <v>1095</v>
+      </c>
+      <c r="V66" t="s">
+        <v>1093</v>
+      </c>
+      <c r="W66">
+        <v>0.1</v>
+      </c>
+      <c r="Y66" t="str">
+        <f t="shared" si="32"/>
+        <v>dm-Lo</v>
+      </c>
+      <c r="Z66" t="str">
+        <f t="shared" si="33"/>
+        <v>cp-00</v>
+      </c>
+      <c r="AA66" t="str">
+        <f t="shared" si="34"/>
+        <v>CF6</v>
+      </c>
+      <c r="AB66" t="str">
+        <f t="shared" si="35"/>
+        <v>df-N</v>
+      </c>
+      <c r="AC66" t="str">
+        <f t="shared" si="36"/>
+        <v>tc-0.10</v>
+      </c>
+    </row>
+    <row r="67" spans="2:29">
+      <c r="B67" t="str">
+        <f t="shared" si="25"/>
+        <v>vs~0062</v>
+      </c>
+      <c r="C67" t="str">
+        <f t="shared" si="26"/>
+        <v>tc-0.10.df-N.dm-Hi.cp-00.CF6</v>
+      </c>
+      <c r="H67" t="str">
+        <f t="shared" si="27"/>
+        <v>tc-0.10.df-N.dm-Hi.cp-00.CF6</v>
+      </c>
+      <c r="I67" t="str">
+        <f t="shared" si="28"/>
+        <v>Hi</v>
+      </c>
+      <c r="J67" t="str">
+        <f t="shared" si="29"/>
+        <v>00</v>
+      </c>
+      <c r="K67" t="str">
+        <f t="shared" si="30"/>
+        <v>CF6</v>
+      </c>
+      <c r="L67" t="str">
+        <f t="shared" si="31"/>
+        <v>N</v>
+      </c>
+      <c r="M67" t="str">
+        <f t="shared" si="8"/>
+        <v>0.10</v>
+      </c>
+      <c r="O67">
+        <v>5</v>
+      </c>
+      <c r="P67" t="s">
+        <v>1169</v>
+      </c>
+      <c r="Q67">
+        <v>62</v>
+      </c>
+      <c r="R67" t="s">
+        <v>1094</v>
+      </c>
+      <c r="S67">
+        <v>0</v>
+      </c>
+      <c r="T67" t="s">
+        <v>1088</v>
+      </c>
+      <c r="U67" t="s">
+        <v>1095</v>
+      </c>
+      <c r="V67" t="s">
+        <v>1093</v>
+      </c>
+      <c r="W67">
+        <v>0.1</v>
+      </c>
+      <c r="Y67" t="str">
+        <f t="shared" si="32"/>
+        <v>dm-Hi</v>
+      </c>
+      <c r="Z67" t="str">
+        <f t="shared" si="33"/>
+        <v>cp-00</v>
+      </c>
+      <c r="AA67" t="str">
+        <f t="shared" si="34"/>
+        <v>CF6</v>
+      </c>
+      <c r="AB67" t="str">
+        <f t="shared" si="35"/>
+        <v>df-N</v>
+      </c>
+      <c r="AC67" t="str">
+        <f t="shared" si="36"/>
+        <v>tc-0.10</v>
+      </c>
+    </row>
+    <row r="68" spans="2:29">
+      <c r="B68" t="str">
+        <f t="shared" si="25"/>
+        <v>vs~0063</v>
+      </c>
+      <c r="C68" t="str">
+        <f t="shared" si="26"/>
+        <v>tc-0.10.df-N.dm-Lo.cp-95.CF6</v>
+      </c>
+      <c r="H68" t="str">
+        <f t="shared" si="27"/>
+        <v>tc-0.10.df-N.dm-Lo.cp-95.CF6</v>
+      </c>
+      <c r="I68" t="str">
+        <f t="shared" si="28"/>
+        <v>Lo</v>
+      </c>
+      <c r="J68" t="str">
+        <f t="shared" si="29"/>
+        <v>95</v>
+      </c>
+      <c r="K68" t="str">
+        <f t="shared" si="30"/>
+        <v>CF6</v>
+      </c>
+      <c r="L68" t="str">
+        <f t="shared" si="31"/>
+        <v>N</v>
+      </c>
+      <c r="M68" t="str">
+        <f t="shared" si="8"/>
+        <v>0.10</v>
+      </c>
+      <c r="O68">
+        <v>5</v>
+      </c>
+      <c r="P68" t="s">
+        <v>1170</v>
+      </c>
+      <c r="Q68">
+        <v>63</v>
+      </c>
+      <c r="R68" t="s">
+        <v>1092</v>
+      </c>
+      <c r="S68">
+        <v>95</v>
+      </c>
+      <c r="T68" t="s">
+        <v>1088</v>
+      </c>
+      <c r="U68" t="s">
+        <v>1095</v>
+      </c>
+      <c r="V68" t="s">
+        <v>1093</v>
+      </c>
+      <c r="W68">
+        <v>0.1</v>
+      </c>
+      <c r="Y68" t="str">
+        <f t="shared" si="32"/>
+        <v>dm-Lo</v>
+      </c>
+      <c r="Z68" t="str">
+        <f t="shared" si="33"/>
+        <v>cp-95</v>
+      </c>
+      <c r="AA68" t="str">
+        <f t="shared" si="34"/>
+        <v>CF6</v>
+      </c>
+      <c r="AB68" t="str">
+        <f t="shared" si="35"/>
+        <v>df-N</v>
+      </c>
+      <c r="AC68" t="str">
+        <f t="shared" si="36"/>
+        <v>tc-0.10</v>
+      </c>
+    </row>
+    <row r="69" spans="2:29">
+      <c r="B69" t="str">
+        <f t="shared" si="25"/>
+        <v>vs~0064</v>
+      </c>
+      <c r="C69" t="str">
+        <f t="shared" si="26"/>
+        <v>tc-0.10.df-N.dm-Hi.cp-95.CF6</v>
+      </c>
+      <c r="H69" t="str">
+        <f t="shared" si="27"/>
+        <v>tc-0.10.df-N.dm-Hi.cp-95.CF6</v>
+      </c>
+      <c r="I69" t="str">
+        <f t="shared" si="28"/>
+        <v>Hi</v>
+      </c>
+      <c r="J69" t="str">
+        <f t="shared" si="29"/>
+        <v>95</v>
+      </c>
+      <c r="K69" t="str">
+        <f t="shared" si="30"/>
+        <v>CF6</v>
+      </c>
+      <c r="L69" t="str">
+        <f t="shared" si="31"/>
+        <v>N</v>
+      </c>
+      <c r="M69" t="str">
+        <f t="shared" si="8"/>
+        <v>0.10</v>
+      </c>
+      <c r="O69">
+        <v>5</v>
+      </c>
+      <c r="P69" t="s">
+        <v>1171</v>
+      </c>
+      <c r="Q69">
+        <v>64</v>
+      </c>
+      <c r="R69" t="s">
+        <v>1094</v>
+      </c>
+      <c r="S69">
+        <v>95</v>
+      </c>
+      <c r="T69" t="s">
+        <v>1088</v>
+      </c>
+      <c r="U69" t="s">
+        <v>1095</v>
+      </c>
+      <c r="V69" t="s">
+        <v>1093</v>
+      </c>
+      <c r="W69">
+        <v>0.1</v>
+      </c>
+      <c r="Y69" t="str">
+        <f t="shared" si="32"/>
+        <v>dm-Hi</v>
+      </c>
+      <c r="Z69" t="str">
+        <f t="shared" si="33"/>
+        <v>cp-95</v>
+      </c>
+      <c r="AA69" t="str">
+        <f t="shared" si="34"/>
+        <v>CF6</v>
+      </c>
+      <c r="AB69" t="str">
+        <f t="shared" si="35"/>
+        <v>df-N</v>
+      </c>
+      <c r="AC69" t="str">
+        <f t="shared" si="36"/>
+        <v>tc-0.10</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_ZAF_grids_kan/ReportDefs_vervestacks.xlsx
+++ b/VerveStacks_ZAF_grids_kan/ReportDefs_vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_ZAF_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D5301B1-BCF6-4990-B9FA-C0DD1AF1378A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABC0D6C4-F93C-4BEA-AF85-1E238AB8E068}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7824" uniqueCount="1189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7824" uniqueCount="1237">
   <si>
     <t>Unit</t>
   </si>
@@ -3650,6 +3650,150 @@
   </si>
   <si>
     <t>cr</t>
+  </si>
+  <si>
+    <t>Lo.0.CF1.Y.Eco.1</t>
+  </si>
+  <si>
+    <t>Hi.0.CF1.Y.Eco.1</t>
+  </si>
+  <si>
+    <t>Lo.95.CF1.Y.Eco.1</t>
+  </si>
+  <si>
+    <t>Hi.95.CF1.Y.Eco.1</t>
+  </si>
+  <si>
+    <t>Lo.0.CF1.N.Eco.1</t>
+  </si>
+  <si>
+    <t>Hi.0.CF1.N.Eco.1</t>
+  </si>
+  <si>
+    <t>Lo.95.CF1.N.Eco.1</t>
+  </si>
+  <si>
+    <t>Hi.95.CF1.N.Eco.1</t>
+  </si>
+  <si>
+    <t>Lo.0.CF6.Y.Eco.1</t>
+  </si>
+  <si>
+    <t>Hi.0.CF6.Y.Eco.1</t>
+  </si>
+  <si>
+    <t>Lo.95.CF6.Y.Eco.1</t>
+  </si>
+  <si>
+    <t>Hi.95.CF6.Y.Eco.1</t>
+  </si>
+  <si>
+    <t>Lo.0.CF6.N.Eco.1</t>
+  </si>
+  <si>
+    <t>Hi.0.CF6.N.Eco.1</t>
+  </si>
+  <si>
+    <t>Lo.95.CF6.N.Eco.1</t>
+  </si>
+  <si>
+    <t>Hi.95.CF6.N.Eco.1</t>
+  </si>
+  <si>
+    <t>Lo.0.CF1.Y.Eco.0.25</t>
+  </si>
+  <si>
+    <t>Hi.0.CF1.Y.Eco.0.25</t>
+  </si>
+  <si>
+    <t>Lo.95.CF1.Y.Eco.0.25</t>
+  </si>
+  <si>
+    <t>Hi.95.CF1.Y.Eco.0.25</t>
+  </si>
+  <si>
+    <t>Lo.0.CF1.N.Eco.0.25</t>
+  </si>
+  <si>
+    <t>Hi.0.CF1.N.Eco.0.25</t>
+  </si>
+  <si>
+    <t>Lo.95.CF1.N.Eco.0.25</t>
+  </si>
+  <si>
+    <t>Hi.95.CF1.N.Eco.0.25</t>
+  </si>
+  <si>
+    <t>Lo.0.CF6.Y.Eco.0.25</t>
+  </si>
+  <si>
+    <t>Hi.0.CF6.Y.Eco.0.25</t>
+  </si>
+  <si>
+    <t>Lo.95.CF6.Y.Eco.0.25</t>
+  </si>
+  <si>
+    <t>Hi.95.CF6.Y.Eco.0.25</t>
+  </si>
+  <si>
+    <t>Lo.0.CF6.N.Eco.0.25</t>
+  </si>
+  <si>
+    <t>Hi.0.CF6.N.Eco.0.25</t>
+  </si>
+  <si>
+    <t>Lo.95.CF6.N.Eco.0.25</t>
+  </si>
+  <si>
+    <t>Hi.95.CF6.N.Eco.0.25</t>
+  </si>
+  <si>
+    <t>Lo.0.CF1.Y.Eco.2</t>
+  </si>
+  <si>
+    <t>Hi.0.CF1.Y.Eco.2</t>
+  </si>
+  <si>
+    <t>Lo.95.CF1.Y.Eco.2</t>
+  </si>
+  <si>
+    <t>Hi.95.CF1.Y.Eco.2</t>
+  </si>
+  <si>
+    <t>Lo.0.CF1.N.Eco.2</t>
+  </si>
+  <si>
+    <t>Hi.0.CF1.N.Eco.2</t>
+  </si>
+  <si>
+    <t>Lo.95.CF1.N.Eco.2</t>
+  </si>
+  <si>
+    <t>Hi.95.CF1.N.Eco.2</t>
+  </si>
+  <si>
+    <t>Lo.0.CF6.Y.Eco.2</t>
+  </si>
+  <si>
+    <t>Hi.0.CF6.Y.Eco.2</t>
+  </si>
+  <si>
+    <t>Lo.95.CF6.Y.Eco.2</t>
+  </si>
+  <si>
+    <t>Hi.95.CF6.Y.Eco.2</t>
+  </si>
+  <si>
+    <t>Lo.0.CF6.N.Eco.2</t>
+  </si>
+  <si>
+    <t>Hi.0.CF6.N.Eco.2</t>
+  </si>
+  <si>
+    <t>Lo.95.CF6.N.Eco.2</t>
+  </si>
+  <si>
+    <t>Hi.95.CF6.N.Eco.2</t>
   </si>
 </sst>
 </file>
@@ -34188,11 +34332,11 @@
       </c>
       <c r="C6" t="str">
         <f>H6</f>
-        <v>tc-1.df-Y.cr-Pln.dm-Lo.cp-00.CF1</v>
+        <v>tc-1.00.df-Y.cr-Pln.dm-Lo.cp-00.CF1</v>
       </c>
       <c r="H6" t="str">
         <f>_xlfn.TEXTJOIN(".",TRUE,AE6,AC6:AD6)&amp;"."&amp;_xlfn.TEXTJOIN(".",TRUE,Z6:AB6)</f>
-        <v>tc-1.df-Y.cr-Pln.dm-Lo.cp-00.CF1</v>
+        <v>tc-1.00.df-Y.cr-Pln.dm-Lo.cp-00.CF1</v>
       </c>
       <c r="I6" t="str">
         <f>S6</f>
@@ -34266,45 +34410,45 @@
         <v>cr-Pln</v>
       </c>
       <c r="AE6" t="str">
-        <f>X$1&amp;"-"&amp;X6</f>
-        <v>tc-1</v>
+        <f t="shared" ref="AE6:AE53" si="1">X$1&amp;"-"&amp;TEXT(X6,"0.00")</f>
+        <v>tc-1.00</v>
       </c>
     </row>
     <row r="7" spans="2:31">
       <c r="B7" t="str">
-        <f t="shared" ref="B7:B17" si="1">"vs~"&amp;TEXT(R7,"0000")</f>
+        <f t="shared" ref="B7:B17" si="2">"vs~"&amp;TEXT(R7,"0000")</f>
         <v>vs~0002</v>
       </c>
       <c r="C7" t="str">
-        <f t="shared" ref="C7:C17" si="2">H7</f>
+        <f t="shared" ref="C7:C17" si="3">H7</f>
         <v>tc-1.00.df-Y.cr-Pln.dm-Hi.cp-00.CF1</v>
       </c>
       <c r="H7" t="str">
-        <f t="shared" ref="H7:H69" si="3">_xlfn.TEXTJOIN(".",TRUE,AE7,AC7:AD7)&amp;"."&amp;_xlfn.TEXTJOIN(".",TRUE,Z7:AB7)</f>
+        <f t="shared" ref="H7:H69" si="4">_xlfn.TEXTJOIN(".",TRUE,AE7,AC7:AD7)&amp;"."&amp;_xlfn.TEXTJOIN(".",TRUE,Z7:AB7)</f>
         <v>tc-1.00.df-Y.cr-Pln.dm-Hi.cp-00.CF1</v>
       </c>
       <c r="I7" t="str">
-        <f t="shared" ref="I7:I37" si="4">S7</f>
+        <f t="shared" ref="I7:I37" si="5">S7</f>
         <v>Hi</v>
       </c>
       <c r="J7" t="str">
-        <f t="shared" ref="J7:J37" si="5">TEXT(T7,"00")</f>
+        <f t="shared" ref="J7:J37" si="6">TEXT(T7,"00")</f>
         <v>00</v>
       </c>
       <c r="K7" t="str">
-        <f t="shared" ref="K7:K37" si="6">U7</f>
+        <f t="shared" ref="K7:K37" si="7">U7</f>
         <v>CF1</v>
       </c>
       <c r="L7" t="str">
-        <f t="shared" ref="L7:M37" si="7">V7</f>
+        <f t="shared" ref="L7:M37" si="8">V7</f>
         <v>Y</v>
       </c>
       <c r="M7" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>Pln</v>
       </c>
       <c r="N7" t="str">
-        <f t="shared" ref="N7:N69" si="8">TEXT(X7,"0.00")</f>
+        <f t="shared" ref="N7:N69" si="9">TEXT(X7,"0.00")</f>
         <v>1.00</v>
       </c>
       <c r="P7">
@@ -34335,65 +34479,65 @@
         <v>1</v>
       </c>
       <c r="Z7" t="str">
-        <f t="shared" ref="Z7:Z37" si="9">S$1&amp;"-"&amp;S7</f>
+        <f t="shared" ref="Z7:Z37" si="10">S$1&amp;"-"&amp;S7</f>
         <v>dm-Hi</v>
       </c>
       <c r="AA7" t="str">
-        <f t="shared" ref="AA7:AA53" si="10">T$1&amp;"-"&amp;TEXT(T7,"00")</f>
+        <f t="shared" ref="AA7:AA53" si="11">T$1&amp;"-"&amp;TEXT(T7,"00")</f>
         <v>cp-00</v>
       </c>
       <c r="AB7" t="str">
-        <f t="shared" ref="AB7:AB37" si="11">U7</f>
+        <f t="shared" ref="AB7:AB37" si="12">U7</f>
         <v>CF1</v>
       </c>
       <c r="AC7" t="str">
-        <f t="shared" ref="AC7:AC37" si="12">V$1&amp;"-"&amp;V7</f>
+        <f t="shared" ref="AC7:AC37" si="13">V$1&amp;"-"&amp;V7</f>
         <v>df-Y</v>
       </c>
       <c r="AD7" t="str">
-        <f t="shared" ref="AD7:AD69" si="13">W$1&amp;"-"&amp;W7</f>
+        <f t="shared" ref="AD7:AD69" si="14">W$1&amp;"-"&amp;W7</f>
         <v>cr-Pln</v>
       </c>
       <c r="AE7" t="str">
-        <f t="shared" ref="AE7:AE53" si="14">X$1&amp;"-"&amp;TEXT(X7,"0.00")</f>
+        <f t="shared" si="1"/>
         <v>tc-1.00</v>
       </c>
     </row>
     <row r="8" spans="2:31">
       <c r="B8" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>vs~0003</v>
       </c>
       <c r="C8" t="str">
-        <f t="shared" si="2"/>
-        <v>tc-1.00.df-Y.cr-Pln.dm-Lo.cp-95.CF1</v>
-      </c>
-      <c r="H8" t="str">
         <f t="shared" si="3"/>
         <v>tc-1.00.df-Y.cr-Pln.dm-Lo.cp-95.CF1</v>
       </c>
+      <c r="H8" t="str">
+        <f t="shared" si="4"/>
+        <v>tc-1.00.df-Y.cr-Pln.dm-Lo.cp-95.CF1</v>
+      </c>
       <c r="I8" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Lo</v>
       </c>
       <c r="J8" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>95</v>
       </c>
       <c r="K8" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>CF1</v>
       </c>
       <c r="L8" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>Y</v>
       </c>
       <c r="M8" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>Pln</v>
       </c>
       <c r="N8" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1.00</v>
       </c>
       <c r="P8">
@@ -34424,65 +34568,65 @@
         <v>1</v>
       </c>
       <c r="Z8" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>dm-Lo</v>
       </c>
       <c r="AA8" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>cp-95</v>
       </c>
       <c r="AB8" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>CF1</v>
       </c>
       <c r="AC8" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>df-Y</v>
       </c>
       <c r="AD8" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>cr-Pln</v>
       </c>
       <c r="AE8" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="1"/>
         <v>tc-1.00</v>
       </c>
     </row>
     <row r="9" spans="2:31">
       <c r="B9" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>vs~0004</v>
       </c>
       <c r="C9" t="str">
-        <f t="shared" si="2"/>
-        <v>tc-1.00.df-Y.cr-Pln.dm-Hi.cp-95.CF1</v>
-      </c>
-      <c r="H9" t="str">
         <f t="shared" si="3"/>
         <v>tc-1.00.df-Y.cr-Pln.dm-Hi.cp-95.CF1</v>
       </c>
+      <c r="H9" t="str">
+        <f t="shared" si="4"/>
+        <v>tc-1.00.df-Y.cr-Pln.dm-Hi.cp-95.CF1</v>
+      </c>
       <c r="I9" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Hi</v>
       </c>
       <c r="J9" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>95</v>
       </c>
       <c r="K9" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>CF1</v>
       </c>
       <c r="L9" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>Y</v>
       </c>
       <c r="M9" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>Pln</v>
       </c>
       <c r="N9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1.00</v>
       </c>
       <c r="P9">
@@ -34513,65 +34657,65 @@
         <v>1</v>
       </c>
       <c r="Z9" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>dm-Hi</v>
       </c>
       <c r="AA9" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>cp-95</v>
       </c>
       <c r="AB9" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>CF1</v>
       </c>
       <c r="AC9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>df-Y</v>
       </c>
       <c r="AD9" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>cr-Pln</v>
       </c>
       <c r="AE9" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="1"/>
         <v>tc-1.00</v>
       </c>
     </row>
     <row r="10" spans="2:31">
       <c r="B10" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>vs~0005</v>
       </c>
       <c r="C10" t="str">
-        <f t="shared" si="2"/>
-        <v>tc-1.00.df-N.cr-Pln.dm-Lo.cp-00.CF1</v>
-      </c>
-      <c r="H10" t="str">
         <f t="shared" si="3"/>
         <v>tc-1.00.df-N.cr-Pln.dm-Lo.cp-00.CF1</v>
       </c>
+      <c r="H10" t="str">
+        <f t="shared" si="4"/>
+        <v>tc-1.00.df-N.cr-Pln.dm-Lo.cp-00.CF1</v>
+      </c>
       <c r="I10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Lo</v>
       </c>
       <c r="J10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>00</v>
       </c>
       <c r="K10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>CF1</v>
       </c>
       <c r="L10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>N</v>
       </c>
       <c r="M10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>Pln</v>
       </c>
       <c r="N10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1.00</v>
       </c>
       <c r="P10">
@@ -34602,65 +34746,65 @@
         <v>1</v>
       </c>
       <c r="Z10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>dm-Lo</v>
       </c>
       <c r="AA10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>cp-00</v>
       </c>
       <c r="AB10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>CF1</v>
       </c>
       <c r="AC10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>df-N</v>
       </c>
       <c r="AD10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>cr-Pln</v>
       </c>
       <c r="AE10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="1"/>
         <v>tc-1.00</v>
       </c>
     </row>
     <row r="11" spans="2:31">
       <c r="B11" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>vs~0006</v>
       </c>
       <c r="C11" t="str">
-        <f t="shared" si="2"/>
-        <v>tc-1.00.df-N.cr-Pln.dm-Hi.cp-00.CF1</v>
-      </c>
-      <c r="H11" t="str">
         <f t="shared" si="3"/>
         <v>tc-1.00.df-N.cr-Pln.dm-Hi.cp-00.CF1</v>
       </c>
+      <c r="H11" t="str">
+        <f t="shared" si="4"/>
+        <v>tc-1.00.df-N.cr-Pln.dm-Hi.cp-00.CF1</v>
+      </c>
       <c r="I11" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Hi</v>
       </c>
       <c r="J11" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>00</v>
       </c>
       <c r="K11" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>CF1</v>
       </c>
       <c r="L11" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>N</v>
       </c>
       <c r="M11" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>Pln</v>
       </c>
       <c r="N11" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1.00</v>
       </c>
       <c r="P11">
@@ -34691,65 +34835,65 @@
         <v>1</v>
       </c>
       <c r="Z11" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>dm-Hi</v>
       </c>
       <c r="AA11" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>cp-00</v>
       </c>
       <c r="AB11" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>CF1</v>
       </c>
       <c r="AC11" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>df-N</v>
       </c>
       <c r="AD11" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>cr-Pln</v>
       </c>
       <c r="AE11" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="1"/>
         <v>tc-1.00</v>
       </c>
     </row>
     <row r="12" spans="2:31">
       <c r="B12" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>vs~0007</v>
       </c>
       <c r="C12" t="str">
-        <f t="shared" si="2"/>
-        <v>tc-1.00.df-N.cr-Pln.dm-Lo.cp-95.CF1</v>
-      </c>
-      <c r="H12" t="str">
         <f t="shared" si="3"/>
         <v>tc-1.00.df-N.cr-Pln.dm-Lo.cp-95.CF1</v>
       </c>
+      <c r="H12" t="str">
+        <f t="shared" si="4"/>
+        <v>tc-1.00.df-N.cr-Pln.dm-Lo.cp-95.CF1</v>
+      </c>
       <c r="I12" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Lo</v>
       </c>
       <c r="J12" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>95</v>
       </c>
       <c r="K12" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>CF1</v>
       </c>
       <c r="L12" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>N</v>
       </c>
       <c r="M12" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>Pln</v>
       </c>
       <c r="N12" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1.00</v>
       </c>
       <c r="P12">
@@ -34780,65 +34924,65 @@
         <v>1</v>
       </c>
       <c r="Z12" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>dm-Lo</v>
       </c>
       <c r="AA12" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>cp-95</v>
       </c>
       <c r="AB12" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>CF1</v>
       </c>
       <c r="AC12" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>df-N</v>
       </c>
       <c r="AD12" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>cr-Pln</v>
       </c>
       <c r="AE12" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="1"/>
         <v>tc-1.00</v>
       </c>
     </row>
     <row r="13" spans="2:31">
       <c r="B13" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>vs~0008</v>
       </c>
       <c r="C13" t="str">
-        <f t="shared" si="2"/>
-        <v>tc-1.00.df-N.cr-Pln.dm-Hi.cp-95.CF1</v>
-      </c>
-      <c r="H13" t="str">
         <f t="shared" si="3"/>
         <v>tc-1.00.df-N.cr-Pln.dm-Hi.cp-95.CF1</v>
       </c>
+      <c r="H13" t="str">
+        <f t="shared" si="4"/>
+        <v>tc-1.00.df-N.cr-Pln.dm-Hi.cp-95.CF1</v>
+      </c>
       <c r="I13" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Hi</v>
       </c>
       <c r="J13" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>95</v>
       </c>
       <c r="K13" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>CF1</v>
       </c>
       <c r="L13" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>N</v>
       </c>
       <c r="M13" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>Pln</v>
       </c>
       <c r="N13" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1.00</v>
       </c>
       <c r="P13">
@@ -34869,65 +35013,65 @@
         <v>1</v>
       </c>
       <c r="Z13" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>dm-Hi</v>
       </c>
       <c r="AA13" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>cp-95</v>
       </c>
       <c r="AB13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>CF1</v>
       </c>
       <c r="AC13" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>df-N</v>
       </c>
       <c r="AD13" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>cr-Pln</v>
       </c>
       <c r="AE13" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="1"/>
         <v>tc-1.00</v>
       </c>
     </row>
     <row r="14" spans="2:31">
       <c r="B14" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>vs~0009</v>
       </c>
       <c r="C14" t="str">
-        <f t="shared" si="2"/>
-        <v>tc-1.00.df-Y.cr-Pln.dm-Lo.cp-00.CF6</v>
-      </c>
-      <c r="H14" t="str">
         <f t="shared" si="3"/>
         <v>tc-1.00.df-Y.cr-Pln.dm-Lo.cp-00.CF6</v>
       </c>
+      <c r="H14" t="str">
+        <f t="shared" si="4"/>
+        <v>tc-1.00.df-Y.cr-Pln.dm-Lo.cp-00.CF6</v>
+      </c>
       <c r="I14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Lo</v>
       </c>
       <c r="J14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>00</v>
       </c>
       <c r="K14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>CF6</v>
       </c>
       <c r="L14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>Y</v>
       </c>
       <c r="M14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>Pln</v>
       </c>
       <c r="N14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1.00</v>
       </c>
       <c r="P14">
@@ -34958,65 +35102,65 @@
         <v>1</v>
       </c>
       <c r="Z14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>dm-Lo</v>
       </c>
       <c r="AA14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>cp-00</v>
       </c>
       <c r="AB14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>CF6</v>
       </c>
       <c r="AC14" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>df-Y</v>
       </c>
       <c r="AD14" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>cr-Pln</v>
       </c>
       <c r="AE14" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="1"/>
         <v>tc-1.00</v>
       </c>
     </row>
     <row r="15" spans="2:31">
       <c r="B15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>vs~0010</v>
       </c>
       <c r="C15" t="str">
-        <f t="shared" si="2"/>
-        <v>tc-1.00.df-Y.cr-Pln.dm-Hi.cp-00.CF6</v>
-      </c>
-      <c r="H15" t="str">
         <f t="shared" si="3"/>
         <v>tc-1.00.df-Y.cr-Pln.dm-Hi.cp-00.CF6</v>
       </c>
+      <c r="H15" t="str">
+        <f t="shared" si="4"/>
+        <v>tc-1.00.df-Y.cr-Pln.dm-Hi.cp-00.CF6</v>
+      </c>
       <c r="I15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Hi</v>
       </c>
       <c r="J15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>00</v>
       </c>
       <c r="K15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>CF6</v>
       </c>
       <c r="L15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>Y</v>
       </c>
       <c r="M15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>Pln</v>
       </c>
       <c r="N15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1.00</v>
       </c>
       <c r="P15">
@@ -35047,65 +35191,65 @@
         <v>1</v>
       </c>
       <c r="Z15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>dm-Hi</v>
       </c>
       <c r="AA15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>cp-00</v>
       </c>
       <c r="AB15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>CF6</v>
       </c>
       <c r="AC15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>df-Y</v>
       </c>
       <c r="AD15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>cr-Pln</v>
       </c>
       <c r="AE15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="1"/>
         <v>tc-1.00</v>
       </c>
     </row>
     <row r="16" spans="2:31">
       <c r="B16" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>vs~0011</v>
       </c>
       <c r="C16" t="str">
-        <f t="shared" si="2"/>
-        <v>tc-1.00.df-Y.cr-Pln.dm-Lo.cp-95.CF6</v>
-      </c>
-      <c r="H16" t="str">
         <f t="shared" si="3"/>
         <v>tc-1.00.df-Y.cr-Pln.dm-Lo.cp-95.CF6</v>
       </c>
+      <c r="H16" t="str">
+        <f t="shared" si="4"/>
+        <v>tc-1.00.df-Y.cr-Pln.dm-Lo.cp-95.CF6</v>
+      </c>
       <c r="I16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Lo</v>
       </c>
       <c r="J16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>95</v>
       </c>
       <c r="K16" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>CF6</v>
       </c>
       <c r="L16" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>Y</v>
       </c>
       <c r="M16" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>Pln</v>
       </c>
       <c r="N16" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1.00</v>
       </c>
       <c r="P16">
@@ -35136,65 +35280,65 @@
         <v>1</v>
       </c>
       <c r="Z16" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>dm-Lo</v>
       </c>
       <c r="AA16" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>cp-95</v>
       </c>
       <c r="AB16" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>CF6</v>
       </c>
       <c r="AC16" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>df-Y</v>
       </c>
       <c r="AD16" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>cr-Pln</v>
       </c>
       <c r="AE16" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="1"/>
         <v>tc-1.00</v>
       </c>
     </row>
     <row r="17" spans="2:31">
       <c r="B17" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>vs~0012</v>
       </c>
       <c r="C17" t="str">
-        <f t="shared" si="2"/>
-        <v>tc-1.00.df-Y.cr-Pln.dm-Hi.cp-95.CF6</v>
-      </c>
-      <c r="H17" t="str">
         <f t="shared" si="3"/>
         <v>tc-1.00.df-Y.cr-Pln.dm-Hi.cp-95.CF6</v>
       </c>
+      <c r="H17" t="str">
+        <f t="shared" si="4"/>
+        <v>tc-1.00.df-Y.cr-Pln.dm-Hi.cp-95.CF6</v>
+      </c>
       <c r="I17" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Hi</v>
       </c>
       <c r="J17" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>95</v>
       </c>
       <c r="K17" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>CF6</v>
       </c>
       <c r="L17" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>Y</v>
       </c>
       <c r="M17" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>Pln</v>
       </c>
       <c r="N17" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1.00</v>
       </c>
       <c r="P17">
@@ -35225,27 +35369,27 @@
         <v>1</v>
       </c>
       <c r="Z17" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>dm-Hi</v>
       </c>
       <c r="AA17" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>cp-95</v>
       </c>
       <c r="AB17" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>CF6</v>
       </c>
       <c r="AC17" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>df-Y</v>
       </c>
       <c r="AD17" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>cr-Pln</v>
       </c>
       <c r="AE17" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="1"/>
         <v>tc-1.00</v>
       </c>
     </row>
@@ -35259,31 +35403,31 @@
         <v>tc-1.00.df-N.cr-Pln.dm-Lo.cp-00.CF6</v>
       </c>
       <c r="H18" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>tc-1.00.df-N.cr-Pln.dm-Lo.cp-00.CF6</v>
       </c>
       <c r="I18" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Lo</v>
       </c>
       <c r="J18" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>00</v>
       </c>
       <c r="K18" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>CF6</v>
       </c>
       <c r="L18" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>N</v>
       </c>
       <c r="M18" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>Pln</v>
       </c>
       <c r="N18" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1.00</v>
       </c>
       <c r="P18">
@@ -35314,27 +35458,27 @@
         <v>1</v>
       </c>
       <c r="Z18" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>dm-Lo</v>
       </c>
       <c r="AA18" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>cp-00</v>
       </c>
       <c r="AB18" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>CF6</v>
       </c>
       <c r="AC18" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>df-N</v>
       </c>
       <c r="AD18" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>cr-Pln</v>
       </c>
       <c r="AE18" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="1"/>
         <v>tc-1.00</v>
       </c>
     </row>
@@ -35348,31 +35492,31 @@
         <v>tc-1.00.df-N.cr-Pln.dm-Hi.cp-00.CF6</v>
       </c>
       <c r="H19" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>tc-1.00.df-N.cr-Pln.dm-Hi.cp-00.CF6</v>
       </c>
       <c r="I19" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Hi</v>
       </c>
       <c r="J19" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>00</v>
       </c>
       <c r="K19" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>CF6</v>
       </c>
       <c r="L19" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>N</v>
       </c>
       <c r="M19" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>Pln</v>
       </c>
       <c r="N19" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1.00</v>
       </c>
       <c r="P19">
@@ -35403,27 +35547,27 @@
         <v>1</v>
       </c>
       <c r="Z19" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>dm-Hi</v>
       </c>
       <c r="AA19" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>cp-00</v>
       </c>
       <c r="AB19" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>CF6</v>
       </c>
       <c r="AC19" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>df-N</v>
       </c>
       <c r="AD19" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>cr-Pln</v>
       </c>
       <c r="AE19" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="1"/>
         <v>tc-1.00</v>
       </c>
     </row>
@@ -35437,31 +35581,31 @@
         <v>tc-1.00.df-N.cr-Pln.dm-Lo.cp-95.CF6</v>
       </c>
       <c r="H20" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>tc-1.00.df-N.cr-Pln.dm-Lo.cp-95.CF6</v>
       </c>
       <c r="I20" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Lo</v>
       </c>
       <c r="J20" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>95</v>
       </c>
       <c r="K20" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>CF6</v>
       </c>
       <c r="L20" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>N</v>
       </c>
       <c r="M20" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>Pln</v>
       </c>
       <c r="N20" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1.00</v>
       </c>
       <c r="P20">
@@ -35492,27 +35636,27 @@
         <v>1</v>
       </c>
       <c r="Z20" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>dm-Lo</v>
       </c>
       <c r="AA20" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>cp-95</v>
       </c>
       <c r="AB20" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>CF6</v>
       </c>
       <c r="AC20" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>df-N</v>
       </c>
       <c r="AD20" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>cr-Pln</v>
       </c>
       <c r="AE20" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="1"/>
         <v>tc-1.00</v>
       </c>
     </row>
@@ -35526,31 +35670,31 @@
         <v>tc-1.00.df-N.cr-Pln.dm-Hi.cp-95.CF6</v>
       </c>
       <c r="H21" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>tc-1.00.df-N.cr-Pln.dm-Hi.cp-95.CF6</v>
       </c>
       <c r="I21" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Hi</v>
       </c>
       <c r="J21" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>95</v>
       </c>
       <c r="K21" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>CF6</v>
       </c>
       <c r="L21" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>N</v>
       </c>
       <c r="M21" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>Pln</v>
       </c>
       <c r="N21" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1.00</v>
       </c>
       <c r="P21">
@@ -35581,27 +35725,27 @@
         <v>1</v>
       </c>
       <c r="Z21" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>dm-Hi</v>
       </c>
       <c r="AA21" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>cp-95</v>
       </c>
       <c r="AB21" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>CF6</v>
       </c>
       <c r="AC21" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>df-N</v>
       </c>
       <c r="AD21" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>cr-Pln</v>
       </c>
       <c r="AE21" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="1"/>
         <v>tc-1.00</v>
       </c>
     </row>
@@ -35615,31 +35759,31 @@
         <v>tc-0.25.df-Y.cr-Pln.dm-Lo.cp-00.CF1</v>
       </c>
       <c r="H22" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>tc-0.25.df-Y.cr-Pln.dm-Lo.cp-00.CF1</v>
       </c>
       <c r="I22" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Lo</v>
       </c>
       <c r="J22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>00</v>
       </c>
       <c r="K22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>CF1</v>
       </c>
       <c r="L22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>Y</v>
       </c>
       <c r="M22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>Pln</v>
       </c>
       <c r="N22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0.25</v>
       </c>
       <c r="P22">
@@ -35670,27 +35814,27 @@
         <v>0.25</v>
       </c>
       <c r="Z22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>dm-Lo</v>
       </c>
       <c r="AA22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>cp-00</v>
       </c>
       <c r="AB22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>CF1</v>
       </c>
       <c r="AC22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>df-Y</v>
       </c>
       <c r="AD22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>cr-Pln</v>
       </c>
       <c r="AE22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="1"/>
         <v>tc-0.25</v>
       </c>
     </row>
@@ -35704,31 +35848,31 @@
         <v>tc-0.25.df-Y.cr-Pln.dm-Hi.cp-00.CF1</v>
       </c>
       <c r="H23" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>tc-0.25.df-Y.cr-Pln.dm-Hi.cp-00.CF1</v>
       </c>
       <c r="I23" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Hi</v>
       </c>
       <c r="J23" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>00</v>
       </c>
       <c r="K23" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>CF1</v>
       </c>
       <c r="L23" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>Y</v>
       </c>
       <c r="M23" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>Pln</v>
       </c>
       <c r="N23" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0.25</v>
       </c>
       <c r="P23">
@@ -35759,27 +35903,27 @@
         <v>0.25</v>
       </c>
       <c r="Z23" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>dm-Hi</v>
       </c>
       <c r="AA23" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>cp-00</v>
       </c>
       <c r="AB23" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>CF1</v>
       </c>
       <c r="AC23" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>df-Y</v>
       </c>
       <c r="AD23" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>cr-Pln</v>
       </c>
       <c r="AE23" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="1"/>
         <v>tc-0.25</v>
       </c>
     </row>
@@ -35793,31 +35937,31 @@
         <v>tc-0.25.df-Y.cr-Pln.dm-Lo.cp-95.CF1</v>
       </c>
       <c r="H24" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>tc-0.25.df-Y.cr-Pln.dm-Lo.cp-95.CF1</v>
       </c>
       <c r="I24" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Lo</v>
       </c>
       <c r="J24" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>95</v>
       </c>
       <c r="K24" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>CF1</v>
       </c>
       <c r="L24" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>Y</v>
       </c>
       <c r="M24" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>Pln</v>
       </c>
       <c r="N24" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0.25</v>
       </c>
       <c r="P24">
@@ -35848,27 +35992,27 @@
         <v>0.25</v>
       </c>
       <c r="Z24" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>dm-Lo</v>
       </c>
       <c r="AA24" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>cp-95</v>
       </c>
       <c r="AB24" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>CF1</v>
       </c>
       <c r="AC24" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>df-Y</v>
       </c>
       <c r="AD24" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>cr-Pln</v>
       </c>
       <c r="AE24" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="1"/>
         <v>tc-0.25</v>
       </c>
     </row>
@@ -35882,31 +36026,31 @@
         <v>tc-0.25.df-Y.cr-Pln.dm-Hi.cp-95.CF1</v>
       </c>
       <c r="H25" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>tc-0.25.df-Y.cr-Pln.dm-Hi.cp-95.CF1</v>
       </c>
       <c r="I25" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Hi</v>
       </c>
       <c r="J25" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>95</v>
       </c>
       <c r="K25" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>CF1</v>
       </c>
       <c r="L25" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>Y</v>
       </c>
       <c r="M25" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>Pln</v>
       </c>
       <c r="N25" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0.25</v>
       </c>
       <c r="P25">
@@ -35937,27 +36081,27 @@
         <v>0.25</v>
       </c>
       <c r="Z25" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>dm-Hi</v>
       </c>
       <c r="AA25" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>cp-95</v>
       </c>
       <c r="AB25" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>CF1</v>
       </c>
       <c r="AC25" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>df-Y</v>
       </c>
       <c r="AD25" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>cr-Pln</v>
       </c>
       <c r="AE25" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="1"/>
         <v>tc-0.25</v>
       </c>
     </row>
@@ -35971,31 +36115,31 @@
         <v>tc-0.25.df-N.cr-Pln.dm-Lo.cp-00.CF1</v>
       </c>
       <c r="H26" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>tc-0.25.df-N.cr-Pln.dm-Lo.cp-00.CF1</v>
       </c>
       <c r="I26" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Lo</v>
       </c>
       <c r="J26" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>00</v>
       </c>
       <c r="K26" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>CF1</v>
       </c>
       <c r="L26" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>N</v>
       </c>
       <c r="M26" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>Pln</v>
       </c>
       <c r="N26" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0.25</v>
       </c>
       <c r="P26">
@@ -36026,27 +36170,27 @@
         <v>0.25</v>
       </c>
       <c r="Z26" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>dm-Lo</v>
       </c>
       <c r="AA26" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>cp-00</v>
       </c>
       <c r="AB26" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>CF1</v>
       </c>
       <c r="AC26" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>df-N</v>
       </c>
       <c r="AD26" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>cr-Pln</v>
       </c>
       <c r="AE26" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="1"/>
         <v>tc-0.25</v>
       </c>
     </row>
@@ -36060,31 +36204,31 @@
         <v>tc-0.25.df-N.cr-Pln.dm-Hi.cp-00.CF1</v>
       </c>
       <c r="H27" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>tc-0.25.df-N.cr-Pln.dm-Hi.cp-00.CF1</v>
       </c>
       <c r="I27" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Hi</v>
       </c>
       <c r="J27" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>00</v>
       </c>
       <c r="K27" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>CF1</v>
       </c>
       <c r="L27" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>N</v>
       </c>
       <c r="M27" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>Pln</v>
       </c>
       <c r="N27" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0.25</v>
       </c>
       <c r="P27">
@@ -36115,27 +36259,27 @@
         <v>0.25</v>
       </c>
       <c r="Z27" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>dm-Hi</v>
       </c>
       <c r="AA27" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>cp-00</v>
       </c>
       <c r="AB27" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>CF1</v>
       </c>
       <c r="AC27" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>df-N</v>
       </c>
       <c r="AD27" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>cr-Pln</v>
       </c>
       <c r="AE27" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="1"/>
         <v>tc-0.25</v>
       </c>
     </row>
@@ -36149,31 +36293,31 @@
         <v>tc-0.25.df-N.cr-Pln.dm-Lo.cp-95.CF1</v>
       </c>
       <c r="H28" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>tc-0.25.df-N.cr-Pln.dm-Lo.cp-95.CF1</v>
       </c>
       <c r="I28" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Lo</v>
       </c>
       <c r="J28" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>95</v>
       </c>
       <c r="K28" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>CF1</v>
       </c>
       <c r="L28" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>N</v>
       </c>
       <c r="M28" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>Pln</v>
       </c>
       <c r="N28" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0.25</v>
       </c>
       <c r="P28">
@@ -36204,27 +36348,27 @@
         <v>0.25</v>
       </c>
       <c r="Z28" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>dm-Lo</v>
       </c>
       <c r="AA28" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>cp-95</v>
       </c>
       <c r="AB28" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>CF1</v>
       </c>
       <c r="AC28" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>df-N</v>
       </c>
       <c r="AD28" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>cr-Pln</v>
       </c>
       <c r="AE28" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="1"/>
         <v>tc-0.25</v>
       </c>
     </row>
@@ -36238,31 +36382,31 @@
         <v>tc-0.25.df-N.cr-Pln.dm-Hi.cp-95.CF1</v>
       </c>
       <c r="H29" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>tc-0.25.df-N.cr-Pln.dm-Hi.cp-95.CF1</v>
       </c>
       <c r="I29" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Hi</v>
       </c>
       <c r="J29" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>95</v>
       </c>
       <c r="K29" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>CF1</v>
       </c>
       <c r="L29" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>N</v>
       </c>
       <c r="M29" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>Pln</v>
       </c>
       <c r="N29" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0.25</v>
       </c>
       <c r="P29">
@@ -36293,27 +36437,27 @@
         <v>0.25</v>
       </c>
       <c r="Z29" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>dm-Hi</v>
       </c>
       <c r="AA29" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>cp-95</v>
       </c>
       <c r="AB29" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>CF1</v>
       </c>
       <c r="AC29" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>df-N</v>
       </c>
       <c r="AD29" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>cr-Pln</v>
       </c>
       <c r="AE29" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="1"/>
         <v>tc-0.25</v>
       </c>
     </row>
@@ -36327,31 +36471,31 @@
         <v>tc-0.25.df-Y.cr-Pln.dm-Lo.cp-00.CF6</v>
       </c>
       <c r="H30" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>tc-0.25.df-Y.cr-Pln.dm-Lo.cp-00.CF6</v>
       </c>
       <c r="I30" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Lo</v>
       </c>
       <c r="J30" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>00</v>
       </c>
       <c r="K30" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>CF6</v>
       </c>
       <c r="L30" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>Y</v>
       </c>
       <c r="M30" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>Pln</v>
       </c>
       <c r="N30" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0.25</v>
       </c>
       <c r="P30">
@@ -36382,27 +36526,27 @@
         <v>0.25</v>
       </c>
       <c r="Z30" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>dm-Lo</v>
       </c>
       <c r="AA30" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>cp-00</v>
       </c>
       <c r="AB30" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>CF6</v>
       </c>
       <c r="AC30" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>df-Y</v>
       </c>
       <c r="AD30" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>cr-Pln</v>
       </c>
       <c r="AE30" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="1"/>
         <v>tc-0.25</v>
       </c>
     </row>
@@ -36416,31 +36560,31 @@
         <v>tc-0.25.df-Y.cr-Pln.dm-Hi.cp-00.CF6</v>
       </c>
       <c r="H31" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>tc-0.25.df-Y.cr-Pln.dm-Hi.cp-00.CF6</v>
       </c>
       <c r="I31" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Hi</v>
       </c>
       <c r="J31" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>00</v>
       </c>
       <c r="K31" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>CF6</v>
       </c>
       <c r="L31" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>Y</v>
       </c>
       <c r="M31" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>Pln</v>
       </c>
       <c r="N31" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0.25</v>
       </c>
       <c r="P31">
@@ -36471,27 +36615,27 @@
         <v>0.25</v>
       </c>
       <c r="Z31" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>dm-Hi</v>
       </c>
       <c r="AA31" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>cp-00</v>
       </c>
       <c r="AB31" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>CF6</v>
       </c>
       <c r="AC31" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>df-Y</v>
       </c>
       <c r="AD31" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>cr-Pln</v>
       </c>
       <c r="AE31" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="1"/>
         <v>tc-0.25</v>
       </c>
     </row>
@@ -36505,31 +36649,31 @@
         <v>tc-0.25.df-Y.cr-Pln.dm-Lo.cp-95.CF6</v>
       </c>
       <c r="H32" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>tc-0.25.df-Y.cr-Pln.dm-Lo.cp-95.CF6</v>
       </c>
       <c r="I32" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Lo</v>
       </c>
       <c r="J32" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>95</v>
       </c>
       <c r="K32" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>CF6</v>
       </c>
       <c r="L32" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>Y</v>
       </c>
       <c r="M32" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>Pln</v>
       </c>
       <c r="N32" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0.25</v>
       </c>
       <c r="P32">
@@ -36560,27 +36704,27 @@
         <v>0.25</v>
       </c>
       <c r="Z32" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>dm-Lo</v>
       </c>
       <c r="AA32" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>cp-95</v>
       </c>
       <c r="AB32" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>CF6</v>
       </c>
       <c r="AC32" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>df-Y</v>
       </c>
       <c r="AD32" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>cr-Pln</v>
       </c>
       <c r="AE32" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="1"/>
         <v>tc-0.25</v>
       </c>
     </row>
@@ -36594,31 +36738,31 @@
         <v>tc-0.25.df-Y.cr-Pln.dm-Hi.cp-95.CF6</v>
       </c>
       <c r="H33" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>tc-0.25.df-Y.cr-Pln.dm-Hi.cp-95.CF6</v>
       </c>
       <c r="I33" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Hi</v>
       </c>
       <c r="J33" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>95</v>
       </c>
       <c r="K33" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>CF6</v>
       </c>
       <c r="L33" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>Y</v>
       </c>
       <c r="M33" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>Pln</v>
       </c>
       <c r="N33" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0.25</v>
       </c>
       <c r="P33">
@@ -36649,27 +36793,27 @@
         <v>0.25</v>
       </c>
       <c r="Z33" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>dm-Hi</v>
       </c>
       <c r="AA33" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>cp-95</v>
       </c>
       <c r="AB33" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>CF6</v>
       </c>
       <c r="AC33" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>df-Y</v>
       </c>
       <c r="AD33" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>cr-Pln</v>
       </c>
       <c r="AE33" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="1"/>
         <v>tc-0.25</v>
       </c>
     </row>
@@ -36683,31 +36827,31 @@
         <v>tc-0.25.df-N.cr-Pln.dm-Lo.cp-00.CF6</v>
       </c>
       <c r="H34" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>tc-0.25.df-N.cr-Pln.dm-Lo.cp-00.CF6</v>
       </c>
       <c r="I34" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Lo</v>
       </c>
       <c r="J34" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>00</v>
       </c>
       <c r="K34" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>CF6</v>
       </c>
       <c r="L34" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>N</v>
       </c>
       <c r="M34" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>Pln</v>
       </c>
       <c r="N34" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0.25</v>
       </c>
       <c r="P34">
@@ -36738,27 +36882,27 @@
         <v>0.25</v>
       </c>
       <c r="Z34" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>dm-Lo</v>
       </c>
       <c r="AA34" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>cp-00</v>
       </c>
       <c r="AB34" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>CF6</v>
       </c>
       <c r="AC34" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>df-N</v>
       </c>
       <c r="AD34" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>cr-Pln</v>
       </c>
       <c r="AE34" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="1"/>
         <v>tc-0.25</v>
       </c>
     </row>
@@ -36772,31 +36916,31 @@
         <v>tc-0.25.df-N.cr-Pln.dm-Hi.cp-00.CF6</v>
       </c>
       <c r="H35" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>tc-0.25.df-N.cr-Pln.dm-Hi.cp-00.CF6</v>
       </c>
       <c r="I35" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Hi</v>
       </c>
       <c r="J35" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>00</v>
       </c>
       <c r="K35" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>CF6</v>
       </c>
       <c r="L35" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>N</v>
       </c>
       <c r="M35" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>Pln</v>
       </c>
       <c r="N35" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0.25</v>
       </c>
       <c r="P35">
@@ -36827,27 +36971,27 @@
         <v>0.25</v>
       </c>
       <c r="Z35" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>dm-Hi</v>
       </c>
       <c r="AA35" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>cp-00</v>
       </c>
       <c r="AB35" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>CF6</v>
       </c>
       <c r="AC35" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>df-N</v>
       </c>
       <c r="AD35" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>cr-Pln</v>
       </c>
       <c r="AE35" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="1"/>
         <v>tc-0.25</v>
       </c>
     </row>
@@ -36861,31 +37005,31 @@
         <v>tc-0.25.df-N.cr-Pln.dm-Lo.cp-95.CF6</v>
       </c>
       <c r="H36" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>tc-0.25.df-N.cr-Pln.dm-Lo.cp-95.CF6</v>
       </c>
       <c r="I36" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Lo</v>
       </c>
       <c r="J36" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>95</v>
       </c>
       <c r="K36" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>CF6</v>
       </c>
       <c r="L36" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>N</v>
       </c>
       <c r="M36" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>Pln</v>
       </c>
       <c r="N36" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0.25</v>
       </c>
       <c r="P36">
@@ -36916,27 +37060,27 @@
         <v>0.25</v>
       </c>
       <c r="Z36" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>dm-Lo</v>
       </c>
       <c r="AA36" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>cp-95</v>
       </c>
       <c r="AB36" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>CF6</v>
       </c>
       <c r="AC36" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>df-N</v>
       </c>
       <c r="AD36" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>cr-Pln</v>
       </c>
       <c r="AE36" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="1"/>
         <v>tc-0.25</v>
       </c>
     </row>
@@ -36950,31 +37094,31 @@
         <v>tc-0.25.df-N.cr-Pln.dm-Hi.cp-95.CF6</v>
       </c>
       <c r="H37" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>tc-0.25.df-N.cr-Pln.dm-Hi.cp-95.CF6</v>
       </c>
       <c r="I37" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Hi</v>
       </c>
       <c r="J37" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>95</v>
       </c>
       <c r="K37" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>CF6</v>
       </c>
       <c r="L37" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>N</v>
       </c>
       <c r="M37" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>Pln</v>
       </c>
       <c r="N37" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0.25</v>
       </c>
       <c r="P37">
@@ -37005,27 +37149,27 @@
         <v>0.25</v>
       </c>
       <c r="Z37" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>dm-Hi</v>
       </c>
       <c r="AA37" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>cp-95</v>
       </c>
       <c r="AB37" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>CF6</v>
       </c>
       <c r="AC37" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>df-N</v>
       </c>
       <c r="AD37" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>cr-Pln</v>
       </c>
       <c r="AE37" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="1"/>
         <v>tc-0.25</v>
       </c>
     </row>
@@ -37039,7 +37183,7 @@
         <v>tc-2.00.df-Y.cr-Pln.dm-Lo.cp-00.CF1</v>
       </c>
       <c r="H38" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>tc-2.00.df-Y.cr-Pln.dm-Lo.cp-00.CF1</v>
       </c>
       <c r="I38" t="str">
@@ -37063,7 +37207,7 @@
         <v>Pln</v>
       </c>
       <c r="N38" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>2.00</v>
       </c>
       <c r="P38">
@@ -37098,7 +37242,7 @@
         <v>dm-Lo</v>
       </c>
       <c r="AA38" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>cp-00</v>
       </c>
       <c r="AB38" t="str">
@@ -37110,11 +37254,11 @@
         <v>df-Y</v>
       </c>
       <c r="AD38" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>cr-Pln</v>
       </c>
       <c r="AE38" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="1"/>
         <v>tc-2.00</v>
       </c>
     </row>
@@ -37128,7 +37272,7 @@
         <v>tc-2.00.df-Y.cr-Pln.dm-Hi.cp-00.CF1</v>
       </c>
       <c r="H39" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>tc-2.00.df-Y.cr-Pln.dm-Hi.cp-00.CF1</v>
       </c>
       <c r="I39" t="str">
@@ -37152,7 +37296,7 @@
         <v>Pln</v>
       </c>
       <c r="N39" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>2.00</v>
       </c>
       <c r="P39">
@@ -37187,7 +37331,7 @@
         <v>dm-Hi</v>
       </c>
       <c r="AA39" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>cp-00</v>
       </c>
       <c r="AB39" t="str">
@@ -37199,11 +37343,11 @@
         <v>df-Y</v>
       </c>
       <c r="AD39" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>cr-Pln</v>
       </c>
       <c r="AE39" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="1"/>
         <v>tc-2.00</v>
       </c>
     </row>
@@ -37217,7 +37361,7 @@
         <v>tc-2.00.df-Y.cr-Pln.dm-Lo.cp-95.CF1</v>
       </c>
       <c r="H40" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>tc-2.00.df-Y.cr-Pln.dm-Lo.cp-95.CF1</v>
       </c>
       <c r="I40" t="str">
@@ -37241,7 +37385,7 @@
         <v>Pln</v>
       </c>
       <c r="N40" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>2.00</v>
       </c>
       <c r="P40">
@@ -37276,7 +37420,7 @@
         <v>dm-Lo</v>
       </c>
       <c r="AA40" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>cp-95</v>
       </c>
       <c r="AB40" t="str">
@@ -37288,11 +37432,11 @@
         <v>df-Y</v>
       </c>
       <c r="AD40" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>cr-Pln</v>
       </c>
       <c r="AE40" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="1"/>
         <v>tc-2.00</v>
       </c>
     </row>
@@ -37306,7 +37450,7 @@
         <v>tc-2.00.df-Y.cr-Pln.dm-Hi.cp-95.CF1</v>
       </c>
       <c r="H41" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>tc-2.00.df-Y.cr-Pln.dm-Hi.cp-95.CF1</v>
       </c>
       <c r="I41" t="str">
@@ -37330,7 +37474,7 @@
         <v>Pln</v>
       </c>
       <c r="N41" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>2.00</v>
       </c>
       <c r="P41">
@@ -37365,7 +37509,7 @@
         <v>dm-Hi</v>
       </c>
       <c r="AA41" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>cp-95</v>
       </c>
       <c r="AB41" t="str">
@@ -37377,11 +37521,11 @@
         <v>df-Y</v>
       </c>
       <c r="AD41" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>cr-Pln</v>
       </c>
       <c r="AE41" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="1"/>
         <v>tc-2.00</v>
       </c>
     </row>
@@ -37395,7 +37539,7 @@
         <v>tc-2.00.df-N.cr-Pln.dm-Lo.cp-00.CF1</v>
       </c>
       <c r="H42" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>tc-2.00.df-N.cr-Pln.dm-Lo.cp-00.CF1</v>
       </c>
       <c r="I42" t="str">
@@ -37419,7 +37563,7 @@
         <v>Pln</v>
       </c>
       <c r="N42" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>2.00</v>
       </c>
       <c r="P42">
@@ -37454,7 +37598,7 @@
         <v>dm-Lo</v>
       </c>
       <c r="AA42" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>cp-00</v>
       </c>
       <c r="AB42" t="str">
@@ -37466,11 +37610,11 @@
         <v>df-N</v>
       </c>
       <c r="AD42" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>cr-Pln</v>
       </c>
       <c r="AE42" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="1"/>
         <v>tc-2.00</v>
       </c>
     </row>
@@ -37484,7 +37628,7 @@
         <v>tc-2.00.df-N.cr-Pln.dm-Hi.cp-00.CF1</v>
       </c>
       <c r="H43" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>tc-2.00.df-N.cr-Pln.dm-Hi.cp-00.CF1</v>
       </c>
       <c r="I43" t="str">
@@ -37508,7 +37652,7 @@
         <v>Pln</v>
       </c>
       <c r="N43" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>2.00</v>
       </c>
       <c r="P43">
@@ -37543,7 +37687,7 @@
         <v>dm-Hi</v>
       </c>
       <c r="AA43" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>cp-00</v>
       </c>
       <c r="AB43" t="str">
@@ -37555,11 +37699,11 @@
         <v>df-N</v>
       </c>
       <c r="AD43" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>cr-Pln</v>
       </c>
       <c r="AE43" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="1"/>
         <v>tc-2.00</v>
       </c>
     </row>
@@ -37573,7 +37717,7 @@
         <v>tc-2.00.df-N.cr-Pln.dm-Lo.cp-95.CF1</v>
       </c>
       <c r="H44" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>tc-2.00.df-N.cr-Pln.dm-Lo.cp-95.CF1</v>
       </c>
       <c r="I44" t="str">
@@ -37597,7 +37741,7 @@
         <v>Pln</v>
       </c>
       <c r="N44" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>2.00</v>
       </c>
       <c r="P44">
@@ -37632,7 +37776,7 @@
         <v>dm-Lo</v>
       </c>
       <c r="AA44" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>cp-95</v>
       </c>
       <c r="AB44" t="str">
@@ -37644,11 +37788,11 @@
         <v>df-N</v>
       </c>
       <c r="AD44" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>cr-Pln</v>
       </c>
       <c r="AE44" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="1"/>
         <v>tc-2.00</v>
       </c>
     </row>
@@ -37662,7 +37806,7 @@
         <v>tc-2.00.df-N.cr-Pln.dm-Hi.cp-95.CF1</v>
       </c>
       <c r="H45" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>tc-2.00.df-N.cr-Pln.dm-Hi.cp-95.CF1</v>
       </c>
       <c r="I45" t="str">
@@ -37686,7 +37830,7 @@
         <v>Pln</v>
       </c>
       <c r="N45" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>2.00</v>
       </c>
       <c r="P45">
@@ -37721,7 +37865,7 @@
         <v>dm-Hi</v>
       </c>
       <c r="AA45" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>cp-95</v>
       </c>
       <c r="AB45" t="str">
@@ -37733,11 +37877,11 @@
         <v>df-N</v>
       </c>
       <c r="AD45" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>cr-Pln</v>
       </c>
       <c r="AE45" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="1"/>
         <v>tc-2.00</v>
       </c>
     </row>
@@ -37751,7 +37895,7 @@
         <v>tc-2.00.df-Y.cr-Pln.dm-Lo.cp-00.CF6</v>
       </c>
       <c r="H46" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>tc-2.00.df-Y.cr-Pln.dm-Lo.cp-00.CF6</v>
       </c>
       <c r="I46" t="str">
@@ -37775,7 +37919,7 @@
         <v>Pln</v>
       </c>
       <c r="N46" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>2.00</v>
       </c>
       <c r="P46">
@@ -37810,7 +37954,7 @@
         <v>dm-Lo</v>
       </c>
       <c r="AA46" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>cp-00</v>
       </c>
       <c r="AB46" t="str">
@@ -37822,11 +37966,11 @@
         <v>df-Y</v>
       </c>
       <c r="AD46" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>cr-Pln</v>
       </c>
       <c r="AE46" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="1"/>
         <v>tc-2.00</v>
       </c>
     </row>
@@ -37840,7 +37984,7 @@
         <v>tc-2.00.df-Y.cr-Pln.dm-Hi.cp-00.CF6</v>
       </c>
       <c r="H47" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>tc-2.00.df-Y.cr-Pln.dm-Hi.cp-00.CF6</v>
       </c>
       <c r="I47" t="str">
@@ -37864,7 +38008,7 @@
         <v>Pln</v>
       </c>
       <c r="N47" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>2.00</v>
       </c>
       <c r="P47">
@@ -37899,7 +38043,7 @@
         <v>dm-Hi</v>
       </c>
       <c r="AA47" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>cp-00</v>
       </c>
       <c r="AB47" t="str">
@@ -37911,11 +38055,11 @@
         <v>df-Y</v>
       </c>
       <c r="AD47" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>cr-Pln</v>
       </c>
       <c r="AE47" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="1"/>
         <v>tc-2.00</v>
       </c>
     </row>
@@ -37929,7 +38073,7 @@
         <v>tc-2.00.df-Y.cr-Pln.dm-Lo.cp-95.CF6</v>
       </c>
       <c r="H48" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>tc-2.00.df-Y.cr-Pln.dm-Lo.cp-95.CF6</v>
       </c>
       <c r="I48" t="str">
@@ -37953,7 +38097,7 @@
         <v>Pln</v>
       </c>
       <c r="N48" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>2.00</v>
       </c>
       <c r="P48">
@@ -37988,7 +38132,7 @@
         <v>dm-Lo</v>
       </c>
       <c r="AA48" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>cp-95</v>
       </c>
       <c r="AB48" t="str">
@@ -38000,11 +38144,11 @@
         <v>df-Y</v>
       </c>
       <c r="AD48" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>cr-Pln</v>
       </c>
       <c r="AE48" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="1"/>
         <v>tc-2.00</v>
       </c>
     </row>
@@ -38018,7 +38162,7 @@
         <v>tc-2.00.df-Y.cr-Pln.dm-Hi.cp-95.CF6</v>
       </c>
       <c r="H49" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>tc-2.00.df-Y.cr-Pln.dm-Hi.cp-95.CF6</v>
       </c>
       <c r="I49" t="str">
@@ -38042,7 +38186,7 @@
         <v>Pln</v>
       </c>
       <c r="N49" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>2.00</v>
       </c>
       <c r="P49">
@@ -38077,7 +38221,7 @@
         <v>dm-Hi</v>
       </c>
       <c r="AA49" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>cp-95</v>
       </c>
       <c r="AB49" t="str">
@@ -38089,11 +38233,11 @@
         <v>df-Y</v>
       </c>
       <c r="AD49" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>cr-Pln</v>
       </c>
       <c r="AE49" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="1"/>
         <v>tc-2.00</v>
       </c>
     </row>
@@ -38107,7 +38251,7 @@
         <v>tc-2.00.df-N.cr-Pln.dm-Lo.cp-00.CF6</v>
       </c>
       <c r="H50" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>tc-2.00.df-N.cr-Pln.dm-Lo.cp-00.CF6</v>
       </c>
       <c r="I50" t="str">
@@ -38131,7 +38275,7 @@
         <v>Pln</v>
       </c>
       <c r="N50" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>2.00</v>
       </c>
       <c r="P50">
@@ -38166,7 +38310,7 @@
         <v>dm-Lo</v>
       </c>
       <c r="AA50" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>cp-00</v>
       </c>
       <c r="AB50" t="str">
@@ -38178,11 +38322,11 @@
         <v>df-N</v>
       </c>
       <c r="AD50" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>cr-Pln</v>
       </c>
       <c r="AE50" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="1"/>
         <v>tc-2.00</v>
       </c>
     </row>
@@ -38196,7 +38340,7 @@
         <v>tc-2.00.df-N.cr-Pln.dm-Hi.cp-00.CF6</v>
       </c>
       <c r="H51" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>tc-2.00.df-N.cr-Pln.dm-Hi.cp-00.CF6</v>
       </c>
       <c r="I51" t="str">
@@ -38220,7 +38364,7 @@
         <v>Pln</v>
       </c>
       <c r="N51" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>2.00</v>
       </c>
       <c r="P51">
@@ -38255,7 +38399,7 @@
         <v>dm-Hi</v>
       </c>
       <c r="AA51" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>cp-00</v>
       </c>
       <c r="AB51" t="str">
@@ -38267,11 +38411,11 @@
         <v>df-N</v>
       </c>
       <c r="AD51" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>cr-Pln</v>
       </c>
       <c r="AE51" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="1"/>
         <v>tc-2.00</v>
       </c>
     </row>
@@ -38285,7 +38429,7 @@
         <v>tc-2.00.df-N.cr-Pln.dm-Lo.cp-95.CF6</v>
       </c>
       <c r="H52" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>tc-2.00.df-N.cr-Pln.dm-Lo.cp-95.CF6</v>
       </c>
       <c r="I52" t="str">
@@ -38309,7 +38453,7 @@
         <v>Pln</v>
       </c>
       <c r="N52" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>2.00</v>
       </c>
       <c r="P52">
@@ -38344,7 +38488,7 @@
         <v>dm-Lo</v>
       </c>
       <c r="AA52" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>cp-95</v>
       </c>
       <c r="AB52" t="str">
@@ -38356,11 +38500,11 @@
         <v>df-N</v>
       </c>
       <c r="AD52" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>cr-Pln</v>
       </c>
       <c r="AE52" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="1"/>
         <v>tc-2.00</v>
       </c>
     </row>
@@ -38374,7 +38518,7 @@
         <v>tc-2.00.df-N.cr-Pln.dm-Hi.cp-95.CF6</v>
       </c>
       <c r="H53" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>tc-2.00.df-N.cr-Pln.dm-Hi.cp-95.CF6</v>
       </c>
       <c r="I53" t="str">
@@ -38398,7 +38542,7 @@
         <v>Pln</v>
       </c>
       <c r="N53" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>2.00</v>
       </c>
       <c r="P53">
@@ -38433,7 +38577,7 @@
         <v>dm-Hi</v>
       </c>
       <c r="AA53" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>cp-95</v>
       </c>
       <c r="AB53" t="str">
@@ -38445,11 +38589,11 @@
         <v>df-N</v>
       </c>
       <c r="AD53" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>cr-Pln</v>
       </c>
       <c r="AE53" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="1"/>
         <v>tc-2.00</v>
       </c>
     </row>
@@ -38463,7 +38607,7 @@
         <v>tc-0.10.df-Y.cr-Pln.dm-Lo.cp-00.CF1</v>
       </c>
       <c r="H54" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>tc-0.10.df-Y.cr-Pln.dm-Lo.cp-00.CF1</v>
       </c>
       <c r="I54" t="str">
@@ -38487,7 +38631,7 @@
         <v>Pln</v>
       </c>
       <c r="N54" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0.10</v>
       </c>
       <c r="P54">
@@ -38534,7 +38678,7 @@
         <v>df-Y</v>
       </c>
       <c r="AD54" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>cr-Pln</v>
       </c>
       <c r="AE54" t="str">
@@ -38552,7 +38696,7 @@
         <v>tc-0.10.df-Y.cr-Pln.dm-Hi.cp-00.CF1</v>
       </c>
       <c r="H55" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>tc-0.10.df-Y.cr-Pln.dm-Hi.cp-00.CF1</v>
       </c>
       <c r="I55" t="str">
@@ -38576,7 +38720,7 @@
         <v>Pln</v>
       </c>
       <c r="N55" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0.10</v>
       </c>
       <c r="P55">
@@ -38623,7 +38767,7 @@
         <v>df-Y</v>
       </c>
       <c r="AD55" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>cr-Pln</v>
       </c>
       <c r="AE55" t="str">
@@ -38641,7 +38785,7 @@
         <v>tc-0.10.df-Y.cr-Pln.dm-Lo.cp-95.CF1</v>
       </c>
       <c r="H56" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>tc-0.10.df-Y.cr-Pln.dm-Lo.cp-95.CF1</v>
       </c>
       <c r="I56" t="str">
@@ -38665,7 +38809,7 @@
         <v>Pln</v>
       </c>
       <c r="N56" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0.10</v>
       </c>
       <c r="P56">
@@ -38712,7 +38856,7 @@
         <v>df-Y</v>
       </c>
       <c r="AD56" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>cr-Pln</v>
       </c>
       <c r="AE56" t="str">
@@ -38730,7 +38874,7 @@
         <v>tc-0.10.df-Y.cr-Pln.dm-Hi.cp-95.CF1</v>
       </c>
       <c r="H57" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>tc-0.10.df-Y.cr-Pln.dm-Hi.cp-95.CF1</v>
       </c>
       <c r="I57" t="str">
@@ -38754,7 +38898,7 @@
         <v>Pln</v>
       </c>
       <c r="N57" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0.10</v>
       </c>
       <c r="P57">
@@ -38801,7 +38945,7 @@
         <v>df-Y</v>
       </c>
       <c r="AD57" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>cr-Pln</v>
       </c>
       <c r="AE57" t="str">
@@ -38819,7 +38963,7 @@
         <v>tc-0.10.df-N.cr-Pln.dm-Lo.cp-00.CF1</v>
       </c>
       <c r="H58" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>tc-0.10.df-N.cr-Pln.dm-Lo.cp-00.CF1</v>
       </c>
       <c r="I58" t="str">
@@ -38843,7 +38987,7 @@
         <v>Pln</v>
       </c>
       <c r="N58" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0.10</v>
       </c>
       <c r="P58">
@@ -38890,7 +39034,7 @@
         <v>df-N</v>
       </c>
       <c r="AD58" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>cr-Pln</v>
       </c>
       <c r="AE58" t="str">
@@ -38908,7 +39052,7 @@
         <v>tc-0.10.df-N.cr-Pln.dm-Hi.cp-00.CF1</v>
       </c>
       <c r="H59" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>tc-0.10.df-N.cr-Pln.dm-Hi.cp-00.CF1</v>
       </c>
       <c r="I59" t="str">
@@ -38932,7 +39076,7 @@
         <v>Pln</v>
       </c>
       <c r="N59" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0.10</v>
       </c>
       <c r="P59">
@@ -38979,7 +39123,7 @@
         <v>df-N</v>
       </c>
       <c r="AD59" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>cr-Pln</v>
       </c>
       <c r="AE59" t="str">
@@ -38997,7 +39141,7 @@
         <v>tc-0.10.df-N.cr-Pln.dm-Lo.cp-95.CF1</v>
       </c>
       <c r="H60" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>tc-0.10.df-N.cr-Pln.dm-Lo.cp-95.CF1</v>
       </c>
       <c r="I60" t="str">
@@ -39021,7 +39165,7 @@
         <v>Pln</v>
       </c>
       <c r="N60" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0.10</v>
       </c>
       <c r="P60">
@@ -39068,7 +39212,7 @@
         <v>df-N</v>
       </c>
       <c r="AD60" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>cr-Pln</v>
       </c>
       <c r="AE60" t="str">
@@ -39086,7 +39230,7 @@
         <v>tc-0.10.df-N.cr-Pln.dm-Hi.cp-95.CF1</v>
       </c>
       <c r="H61" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>tc-0.10.df-N.cr-Pln.dm-Hi.cp-95.CF1</v>
       </c>
       <c r="I61" t="str">
@@ -39110,7 +39254,7 @@
         <v>Pln</v>
       </c>
       <c r="N61" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0.10</v>
       </c>
       <c r="P61">
@@ -39157,7 +39301,7 @@
         <v>df-N</v>
       </c>
       <c r="AD61" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>cr-Pln</v>
       </c>
       <c r="AE61" t="str">
@@ -39175,7 +39319,7 @@
         <v>tc-0.10.df-Y.cr-Pln.dm-Lo.cp-00.CF6</v>
       </c>
       <c r="H62" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>tc-0.10.df-Y.cr-Pln.dm-Lo.cp-00.CF6</v>
       </c>
       <c r="I62" t="str">
@@ -39199,7 +39343,7 @@
         <v>Pln</v>
       </c>
       <c r="N62" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0.10</v>
       </c>
       <c r="P62">
@@ -39246,7 +39390,7 @@
         <v>df-Y</v>
       </c>
       <c r="AD62" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>cr-Pln</v>
       </c>
       <c r="AE62" t="str">
@@ -39264,7 +39408,7 @@
         <v>tc-0.10.df-Y.cr-Pln.dm-Hi.cp-00.CF6</v>
       </c>
       <c r="H63" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>tc-0.10.df-Y.cr-Pln.dm-Hi.cp-00.CF6</v>
       </c>
       <c r="I63" t="str">
@@ -39288,7 +39432,7 @@
         <v>Pln</v>
       </c>
       <c r="N63" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0.10</v>
       </c>
       <c r="P63">
@@ -39335,7 +39479,7 @@
         <v>df-Y</v>
       </c>
       <c r="AD63" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>cr-Pln</v>
       </c>
       <c r="AE63" t="str">
@@ -39353,7 +39497,7 @@
         <v>tc-0.10.df-Y.cr-Pln.dm-Lo.cp-95.CF6</v>
       </c>
       <c r="H64" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>tc-0.10.df-Y.cr-Pln.dm-Lo.cp-95.CF6</v>
       </c>
       <c r="I64" t="str">
@@ -39377,7 +39521,7 @@
         <v>Pln</v>
       </c>
       <c r="N64" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0.10</v>
       </c>
       <c r="P64">
@@ -39424,7 +39568,7 @@
         <v>df-Y</v>
       </c>
       <c r="AD64" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>cr-Pln</v>
       </c>
       <c r="AE64" t="str">
@@ -39442,7 +39586,7 @@
         <v>tc-0.10.df-Y.cr-Pln.dm-Hi.cp-95.CF6</v>
       </c>
       <c r="H65" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>tc-0.10.df-Y.cr-Pln.dm-Hi.cp-95.CF6</v>
       </c>
       <c r="I65" t="str">
@@ -39466,7 +39610,7 @@
         <v>Pln</v>
       </c>
       <c r="N65" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0.10</v>
       </c>
       <c r="P65">
@@ -39513,7 +39657,7 @@
         <v>df-Y</v>
       </c>
       <c r="AD65" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>cr-Pln</v>
       </c>
       <c r="AE65" t="str">
@@ -39531,7 +39675,7 @@
         <v>tc-0.10.df-N.cr-Pln.dm-Lo.cp-00.CF6</v>
       </c>
       <c r="H66" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>tc-0.10.df-N.cr-Pln.dm-Lo.cp-00.CF6</v>
       </c>
       <c r="I66" t="str">
@@ -39555,7 +39699,7 @@
         <v>Pln</v>
       </c>
       <c r="N66" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0.10</v>
       </c>
       <c r="P66">
@@ -39602,7 +39746,7 @@
         <v>df-N</v>
       </c>
       <c r="AD66" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>cr-Pln</v>
       </c>
       <c r="AE66" t="str">
@@ -39620,7 +39764,7 @@
         <v>tc-0.10.df-N.cr-Pln.dm-Hi.cp-00.CF6</v>
       </c>
       <c r="H67" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>tc-0.10.df-N.cr-Pln.dm-Hi.cp-00.CF6</v>
       </c>
       <c r="I67" t="str">
@@ -39644,7 +39788,7 @@
         <v>Pln</v>
       </c>
       <c r="N67" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0.10</v>
       </c>
       <c r="P67">
@@ -39691,7 +39835,7 @@
         <v>df-N</v>
       </c>
       <c r="AD67" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>cr-Pln</v>
       </c>
       <c r="AE67" t="str">
@@ -39709,7 +39853,7 @@
         <v>tc-0.10.df-N.cr-Pln.dm-Lo.cp-95.CF6</v>
       </c>
       <c r="H68" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>tc-0.10.df-N.cr-Pln.dm-Lo.cp-95.CF6</v>
       </c>
       <c r="I68" t="str">
@@ -39733,7 +39877,7 @@
         <v>Pln</v>
       </c>
       <c r="N68" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0.10</v>
       </c>
       <c r="P68">
@@ -39780,7 +39924,7 @@
         <v>df-N</v>
       </c>
       <c r="AD68" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>cr-Pln</v>
       </c>
       <c r="AE68" t="str">
@@ -39798,7 +39942,7 @@
         <v>tc-0.10.df-N.cr-Pln.dm-Hi.cp-95.CF6</v>
       </c>
       <c r="H69" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>tc-0.10.df-N.cr-Pln.dm-Hi.cp-95.CF6</v>
       </c>
       <c r="I69" t="str">
@@ -39822,7 +39966,7 @@
         <v>Pln</v>
       </c>
       <c r="N69" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0.10</v>
       </c>
       <c r="P69">
@@ -39869,7 +40013,7 @@
         <v>df-N</v>
       </c>
       <c r="AD69" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>cr-Pln</v>
       </c>
       <c r="AE69" t="str">
@@ -39884,11 +40028,11 @@
       </c>
       <c r="C70" t="str">
         <f t="shared" ref="C70:C133" si="38">H70</f>
-        <v>tc-0.10.df-Y.cr-Eco.dm-Lo.cp-00.CF1</v>
+        <v>tc-1.00.df-Y.cr-Eco.dm-Lo.cp-00.CF1</v>
       </c>
       <c r="H70" t="str">
         <f t="shared" ref="H70:H133" si="39">_xlfn.TEXTJOIN(".",TRUE,AE70,AC70:AD70)&amp;"."&amp;_xlfn.TEXTJOIN(".",TRUE,Z70:AB70)</f>
-        <v>tc-0.10.df-Y.cr-Eco.dm-Lo.cp-00.CF1</v>
+        <v>tc-1.00.df-Y.cr-Eco.dm-Lo.cp-00.CF1</v>
       </c>
       <c r="I70" t="str">
         <f t="shared" ref="I70:I133" si="40">S70</f>
@@ -39912,13 +40056,13 @@
       </c>
       <c r="N70" t="str">
         <f t="shared" ref="N70:N133" si="45">TEXT(X70,"0.00")</f>
-        <v>0.10</v>
+        <v>1.00</v>
       </c>
       <c r="P70">
         <v>5</v>
       </c>
       <c r="Q70" t="s">
-        <v>1171</v>
+        <v>1189</v>
       </c>
       <c r="R70">
         <v>65</v>
@@ -39939,7 +40083,7 @@
         <v>1172</v>
       </c>
       <c r="X70">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="Z70" t="str">
         <f t="shared" ref="Z70:Z133" si="46">S$1&amp;"-"&amp;S70</f>
@@ -39963,7 +40107,7 @@
       </c>
       <c r="AE70" t="str">
         <f t="shared" ref="AE70:AE133" si="51">X$1&amp;"-"&amp;TEXT(X70,"0.00")</f>
-        <v>tc-0.10</v>
+        <v>tc-1.00</v>
       </c>
     </row>
     <row r="71" spans="2:31">
@@ -39973,11 +40117,11 @@
       </c>
       <c r="C71" t="str">
         <f t="shared" si="38"/>
-        <v>tc-0.10.df-Y.cr-Eco.dm-Hi.cp-00.CF1</v>
+        <v>tc-1.00.df-Y.cr-Eco.dm-Hi.cp-00.CF1</v>
       </c>
       <c r="H71" t="str">
         <f t="shared" si="39"/>
-        <v>tc-0.10.df-Y.cr-Eco.dm-Hi.cp-00.CF1</v>
+        <v>tc-1.00.df-Y.cr-Eco.dm-Hi.cp-00.CF1</v>
       </c>
       <c r="I71" t="str">
         <f t="shared" si="40"/>
@@ -40001,13 +40145,13 @@
       </c>
       <c r="N71" t="str">
         <f t="shared" si="45"/>
-        <v>0.10</v>
+        <v>1.00</v>
       </c>
       <c r="P71">
         <v>5</v>
       </c>
       <c r="Q71" t="s">
-        <v>1173</v>
+        <v>1190</v>
       </c>
       <c r="R71">
         <v>66</v>
@@ -40028,7 +40172,7 @@
         <v>1172</v>
       </c>
       <c r="X71">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="Z71" t="str">
         <f t="shared" si="46"/>
@@ -40052,7 +40196,7 @@
       </c>
       <c r="AE71" t="str">
         <f t="shared" si="51"/>
-        <v>tc-0.10</v>
+        <v>tc-1.00</v>
       </c>
     </row>
     <row r="72" spans="2:31">
@@ -40062,11 +40206,11 @@
       </c>
       <c r="C72" t="str">
         <f t="shared" si="38"/>
-        <v>tc-0.10.df-Y.cr-Eco.dm-Lo.cp-95.CF1</v>
+        <v>tc-1.00.df-Y.cr-Eco.dm-Lo.cp-95.CF1</v>
       </c>
       <c r="H72" t="str">
         <f t="shared" si="39"/>
-        <v>tc-0.10.df-Y.cr-Eco.dm-Lo.cp-95.CF1</v>
+        <v>tc-1.00.df-Y.cr-Eco.dm-Lo.cp-95.CF1</v>
       </c>
       <c r="I72" t="str">
         <f t="shared" si="40"/>
@@ -40090,13 +40234,13 @@
       </c>
       <c r="N72" t="str">
         <f t="shared" si="45"/>
-        <v>0.10</v>
+        <v>1.00</v>
       </c>
       <c r="P72">
         <v>5</v>
       </c>
       <c r="Q72" t="s">
-        <v>1174</v>
+        <v>1191</v>
       </c>
       <c r="R72">
         <v>67</v>
@@ -40117,7 +40261,7 @@
         <v>1172</v>
       </c>
       <c r="X72">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="Z72" t="str">
         <f t="shared" si="46"/>
@@ -40141,7 +40285,7 @@
       </c>
       <c r="AE72" t="str">
         <f t="shared" si="51"/>
-        <v>tc-0.10</v>
+        <v>tc-1.00</v>
       </c>
     </row>
     <row r="73" spans="2:31">
@@ -40151,11 +40295,11 @@
       </c>
       <c r="C73" t="str">
         <f t="shared" si="38"/>
-        <v>tc-0.10.df-Y.cr-Eco.dm-Hi.cp-95.CF1</v>
+        <v>tc-1.00.df-Y.cr-Eco.dm-Hi.cp-95.CF1</v>
       </c>
       <c r="H73" t="str">
         <f t="shared" si="39"/>
-        <v>tc-0.10.df-Y.cr-Eco.dm-Hi.cp-95.CF1</v>
+        <v>tc-1.00.df-Y.cr-Eco.dm-Hi.cp-95.CF1</v>
       </c>
       <c r="I73" t="str">
         <f t="shared" si="40"/>
@@ -40179,13 +40323,13 @@
       </c>
       <c r="N73" t="str">
         <f t="shared" si="45"/>
-        <v>0.10</v>
+        <v>1.00</v>
       </c>
       <c r="P73">
         <v>5</v>
       </c>
       <c r="Q73" t="s">
-        <v>1175</v>
+        <v>1192</v>
       </c>
       <c r="R73">
         <v>68</v>
@@ -40206,7 +40350,7 @@
         <v>1172</v>
       </c>
       <c r="X73">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="Z73" t="str">
         <f t="shared" si="46"/>
@@ -40230,7 +40374,7 @@
       </c>
       <c r="AE73" t="str">
         <f t="shared" si="51"/>
-        <v>tc-0.10</v>
+        <v>tc-1.00</v>
       </c>
     </row>
     <row r="74" spans="2:31">
@@ -40240,11 +40384,11 @@
       </c>
       <c r="C74" t="str">
         <f t="shared" si="38"/>
-        <v>tc-0.10.df-N.cr-Eco.dm-Lo.cp-00.CF1</v>
+        <v>tc-1.00.df-N.cr-Eco.dm-Lo.cp-00.CF1</v>
       </c>
       <c r="H74" t="str">
         <f t="shared" si="39"/>
-        <v>tc-0.10.df-N.cr-Eco.dm-Lo.cp-00.CF1</v>
+        <v>tc-1.00.df-N.cr-Eco.dm-Lo.cp-00.CF1</v>
       </c>
       <c r="I74" t="str">
         <f t="shared" si="40"/>
@@ -40268,13 +40412,13 @@
       </c>
       <c r="N74" t="str">
         <f t="shared" si="45"/>
-        <v>0.10</v>
+        <v>1.00</v>
       </c>
       <c r="P74">
         <v>5</v>
       </c>
       <c r="Q74" t="s">
-        <v>1176</v>
+        <v>1193</v>
       </c>
       <c r="R74">
         <v>69</v>
@@ -40295,7 +40439,7 @@
         <v>1172</v>
       </c>
       <c r="X74">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="Z74" t="str">
         <f t="shared" si="46"/>
@@ -40319,7 +40463,7 @@
       </c>
       <c r="AE74" t="str">
         <f t="shared" si="51"/>
-        <v>tc-0.10</v>
+        <v>tc-1.00</v>
       </c>
     </row>
     <row r="75" spans="2:31">
@@ -40329,11 +40473,11 @@
       </c>
       <c r="C75" t="str">
         <f t="shared" si="38"/>
-        <v>tc-0.10.df-N.cr-Eco.dm-Hi.cp-00.CF1</v>
+        <v>tc-1.00.df-N.cr-Eco.dm-Hi.cp-00.CF1</v>
       </c>
       <c r="H75" t="str">
         <f t="shared" si="39"/>
-        <v>tc-0.10.df-N.cr-Eco.dm-Hi.cp-00.CF1</v>
+        <v>tc-1.00.df-N.cr-Eco.dm-Hi.cp-00.CF1</v>
       </c>
       <c r="I75" t="str">
         <f t="shared" si="40"/>
@@ -40357,13 +40501,13 @@
       </c>
       <c r="N75" t="str">
         <f t="shared" si="45"/>
-        <v>0.10</v>
+        <v>1.00</v>
       </c>
       <c r="P75">
         <v>5</v>
       </c>
       <c r="Q75" t="s">
-        <v>1177</v>
+        <v>1194</v>
       </c>
       <c r="R75">
         <v>70</v>
@@ -40384,7 +40528,7 @@
         <v>1172</v>
       </c>
       <c r="X75">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="Z75" t="str">
         <f t="shared" si="46"/>
@@ -40408,7 +40552,7 @@
       </c>
       <c r="AE75" t="str">
         <f t="shared" si="51"/>
-        <v>tc-0.10</v>
+        <v>tc-1.00</v>
       </c>
     </row>
     <row r="76" spans="2:31">
@@ -40418,11 +40562,11 @@
       </c>
       <c r="C76" t="str">
         <f t="shared" si="38"/>
-        <v>tc-0.10.df-N.cr-Eco.dm-Lo.cp-95.CF1</v>
+        <v>tc-1.00.df-N.cr-Eco.dm-Lo.cp-95.CF1</v>
       </c>
       <c r="H76" t="str">
         <f t="shared" si="39"/>
-        <v>tc-0.10.df-N.cr-Eco.dm-Lo.cp-95.CF1</v>
+        <v>tc-1.00.df-N.cr-Eco.dm-Lo.cp-95.CF1</v>
       </c>
       <c r="I76" t="str">
         <f t="shared" si="40"/>
@@ -40446,13 +40590,13 @@
       </c>
       <c r="N76" t="str">
         <f t="shared" si="45"/>
-        <v>0.10</v>
+        <v>1.00</v>
       </c>
       <c r="P76">
         <v>5</v>
       </c>
       <c r="Q76" t="s">
-        <v>1178</v>
+        <v>1195</v>
       </c>
       <c r="R76">
         <v>71</v>
@@ -40473,7 +40617,7 @@
         <v>1172</v>
       </c>
       <c r="X76">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="Z76" t="str">
         <f t="shared" si="46"/>
@@ -40497,7 +40641,7 @@
       </c>
       <c r="AE76" t="str">
         <f t="shared" si="51"/>
-        <v>tc-0.10</v>
+        <v>tc-1.00</v>
       </c>
     </row>
     <row r="77" spans="2:31">
@@ -40507,11 +40651,11 @@
       </c>
       <c r="C77" t="str">
         <f t="shared" si="38"/>
-        <v>tc-0.10.df-N.cr-Eco.dm-Hi.cp-95.CF1</v>
+        <v>tc-1.00.df-N.cr-Eco.dm-Hi.cp-95.CF1</v>
       </c>
       <c r="H77" t="str">
         <f t="shared" si="39"/>
-        <v>tc-0.10.df-N.cr-Eco.dm-Hi.cp-95.CF1</v>
+        <v>tc-1.00.df-N.cr-Eco.dm-Hi.cp-95.CF1</v>
       </c>
       <c r="I77" t="str">
         <f t="shared" si="40"/>
@@ -40535,13 +40679,13 @@
       </c>
       <c r="N77" t="str">
         <f t="shared" si="45"/>
-        <v>0.10</v>
+        <v>1.00</v>
       </c>
       <c r="P77">
         <v>5</v>
       </c>
       <c r="Q77" t="s">
-        <v>1179</v>
+        <v>1196</v>
       </c>
       <c r="R77">
         <v>72</v>
@@ -40562,7 +40706,7 @@
         <v>1172</v>
       </c>
       <c r="X77">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="Z77" t="str">
         <f t="shared" si="46"/>
@@ -40586,7 +40730,7 @@
       </c>
       <c r="AE77" t="str">
         <f t="shared" si="51"/>
-        <v>tc-0.10</v>
+        <v>tc-1.00</v>
       </c>
     </row>
     <row r="78" spans="2:31">
@@ -40596,11 +40740,11 @@
       </c>
       <c r="C78" t="str">
         <f t="shared" si="38"/>
-        <v>tc-0.10.df-Y.cr-Eco.dm-Lo.cp-00.CF6</v>
+        <v>tc-1.00.df-Y.cr-Eco.dm-Lo.cp-00.CF6</v>
       </c>
       <c r="H78" t="str">
         <f t="shared" si="39"/>
-        <v>tc-0.10.df-Y.cr-Eco.dm-Lo.cp-00.CF6</v>
+        <v>tc-1.00.df-Y.cr-Eco.dm-Lo.cp-00.CF6</v>
       </c>
       <c r="I78" t="str">
         <f t="shared" si="40"/>
@@ -40624,13 +40768,13 @@
       </c>
       <c r="N78" t="str">
         <f t="shared" si="45"/>
-        <v>0.10</v>
+        <v>1.00</v>
       </c>
       <c r="P78">
         <v>5</v>
       </c>
       <c r="Q78" t="s">
-        <v>1180</v>
+        <v>1197</v>
       </c>
       <c r="R78">
         <v>73</v>
@@ -40651,7 +40795,7 @@
         <v>1172</v>
       </c>
       <c r="X78">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="Z78" t="str">
         <f t="shared" si="46"/>
@@ -40675,7 +40819,7 @@
       </c>
       <c r="AE78" t="str">
         <f t="shared" si="51"/>
-        <v>tc-0.10</v>
+        <v>tc-1.00</v>
       </c>
     </row>
     <row r="79" spans="2:31">
@@ -40685,11 +40829,11 @@
       </c>
       <c r="C79" t="str">
         <f t="shared" si="38"/>
-        <v>tc-0.10.df-Y.cr-Eco.dm-Hi.cp-00.CF6</v>
+        <v>tc-1.00.df-Y.cr-Eco.dm-Hi.cp-00.CF6</v>
       </c>
       <c r="H79" t="str">
         <f t="shared" si="39"/>
-        <v>tc-0.10.df-Y.cr-Eco.dm-Hi.cp-00.CF6</v>
+        <v>tc-1.00.df-Y.cr-Eco.dm-Hi.cp-00.CF6</v>
       </c>
       <c r="I79" t="str">
         <f t="shared" si="40"/>
@@ -40713,13 +40857,13 @@
       </c>
       <c r="N79" t="str">
         <f t="shared" si="45"/>
-        <v>0.10</v>
+        <v>1.00</v>
       </c>
       <c r="P79">
         <v>5</v>
       </c>
       <c r="Q79" t="s">
-        <v>1181</v>
+        <v>1198</v>
       </c>
       <c r="R79">
         <v>74</v>
@@ -40740,7 +40884,7 @@
         <v>1172</v>
       </c>
       <c r="X79">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="Z79" t="str">
         <f t="shared" si="46"/>
@@ -40764,7 +40908,7 @@
       </c>
       <c r="AE79" t="str">
         <f t="shared" si="51"/>
-        <v>tc-0.10</v>
+        <v>tc-1.00</v>
       </c>
     </row>
     <row r="80" spans="2:31">
@@ -40774,11 +40918,11 @@
       </c>
       <c r="C80" t="str">
         <f t="shared" si="38"/>
-        <v>tc-0.10.df-Y.cr-Eco.dm-Lo.cp-95.CF6</v>
+        <v>tc-1.00.df-Y.cr-Eco.dm-Lo.cp-95.CF6</v>
       </c>
       <c r="H80" t="str">
         <f t="shared" si="39"/>
-        <v>tc-0.10.df-Y.cr-Eco.dm-Lo.cp-95.CF6</v>
+        <v>tc-1.00.df-Y.cr-Eco.dm-Lo.cp-95.CF6</v>
       </c>
       <c r="I80" t="str">
         <f t="shared" si="40"/>
@@ -40802,13 +40946,13 @@
       </c>
       <c r="N80" t="str">
         <f t="shared" si="45"/>
-        <v>0.10</v>
+        <v>1.00</v>
       </c>
       <c r="P80">
         <v>5</v>
       </c>
       <c r="Q80" t="s">
-        <v>1182</v>
+        <v>1199</v>
       </c>
       <c r="R80">
         <v>75</v>
@@ -40829,7 +40973,7 @@
         <v>1172</v>
       </c>
       <c r="X80">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="Z80" t="str">
         <f t="shared" si="46"/>
@@ -40853,7 +40997,7 @@
       </c>
       <c r="AE80" t="str">
         <f t="shared" si="51"/>
-        <v>tc-0.10</v>
+        <v>tc-1.00</v>
       </c>
     </row>
     <row r="81" spans="2:31">
@@ -40863,11 +41007,11 @@
       </c>
       <c r="C81" t="str">
         <f t="shared" si="38"/>
-        <v>tc-0.10.df-Y.cr-Eco.dm-Hi.cp-95.CF6</v>
+        <v>tc-1.00.df-Y.cr-Eco.dm-Hi.cp-95.CF6</v>
       </c>
       <c r="H81" t="str">
         <f t="shared" si="39"/>
-        <v>tc-0.10.df-Y.cr-Eco.dm-Hi.cp-95.CF6</v>
+        <v>tc-1.00.df-Y.cr-Eco.dm-Hi.cp-95.CF6</v>
       </c>
       <c r="I81" t="str">
         <f t="shared" si="40"/>
@@ -40891,13 +41035,13 @@
       </c>
       <c r="N81" t="str">
         <f t="shared" si="45"/>
-        <v>0.10</v>
+        <v>1.00</v>
       </c>
       <c r="P81">
         <v>5</v>
       </c>
       <c r="Q81" t="s">
-        <v>1183</v>
+        <v>1200</v>
       </c>
       <c r="R81">
         <v>76</v>
@@ -40918,7 +41062,7 @@
         <v>1172</v>
       </c>
       <c r="X81">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="Z81" t="str">
         <f t="shared" si="46"/>
@@ -40942,7 +41086,7 @@
       </c>
       <c r="AE81" t="str">
         <f t="shared" si="51"/>
-        <v>tc-0.10</v>
+        <v>tc-1.00</v>
       </c>
     </row>
     <row r="82" spans="2:31">
@@ -40952,11 +41096,11 @@
       </c>
       <c r="C82" t="str">
         <f t="shared" si="38"/>
-        <v>tc-0.10.df-N.cr-Eco.dm-Lo.cp-00.CF6</v>
+        <v>tc-1.00.df-N.cr-Eco.dm-Lo.cp-00.CF6</v>
       </c>
       <c r="H82" t="str">
         <f t="shared" si="39"/>
-        <v>tc-0.10.df-N.cr-Eco.dm-Lo.cp-00.CF6</v>
+        <v>tc-1.00.df-N.cr-Eco.dm-Lo.cp-00.CF6</v>
       </c>
       <c r="I82" t="str">
         <f t="shared" si="40"/>
@@ -40980,13 +41124,13 @@
       </c>
       <c r="N82" t="str">
         <f t="shared" si="45"/>
-        <v>0.10</v>
+        <v>1.00</v>
       </c>
       <c r="P82">
         <v>5</v>
       </c>
       <c r="Q82" t="s">
-        <v>1184</v>
+        <v>1201</v>
       </c>
       <c r="R82">
         <v>77</v>
@@ -41007,7 +41151,7 @@
         <v>1172</v>
       </c>
       <c r="X82">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="Z82" t="str">
         <f t="shared" si="46"/>
@@ -41031,7 +41175,7 @@
       </c>
       <c r="AE82" t="str">
         <f t="shared" si="51"/>
-        <v>tc-0.10</v>
+        <v>tc-1.00</v>
       </c>
     </row>
     <row r="83" spans="2:31">
@@ -41041,11 +41185,11 @@
       </c>
       <c r="C83" t="str">
         <f t="shared" si="38"/>
-        <v>tc-0.10.df-N.cr-Eco.dm-Hi.cp-00.CF6</v>
+        <v>tc-1.00.df-N.cr-Eco.dm-Hi.cp-00.CF6</v>
       </c>
       <c r="H83" t="str">
         <f t="shared" si="39"/>
-        <v>tc-0.10.df-N.cr-Eco.dm-Hi.cp-00.CF6</v>
+        <v>tc-1.00.df-N.cr-Eco.dm-Hi.cp-00.CF6</v>
       </c>
       <c r="I83" t="str">
         <f t="shared" si="40"/>
@@ -41069,13 +41213,13 @@
       </c>
       <c r="N83" t="str">
         <f t="shared" si="45"/>
-        <v>0.10</v>
+        <v>1.00</v>
       </c>
       <c r="P83">
         <v>5</v>
       </c>
       <c r="Q83" t="s">
-        <v>1185</v>
+        <v>1202</v>
       </c>
       <c r="R83">
         <v>78</v>
@@ -41096,7 +41240,7 @@
         <v>1172</v>
       </c>
       <c r="X83">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="Z83" t="str">
         <f t="shared" si="46"/>
@@ -41120,7 +41264,7 @@
       </c>
       <c r="AE83" t="str">
         <f t="shared" si="51"/>
-        <v>tc-0.10</v>
+        <v>tc-1.00</v>
       </c>
     </row>
     <row r="84" spans="2:31">
@@ -41130,11 +41274,11 @@
       </c>
       <c r="C84" t="str">
         <f t="shared" si="38"/>
-        <v>tc-0.10.df-N.cr-Eco.dm-Lo.cp-95.CF6</v>
+        <v>tc-1.00.df-N.cr-Eco.dm-Lo.cp-95.CF6</v>
       </c>
       <c r="H84" t="str">
         <f t="shared" si="39"/>
-        <v>tc-0.10.df-N.cr-Eco.dm-Lo.cp-95.CF6</v>
+        <v>tc-1.00.df-N.cr-Eco.dm-Lo.cp-95.CF6</v>
       </c>
       <c r="I84" t="str">
         <f t="shared" si="40"/>
@@ -41158,13 +41302,13 @@
       </c>
       <c r="N84" t="str">
         <f t="shared" si="45"/>
-        <v>0.10</v>
+        <v>1.00</v>
       </c>
       <c r="P84">
         <v>5</v>
       </c>
       <c r="Q84" t="s">
-        <v>1186</v>
+        <v>1203</v>
       </c>
       <c r="R84">
         <v>79</v>
@@ -41185,7 +41329,7 @@
         <v>1172</v>
       </c>
       <c r="X84">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="Z84" t="str">
         <f t="shared" si="46"/>
@@ -41209,7 +41353,7 @@
       </c>
       <c r="AE84" t="str">
         <f t="shared" si="51"/>
-        <v>tc-0.10</v>
+        <v>tc-1.00</v>
       </c>
     </row>
     <row r="85" spans="2:31">
@@ -41219,11 +41363,11 @@
       </c>
       <c r="C85" t="str">
         <f t="shared" si="38"/>
-        <v>tc-0.10.df-N.cr-Eco.dm-Hi.cp-95.CF6</v>
+        <v>tc-1.00.df-N.cr-Eco.dm-Hi.cp-95.CF6</v>
       </c>
       <c r="H85" t="str">
         <f t="shared" si="39"/>
-        <v>tc-0.10.df-N.cr-Eco.dm-Hi.cp-95.CF6</v>
+        <v>tc-1.00.df-N.cr-Eco.dm-Hi.cp-95.CF6</v>
       </c>
       <c r="I85" t="str">
         <f t="shared" si="40"/>
@@ -41247,13 +41391,13 @@
       </c>
       <c r="N85" t="str">
         <f t="shared" si="45"/>
-        <v>0.10</v>
+        <v>1.00</v>
       </c>
       <c r="P85">
         <v>5</v>
       </c>
       <c r="Q85" t="s">
-        <v>1187</v>
+        <v>1204</v>
       </c>
       <c r="R85">
         <v>80</v>
@@ -41274,7 +41418,7 @@
         <v>1172</v>
       </c>
       <c r="X85">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="Z85" t="str">
         <f t="shared" si="46"/>
@@ -41298,7 +41442,7 @@
       </c>
       <c r="AE85" t="str">
         <f t="shared" si="51"/>
-        <v>tc-0.10</v>
+        <v>tc-1.00</v>
       </c>
     </row>
     <row r="86" spans="2:31">
@@ -41308,11 +41452,11 @@
       </c>
       <c r="C86" t="str">
         <f t="shared" si="38"/>
-        <v>tc-0.10.df-Y.cr-Eco.dm-Lo.cp-00.CF1</v>
+        <v>tc-0.25.df-Y.cr-Eco.dm-Lo.cp-00.CF1</v>
       </c>
       <c r="H86" t="str">
         <f t="shared" si="39"/>
-        <v>tc-0.10.df-Y.cr-Eco.dm-Lo.cp-00.CF1</v>
+        <v>tc-0.25.df-Y.cr-Eco.dm-Lo.cp-00.CF1</v>
       </c>
       <c r="I86" t="str">
         <f t="shared" si="40"/>
@@ -41336,13 +41480,13 @@
       </c>
       <c r="N86" t="str">
         <f t="shared" si="45"/>
-        <v>0.10</v>
+        <v>0.25</v>
       </c>
       <c r="P86">
         <v>5</v>
       </c>
       <c r="Q86" t="s">
-        <v>1171</v>
+        <v>1205</v>
       </c>
       <c r="R86">
         <v>81</v>
@@ -41363,7 +41507,7 @@
         <v>1172</v>
       </c>
       <c r="X86">
-        <v>0.1</v>
+        <v>0.25</v>
       </c>
       <c r="Z86" t="str">
         <f t="shared" si="46"/>
@@ -41387,7 +41531,7 @@
       </c>
       <c r="AE86" t="str">
         <f t="shared" si="51"/>
-        <v>tc-0.10</v>
+        <v>tc-0.25</v>
       </c>
     </row>
     <row r="87" spans="2:31">
@@ -41397,11 +41541,11 @@
       </c>
       <c r="C87" t="str">
         <f t="shared" si="38"/>
-        <v>tc-0.10.df-Y.cr-Eco.dm-Hi.cp-00.CF1</v>
+        <v>tc-0.25.df-Y.cr-Eco.dm-Hi.cp-00.CF1</v>
       </c>
       <c r="H87" t="str">
         <f t="shared" si="39"/>
-        <v>tc-0.10.df-Y.cr-Eco.dm-Hi.cp-00.CF1</v>
+        <v>tc-0.25.df-Y.cr-Eco.dm-Hi.cp-00.CF1</v>
       </c>
       <c r="I87" t="str">
         <f t="shared" si="40"/>
@@ -41425,13 +41569,13 @@
       </c>
       <c r="N87" t="str">
         <f t="shared" si="45"/>
-        <v>0.10</v>
+        <v>0.25</v>
       </c>
       <c r="P87">
         <v>5</v>
       </c>
       <c r="Q87" t="s">
-        <v>1173</v>
+        <v>1206</v>
       </c>
       <c r="R87">
         <v>82</v>
@@ -41452,7 +41596,7 @@
         <v>1172</v>
       </c>
       <c r="X87">
-        <v>0.1</v>
+        <v>0.25</v>
       </c>
       <c r="Z87" t="str">
         <f t="shared" si="46"/>
@@ -41476,7 +41620,7 @@
       </c>
       <c r="AE87" t="str">
         <f t="shared" si="51"/>
-        <v>tc-0.10</v>
+        <v>tc-0.25</v>
       </c>
     </row>
     <row r="88" spans="2:31">
@@ -41486,11 +41630,11 @@
       </c>
       <c r="C88" t="str">
         <f t="shared" si="38"/>
-        <v>tc-0.10.df-Y.cr-Eco.dm-Lo.cp-95.CF1</v>
+        <v>tc-0.25.df-Y.cr-Eco.dm-Lo.cp-95.CF1</v>
       </c>
       <c r="H88" t="str">
         <f t="shared" si="39"/>
-        <v>tc-0.10.df-Y.cr-Eco.dm-Lo.cp-95.CF1</v>
+        <v>tc-0.25.df-Y.cr-Eco.dm-Lo.cp-95.CF1</v>
       </c>
       <c r="I88" t="str">
         <f t="shared" si="40"/>
@@ -41514,13 +41658,13 @@
       </c>
       <c r="N88" t="str">
         <f t="shared" si="45"/>
-        <v>0.10</v>
+        <v>0.25</v>
       </c>
       <c r="P88">
         <v>5</v>
       </c>
       <c r="Q88" t="s">
-        <v>1174</v>
+        <v>1207</v>
       </c>
       <c r="R88">
         <v>83</v>
@@ -41541,7 +41685,7 @@
         <v>1172</v>
       </c>
       <c r="X88">
-        <v>0.1</v>
+        <v>0.25</v>
       </c>
       <c r="Z88" t="str">
         <f t="shared" si="46"/>
@@ -41565,7 +41709,7 @@
       </c>
       <c r="AE88" t="str">
         <f t="shared" si="51"/>
-        <v>tc-0.10</v>
+        <v>tc-0.25</v>
       </c>
     </row>
     <row r="89" spans="2:31">
@@ -41575,11 +41719,11 @@
       </c>
       <c r="C89" t="str">
         <f t="shared" si="38"/>
-        <v>tc-0.10.df-Y.cr-Eco.dm-Hi.cp-95.CF1</v>
+        <v>tc-0.25.df-Y.cr-Eco.dm-Hi.cp-95.CF1</v>
       </c>
       <c r="H89" t="str">
         <f t="shared" si="39"/>
-        <v>tc-0.10.df-Y.cr-Eco.dm-Hi.cp-95.CF1</v>
+        <v>tc-0.25.df-Y.cr-Eco.dm-Hi.cp-95.CF1</v>
       </c>
       <c r="I89" t="str">
         <f t="shared" si="40"/>
@@ -41603,13 +41747,13 @@
       </c>
       <c r="N89" t="str">
         <f t="shared" si="45"/>
-        <v>0.10</v>
+        <v>0.25</v>
       </c>
       <c r="P89">
         <v>5</v>
       </c>
       <c r="Q89" t="s">
-        <v>1175</v>
+        <v>1208</v>
       </c>
       <c r="R89">
         <v>84</v>
@@ -41630,7 +41774,7 @@
         <v>1172</v>
       </c>
       <c r="X89">
-        <v>0.1</v>
+        <v>0.25</v>
       </c>
       <c r="Z89" t="str">
         <f t="shared" si="46"/>
@@ -41654,7 +41798,7 @@
       </c>
       <c r="AE89" t="str">
         <f t="shared" si="51"/>
-        <v>tc-0.10</v>
+        <v>tc-0.25</v>
       </c>
     </row>
     <row r="90" spans="2:31">
@@ -41664,11 +41808,11 @@
       </c>
       <c r="C90" t="str">
         <f t="shared" si="38"/>
-        <v>tc-0.10.df-N.cr-Eco.dm-Lo.cp-00.CF1</v>
+        <v>tc-0.25.df-N.cr-Eco.dm-Lo.cp-00.CF1</v>
       </c>
       <c r="H90" t="str">
         <f t="shared" si="39"/>
-        <v>tc-0.10.df-N.cr-Eco.dm-Lo.cp-00.CF1</v>
+        <v>tc-0.25.df-N.cr-Eco.dm-Lo.cp-00.CF1</v>
       </c>
       <c r="I90" t="str">
         <f t="shared" si="40"/>
@@ -41692,13 +41836,13 @@
       </c>
       <c r="N90" t="str">
         <f t="shared" si="45"/>
-        <v>0.10</v>
+        <v>0.25</v>
       </c>
       <c r="P90">
         <v>5</v>
       </c>
       <c r="Q90" t="s">
-        <v>1176</v>
+        <v>1209</v>
       </c>
       <c r="R90">
         <v>85</v>
@@ -41719,7 +41863,7 @@
         <v>1172</v>
       </c>
       <c r="X90">
-        <v>0.1</v>
+        <v>0.25</v>
       </c>
       <c r="Z90" t="str">
         <f t="shared" si="46"/>
@@ -41743,7 +41887,7 @@
       </c>
       <c r="AE90" t="str">
         <f t="shared" si="51"/>
-        <v>tc-0.10</v>
+        <v>tc-0.25</v>
       </c>
     </row>
     <row r="91" spans="2:31">
@@ -41753,11 +41897,11 @@
       </c>
       <c r="C91" t="str">
         <f t="shared" si="38"/>
-        <v>tc-0.10.df-N.cr-Eco.dm-Hi.cp-00.CF1</v>
+        <v>tc-0.25.df-N.cr-Eco.dm-Hi.cp-00.CF1</v>
       </c>
       <c r="H91" t="str">
         <f t="shared" si="39"/>
-        <v>tc-0.10.df-N.cr-Eco.dm-Hi.cp-00.CF1</v>
+        <v>tc-0.25.df-N.cr-Eco.dm-Hi.cp-00.CF1</v>
       </c>
       <c r="I91" t="str">
         <f t="shared" si="40"/>
@@ -41781,13 +41925,13 @@
       </c>
       <c r="N91" t="str">
         <f t="shared" si="45"/>
-        <v>0.10</v>
+        <v>0.25</v>
       </c>
       <c r="P91">
         <v>5</v>
       </c>
       <c r="Q91" t="s">
-        <v>1177</v>
+        <v>1210</v>
       </c>
       <c r="R91">
         <v>86</v>
@@ -41808,7 +41952,7 @@
         <v>1172</v>
       </c>
       <c r="X91">
-        <v>0.1</v>
+        <v>0.25</v>
       </c>
       <c r="Z91" t="str">
         <f t="shared" si="46"/>
@@ -41832,7 +41976,7 @@
       </c>
       <c r="AE91" t="str">
         <f t="shared" si="51"/>
-        <v>tc-0.10</v>
+        <v>tc-0.25</v>
       </c>
     </row>
     <row r="92" spans="2:31">
@@ -41842,11 +41986,11 @@
       </c>
       <c r="C92" t="str">
         <f t="shared" si="38"/>
-        <v>tc-0.10.df-N.cr-Eco.dm-Lo.cp-95.CF1</v>
+        <v>tc-0.25.df-N.cr-Eco.dm-Lo.cp-95.CF1</v>
       </c>
       <c r="H92" t="str">
         <f t="shared" si="39"/>
-        <v>tc-0.10.df-N.cr-Eco.dm-Lo.cp-95.CF1</v>
+        <v>tc-0.25.df-N.cr-Eco.dm-Lo.cp-95.CF1</v>
       </c>
       <c r="I92" t="str">
         <f t="shared" si="40"/>
@@ -41870,13 +42014,13 @@
       </c>
       <c r="N92" t="str">
         <f t="shared" si="45"/>
-        <v>0.10</v>
+        <v>0.25</v>
       </c>
       <c r="P92">
         <v>5</v>
       </c>
       <c r="Q92" t="s">
-        <v>1178</v>
+        <v>1211</v>
       </c>
       <c r="R92">
         <v>87</v>
@@ -41897,7 +42041,7 @@
         <v>1172</v>
       </c>
       <c r="X92">
-        <v>0.1</v>
+        <v>0.25</v>
       </c>
       <c r="Z92" t="str">
         <f t="shared" si="46"/>
@@ -41921,7 +42065,7 @@
       </c>
       <c r="AE92" t="str">
         <f t="shared" si="51"/>
-        <v>tc-0.10</v>
+        <v>tc-0.25</v>
       </c>
     </row>
     <row r="93" spans="2:31">
@@ -41931,11 +42075,11 @@
       </c>
       <c r="C93" t="str">
         <f t="shared" si="38"/>
-        <v>tc-0.10.df-N.cr-Eco.dm-Hi.cp-95.CF1</v>
+        <v>tc-0.25.df-N.cr-Eco.dm-Hi.cp-95.CF1</v>
       </c>
       <c r="H93" t="str">
         <f t="shared" si="39"/>
-        <v>tc-0.10.df-N.cr-Eco.dm-Hi.cp-95.CF1</v>
+        <v>tc-0.25.df-N.cr-Eco.dm-Hi.cp-95.CF1</v>
       </c>
       <c r="I93" t="str">
         <f t="shared" si="40"/>
@@ -41959,13 +42103,13 @@
       </c>
       <c r="N93" t="str">
         <f t="shared" si="45"/>
-        <v>0.10</v>
+        <v>0.25</v>
       </c>
       <c r="P93">
         <v>5</v>
       </c>
       <c r="Q93" t="s">
-        <v>1179</v>
+        <v>1212</v>
       </c>
       <c r="R93">
         <v>88</v>
@@ -41986,7 +42130,7 @@
         <v>1172</v>
       </c>
       <c r="X93">
-        <v>0.1</v>
+        <v>0.25</v>
       </c>
       <c r="Z93" t="str">
         <f t="shared" si="46"/>
@@ -42010,7 +42154,7 @@
       </c>
       <c r="AE93" t="str">
         <f t="shared" si="51"/>
-        <v>tc-0.10</v>
+        <v>tc-0.25</v>
       </c>
     </row>
     <row r="94" spans="2:31">
@@ -42020,11 +42164,11 @@
       </c>
       <c r="C94" t="str">
         <f t="shared" si="38"/>
-        <v>tc-0.10.df-Y.cr-Eco.dm-Lo.cp-00.CF6</v>
+        <v>tc-0.25.df-Y.cr-Eco.dm-Lo.cp-00.CF6</v>
       </c>
       <c r="H94" t="str">
         <f t="shared" si="39"/>
-        <v>tc-0.10.df-Y.cr-Eco.dm-Lo.cp-00.CF6</v>
+        <v>tc-0.25.df-Y.cr-Eco.dm-Lo.cp-00.CF6</v>
       </c>
       <c r="I94" t="str">
         <f t="shared" si="40"/>
@@ -42048,13 +42192,13 @@
       </c>
       <c r="N94" t="str">
         <f t="shared" si="45"/>
-        <v>0.10</v>
+        <v>0.25</v>
       </c>
       <c r="P94">
         <v>5</v>
       </c>
       <c r="Q94" t="s">
-        <v>1180</v>
+        <v>1213</v>
       </c>
       <c r="R94">
         <v>89</v>
@@ -42075,7 +42219,7 @@
         <v>1172</v>
       </c>
       <c r="X94">
-        <v>0.1</v>
+        <v>0.25</v>
       </c>
       <c r="Z94" t="str">
         <f t="shared" si="46"/>
@@ -42099,7 +42243,7 @@
       </c>
       <c r="AE94" t="str">
         <f t="shared" si="51"/>
-        <v>tc-0.10</v>
+        <v>tc-0.25</v>
       </c>
     </row>
     <row r="95" spans="2:31">
@@ -42109,11 +42253,11 @@
       </c>
       <c r="C95" t="str">
         <f t="shared" si="38"/>
-        <v>tc-0.10.df-Y.cr-Eco.dm-Hi.cp-00.CF6</v>
+        <v>tc-0.25.df-Y.cr-Eco.dm-Hi.cp-00.CF6</v>
       </c>
       <c r="H95" t="str">
         <f t="shared" si="39"/>
-        <v>tc-0.10.df-Y.cr-Eco.dm-Hi.cp-00.CF6</v>
+        <v>tc-0.25.df-Y.cr-Eco.dm-Hi.cp-00.CF6</v>
       </c>
       <c r="I95" t="str">
         <f t="shared" si="40"/>
@@ -42137,13 +42281,13 @@
       </c>
       <c r="N95" t="str">
         <f t="shared" si="45"/>
-        <v>0.10</v>
+        <v>0.25</v>
       </c>
       <c r="P95">
         <v>5</v>
       </c>
       <c r="Q95" t="s">
-        <v>1181</v>
+        <v>1214</v>
       </c>
       <c r="R95">
         <v>90</v>
@@ -42164,7 +42308,7 @@
         <v>1172</v>
       </c>
       <c r="X95">
-        <v>0.1</v>
+        <v>0.25</v>
       </c>
       <c r="Z95" t="str">
         <f t="shared" si="46"/>
@@ -42188,7 +42332,7 @@
       </c>
       <c r="AE95" t="str">
         <f t="shared" si="51"/>
-        <v>tc-0.10</v>
+        <v>tc-0.25</v>
       </c>
     </row>
     <row r="96" spans="2:31">
@@ -42198,11 +42342,11 @@
       </c>
       <c r="C96" t="str">
         <f t="shared" si="38"/>
-        <v>tc-0.10.df-Y.cr-Eco.dm-Lo.cp-95.CF6</v>
+        <v>tc-0.25.df-Y.cr-Eco.dm-Lo.cp-95.CF6</v>
       </c>
       <c r="H96" t="str">
         <f t="shared" si="39"/>
-        <v>tc-0.10.df-Y.cr-Eco.dm-Lo.cp-95.CF6</v>
+        <v>tc-0.25.df-Y.cr-Eco.dm-Lo.cp-95.CF6</v>
       </c>
       <c r="I96" t="str">
         <f t="shared" si="40"/>
@@ -42226,13 +42370,13 @@
       </c>
       <c r="N96" t="str">
         <f t="shared" si="45"/>
-        <v>0.10</v>
+        <v>0.25</v>
       </c>
       <c r="P96">
         <v>5</v>
       </c>
       <c r="Q96" t="s">
-        <v>1182</v>
+        <v>1215</v>
       </c>
       <c r="R96">
         <v>91</v>
@@ -42253,7 +42397,7 @@
         <v>1172</v>
       </c>
       <c r="X96">
-        <v>0.1</v>
+        <v>0.25</v>
       </c>
       <c r="Z96" t="str">
         <f t="shared" si="46"/>
@@ -42277,7 +42421,7 @@
       </c>
       <c r="AE96" t="str">
         <f t="shared" si="51"/>
-        <v>tc-0.10</v>
+        <v>tc-0.25</v>
       </c>
     </row>
     <row r="97" spans="2:31">
@@ -42287,11 +42431,11 @@
       </c>
       <c r="C97" t="str">
         <f t="shared" si="38"/>
-        <v>tc-0.10.df-Y.cr-Eco.dm-Hi.cp-95.CF6</v>
+        <v>tc-0.25.df-Y.cr-Eco.dm-Hi.cp-95.CF6</v>
       </c>
       <c r="H97" t="str">
         <f t="shared" si="39"/>
-        <v>tc-0.10.df-Y.cr-Eco.dm-Hi.cp-95.CF6</v>
+        <v>tc-0.25.df-Y.cr-Eco.dm-Hi.cp-95.CF6</v>
       </c>
       <c r="I97" t="str">
         <f t="shared" si="40"/>
@@ -42315,13 +42459,13 @@
       </c>
       <c r="N97" t="str">
         <f t="shared" si="45"/>
-        <v>0.10</v>
+        <v>0.25</v>
       </c>
       <c r="P97">
         <v>5</v>
       </c>
       <c r="Q97" t="s">
-        <v>1183</v>
+        <v>1216</v>
       </c>
       <c r="R97">
         <v>92</v>
@@ -42342,7 +42486,7 @@
         <v>1172</v>
       </c>
       <c r="X97">
-        <v>0.1</v>
+        <v>0.25</v>
       </c>
       <c r="Z97" t="str">
         <f t="shared" si="46"/>
@@ -42366,7 +42510,7 @@
       </c>
       <c r="AE97" t="str">
         <f t="shared" si="51"/>
-        <v>tc-0.10</v>
+        <v>tc-0.25</v>
       </c>
     </row>
     <row r="98" spans="2:31">
@@ -42376,11 +42520,11 @@
       </c>
       <c r="C98" t="str">
         <f t="shared" si="38"/>
-        <v>tc-0.10.df-N.cr-Eco.dm-Lo.cp-00.CF6</v>
+        <v>tc-0.25.df-N.cr-Eco.dm-Lo.cp-00.CF6</v>
       </c>
       <c r="H98" t="str">
         <f t="shared" si="39"/>
-        <v>tc-0.10.df-N.cr-Eco.dm-Lo.cp-00.CF6</v>
+        <v>tc-0.25.df-N.cr-Eco.dm-Lo.cp-00.CF6</v>
       </c>
       <c r="I98" t="str">
         <f t="shared" si="40"/>
@@ -42404,13 +42548,13 @@
       </c>
       <c r="N98" t="str">
         <f t="shared" si="45"/>
-        <v>0.10</v>
+        <v>0.25</v>
       </c>
       <c r="P98">
         <v>5</v>
       </c>
       <c r="Q98" t="s">
-        <v>1184</v>
+        <v>1217</v>
       </c>
       <c r="R98">
         <v>93</v>
@@ -42431,7 +42575,7 @@
         <v>1172</v>
       </c>
       <c r="X98">
-        <v>0.1</v>
+        <v>0.25</v>
       </c>
       <c r="Z98" t="str">
         <f t="shared" si="46"/>
@@ -42455,7 +42599,7 @@
       </c>
       <c r="AE98" t="str">
         <f t="shared" si="51"/>
-        <v>tc-0.10</v>
+        <v>tc-0.25</v>
       </c>
     </row>
     <row r="99" spans="2:31">
@@ -42465,11 +42609,11 @@
       </c>
       <c r="C99" t="str">
         <f t="shared" si="38"/>
-        <v>tc-0.10.df-N.cr-Eco.dm-Hi.cp-00.CF6</v>
+        <v>tc-0.25.df-N.cr-Eco.dm-Hi.cp-00.CF6</v>
       </c>
       <c r="H99" t="str">
         <f t="shared" si="39"/>
-        <v>tc-0.10.df-N.cr-Eco.dm-Hi.cp-00.CF6</v>
+        <v>tc-0.25.df-N.cr-Eco.dm-Hi.cp-00.CF6</v>
       </c>
       <c r="I99" t="str">
         <f t="shared" si="40"/>
@@ -42493,13 +42637,13 @@
       </c>
       <c r="N99" t="str">
         <f t="shared" si="45"/>
-        <v>0.10</v>
+        <v>0.25</v>
       </c>
       <c r="P99">
         <v>5</v>
       </c>
       <c r="Q99" t="s">
-        <v>1185</v>
+        <v>1218</v>
       </c>
       <c r="R99">
         <v>94</v>
@@ -42520,7 +42664,7 @@
         <v>1172</v>
       </c>
       <c r="X99">
-        <v>0.1</v>
+        <v>0.25</v>
       </c>
       <c r="Z99" t="str">
         <f t="shared" si="46"/>
@@ -42544,7 +42688,7 @@
       </c>
       <c r="AE99" t="str">
         <f t="shared" si="51"/>
-        <v>tc-0.10</v>
+        <v>tc-0.25</v>
       </c>
     </row>
     <row r="100" spans="2:31">
@@ -42554,11 +42698,11 @@
       </c>
       <c r="C100" t="str">
         <f t="shared" si="38"/>
-        <v>tc-0.10.df-N.cr-Eco.dm-Lo.cp-95.CF6</v>
+        <v>tc-0.25.df-N.cr-Eco.dm-Lo.cp-95.CF6</v>
       </c>
       <c r="H100" t="str">
         <f t="shared" si="39"/>
-        <v>tc-0.10.df-N.cr-Eco.dm-Lo.cp-95.CF6</v>
+        <v>tc-0.25.df-N.cr-Eco.dm-Lo.cp-95.CF6</v>
       </c>
       <c r="I100" t="str">
         <f t="shared" si="40"/>
@@ -42582,13 +42726,13 @@
       </c>
       <c r="N100" t="str">
         <f t="shared" si="45"/>
-        <v>0.10</v>
+        <v>0.25</v>
       </c>
       <c r="P100">
         <v>5</v>
       </c>
       <c r="Q100" t="s">
-        <v>1186</v>
+        <v>1219</v>
       </c>
       <c r="R100">
         <v>95</v>
@@ -42609,7 +42753,7 @@
         <v>1172</v>
       </c>
       <c r="X100">
-        <v>0.1</v>
+        <v>0.25</v>
       </c>
       <c r="Z100" t="str">
         <f t="shared" si="46"/>
@@ -42633,7 +42777,7 @@
       </c>
       <c r="AE100" t="str">
         <f t="shared" si="51"/>
-        <v>tc-0.10</v>
+        <v>tc-0.25</v>
       </c>
     </row>
     <row r="101" spans="2:31">
@@ -42643,11 +42787,11 @@
       </c>
       <c r="C101" t="str">
         <f t="shared" si="38"/>
-        <v>tc-0.10.df-N.cr-Eco.dm-Hi.cp-95.CF6</v>
+        <v>tc-0.25.df-N.cr-Eco.dm-Hi.cp-95.CF6</v>
       </c>
       <c r="H101" t="str">
         <f t="shared" si="39"/>
-        <v>tc-0.10.df-N.cr-Eco.dm-Hi.cp-95.CF6</v>
+        <v>tc-0.25.df-N.cr-Eco.dm-Hi.cp-95.CF6</v>
       </c>
       <c r="I101" t="str">
         <f t="shared" si="40"/>
@@ -42671,13 +42815,13 @@
       </c>
       <c r="N101" t="str">
         <f t="shared" si="45"/>
-        <v>0.10</v>
+        <v>0.25</v>
       </c>
       <c r="P101">
         <v>5</v>
       </c>
       <c r="Q101" t="s">
-        <v>1187</v>
+        <v>1220</v>
       </c>
       <c r="R101">
         <v>96</v>
@@ -42698,7 +42842,7 @@
         <v>1172</v>
       </c>
       <c r="X101">
-        <v>0.1</v>
+        <v>0.25</v>
       </c>
       <c r="Z101" t="str">
         <f t="shared" si="46"/>
@@ -42722,7 +42866,7 @@
       </c>
       <c r="AE101" t="str">
         <f t="shared" si="51"/>
-        <v>tc-0.10</v>
+        <v>tc-0.25</v>
       </c>
     </row>
     <row r="102" spans="2:31">
@@ -42732,11 +42876,11 @@
       </c>
       <c r="C102" t="str">
         <f t="shared" si="38"/>
-        <v>tc-0.10.df-Y.cr-Eco.dm-Lo.cp-00.CF1</v>
+        <v>tc-2.00.df-Y.cr-Eco.dm-Lo.cp-00.CF1</v>
       </c>
       <c r="H102" t="str">
         <f t="shared" si="39"/>
-        <v>tc-0.10.df-Y.cr-Eco.dm-Lo.cp-00.CF1</v>
+        <v>tc-2.00.df-Y.cr-Eco.dm-Lo.cp-00.CF1</v>
       </c>
       <c r="I102" t="str">
         <f t="shared" si="40"/>
@@ -42760,13 +42904,13 @@
       </c>
       <c r="N102" t="str">
         <f t="shared" si="45"/>
-        <v>0.10</v>
+        <v>2.00</v>
       </c>
       <c r="P102">
         <v>5</v>
       </c>
       <c r="Q102" t="s">
-        <v>1171</v>
+        <v>1221</v>
       </c>
       <c r="R102">
         <v>97</v>
@@ -42787,7 +42931,7 @@
         <v>1172</v>
       </c>
       <c r="X102">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="Z102" t="str">
         <f t="shared" si="46"/>
@@ -42811,7 +42955,7 @@
       </c>
       <c r="AE102" t="str">
         <f t="shared" si="51"/>
-        <v>tc-0.10</v>
+        <v>tc-2.00</v>
       </c>
     </row>
     <row r="103" spans="2:31">
@@ -42821,11 +42965,11 @@
       </c>
       <c r="C103" t="str">
         <f t="shared" si="38"/>
-        <v>tc-0.10.df-Y.cr-Eco.dm-Hi.cp-00.CF1</v>
+        <v>tc-2.00.df-Y.cr-Eco.dm-Hi.cp-00.CF1</v>
       </c>
       <c r="H103" t="str">
         <f t="shared" si="39"/>
-        <v>tc-0.10.df-Y.cr-Eco.dm-Hi.cp-00.CF1</v>
+        <v>tc-2.00.df-Y.cr-Eco.dm-Hi.cp-00.CF1</v>
       </c>
       <c r="I103" t="str">
         <f t="shared" si="40"/>
@@ -42849,13 +42993,13 @@
       </c>
       <c r="N103" t="str">
         <f t="shared" si="45"/>
-        <v>0.10</v>
+        <v>2.00</v>
       </c>
       <c r="P103">
         <v>5</v>
       </c>
       <c r="Q103" t="s">
-        <v>1173</v>
+        <v>1222</v>
       </c>
       <c r="R103">
         <v>98</v>
@@ -42876,7 +43020,7 @@
         <v>1172</v>
       </c>
       <c r="X103">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="Z103" t="str">
         <f t="shared" si="46"/>
@@ -42900,7 +43044,7 @@
       </c>
       <c r="AE103" t="str">
         <f t="shared" si="51"/>
-        <v>tc-0.10</v>
+        <v>tc-2.00</v>
       </c>
     </row>
     <row r="104" spans="2:31">
@@ -42910,11 +43054,11 @@
       </c>
       <c r="C104" t="str">
         <f t="shared" si="38"/>
-        <v>tc-0.10.df-Y.cr-Eco.dm-Lo.cp-95.CF1</v>
+        <v>tc-2.00.df-Y.cr-Eco.dm-Lo.cp-95.CF1</v>
       </c>
       <c r="H104" t="str">
         <f t="shared" si="39"/>
-        <v>tc-0.10.df-Y.cr-Eco.dm-Lo.cp-95.CF1</v>
+        <v>tc-2.00.df-Y.cr-Eco.dm-Lo.cp-95.CF1</v>
       </c>
       <c r="I104" t="str">
         <f t="shared" si="40"/>
@@ -42938,13 +43082,13 @@
       </c>
       <c r="N104" t="str">
         <f t="shared" si="45"/>
-        <v>0.10</v>
+        <v>2.00</v>
       </c>
       <c r="P104">
         <v>5</v>
       </c>
       <c r="Q104" t="s">
-        <v>1174</v>
+        <v>1223</v>
       </c>
       <c r="R104">
         <v>99</v>
@@ -42965,7 +43109,7 @@
         <v>1172</v>
       </c>
       <c r="X104">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="Z104" t="str">
         <f t="shared" si="46"/>
@@ -42989,7 +43133,7 @@
       </c>
       <c r="AE104" t="str">
         <f t="shared" si="51"/>
-        <v>tc-0.10</v>
+        <v>tc-2.00</v>
       </c>
     </row>
     <row r="105" spans="2:31">
@@ -42999,11 +43143,11 @@
       </c>
       <c r="C105" t="str">
         <f t="shared" si="38"/>
-        <v>tc-0.10.df-Y.cr-Eco.dm-Hi.cp-95.CF1</v>
+        <v>tc-2.00.df-Y.cr-Eco.dm-Hi.cp-95.CF1</v>
       </c>
       <c r="H105" t="str">
         <f t="shared" si="39"/>
-        <v>tc-0.10.df-Y.cr-Eco.dm-Hi.cp-95.CF1</v>
+        <v>tc-2.00.df-Y.cr-Eco.dm-Hi.cp-95.CF1</v>
       </c>
       <c r="I105" t="str">
         <f t="shared" si="40"/>
@@ -43027,13 +43171,13 @@
       </c>
       <c r="N105" t="str">
         <f t="shared" si="45"/>
-        <v>0.10</v>
+        <v>2.00</v>
       </c>
       <c r="P105">
         <v>5</v>
       </c>
       <c r="Q105" t="s">
-        <v>1175</v>
+        <v>1224</v>
       </c>
       <c r="R105">
         <v>100</v>
@@ -43054,7 +43198,7 @@
         <v>1172</v>
       </c>
       <c r="X105">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="Z105" t="str">
         <f t="shared" si="46"/>
@@ -43078,7 +43222,7 @@
       </c>
       <c r="AE105" t="str">
         <f t="shared" si="51"/>
-        <v>tc-0.10</v>
+        <v>tc-2.00</v>
       </c>
     </row>
     <row r="106" spans="2:31">
@@ -43088,11 +43232,11 @@
       </c>
       <c r="C106" t="str">
         <f t="shared" si="38"/>
-        <v>tc-0.10.df-N.cr-Eco.dm-Lo.cp-00.CF1</v>
+        <v>tc-2.00.df-N.cr-Eco.dm-Lo.cp-00.CF1</v>
       </c>
       <c r="H106" t="str">
         <f t="shared" si="39"/>
-        <v>tc-0.10.df-N.cr-Eco.dm-Lo.cp-00.CF1</v>
+        <v>tc-2.00.df-N.cr-Eco.dm-Lo.cp-00.CF1</v>
       </c>
       <c r="I106" t="str">
         <f t="shared" si="40"/>
@@ -43116,13 +43260,13 @@
       </c>
       <c r="N106" t="str">
         <f t="shared" si="45"/>
-        <v>0.10</v>
+        <v>2.00</v>
       </c>
       <c r="P106">
         <v>5</v>
       </c>
       <c r="Q106" t="s">
-        <v>1176</v>
+        <v>1225</v>
       </c>
       <c r="R106">
         <v>101</v>
@@ -43143,7 +43287,7 @@
         <v>1172</v>
       </c>
       <c r="X106">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="Z106" t="str">
         <f t="shared" si="46"/>
@@ -43167,7 +43311,7 @@
       </c>
       <c r="AE106" t="str">
         <f t="shared" si="51"/>
-        <v>tc-0.10</v>
+        <v>tc-2.00</v>
       </c>
     </row>
     <row r="107" spans="2:31">
@@ -43177,11 +43321,11 @@
       </c>
       <c r="C107" t="str">
         <f t="shared" si="38"/>
-        <v>tc-0.10.df-N.cr-Eco.dm-Hi.cp-00.CF1</v>
+        <v>tc-2.00.df-N.cr-Eco.dm-Hi.cp-00.CF1</v>
       </c>
       <c r="H107" t="str">
         <f t="shared" si="39"/>
-        <v>tc-0.10.df-N.cr-Eco.dm-Hi.cp-00.CF1</v>
+        <v>tc-2.00.df-N.cr-Eco.dm-Hi.cp-00.CF1</v>
       </c>
       <c r="I107" t="str">
         <f t="shared" si="40"/>
@@ -43205,13 +43349,13 @@
       </c>
       <c r="N107" t="str">
         <f t="shared" si="45"/>
-        <v>0.10</v>
+        <v>2.00</v>
       </c>
       <c r="P107">
         <v>5</v>
       </c>
       <c r="Q107" t="s">
-        <v>1177</v>
+        <v>1226</v>
       </c>
       <c r="R107">
         <v>102</v>
@@ -43232,7 +43376,7 @@
         <v>1172</v>
       </c>
       <c r="X107">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="Z107" t="str">
         <f t="shared" si="46"/>
@@ -43256,7 +43400,7 @@
       </c>
       <c r="AE107" t="str">
         <f t="shared" si="51"/>
-        <v>tc-0.10</v>
+        <v>tc-2.00</v>
       </c>
     </row>
     <row r="108" spans="2:31">
@@ -43266,11 +43410,11 @@
       </c>
       <c r="C108" t="str">
         <f t="shared" si="38"/>
-        <v>tc-0.10.df-N.cr-Eco.dm-Lo.cp-95.CF1</v>
+        <v>tc-2.00.df-N.cr-Eco.dm-Lo.cp-95.CF1</v>
       </c>
       <c r="H108" t="str">
         <f t="shared" si="39"/>
-        <v>tc-0.10.df-N.cr-Eco.dm-Lo.cp-95.CF1</v>
+        <v>tc-2.00.df-N.cr-Eco.dm-Lo.cp-95.CF1</v>
       </c>
       <c r="I108" t="str">
         <f t="shared" si="40"/>
@@ -43294,13 +43438,13 @@
       </c>
       <c r="N108" t="str">
         <f t="shared" si="45"/>
-        <v>0.10</v>
+        <v>2.00</v>
       </c>
       <c r="P108">
         <v>5</v>
       </c>
       <c r="Q108" t="s">
-        <v>1178</v>
+        <v>1227</v>
       </c>
       <c r="R108">
         <v>103</v>
@@ -43321,7 +43465,7 @@
         <v>1172</v>
       </c>
       <c r="X108">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="Z108" t="str">
         <f t="shared" si="46"/>
@@ -43345,7 +43489,7 @@
       </c>
       <c r="AE108" t="str">
         <f t="shared" si="51"/>
-        <v>tc-0.10</v>
+        <v>tc-2.00</v>
       </c>
     </row>
     <row r="109" spans="2:31">
@@ -43355,11 +43499,11 @@
       </c>
       <c r="C109" t="str">
         <f t="shared" si="38"/>
-        <v>tc-0.10.df-N.cr-Eco.dm-Hi.cp-95.CF1</v>
+        <v>tc-2.00.df-N.cr-Eco.dm-Hi.cp-95.CF1</v>
       </c>
       <c r="H109" t="str">
         <f t="shared" si="39"/>
-        <v>tc-0.10.df-N.cr-Eco.dm-Hi.cp-95.CF1</v>
+        <v>tc-2.00.df-N.cr-Eco.dm-Hi.cp-95.CF1</v>
       </c>
       <c r="I109" t="str">
         <f t="shared" si="40"/>
@@ -43383,13 +43527,13 @@
       </c>
       <c r="N109" t="str">
         <f t="shared" si="45"/>
-        <v>0.10</v>
+        <v>2.00</v>
       </c>
       <c r="P109">
         <v>5</v>
       </c>
       <c r="Q109" t="s">
-        <v>1179</v>
+        <v>1228</v>
       </c>
       <c r="R109">
         <v>104</v>
@@ -43410,7 +43554,7 @@
         <v>1172</v>
       </c>
       <c r="X109">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="Z109" t="str">
         <f t="shared" si="46"/>
@@ -43434,7 +43578,7 @@
       </c>
       <c r="AE109" t="str">
         <f t="shared" si="51"/>
-        <v>tc-0.10</v>
+        <v>tc-2.00</v>
       </c>
     </row>
     <row r="110" spans="2:31">
@@ -43444,11 +43588,11 @@
       </c>
       <c r="C110" t="str">
         <f t="shared" si="38"/>
-        <v>tc-0.10.df-Y.cr-Eco.dm-Lo.cp-00.CF6</v>
+        <v>tc-2.00.df-Y.cr-Eco.dm-Lo.cp-00.CF6</v>
       </c>
       <c r="H110" t="str">
         <f t="shared" si="39"/>
-        <v>tc-0.10.df-Y.cr-Eco.dm-Lo.cp-00.CF6</v>
+        <v>tc-2.00.df-Y.cr-Eco.dm-Lo.cp-00.CF6</v>
       </c>
       <c r="I110" t="str">
         <f t="shared" si="40"/>
@@ -43472,13 +43616,13 @@
       </c>
       <c r="N110" t="str">
         <f t="shared" si="45"/>
-        <v>0.10</v>
+        <v>2.00</v>
       </c>
       <c r="P110">
         <v>5</v>
       </c>
       <c r="Q110" t="s">
-        <v>1180</v>
+        <v>1229</v>
       </c>
       <c r="R110">
         <v>105</v>
@@ -43499,7 +43643,7 @@
         <v>1172</v>
       </c>
       <c r="X110">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="Z110" t="str">
         <f t="shared" si="46"/>
@@ -43523,7 +43667,7 @@
       </c>
       <c r="AE110" t="str">
         <f t="shared" si="51"/>
-        <v>tc-0.10</v>
+        <v>tc-2.00</v>
       </c>
     </row>
     <row r="111" spans="2:31">
@@ -43533,11 +43677,11 @@
       </c>
       <c r="C111" t="str">
         <f t="shared" si="38"/>
-        <v>tc-0.10.df-Y.cr-Eco.dm-Hi.cp-00.CF6</v>
+        <v>tc-2.00.df-Y.cr-Eco.dm-Hi.cp-00.CF6</v>
       </c>
       <c r="H111" t="str">
         <f t="shared" si="39"/>
-        <v>tc-0.10.df-Y.cr-Eco.dm-Hi.cp-00.CF6</v>
+        <v>tc-2.00.df-Y.cr-Eco.dm-Hi.cp-00.CF6</v>
       </c>
       <c r="I111" t="str">
         <f t="shared" si="40"/>
@@ -43561,13 +43705,13 @@
       </c>
       <c r="N111" t="str">
         <f t="shared" si="45"/>
-        <v>0.10</v>
+        <v>2.00</v>
       </c>
       <c r="P111">
         <v>5</v>
       </c>
       <c r="Q111" t="s">
-        <v>1181</v>
+        <v>1230</v>
       </c>
       <c r="R111">
         <v>106</v>
@@ -43588,7 +43732,7 @@
         <v>1172</v>
       </c>
       <c r="X111">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="Z111" t="str">
         <f t="shared" si="46"/>
@@ -43612,7 +43756,7 @@
       </c>
       <c r="AE111" t="str">
         <f t="shared" si="51"/>
-        <v>tc-0.10</v>
+        <v>tc-2.00</v>
       </c>
     </row>
     <row r="112" spans="2:31">
@@ -43622,11 +43766,11 @@
       </c>
       <c r="C112" t="str">
         <f t="shared" si="38"/>
-        <v>tc-0.10.df-Y.cr-Eco.dm-Lo.cp-95.CF6</v>
+        <v>tc-2.00.df-Y.cr-Eco.dm-Lo.cp-95.CF6</v>
       </c>
       <c r="H112" t="str">
         <f t="shared" si="39"/>
-        <v>tc-0.10.df-Y.cr-Eco.dm-Lo.cp-95.CF6</v>
+        <v>tc-2.00.df-Y.cr-Eco.dm-Lo.cp-95.CF6</v>
       </c>
       <c r="I112" t="str">
         <f t="shared" si="40"/>
@@ -43650,13 +43794,13 @@
       </c>
       <c r="N112" t="str">
         <f t="shared" si="45"/>
-        <v>0.10</v>
+        <v>2.00</v>
       </c>
       <c r="P112">
         <v>5</v>
       </c>
       <c r="Q112" t="s">
-        <v>1182</v>
+        <v>1231</v>
       </c>
       <c r="R112">
         <v>107</v>
@@ -43677,7 +43821,7 @@
         <v>1172</v>
       </c>
       <c r="X112">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="Z112" t="str">
         <f t="shared" si="46"/>
@@ -43701,7 +43845,7 @@
       </c>
       <c r="AE112" t="str">
         <f t="shared" si="51"/>
-        <v>tc-0.10</v>
+        <v>tc-2.00</v>
       </c>
     </row>
     <row r="113" spans="2:31">
@@ -43711,11 +43855,11 @@
       </c>
       <c r="C113" t="str">
         <f t="shared" si="38"/>
-        <v>tc-0.10.df-Y.cr-Eco.dm-Hi.cp-95.CF6</v>
+        <v>tc-2.00.df-Y.cr-Eco.dm-Hi.cp-95.CF6</v>
       </c>
       <c r="H113" t="str">
         <f t="shared" si="39"/>
-        <v>tc-0.10.df-Y.cr-Eco.dm-Hi.cp-95.CF6</v>
+        <v>tc-2.00.df-Y.cr-Eco.dm-Hi.cp-95.CF6</v>
       </c>
       <c r="I113" t="str">
         <f t="shared" si="40"/>
@@ -43739,13 +43883,13 @@
       </c>
       <c r="N113" t="str">
         <f t="shared" si="45"/>
-        <v>0.10</v>
+        <v>2.00</v>
       </c>
       <c r="P113">
         <v>5</v>
       </c>
       <c r="Q113" t="s">
-        <v>1183</v>
+        <v>1232</v>
       </c>
       <c r="R113">
         <v>108</v>
@@ -43766,7 +43910,7 @@
         <v>1172</v>
       </c>
       <c r="X113">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="Z113" t="str">
         <f t="shared" si="46"/>
@@ -43790,7 +43934,7 @@
       </c>
       <c r="AE113" t="str">
         <f t="shared" si="51"/>
-        <v>tc-0.10</v>
+        <v>tc-2.00</v>
       </c>
     </row>
     <row r="114" spans="2:31">
@@ -43800,11 +43944,11 @@
       </c>
       <c r="C114" t="str">
         <f t="shared" si="38"/>
-        <v>tc-0.10.df-N.cr-Eco.dm-Lo.cp-00.CF6</v>
+        <v>tc-2.00.df-N.cr-Eco.dm-Lo.cp-00.CF6</v>
       </c>
       <c r="H114" t="str">
         <f t="shared" si="39"/>
-        <v>tc-0.10.df-N.cr-Eco.dm-Lo.cp-00.CF6</v>
+        <v>tc-2.00.df-N.cr-Eco.dm-Lo.cp-00.CF6</v>
       </c>
       <c r="I114" t="str">
         <f t="shared" si="40"/>
@@ -43828,13 +43972,13 @@
       </c>
       <c r="N114" t="str">
         <f t="shared" si="45"/>
-        <v>0.10</v>
+        <v>2.00</v>
       </c>
       <c r="P114">
         <v>5</v>
       </c>
       <c r="Q114" t="s">
-        <v>1184</v>
+        <v>1233</v>
       </c>
       <c r="R114">
         <v>109</v>
@@ -43855,7 +43999,7 @@
         <v>1172</v>
       </c>
       <c r="X114">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="Z114" t="str">
         <f t="shared" si="46"/>
@@ -43879,7 +44023,7 @@
       </c>
       <c r="AE114" t="str">
         <f t="shared" si="51"/>
-        <v>tc-0.10</v>
+        <v>tc-2.00</v>
       </c>
     </row>
     <row r="115" spans="2:31">
@@ -43889,11 +44033,11 @@
       </c>
       <c r="C115" t="str">
         <f t="shared" si="38"/>
-        <v>tc-0.10.df-N.cr-Eco.dm-Hi.cp-00.CF6</v>
+        <v>tc-2.00.df-N.cr-Eco.dm-Hi.cp-00.CF6</v>
       </c>
       <c r="H115" t="str">
         <f t="shared" si="39"/>
-        <v>tc-0.10.df-N.cr-Eco.dm-Hi.cp-00.CF6</v>
+        <v>tc-2.00.df-N.cr-Eco.dm-Hi.cp-00.CF6</v>
       </c>
       <c r="I115" t="str">
         <f t="shared" si="40"/>
@@ -43917,13 +44061,13 @@
       </c>
       <c r="N115" t="str">
         <f t="shared" si="45"/>
-        <v>0.10</v>
+        <v>2.00</v>
       </c>
       <c r="P115">
         <v>5</v>
       </c>
       <c r="Q115" t="s">
-        <v>1185</v>
+        <v>1234</v>
       </c>
       <c r="R115">
         <v>110</v>
@@ -43944,7 +44088,7 @@
         <v>1172</v>
       </c>
       <c r="X115">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="Z115" t="str">
         <f t="shared" si="46"/>
@@ -43968,7 +44112,7 @@
       </c>
       <c r="AE115" t="str">
         <f t="shared" si="51"/>
-        <v>tc-0.10</v>
+        <v>tc-2.00</v>
       </c>
     </row>
     <row r="116" spans="2:31">
@@ -43978,11 +44122,11 @@
       </c>
       <c r="C116" t="str">
         <f t="shared" si="38"/>
-        <v>tc-0.10.df-N.cr-Eco.dm-Lo.cp-95.CF6</v>
+        <v>tc-2.00.df-N.cr-Eco.dm-Lo.cp-95.CF6</v>
       </c>
       <c r="H116" t="str">
         <f t="shared" si="39"/>
-        <v>tc-0.10.df-N.cr-Eco.dm-Lo.cp-95.CF6</v>
+        <v>tc-2.00.df-N.cr-Eco.dm-Lo.cp-95.CF6</v>
       </c>
       <c r="I116" t="str">
         <f t="shared" si="40"/>
@@ -44006,13 +44150,13 @@
       </c>
       <c r="N116" t="str">
         <f t="shared" si="45"/>
-        <v>0.10</v>
+        <v>2.00</v>
       </c>
       <c r="P116">
         <v>5</v>
       </c>
       <c r="Q116" t="s">
-        <v>1186</v>
+        <v>1235</v>
       </c>
       <c r="R116">
         <v>111</v>
@@ -44033,7 +44177,7 @@
         <v>1172</v>
       </c>
       <c r="X116">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="Z116" t="str">
         <f t="shared" si="46"/>
@@ -44057,7 +44201,7 @@
       </c>
       <c r="AE116" t="str">
         <f t="shared" si="51"/>
-        <v>tc-0.10</v>
+        <v>tc-2.00</v>
       </c>
     </row>
     <row r="117" spans="2:31">
@@ -44067,11 +44211,11 @@
       </c>
       <c r="C117" t="str">
         <f t="shared" si="38"/>
-        <v>tc-0.10.df-N.cr-Eco.dm-Hi.cp-95.CF6</v>
+        <v>tc-2.00.df-N.cr-Eco.dm-Hi.cp-95.CF6</v>
       </c>
       <c r="H117" t="str">
         <f t="shared" si="39"/>
-        <v>tc-0.10.df-N.cr-Eco.dm-Hi.cp-95.CF6</v>
+        <v>tc-2.00.df-N.cr-Eco.dm-Hi.cp-95.CF6</v>
       </c>
       <c r="I117" t="str">
         <f t="shared" si="40"/>
@@ -44095,13 +44239,13 @@
       </c>
       <c r="N117" t="str">
         <f t="shared" si="45"/>
-        <v>0.10</v>
+        <v>2.00</v>
       </c>
       <c r="P117">
         <v>5</v>
       </c>
       <c r="Q117" t="s">
-        <v>1187</v>
+        <v>1236</v>
       </c>
       <c r="R117">
         <v>112</v>
@@ -44122,7 +44266,7 @@
         <v>1172</v>
       </c>
       <c r="X117">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="Z117" t="str">
         <f t="shared" si="46"/>
@@ -44146,7 +44290,7 @@
       </c>
       <c r="AE117" t="str">
         <f t="shared" si="51"/>
-        <v>tc-0.10</v>
+        <v>tc-2.00</v>
       </c>
     </row>
     <row r="118" spans="2:31">

--- a/VerveStacks_ZAF_grids_kan/ReportDefs_vervestacks.xlsx
+++ b/VerveStacks_ZAF_grids_kan/ReportDefs_vervestacks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_ZAF_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BA61B3F-4721-40B6-BDF6-0435BB668AB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1461735-911B-42A1-913D-3CF00CB158CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="geolocation" sheetId="72" r:id="rId1"/>
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7832" uniqueCount="1240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7855" uniqueCount="1246">
   <si>
     <t>Unit</t>
   </si>
@@ -3803,6 +3803,24 @@
   </si>
   <si>
     <t>TxCost</t>
+  </si>
+  <si>
+    <t>CO2 intensity</t>
+  </si>
+  <si>
+    <t>t/TJ</t>
+  </si>
+  <si>
+    <t>Efficiency</t>
+  </si>
+  <si>
+    <t>kg/Mwh</t>
+  </si>
+  <si>
+    <t>pc</t>
+  </si>
+  <si>
+    <t>Elec Fuel Consumption</t>
   </si>
 </sst>
 </file>
@@ -27219,7 +27237,7 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr codeName="Sheet31"/>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="10.1328125" bestFit="1" customWidth="1"/>
@@ -27322,6 +27340,34 @@
       </c>
       <c r="D7">
         <v>-1000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>77</v>
+      </c>
+      <c r="B8" t="s">
+        <v>1241</v>
+      </c>
+      <c r="C8" t="s">
+        <v>1243</v>
+      </c>
+      <c r="D8">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>77</v>
+      </c>
+      <c r="B9" t="s">
+        <v>1244</v>
+      </c>
+      <c r="C9" t="s">
+        <v>104</v>
+      </c>
+      <c r="D9">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -45735,7 +45781,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet19"/>
-  <dimension ref="A1:U29"/>
+  <dimension ref="A1:U30"/>
   <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13.86328125" bestFit="1" customWidth="1"/>
@@ -45889,42 +45935,48 @@
     </row>
     <row r="6" spans="1:21">
       <c r="A6" t="s">
-        <v>54</v>
+        <v>141</v>
       </c>
       <c r="C6" t="s">
-        <v>132</v>
-      </c>
-      <c r="D6" s="2"/>
+        <v>277</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>137</v>
+      </c>
       <c r="H6" t="s">
         <v>25</v>
       </c>
-      <c r="I6" s="2" t="s">
-        <v>91</v>
-      </c>
       <c r="K6" t="s">
-        <v>287</v>
+        <v>140</v>
       </c>
       <c r="N6" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>110</v>
+        <v>1245</v>
       </c>
       <c r="T6" s="3"/>
       <c r="U6" s="3"/>
     </row>
     <row r="7" spans="1:21">
       <c r="A7" t="s">
-        <v>4</v>
+        <v>54</v>
+      </c>
+      <c r="C7" t="s">
+        <v>132</v>
+      </c>
+      <c r="D7" s="2"/>
+      <c r="H7" t="s">
+        <v>25</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>116</v>
+        <v>91</v>
       </c>
       <c r="K7" t="s">
-        <v>118</v>
+        <v>287</v>
       </c>
       <c r="N7" t="s">
-        <v>120</v>
+        <v>37</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>110</v>
       </c>
       <c r="T7" s="3"/>
       <c r="U7" s="3"/>
@@ -45934,42 +45986,36 @@
         <v>4</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="K8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="N8" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="T8" s="3"/>
       <c r="U8" s="3"/>
     </row>
     <row r="9" spans="1:21">
       <c r="A9" t="s">
-        <v>1099</v>
-      </c>
-      <c r="C9" t="s">
-        <v>1096</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>109</v>
+        <v>4</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>117</v>
       </c>
       <c r="K9" t="s">
-        <v>232</v>
-      </c>
-      <c r="M9" t="s">
-        <v>1100</v>
+        <v>119</v>
       </c>
       <c r="N9" t="s">
-        <v>1101</v>
+        <v>121</v>
       </c>
       <c r="T9" s="3"/>
       <c r="U9" s="3"/>
     </row>
     <row r="10" spans="1:21">
       <c r="A10" t="s">
-        <v>280</v>
+        <v>1099</v>
       </c>
       <c r="C10" t="s">
         <v>1096</v>
@@ -45980,13 +46026,18 @@
       <c r="K10" t="s">
         <v>232</v>
       </c>
+      <c r="M10" t="s">
+        <v>1100</v>
+      </c>
       <c r="N10" t="s">
-        <v>75</v>
-      </c>
+        <v>1101</v>
+      </c>
+      <c r="T10" s="3"/>
+      <c r="U10" s="3"/>
     </row>
     <row r="11" spans="1:21">
       <c r="A11" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="C11" t="s">
         <v>1096</v>
@@ -46003,10 +46054,10 @@
     </row>
     <row r="12" spans="1:21">
       <c r="A12" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C12" t="s">
-        <v>107</v>
+        <v>1096</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>109</v>
@@ -46015,12 +46066,12 @@
         <v>232</v>
       </c>
       <c r="N12" t="s">
-        <v>274</v>
+        <v>75</v>
       </c>
     </row>
     <row r="13" spans="1:21">
       <c r="A13" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="C13" t="s">
         <v>107</v>
@@ -46037,7 +46088,7 @@
     </row>
     <row r="14" spans="1:21">
       <c r="A14" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C14" t="s">
         <v>107</v>
@@ -46049,51 +46100,42 @@
         <v>232</v>
       </c>
       <c r="N14" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="15" spans="1:21">
       <c r="A15" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="C15" t="s">
-        <v>277</v>
-      </c>
-      <c r="D15" s="2"/>
-      <c r="I15" t="s">
-        <v>278</v>
+        <v>107</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>109</v>
       </c>
       <c r="K15" t="s">
         <v>232</v>
       </c>
       <c r="N15" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="16" spans="1:21">
-      <c r="A16" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="H16" t="s">
-        <v>25</v>
-      </c>
+      <c r="A16" t="s">
+        <v>279</v>
+      </c>
+      <c r="C16" t="s">
+        <v>277</v>
+      </c>
+      <c r="D16" s="2"/>
       <c r="I16" t="s">
         <v>278</v>
       </c>
       <c r="K16" t="s">
-        <v>288</v>
+        <v>232</v>
       </c>
       <c r="N16" t="s">
-        <v>1237</v>
-      </c>
-      <c r="P16" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>41</v>
+        <v>276</v>
       </c>
     </row>
     <row r="17" spans="1:17">
@@ -46103,14 +46145,23 @@
       <c r="B17" s="4" t="s">
         <v>50</v>
       </c>
+      <c r="H17" t="s">
+        <v>25</v>
+      </c>
       <c r="I17" t="s">
-        <v>128</v>
+        <v>278</v>
       </c>
       <c r="K17" t="s">
-        <v>129</v>
+        <v>288</v>
       </c>
       <c r="N17" t="s">
-        <v>130</v>
+        <v>1237</v>
+      </c>
+      <c r="P17" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="18" spans="1:17">
@@ -46120,101 +46171,104 @@
       <c r="B18" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="H18" t="s">
+      <c r="I18" t="s">
+        <v>128</v>
+      </c>
+      <c r="K18" t="s">
+        <v>129</v>
+      </c>
+      <c r="N18" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17">
+      <c r="A19" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="H19" t="s">
         <v>1235</v>
       </c>
-      <c r="I18" t="s">
+      <c r="I19" t="s">
         <v>1236</v>
       </c>
-      <c r="K18" t="s">
+      <c r="K19" t="s">
         <v>288</v>
       </c>
-      <c r="N18" t="s">
+      <c r="N19" t="s">
         <v>1238</v>
       </c>
-      <c r="Q18" t="s">
+      <c r="Q19" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="19" spans="1:17">
-      <c r="A19" t="s">
+    <row r="20" spans="1:17">
+      <c r="A20" t="s">
         <v>42</v>
       </c>
-      <c r="K19" t="s">
+      <c r="K20" t="s">
         <v>76</v>
       </c>
-      <c r="N19" t="s">
+      <c r="N20" t="s">
         <v>43</v>
       </c>
-      <c r="P19" t="s">
+      <c r="P20" t="s">
         <v>45</v>
       </c>
-      <c r="Q19" t="s">
+      <c r="Q20" t="s">
         <v>44</v>
-      </c>
-    </row>
-    <row r="20" spans="1:17">
-      <c r="A20" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="K20" t="s">
-        <v>288</v>
-      </c>
-      <c r="N20" t="s">
-        <v>55</v>
-      </c>
-      <c r="Q20" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="21" spans="1:17">
       <c r="A21" s="4" t="s">
-        <v>230</v>
+        <v>51</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>34</v>
       </c>
       <c r="K21" t="s">
-        <v>232</v>
+        <v>288</v>
       </c>
       <c r="N21" t="s">
-        <v>233</v>
+        <v>55</v>
       </c>
       <c r="Q21" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
     </row>
     <row r="22" spans="1:17">
       <c r="A22" s="4" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K22" t="s">
         <v>232</v>
       </c>
       <c r="N22" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="Q22" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="23" spans="1:17">
-      <c r="A23" t="s">
-        <v>6</v>
-      </c>
-      <c r="C23" t="s">
-        <v>1102</v>
+      <c r="A23" s="4" t="s">
+        <v>231</v>
       </c>
       <c r="K23" t="s">
-        <v>7</v>
+        <v>232</v>
       </c>
       <c r="N23" t="s">
-        <v>240</v>
+        <v>234</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="24" spans="1:17">
       <c r="A24" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="C24" t="s">
         <v>1102</v>
@@ -46223,49 +46277,43 @@
         <v>7</v>
       </c>
       <c r="N24" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17">
+      <c r="A25" t="s">
+        <v>34</v>
+      </c>
+      <c r="C25" t="s">
+        <v>1102</v>
+      </c>
+      <c r="K25" t="s">
+        <v>7</v>
+      </c>
+      <c r="N25" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="25" spans="1:17">
-      <c r="A25" s="4" t="s">
+    <row r="26" spans="1:17">
+      <c r="A26" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="D25" t="s">
+      <c r="D26" t="s">
         <v>247</v>
       </c>
-      <c r="I25" t="s">
+      <c r="I26" t="s">
         <v>248</v>
-      </c>
-      <c r="K25" t="s">
-        <v>140</v>
-      </c>
-      <c r="N25" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="26" spans="1:17">
-      <c r="A26" t="s">
-        <v>141</v>
-      </c>
-      <c r="I26" t="s">
-        <v>250</v>
       </c>
       <c r="K26" t="s">
         <v>140</v>
       </c>
       <c r="N26" t="s">
-        <v>268</v>
-      </c>
-      <c r="P26" t="s">
-        <v>265</v>
-      </c>
-      <c r="Q26" t="s">
-        <v>249</v>
+        <v>142</v>
       </c>
     </row>
     <row r="27" spans="1:17">
       <c r="A27" t="s">
-        <v>4</v>
+        <v>141</v>
       </c>
       <c r="I27" t="s">
         <v>250</v>
@@ -46274,7 +46322,7 @@
         <v>140</v>
       </c>
       <c r="N27" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="P27" t="s">
         <v>265</v>
@@ -46285,30 +46333,27 @@
     </row>
     <row r="28" spans="1:17">
       <c r="A28" t="s">
-        <v>6</v>
-      </c>
-      <c r="F28" t="s">
-        <v>272</v>
-      </c>
-      <c r="G28" t="s">
-        <v>272</v>
+        <v>4</v>
+      </c>
+      <c r="I28" t="s">
+        <v>250</v>
       </c>
       <c r="K28" t="s">
-        <v>7</v>
+        <v>140</v>
       </c>
       <c r="N28" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="P28" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="Q28" t="s">
-        <v>39</v>
+        <v>249</v>
       </c>
     </row>
     <row r="29" spans="1:17">
       <c r="A29" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="F29" t="s">
         <v>272</v>
@@ -46320,12 +46365,35 @@
         <v>7</v>
       </c>
       <c r="N29" t="s">
+        <v>270</v>
+      </c>
+      <c r="P29" t="s">
+        <v>266</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17">
+      <c r="A30" t="s">
+        <v>34</v>
+      </c>
+      <c r="F30" t="s">
+        <v>272</v>
+      </c>
+      <c r="G30" t="s">
+        <v>272</v>
+      </c>
+      <c r="K30" t="s">
+        <v>7</v>
+      </c>
+      <c r="N30" t="s">
         <v>271</v>
       </c>
-      <c r="P29" t="s">
+      <c r="P30" t="s">
         <v>267</v>
       </c>
-      <c r="Q29" t="s">
+      <c r="Q30" t="s">
         <v>39</v>
       </c>
     </row>
@@ -46341,7 +46409,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68A8EC7F-95E3-4526-8B78-C58A96098159}">
-  <dimension ref="C1:K3"/>
+  <dimension ref="C1:K5"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="3" max="3" width="17.53125" bestFit="1" customWidth="1"/>
@@ -46402,13 +46470,50 @@
       <c r="F3" t="s">
         <v>102</v>
       </c>
-      <c r="G3" t="s">
-        <v>39</v>
-      </c>
       <c r="I3" t="s">
         <v>103</v>
       </c>
       <c r="J3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" spans="3:11">
+      <c r="C4" t="s">
+        <v>120</v>
+      </c>
+      <c r="D4" t="s">
+        <v>74</v>
+      </c>
+      <c r="E4" t="s">
+        <v>1240</v>
+      </c>
+      <c r="F4" t="s">
+        <v>1241</v>
+      </c>
+      <c r="I4" t="s">
+        <v>103</v>
+      </c>
+      <c r="J4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="3:11">
+      <c r="C5" t="s">
+        <v>74</v>
+      </c>
+      <c r="D5" t="s">
+        <v>1245</v>
+      </c>
+      <c r="E5" t="s">
+        <v>1242</v>
+      </c>
+      <c r="F5" t="s">
+        <v>1244</v>
+      </c>
+      <c r="I5" t="s">
+        <v>103</v>
+      </c>
+      <c r="J5" t="s">
         <v>39</v>
       </c>
     </row>

--- a/VerveStacks_ZAF_grids_kan/ReportDefs_vervestacks.xlsx
+++ b/VerveStacks_ZAF_grids_kan/ReportDefs_vervestacks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_ZAF_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1461735-911B-42A1-913D-3CF00CB158CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF02B6A7-B1A0-4E95-8655-170A94326AB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="4" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="geolocation" sheetId="72" r:id="rId1"/>
@@ -3808,9 +3808,6 @@
     <t>CO2 intensity</t>
   </si>
   <si>
-    <t>t/TJ</t>
-  </si>
-  <si>
     <t>Efficiency</t>
   </si>
   <si>
@@ -3821,6 +3818,9 @@
   </si>
   <si>
     <t>Elec Fuel Consumption</t>
+  </si>
+  <si>
+    <t>mt/TWh</t>
   </si>
 </sst>
 </file>
@@ -27242,7 +27242,7 @@
   <cols>
     <col min="1" max="1" width="10.1328125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="8.73046875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.86328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="2" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.73046875" bestFit="1" customWidth="1"/>
@@ -27347,13 +27347,13 @@
         <v>77</v>
       </c>
       <c r="B8" t="s">
-        <v>1241</v>
+        <v>1245</v>
       </c>
       <c r="C8" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="D8">
-        <v>3.6</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -27361,7 +27361,7 @@
         <v>77</v>
       </c>
       <c r="B9" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="C9" t="s">
         <v>104</v>
@@ -45950,7 +45950,7 @@
         <v>140</v>
       </c>
       <c r="N6" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="T6" s="3"/>
       <c r="U6" s="3"/>
@@ -46488,7 +46488,7 @@
         <v>1240</v>
       </c>
       <c r="F4" t="s">
-        <v>1241</v>
+        <v>1245</v>
       </c>
       <c r="I4" t="s">
         <v>103</v>
@@ -46502,13 +46502,13 @@
         <v>74</v>
       </c>
       <c r="D5" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="E5" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="F5" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="I5" t="s">
         <v>103</v>

--- a/VerveStacks_ZAF_grids_kan/ReportDefs_vervestacks.xlsx
+++ b/VerveStacks_ZAF_grids_kan/ReportDefs_vervestacks.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_ZAF_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF02B6A7-B1A0-4E95-8655-170A94326AB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E5C17D9-1088-4D5F-A997-B4928C2B710C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="4" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7855" uniqueCount="1246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7859" uniqueCount="1248">
   <si>
     <t>Unit</t>
   </si>
@@ -3821,6 +3821,12 @@
   </si>
   <si>
     <t>mt/TWh</t>
+  </si>
+  <si>
+    <t>Oil</t>
+  </si>
+  <si>
+    <t>OIL</t>
   </si>
 </sst>
 </file>
@@ -9442,7 +9448,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10ADB714-E6AA-4E3E-B77B-62B65BA0E218}">
-  <dimension ref="A1:G55"/>
+  <dimension ref="A1:G56"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="14.86328125" bestFit="1" customWidth="1"/>
@@ -9520,7 +9526,7 @@
         <v>63</v>
       </c>
       <c r="C6" t="str">
-        <f t="shared" ref="C6:C29" si="0">D6</f>
+        <f t="shared" ref="C6:C30" si="0">D6</f>
         <v>Int Comb</v>
       </c>
       <c r="D6" t="s">
@@ -9723,12 +9729,14 @@
       <c r="A23" t="s">
         <v>63</v>
       </c>
-      <c r="C23" t="str">
-        <f t="shared" si="0"/>
-        <v>EV Batt</v>
+      <c r="C23" t="s">
+        <v>1246</v>
       </c>
       <c r="D23" t="s">
-        <v>90</v>
+        <v>277</v>
+      </c>
+      <c r="E23" t="s">
+        <v>1247</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -9737,10 +9745,10 @@
       </c>
       <c r="C24" t="str">
         <f t="shared" si="0"/>
-        <v>Demand</v>
+        <v>EV Batt</v>
       </c>
       <c r="D24" t="s">
-        <v>142</v>
+        <v>90</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -9749,10 +9757,10 @@
       </c>
       <c r="C25" t="str">
         <f t="shared" si="0"/>
-        <v>Transformers Dn</v>
+        <v>Demand</v>
       </c>
       <c r="D25" t="s">
-        <v>208</v>
+        <v>142</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -9761,33 +9769,33 @@
       </c>
       <c r="C26" t="str">
         <f t="shared" si="0"/>
-        <v>Transformers Up</v>
+        <v>Transformers Dn</v>
       </c>
       <c r="D26" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" t="s">
         <v>63</v>
       </c>
-      <c r="C27" t="s">
-        <v>1097</v>
+      <c r="C27" t="str">
+        <f t="shared" si="0"/>
+        <v>Transformers Up</v>
       </c>
       <c r="D27" t="s">
-        <v>1098</v>
+        <v>209</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" t="s">
         <v>63</v>
       </c>
-      <c r="C28" t="str">
-        <f t="shared" si="0"/>
-        <v>Aggregators</v>
+      <c r="C28" t="s">
+        <v>1097</v>
       </c>
       <c r="D28" t="s">
-        <v>206</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -9796,24 +9804,22 @@
       </c>
       <c r="C29" t="str">
         <f t="shared" si="0"/>
-        <v>DUMMY_IMP</v>
+        <v>Aggregators</v>
       </c>
       <c r="D29" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" t="s">
         <v>63</v>
       </c>
-      <c r="B30" t="s">
-        <v>344</v>
-      </c>
-      <c r="C30" t="s">
-        <v>122</v>
-      </c>
-      <c r="E30" t="s">
-        <v>126</v>
+      <c r="C30" t="str">
+        <f t="shared" si="0"/>
+        <v>DUMMY_IMP</v>
+      </c>
+      <c r="D30" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -9824,10 +9830,10 @@
         <v>344</v>
       </c>
       <c r="C31" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E31" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -9835,13 +9841,13 @@
         <v>63</v>
       </c>
       <c r="B32" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C32" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E32" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -9852,10 +9858,10 @@
         <v>345</v>
       </c>
       <c r="C33" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E33" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -9863,10 +9869,13 @@
         <v>63</v>
       </c>
       <c r="B34" t="s">
-        <v>92</v>
+        <v>345</v>
       </c>
       <c r="C34" t="s">
-        <v>3</v>
+        <v>125</v>
+      </c>
+      <c r="E34" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -9874,10 +9883,10 @@
         <v>63</v>
       </c>
       <c r="B35" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C35" t="s">
-        <v>94</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -9885,21 +9894,21 @@
         <v>63</v>
       </c>
       <c r="B36" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="C36" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" t="s">
-        <v>242</v>
+        <v>63</v>
       </c>
       <c r="B37" t="s">
-        <v>243</v>
+        <v>105</v>
       </c>
       <c r="C37" t="s">
-        <v>244</v>
+        <v>106</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -9907,10 +9916,10 @@
         <v>242</v>
       </c>
       <c r="B38" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C38" t="s">
-        <v>90</v>
+        <v>244</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -9918,21 +9927,21 @@
         <v>242</v>
       </c>
       <c r="B39" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C39" t="s">
-        <v>222</v>
+        <v>90</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="B40" t="s">
-        <v>112</v>
+        <v>246</v>
       </c>
       <c r="C40" t="s">
-        <v>251</v>
+        <v>222</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -9940,10 +9949,10 @@
         <v>252</v>
       </c>
       <c r="B41" t="s">
-        <v>253</v>
+        <v>112</v>
       </c>
       <c r="C41" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -9951,10 +9960,10 @@
         <v>252</v>
       </c>
       <c r="B42" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C42" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -9962,10 +9971,10 @@
         <v>252</v>
       </c>
       <c r="B43" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C43" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -9973,10 +9982,10 @@
         <v>252</v>
       </c>
       <c r="B44" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C44" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -9984,10 +9993,10 @@
         <v>252</v>
       </c>
       <c r="B45" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C45" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -9995,22 +10004,21 @@
         <v>252</v>
       </c>
       <c r="B46" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C46" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" t="s">
-        <v>273</v>
-      </c>
-      <c r="C47" t="str">
-        <f>E47</f>
-        <v>bioenergy</v>
-      </c>
-      <c r="E47" t="s">
-        <v>164</v>
+        <v>252</v>
+      </c>
+      <c r="B47" t="s">
+        <v>263</v>
+      </c>
+      <c r="C47" t="s">
+        <v>264</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -10018,11 +10026,11 @@
         <v>273</v>
       </c>
       <c r="C48" t="str">
-        <f t="shared" ref="C48:C55" si="1">E48</f>
-        <v>coal</v>
+        <f>E48</f>
+        <v>bioenergy</v>
       </c>
       <c r="E48" t="s">
-        <v>126</v>
+        <v>164</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -10030,11 +10038,11 @@
         <v>273</v>
       </c>
       <c r="C49" t="str">
-        <f t="shared" si="1"/>
-        <v>gas</v>
+        <f t="shared" ref="C49:C56" si="1">E49</f>
+        <v>coal</v>
       </c>
       <c r="E49" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -10043,10 +10051,10 @@
       </c>
       <c r="C50" t="str">
         <f t="shared" si="1"/>
-        <v>hydro</v>
+        <v>gas</v>
       </c>
       <c r="E50" t="s">
-        <v>212</v>
+        <v>127</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -10055,10 +10063,10 @@
       </c>
       <c r="C51" t="str">
         <f t="shared" si="1"/>
-        <v>nuclear</v>
+        <v>hydro</v>
       </c>
       <c r="E51" t="s">
-        <v>166</v>
+        <v>212</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -10067,10 +10075,10 @@
       </c>
       <c r="C52" t="str">
         <f t="shared" si="1"/>
-        <v>oil</v>
+        <v>nuclear</v>
       </c>
       <c r="E52" t="s">
-        <v>213</v>
+        <v>166</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -10079,10 +10087,10 @@
       </c>
       <c r="C53" t="str">
         <f t="shared" si="1"/>
-        <v>solar</v>
+        <v>oil</v>
       </c>
       <c r="E53" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -10091,10 +10099,10 @@
       </c>
       <c r="C54" t="str">
         <f t="shared" si="1"/>
-        <v>windoff</v>
+        <v>solar</v>
       </c>
       <c r="E54" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -10103,9 +10111,21 @@
       </c>
       <c r="C55" t="str">
         <f t="shared" si="1"/>
+        <v>windoff</v>
+      </c>
+      <c r="E55" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" t="s">
+        <v>273</v>
+      </c>
+      <c r="C56" t="str">
+        <f t="shared" si="1"/>
         <v>windon</v>
       </c>
-      <c r="E55" t="s">
+      <c r="E56" t="s">
         <v>215</v>
       </c>
     </row>

--- a/VerveStacks_ZAF_grids_kan/ReportDefs_vervestacks.xlsx
+++ b/VerveStacks_ZAF_grids_kan/ReportDefs_vervestacks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_ZAF_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E5C17D9-1088-4D5F-A997-B4928C2B710C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC884A04-4F07-422C-B143-D7C7B4AC7736}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="4" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="geolocation" sheetId="72" r:id="rId1"/>
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7859" uniqueCount="1248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8186" uniqueCount="1464">
   <si>
     <t>Unit</t>
   </si>
@@ -3827,6 +3827,654 @@
   </si>
   <si>
     <t>OIL</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100348</t>
+  </si>
+  <si>
+    <t>Arnot 1</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100349</t>
+  </si>
+  <si>
+    <t>Arnot 2</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100350</t>
+  </si>
+  <si>
+    <t>Arnot 3</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100351</t>
+  </si>
+  <si>
+    <t>Arnot 4</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100352</t>
+  </si>
+  <si>
+    <t>Arnot 5</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100353</t>
+  </si>
+  <si>
+    <t>Arnot 6</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000101168</t>
+  </si>
+  <si>
+    <t>Camden 1</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000101169</t>
+  </si>
+  <si>
+    <t>Camden 2</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000101170</t>
+  </si>
+  <si>
+    <t>Camden 3</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000101171</t>
+  </si>
+  <si>
+    <t>Camden 4</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000101172</t>
+  </si>
+  <si>
+    <t>Camden 5</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000101173</t>
+  </si>
+  <si>
+    <t>Camden 6</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000101174</t>
+  </si>
+  <si>
+    <t>Camden 7</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000101175</t>
+  </si>
+  <si>
+    <t>Camden 8</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102524</t>
+  </si>
+  <si>
+    <t>Duvha 1</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102525</t>
+  </si>
+  <si>
+    <t>Duvha 2</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102527</t>
+  </si>
+  <si>
+    <t>Duvha 4</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102528</t>
+  </si>
+  <si>
+    <t>Duvha 5</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102529</t>
+  </si>
+  <si>
+    <t>Duvha 6</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000103136</t>
+  </si>
+  <si>
+    <t>Grootvlei 1</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000103137</t>
+  </si>
+  <si>
+    <t>Grootvlei 2</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000103138</t>
+  </si>
+  <si>
+    <t>Grootvlei 3</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000103807</t>
+  </si>
+  <si>
+    <t>Hendrina 10</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000103808</t>
+  </si>
+  <si>
+    <t>Hendrina 2</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000103810</t>
+  </si>
+  <si>
+    <t>Hendrina 4</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000103811</t>
+  </si>
+  <si>
+    <t>Hendrina 5</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000103812</t>
+  </si>
+  <si>
+    <t>Hendrina 6</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000103813</t>
+  </si>
+  <si>
+    <t>Hendrina 7</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105640</t>
+  </si>
+  <si>
+    <t>Kelvin A1</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105641</t>
+  </si>
+  <si>
+    <t>Kelvin A2</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105642</t>
+  </si>
+  <si>
+    <t>Kelvin A3</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105643</t>
+  </si>
+  <si>
+    <t>Kelvin A4</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105644</t>
+  </si>
+  <si>
+    <t>Kelvin A5</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105645</t>
+  </si>
+  <si>
+    <t>Kelvin A6</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105646</t>
+  </si>
+  <si>
+    <t>Kelvin B10</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105647</t>
+  </si>
+  <si>
+    <t>Kelvin B11</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105648</t>
+  </si>
+  <si>
+    <t>Kelvin B12</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105649</t>
+  </si>
+  <si>
+    <t>Kelvin B13</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105650</t>
+  </si>
+  <si>
+    <t>Kelvin B7</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105651</t>
+  </si>
+  <si>
+    <t>Kelvin B8</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105652</t>
+  </si>
+  <si>
+    <t>Kelvin B9</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105663</t>
+  </si>
+  <si>
+    <t>Kendal 1</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105664</t>
+  </si>
+  <si>
+    <t>Kendal 2</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105665</t>
+  </si>
+  <si>
+    <t>Kendal 3</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105666</t>
+  </si>
+  <si>
+    <t>Kendal 4</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105667</t>
+  </si>
+  <si>
+    <t>Kendal 5</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105668</t>
+  </si>
+  <si>
+    <t>Kendal 6</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105828</t>
+  </si>
+  <si>
+    <t>Komati 1</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105829</t>
+  </si>
+  <si>
+    <t>Komati 2</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105830</t>
+  </si>
+  <si>
+    <t>Komati 3</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105831</t>
+  </si>
+  <si>
+    <t>Komati 4</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105832</t>
+  </si>
+  <si>
+    <t>Komati 5</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105833</t>
+  </si>
+  <si>
+    <t>Komati 6</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105834</t>
+  </si>
+  <si>
+    <t>Komati 7</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105835</t>
+  </si>
+  <si>
+    <t>Komati 8</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105836</t>
+  </si>
+  <si>
+    <t>Komati 9</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105964</t>
+  </si>
+  <si>
+    <t>Kriel 1</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105965</t>
+  </si>
+  <si>
+    <t>Kriel 2</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105966</t>
+  </si>
+  <si>
+    <t>Kriel 3</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105967</t>
+  </si>
+  <si>
+    <t>Kriel 4</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105968</t>
+  </si>
+  <si>
+    <t>Kriel 5</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105969</t>
+  </si>
+  <si>
+    <t>Kriel 6</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106240</t>
+  </si>
+  <si>
+    <t>Lethabo 1</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106241</t>
+  </si>
+  <si>
+    <t>Lethabo 2</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106242</t>
+  </si>
+  <si>
+    <t>Lethabo 3</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106243</t>
+  </si>
+  <si>
+    <t>Lethabo 4</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106244</t>
+  </si>
+  <si>
+    <t>Lethabo 5</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106245</t>
+  </si>
+  <si>
+    <t>Lethabo 6</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106600</t>
+  </si>
+  <si>
+    <t>Majuba 1</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106601</t>
+  </si>
+  <si>
+    <t>Majuba 2</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106602</t>
+  </si>
+  <si>
+    <t>Majuba 3</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106603</t>
+  </si>
+  <si>
+    <t>Majuba 4</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106604</t>
+  </si>
+  <si>
+    <t>Majuba 5</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106605</t>
+  </si>
+  <si>
+    <t>Majuba 6</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106720</t>
+  </si>
+  <si>
+    <t>Matimba 1</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106721</t>
+  </si>
+  <si>
+    <t>Matimba 2</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106722</t>
+  </si>
+  <si>
+    <t>Matimba 3</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106723</t>
+  </si>
+  <si>
+    <t>Matimba 4</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106724</t>
+  </si>
+  <si>
+    <t>Matimba 5</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106725</t>
+  </si>
+  <si>
+    <t>Matimba 6</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106726</t>
+  </si>
+  <si>
+    <t>Matla 1</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106727</t>
+  </si>
+  <si>
+    <t>Matla 2</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106728</t>
+  </si>
+  <si>
+    <t>Matla 3</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106729</t>
+  </si>
+  <si>
+    <t>Matla 4</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106730</t>
+  </si>
+  <si>
+    <t>Matla 5</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106731</t>
+  </si>
+  <si>
+    <t>Matla 6</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108568</t>
+  </si>
+  <si>
+    <t>Richards Bay Mill 1</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108569</t>
+  </si>
+  <si>
+    <t>Richards Bay Mill 2</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110396</t>
+  </si>
+  <si>
+    <t>Tutuka 1</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110397</t>
+  </si>
+  <si>
+    <t>Tutuka 2</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110398</t>
+  </si>
+  <si>
+    <t>Tutuka 3</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110399</t>
+  </si>
+  <si>
+    <t>Tutuka 4</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110400</t>
+  </si>
+  <si>
+    <t>Tutuka 5</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110401</t>
+  </si>
+  <si>
+    <t>Tutuka 6</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_G100000106039</t>
+  </si>
+  <si>
+    <t>Kusile 1</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_G100000106040</t>
+  </si>
+  <si>
+    <t>Kusile 2</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_G100000106041</t>
+  </si>
+  <si>
+    <t>Kusile 3</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_G100000106042</t>
+  </si>
+  <si>
+    <t>Kusile 4</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_G100000106043</t>
+  </si>
+  <si>
+    <t>Kusile 5</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_G100000106044</t>
+  </si>
+  <si>
+    <t>Kusile 6</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_G100000106780</t>
+  </si>
+  <si>
+    <t>Medupi 1</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_G100000106781</t>
+  </si>
+  <si>
+    <t>Medupi 2</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_G100000106782</t>
+  </si>
+  <si>
+    <t>Medupi 3</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_G100000106783</t>
+  </si>
+  <si>
+    <t>Medupi 4</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_G100000106784</t>
+  </si>
+  <si>
+    <t>Medupi 5</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_G100000106785</t>
+  </si>
+  <si>
+    <t>Medupi 6</t>
+  </si>
+  <si>
+    <t>coalplant</t>
+  </si>
+  <si>
+    <t>-COAL</t>
+  </si>
+  <si>
+    <t>COAL</t>
+  </si>
+  <si>
+    <t>t,p</t>
   </si>
 </sst>
 </file>
@@ -9448,12 +10096,13 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10ADB714-E6AA-4E3E-B77B-62B65BA0E218}">
-  <dimension ref="A1:G56"/>
+  <dimension ref="A1:G162"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="14.86328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.06640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="18.265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.265625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="6.46484375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.53125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="7.33203125" bestFit="1" customWidth="1"/>
@@ -10127,6 +10776,1172 @@
       </c>
       <c r="E56" t="s">
         <v>215</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B57" t="s">
+        <v>1248</v>
+      </c>
+      <c r="C57" t="s">
+        <v>1249</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B58" t="s">
+        <v>1250</v>
+      </c>
+      <c r="C58" t="s">
+        <v>1251</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B59" t="s">
+        <v>1252</v>
+      </c>
+      <c r="C59" t="s">
+        <v>1253</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B60" t="s">
+        <v>1254</v>
+      </c>
+      <c r="C60" t="s">
+        <v>1255</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B61" t="s">
+        <v>1256</v>
+      </c>
+      <c r="C61" t="s">
+        <v>1257</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B62" t="s">
+        <v>1258</v>
+      </c>
+      <c r="C62" t="s">
+        <v>1259</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B63" t="s">
+        <v>1260</v>
+      </c>
+      <c r="C63" t="s">
+        <v>1261</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B64" t="s">
+        <v>1262</v>
+      </c>
+      <c r="C64" t="s">
+        <v>1263</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3">
+      <c r="A65" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B65" t="s">
+        <v>1264</v>
+      </c>
+      <c r="C65" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3">
+      <c r="A66" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B66" t="s">
+        <v>1266</v>
+      </c>
+      <c r="C66" t="s">
+        <v>1267</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3">
+      <c r="A67" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B67" t="s">
+        <v>1268</v>
+      </c>
+      <c r="C67" t="s">
+        <v>1269</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3">
+      <c r="A68" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B68" t="s">
+        <v>1270</v>
+      </c>
+      <c r="C68" t="s">
+        <v>1271</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3">
+      <c r="A69" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B69" t="s">
+        <v>1272</v>
+      </c>
+      <c r="C69" t="s">
+        <v>1273</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3">
+      <c r="A70" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B70" t="s">
+        <v>1274</v>
+      </c>
+      <c r="C70" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3">
+      <c r="A71" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B71" t="s">
+        <v>1276</v>
+      </c>
+      <c r="C71" t="s">
+        <v>1277</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3">
+      <c r="A72" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B72" t="s">
+        <v>1278</v>
+      </c>
+      <c r="C72" t="s">
+        <v>1279</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3">
+      <c r="A73" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B73" t="s">
+        <v>1280</v>
+      </c>
+      <c r="C73" t="s">
+        <v>1281</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3">
+      <c r="A74" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B74" t="s">
+        <v>1282</v>
+      </c>
+      <c r="C74" t="s">
+        <v>1283</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3">
+      <c r="A75" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B75" t="s">
+        <v>1284</v>
+      </c>
+      <c r="C75" t="s">
+        <v>1285</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3">
+      <c r="A76" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B76" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C76" t="s">
+        <v>1287</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3">
+      <c r="A77" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B77" t="s">
+        <v>1288</v>
+      </c>
+      <c r="C77" t="s">
+        <v>1289</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3">
+      <c r="A78" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B78" t="s">
+        <v>1290</v>
+      </c>
+      <c r="C78" t="s">
+        <v>1291</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3">
+      <c r="A79" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B79" t="s">
+        <v>1292</v>
+      </c>
+      <c r="C79" t="s">
+        <v>1293</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3">
+      <c r="A80" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B80" t="s">
+        <v>1294</v>
+      </c>
+      <c r="C80" t="s">
+        <v>1295</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3">
+      <c r="A81" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B81" t="s">
+        <v>1296</v>
+      </c>
+      <c r="C81" t="s">
+        <v>1297</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3">
+      <c r="A82" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B82" t="s">
+        <v>1298</v>
+      </c>
+      <c r="C82" t="s">
+        <v>1299</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3">
+      <c r="A83" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B83" t="s">
+        <v>1300</v>
+      </c>
+      <c r="C83" t="s">
+        <v>1301</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3">
+      <c r="A84" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B84" t="s">
+        <v>1302</v>
+      </c>
+      <c r="C84" t="s">
+        <v>1303</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3">
+      <c r="A85" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B85" t="s">
+        <v>1304</v>
+      </c>
+      <c r="C85" t="s">
+        <v>1305</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3">
+      <c r="A86" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B86" t="s">
+        <v>1306</v>
+      </c>
+      <c r="C86" t="s">
+        <v>1307</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3">
+      <c r="A87" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B87" t="s">
+        <v>1308</v>
+      </c>
+      <c r="C87" t="s">
+        <v>1309</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3">
+      <c r="A88" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B88" t="s">
+        <v>1310</v>
+      </c>
+      <c r="C88" t="s">
+        <v>1311</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3">
+      <c r="A89" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B89" t="s">
+        <v>1312</v>
+      </c>
+      <c r="C89" t="s">
+        <v>1313</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3">
+      <c r="A90" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B90" t="s">
+        <v>1314</v>
+      </c>
+      <c r="C90" t="s">
+        <v>1315</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3">
+      <c r="A91" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B91" t="s">
+        <v>1316</v>
+      </c>
+      <c r="C91" t="s">
+        <v>1317</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3">
+      <c r="A92" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B92" t="s">
+        <v>1318</v>
+      </c>
+      <c r="C92" t="s">
+        <v>1319</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3">
+      <c r="A93" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B93" t="s">
+        <v>1320</v>
+      </c>
+      <c r="C93" t="s">
+        <v>1321</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3">
+      <c r="A94" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B94" t="s">
+        <v>1322</v>
+      </c>
+      <c r="C94" t="s">
+        <v>1323</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3">
+      <c r="A95" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B95" t="s">
+        <v>1324</v>
+      </c>
+      <c r="C95" t="s">
+        <v>1325</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3">
+      <c r="A96" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B96" t="s">
+        <v>1326</v>
+      </c>
+      <c r="C96" t="s">
+        <v>1327</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3">
+      <c r="A97" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B97" t="s">
+        <v>1328</v>
+      </c>
+      <c r="C97" t="s">
+        <v>1329</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3">
+      <c r="A98" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B98" t="s">
+        <v>1330</v>
+      </c>
+      <c r="C98" t="s">
+        <v>1331</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3">
+      <c r="A99" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B99" t="s">
+        <v>1332</v>
+      </c>
+      <c r="C99" t="s">
+        <v>1333</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3">
+      <c r="A100" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B100" t="s">
+        <v>1334</v>
+      </c>
+      <c r="C100" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3">
+      <c r="A101" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B101" t="s">
+        <v>1336</v>
+      </c>
+      <c r="C101" t="s">
+        <v>1337</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3">
+      <c r="A102" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B102" t="s">
+        <v>1338</v>
+      </c>
+      <c r="C102" t="s">
+        <v>1339</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3">
+      <c r="A103" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B103" t="s">
+        <v>1340</v>
+      </c>
+      <c r="C103" t="s">
+        <v>1341</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3">
+      <c r="A104" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B104" t="s">
+        <v>1342</v>
+      </c>
+      <c r="C104" t="s">
+        <v>1343</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3">
+      <c r="A105" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B105" t="s">
+        <v>1344</v>
+      </c>
+      <c r="C105" t="s">
+        <v>1345</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3">
+      <c r="A106" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B106" t="s">
+        <v>1346</v>
+      </c>
+      <c r="C106" t="s">
+        <v>1347</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3">
+      <c r="A107" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B107" t="s">
+        <v>1348</v>
+      </c>
+      <c r="C107" t="s">
+        <v>1349</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3">
+      <c r="A108" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B108" t="s">
+        <v>1350</v>
+      </c>
+      <c r="C108" t="s">
+        <v>1351</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3">
+      <c r="A109" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B109" t="s">
+        <v>1352</v>
+      </c>
+      <c r="C109" t="s">
+        <v>1353</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3">
+      <c r="A110" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B110" t="s">
+        <v>1354</v>
+      </c>
+      <c r="C110" t="s">
+        <v>1355</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3">
+      <c r="A111" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B111" t="s">
+        <v>1356</v>
+      </c>
+      <c r="C111" t="s">
+        <v>1357</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3">
+      <c r="A112" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B112" t="s">
+        <v>1358</v>
+      </c>
+      <c r="C112" t="s">
+        <v>1359</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3">
+      <c r="A113" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B113" t="s">
+        <v>1360</v>
+      </c>
+      <c r="C113" t="s">
+        <v>1361</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3">
+      <c r="A114" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B114" t="s">
+        <v>1362</v>
+      </c>
+      <c r="C114" t="s">
+        <v>1363</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3">
+      <c r="A115" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B115" t="s">
+        <v>1364</v>
+      </c>
+      <c r="C115" t="s">
+        <v>1365</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3">
+      <c r="A116" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B116" t="s">
+        <v>1366</v>
+      </c>
+      <c r="C116" t="s">
+        <v>1367</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3">
+      <c r="A117" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B117" t="s">
+        <v>1368</v>
+      </c>
+      <c r="C117" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3">
+      <c r="A118" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B118" t="s">
+        <v>1370</v>
+      </c>
+      <c r="C118" t="s">
+        <v>1371</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3">
+      <c r="A119" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B119" t="s">
+        <v>1372</v>
+      </c>
+      <c r="C119" t="s">
+        <v>1373</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3">
+      <c r="A120" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B120" t="s">
+        <v>1374</v>
+      </c>
+      <c r="C120" t="s">
+        <v>1375</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3">
+      <c r="A121" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B121" t="s">
+        <v>1376</v>
+      </c>
+      <c r="C121" t="s">
+        <v>1377</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3">
+      <c r="A122" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B122" t="s">
+        <v>1378</v>
+      </c>
+      <c r="C122" t="s">
+        <v>1379</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3">
+      <c r="A123" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B123" t="s">
+        <v>1380</v>
+      </c>
+      <c r="C123" t="s">
+        <v>1381</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3">
+      <c r="A124" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B124" t="s">
+        <v>1382</v>
+      </c>
+      <c r="C124" t="s">
+        <v>1383</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3">
+      <c r="A125" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B125" t="s">
+        <v>1384</v>
+      </c>
+      <c r="C125" t="s">
+        <v>1385</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3">
+      <c r="A126" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B126" t="s">
+        <v>1386</v>
+      </c>
+      <c r="C126" t="s">
+        <v>1387</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3">
+      <c r="A127" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B127" t="s">
+        <v>1388</v>
+      </c>
+      <c r="C127" t="s">
+        <v>1389</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3">
+      <c r="A128" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B128" t="s">
+        <v>1390</v>
+      </c>
+      <c r="C128" t="s">
+        <v>1391</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3">
+      <c r="A129" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B129" t="s">
+        <v>1392</v>
+      </c>
+      <c r="C129" t="s">
+        <v>1393</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3">
+      <c r="A130" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B130" t="s">
+        <v>1394</v>
+      </c>
+      <c r="C130" t="s">
+        <v>1395</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3">
+      <c r="A131" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B131" t="s">
+        <v>1396</v>
+      </c>
+      <c r="C131" t="s">
+        <v>1397</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3">
+      <c r="A132" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B132" t="s">
+        <v>1398</v>
+      </c>
+      <c r="C132" t="s">
+        <v>1399</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3">
+      <c r="A133" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B133" t="s">
+        <v>1400</v>
+      </c>
+      <c r="C133" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3">
+      <c r="A134" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B134" t="s">
+        <v>1402</v>
+      </c>
+      <c r="C134" t="s">
+        <v>1403</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3">
+      <c r="A135" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B135" t="s">
+        <v>1404</v>
+      </c>
+      <c r="C135" t="s">
+        <v>1405</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3">
+      <c r="A136" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B136" t="s">
+        <v>1406</v>
+      </c>
+      <c r="C136" t="s">
+        <v>1407</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3">
+      <c r="A137" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B137" t="s">
+        <v>1408</v>
+      </c>
+      <c r="C137" t="s">
+        <v>1409</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3">
+      <c r="A138" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B138" t="s">
+        <v>1410</v>
+      </c>
+      <c r="C138" t="s">
+        <v>1411</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3">
+      <c r="A139" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B139" t="s">
+        <v>1412</v>
+      </c>
+      <c r="C139" t="s">
+        <v>1413</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3">
+      <c r="A140" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B140" t="s">
+        <v>1414</v>
+      </c>
+      <c r="C140" t="s">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3">
+      <c r="A141" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B141" t="s">
+        <v>1416</v>
+      </c>
+      <c r="C141" t="s">
+        <v>1417</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3">
+      <c r="A142" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B142" t="s">
+        <v>1418</v>
+      </c>
+      <c r="C142" t="s">
+        <v>1419</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3">
+      <c r="A143" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B143" t="s">
+        <v>1420</v>
+      </c>
+      <c r="C143" t="s">
+        <v>1421</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3">
+      <c r="A144" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B144" t="s">
+        <v>1422</v>
+      </c>
+      <c r="C144" t="s">
+        <v>1423</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3">
+      <c r="A145" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B145" t="s">
+        <v>1424</v>
+      </c>
+      <c r="C145" t="s">
+        <v>1425</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3">
+      <c r="A146" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B146" t="s">
+        <v>1426</v>
+      </c>
+      <c r="C146" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3">
+      <c r="A147" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B147" t="s">
+        <v>1428</v>
+      </c>
+      <c r="C147" t="s">
+        <v>1429</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3">
+      <c r="A148" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B148" t="s">
+        <v>1430</v>
+      </c>
+      <c r="C148" t="s">
+        <v>1431</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3">
+      <c r="A149" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B149" t="s">
+        <v>1432</v>
+      </c>
+      <c r="C149" t="s">
+        <v>1433</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3">
+      <c r="A150" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B150" t="s">
+        <v>1434</v>
+      </c>
+      <c r="C150" t="s">
+        <v>1435</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3">
+      <c r="A151" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B151" t="s">
+        <v>1436</v>
+      </c>
+      <c r="C151" t="s">
+        <v>1437</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3">
+      <c r="A152" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B152" t="s">
+        <v>1438</v>
+      </c>
+      <c r="C152" t="s">
+        <v>1439</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3">
+      <c r="A153" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B153" t="s">
+        <v>1440</v>
+      </c>
+      <c r="C153" t="s">
+        <v>1441</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3">
+      <c r="A154" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B154" t="s">
+        <v>1442</v>
+      </c>
+      <c r="C154" t="s">
+        <v>1443</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3">
+      <c r="A155" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B155" t="s">
+        <v>1444</v>
+      </c>
+      <c r="C155" t="s">
+        <v>1445</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3">
+      <c r="A156" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B156" t="s">
+        <v>1446</v>
+      </c>
+      <c r="C156" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3">
+      <c r="A157" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B157" t="s">
+        <v>1448</v>
+      </c>
+      <c r="C157" t="s">
+        <v>1449</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3">
+      <c r="A158" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B158" t="s">
+        <v>1450</v>
+      </c>
+      <c r="C158" t="s">
+        <v>1451</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3">
+      <c r="A159" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B159" t="s">
+        <v>1452</v>
+      </c>
+      <c r="C159" t="s">
+        <v>1453</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3">
+      <c r="A160" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B160" t="s">
+        <v>1454</v>
+      </c>
+      <c r="C160" t="s">
+        <v>1455</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3">
+      <c r="A161" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B161" t="s">
+        <v>1456</v>
+      </c>
+      <c r="C161" t="s">
+        <v>1457</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3">
+      <c r="A162" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B162" t="s">
+        <v>1458</v>
+      </c>
+      <c r="C162" t="s">
+        <v>1459</v>
       </c>
     </row>
   </sheetData>
@@ -45801,7 +47616,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet19"/>
-  <dimension ref="A1:U30"/>
+  <dimension ref="A1:U31"/>
   <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13.86328125" bestFit="1" customWidth="1"/>
@@ -45983,6 +47798,9 @@
         <v>132</v>
       </c>
       <c r="D7" s="2"/>
+      <c r="F7" s="2" t="s">
+        <v>1461</v>
+      </c>
       <c r="H7" t="s">
         <v>25</v>
       </c>
@@ -46003,16 +47821,29 @@
     </row>
     <row r="8" spans="1:21">
       <c r="A8" t="s">
-        <v>4</v>
+        <v>54</v>
+      </c>
+      <c r="C8" t="s">
+        <v>132</v>
+      </c>
+      <c r="D8" s="2"/>
+      <c r="F8" t="s">
+        <v>1462</v>
+      </c>
+      <c r="H8" t="s">
+        <v>25</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>116</v>
+        <v>91</v>
       </c>
       <c r="K8" t="s">
-        <v>118</v>
+        <v>287</v>
       </c>
       <c r="N8" t="s">
-        <v>120</v>
+        <v>37</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>1463</v>
       </c>
       <c r="T8" s="3"/>
       <c r="U8" s="3"/>
@@ -46022,42 +47853,36 @@
         <v>4</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="K9" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="N9" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="T9" s="3"/>
       <c r="U9" s="3"/>
     </row>
     <row r="10" spans="1:21">
       <c r="A10" t="s">
-        <v>1099</v>
-      </c>
-      <c r="C10" t="s">
-        <v>1096</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>109</v>
+        <v>4</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>117</v>
       </c>
       <c r="K10" t="s">
-        <v>232</v>
-      </c>
-      <c r="M10" t="s">
-        <v>1100</v>
+        <v>119</v>
       </c>
       <c r="N10" t="s">
-        <v>1101</v>
+        <v>121</v>
       </c>
       <c r="T10" s="3"/>
       <c r="U10" s="3"/>
     </row>
     <row r="11" spans="1:21">
       <c r="A11" t="s">
-        <v>280</v>
+        <v>1099</v>
       </c>
       <c r="C11" t="s">
         <v>1096</v>
@@ -46068,13 +47893,18 @@
       <c r="K11" t="s">
         <v>232</v>
       </c>
+      <c r="M11" t="s">
+        <v>1100</v>
+      </c>
       <c r="N11" t="s">
-        <v>75</v>
-      </c>
+        <v>1101</v>
+      </c>
+      <c r="T11" s="3"/>
+      <c r="U11" s="3"/>
     </row>
     <row r="12" spans="1:21">
       <c r="A12" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="C12" t="s">
         <v>1096</v>
@@ -46091,10 +47921,10 @@
     </row>
     <row r="13" spans="1:21">
       <c r="A13" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C13" t="s">
-        <v>107</v>
+        <v>1096</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>109</v>
@@ -46103,12 +47933,12 @@
         <v>232</v>
       </c>
       <c r="N13" t="s">
-        <v>274</v>
+        <v>75</v>
       </c>
     </row>
     <row r="14" spans="1:21">
       <c r="A14" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="C14" t="s">
         <v>107</v>
@@ -46125,7 +47955,7 @@
     </row>
     <row r="15" spans="1:21">
       <c r="A15" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C15" t="s">
         <v>107</v>
@@ -46137,51 +47967,42 @@
         <v>232</v>
       </c>
       <c r="N15" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="16" spans="1:21">
       <c r="A16" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="C16" t="s">
-        <v>277</v>
-      </c>
-      <c r="D16" s="2"/>
-      <c r="I16" t="s">
-        <v>278</v>
+        <v>107</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>109</v>
       </c>
       <c r="K16" t="s">
         <v>232</v>
       </c>
       <c r="N16" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="17" spans="1:17">
-      <c r="A17" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="H17" t="s">
-        <v>25</v>
-      </c>
+      <c r="A17" t="s">
+        <v>279</v>
+      </c>
+      <c r="C17" t="s">
+        <v>277</v>
+      </c>
+      <c r="D17" s="2"/>
       <c r="I17" t="s">
         <v>278</v>
       </c>
       <c r="K17" t="s">
-        <v>288</v>
+        <v>232</v>
       </c>
       <c r="N17" t="s">
-        <v>1237</v>
-      </c>
-      <c r="P17" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q17" t="s">
-        <v>41</v>
+        <v>276</v>
       </c>
     </row>
     <row r="18" spans="1:17">
@@ -46191,14 +48012,23 @@
       <c r="B18" s="4" t="s">
         <v>50</v>
       </c>
+      <c r="H18" t="s">
+        <v>25</v>
+      </c>
       <c r="I18" t="s">
-        <v>128</v>
+        <v>278</v>
       </c>
       <c r="K18" t="s">
-        <v>129</v>
+        <v>288</v>
       </c>
       <c r="N18" t="s">
-        <v>130</v>
+        <v>1237</v>
+      </c>
+      <c r="P18" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="19" spans="1:17">
@@ -46208,101 +48038,104 @@
       <c r="B19" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="H19" t="s">
+      <c r="I19" t="s">
+        <v>128</v>
+      </c>
+      <c r="K19" t="s">
+        <v>129</v>
+      </c>
+      <c r="N19" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17">
+      <c r="A20" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="H20" t="s">
         <v>1235</v>
       </c>
-      <c r="I19" t="s">
+      <c r="I20" t="s">
         <v>1236</v>
       </c>
-      <c r="K19" t="s">
+      <c r="K20" t="s">
         <v>288</v>
       </c>
-      <c r="N19" t="s">
+      <c r="N20" t="s">
         <v>1238</v>
       </c>
-      <c r="Q19" t="s">
+      <c r="Q20" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="20" spans="1:17">
-      <c r="A20" t="s">
+    <row r="21" spans="1:17">
+      <c r="A21" t="s">
         <v>42</v>
       </c>
-      <c r="K20" t="s">
+      <c r="K21" t="s">
         <v>76</v>
       </c>
-      <c r="N20" t="s">
+      <c r="N21" t="s">
         <v>43</v>
       </c>
-      <c r="P20" t="s">
+      <c r="P21" t="s">
         <v>45</v>
       </c>
-      <c r="Q20" t="s">
+      <c r="Q21" t="s">
         <v>44</v>
-      </c>
-    </row>
-    <row r="21" spans="1:17">
-      <c r="A21" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="K21" t="s">
-        <v>288</v>
-      </c>
-      <c r="N21" t="s">
-        <v>55</v>
-      </c>
-      <c r="Q21" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="22" spans="1:17">
       <c r="A22" s="4" t="s">
-        <v>230</v>
+        <v>51</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>34</v>
       </c>
       <c r="K22" t="s">
-        <v>232</v>
+        <v>288</v>
       </c>
       <c r="N22" t="s">
-        <v>233</v>
+        <v>55</v>
       </c>
       <c r="Q22" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
     </row>
     <row r="23" spans="1:17">
       <c r="A23" s="4" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K23" t="s">
         <v>232</v>
       </c>
       <c r="N23" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="Q23" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="24" spans="1:17">
-      <c r="A24" t="s">
-        <v>6</v>
-      </c>
-      <c r="C24" t="s">
-        <v>1102</v>
+      <c r="A24" s="4" t="s">
+        <v>231</v>
       </c>
       <c r="K24" t="s">
-        <v>7</v>
+        <v>232</v>
       </c>
       <c r="N24" t="s">
-        <v>240</v>
+        <v>234</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="25" spans="1:17">
       <c r="A25" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="C25" t="s">
         <v>1102</v>
@@ -46311,49 +48144,43 @@
         <v>7</v>
       </c>
       <c r="N25" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17">
+      <c r="A26" t="s">
+        <v>34</v>
+      </c>
+      <c r="C26" t="s">
+        <v>1102</v>
+      </c>
+      <c r="K26" t="s">
+        <v>7</v>
+      </c>
+      <c r="N26" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="26" spans="1:17">
-      <c r="A26" s="4" t="s">
+    <row r="27" spans="1:17">
+      <c r="A27" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="D26" t="s">
+      <c r="D27" t="s">
         <v>247</v>
       </c>
-      <c r="I26" t="s">
+      <c r="I27" t="s">
         <v>248</v>
-      </c>
-      <c r="K26" t="s">
-        <v>140</v>
-      </c>
-      <c r="N26" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="27" spans="1:17">
-      <c r="A27" t="s">
-        <v>141</v>
-      </c>
-      <c r="I27" t="s">
-        <v>250</v>
       </c>
       <c r="K27" t="s">
         <v>140</v>
       </c>
       <c r="N27" t="s">
-        <v>268</v>
-      </c>
-      <c r="P27" t="s">
-        <v>265</v>
-      </c>
-      <c r="Q27" t="s">
-        <v>249</v>
+        <v>142</v>
       </c>
     </row>
     <row r="28" spans="1:17">
       <c r="A28" t="s">
-        <v>4</v>
+        <v>141</v>
       </c>
       <c r="I28" t="s">
         <v>250</v>
@@ -46362,7 +48189,7 @@
         <v>140</v>
       </c>
       <c r="N28" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="P28" t="s">
         <v>265</v>
@@ -46373,30 +48200,27 @@
     </row>
     <row r="29" spans="1:17">
       <c r="A29" t="s">
-        <v>6</v>
-      </c>
-      <c r="F29" t="s">
-        <v>272</v>
-      </c>
-      <c r="G29" t="s">
-        <v>272</v>
+        <v>4</v>
+      </c>
+      <c r="I29" t="s">
+        <v>250</v>
       </c>
       <c r="K29" t="s">
-        <v>7</v>
+        <v>140</v>
       </c>
       <c r="N29" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="P29" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="Q29" t="s">
-        <v>39</v>
+        <v>249</v>
       </c>
     </row>
     <row r="30" spans="1:17">
       <c r="A30" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="F30" t="s">
         <v>272</v>
@@ -46408,12 +48232,35 @@
         <v>7</v>
       </c>
       <c r="N30" t="s">
+        <v>270</v>
+      </c>
+      <c r="P30" t="s">
+        <v>266</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17">
+      <c r="A31" t="s">
+        <v>34</v>
+      </c>
+      <c r="F31" t="s">
+        <v>272</v>
+      </c>
+      <c r="G31" t="s">
+        <v>272</v>
+      </c>
+      <c r="K31" t="s">
+        <v>7</v>
+      </c>
+      <c r="N31" t="s">
         <v>271</v>
       </c>
-      <c r="P30" t="s">
+      <c r="P31" t="s">
         <v>267</v>
       </c>
-      <c r="Q30" t="s">
+      <c r="Q31" t="s">
         <v>39</v>
       </c>
     </row>

--- a/VerveStacks_ZAF_grids_kan/ReportDefs_vervestacks.xlsx
+++ b/VerveStacks_ZAF_grids_kan/ReportDefs_vervestacks.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_ZAF_grids_kan\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ZAF_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC884A04-4F07-422C-B143-D7C7B4AC7736}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32E143CD-A879-4246-8469-F429F566BE80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8186" uniqueCount="1464">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8187" uniqueCount="1464">
   <si>
     <t>Unit</t>
   </si>
@@ -3790,12 +3790,6 @@
     <t>Hi.95.CF6.N.Eco.2</t>
   </si>
   <si>
-    <t>DEM</t>
-  </si>
-  <si>
-    <t>elc_*</t>
-  </si>
-  <si>
     <t>Price_Fuel</t>
   </si>
   <si>
@@ -4475,6 +4469,12 @@
   </si>
   <si>
     <t>t,p</t>
+  </si>
+  <si>
+    <t>e[_]*,ELC</t>
+  </si>
+  <si>
+    <t>Marginal value of produced electricity</t>
   </si>
 </sst>
 </file>
@@ -10379,13 +10379,13 @@
         <v>63</v>
       </c>
       <c r="C23" t="s">
-        <v>1246</v>
+        <v>1244</v>
       </c>
       <c r="D23" t="s">
         <v>277</v>
       </c>
       <c r="E23" t="s">
-        <v>1247</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -10780,1168 +10780,1168 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="B57" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="C57" t="s">
-        <v>1249</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="B58" t="s">
-        <v>1250</v>
+        <v>1248</v>
       </c>
       <c r="C58" t="s">
-        <v>1251</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="B59" t="s">
-        <v>1252</v>
+        <v>1250</v>
       </c>
       <c r="C59" t="s">
-        <v>1253</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="B60" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="C60" t="s">
-        <v>1255</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="B61" t="s">
-        <v>1256</v>
+        <v>1254</v>
       </c>
       <c r="C61" t="s">
-        <v>1257</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="B62" t="s">
-        <v>1258</v>
+        <v>1256</v>
       </c>
       <c r="C62" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="B63" t="s">
-        <v>1260</v>
+        <v>1258</v>
       </c>
       <c r="C63" t="s">
-        <v>1261</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="B64" t="s">
-        <v>1262</v>
+        <v>1260</v>
       </c>
       <c r="C64" t="s">
-        <v>1263</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="B65" t="s">
-        <v>1264</v>
+        <v>1262</v>
       </c>
       <c r="C65" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="B66" t="s">
-        <v>1266</v>
+        <v>1264</v>
       </c>
       <c r="C66" t="s">
-        <v>1267</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="B67" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
       <c r="C67" t="s">
-        <v>1269</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="B68" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="C68" t="s">
-        <v>1271</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="B69" t="s">
-        <v>1272</v>
+        <v>1270</v>
       </c>
       <c r="C69" t="s">
-        <v>1273</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="B70" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="C70" t="s">
-        <v>1275</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="B71" t="s">
-        <v>1276</v>
+        <v>1274</v>
       </c>
       <c r="C71" t="s">
-        <v>1277</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="B72" t="s">
-        <v>1278</v>
+        <v>1276</v>
       </c>
       <c r="C72" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="B73" t="s">
-        <v>1280</v>
+        <v>1278</v>
       </c>
       <c r="C73" t="s">
-        <v>1281</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="B74" t="s">
-        <v>1282</v>
+        <v>1280</v>
       </c>
       <c r="C74" t="s">
-        <v>1283</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="B75" t="s">
-        <v>1284</v>
+        <v>1282</v>
       </c>
       <c r="C75" t="s">
-        <v>1285</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="B76" t="s">
-        <v>1286</v>
+        <v>1284</v>
       </c>
       <c r="C76" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="B77" t="s">
-        <v>1288</v>
+        <v>1286</v>
       </c>
       <c r="C77" t="s">
-        <v>1289</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="B78" t="s">
-        <v>1290</v>
+        <v>1288</v>
       </c>
       <c r="C78" t="s">
-        <v>1291</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="B79" t="s">
-        <v>1292</v>
+        <v>1290</v>
       </c>
       <c r="C79" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="B80" t="s">
-        <v>1294</v>
+        <v>1292</v>
       </c>
       <c r="C80" t="s">
-        <v>1295</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="B81" t="s">
-        <v>1296</v>
+        <v>1294</v>
       </c>
       <c r="C81" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="B82" t="s">
-        <v>1298</v>
+        <v>1296</v>
       </c>
       <c r="C82" t="s">
-        <v>1299</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="B83" t="s">
-        <v>1300</v>
+        <v>1298</v>
       </c>
       <c r="C83" t="s">
-        <v>1301</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="B84" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="C84" t="s">
-        <v>1303</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="B85" t="s">
-        <v>1304</v>
+        <v>1302</v>
       </c>
       <c r="C85" t="s">
-        <v>1305</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="B86" t="s">
-        <v>1306</v>
+        <v>1304</v>
       </c>
       <c r="C86" t="s">
-        <v>1307</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="B87" t="s">
-        <v>1308</v>
+        <v>1306</v>
       </c>
       <c r="C87" t="s">
-        <v>1309</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="B88" t="s">
-        <v>1310</v>
+        <v>1308</v>
       </c>
       <c r="C88" t="s">
-        <v>1311</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="B89" t="s">
-        <v>1312</v>
+        <v>1310</v>
       </c>
       <c r="C89" t="s">
-        <v>1313</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="B90" t="s">
-        <v>1314</v>
+        <v>1312</v>
       </c>
       <c r="C90" t="s">
-        <v>1315</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="B91" t="s">
-        <v>1316</v>
+        <v>1314</v>
       </c>
       <c r="C91" t="s">
-        <v>1317</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="B92" t="s">
-        <v>1318</v>
+        <v>1316</v>
       </c>
       <c r="C92" t="s">
-        <v>1319</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="B93" t="s">
-        <v>1320</v>
+        <v>1318</v>
       </c>
       <c r="C93" t="s">
-        <v>1321</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="B94" t="s">
-        <v>1322</v>
+        <v>1320</v>
       </c>
       <c r="C94" t="s">
-        <v>1323</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="95" spans="1:3">
       <c r="A95" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="B95" t="s">
-        <v>1324</v>
+        <v>1322</v>
       </c>
       <c r="C95" t="s">
-        <v>1325</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="B96" t="s">
-        <v>1326</v>
+        <v>1324</v>
       </c>
       <c r="C96" t="s">
-        <v>1327</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="97" spans="1:3">
       <c r="A97" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="B97" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="C97" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="98" spans="1:3">
       <c r="A98" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="B98" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="C98" t="s">
-        <v>1331</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="99" spans="1:3">
       <c r="A99" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="B99" t="s">
-        <v>1332</v>
+        <v>1330</v>
       </c>
       <c r="C99" t="s">
-        <v>1333</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="100" spans="1:3">
       <c r="A100" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="B100" t="s">
-        <v>1334</v>
+        <v>1332</v>
       </c>
       <c r="C100" t="s">
-        <v>1335</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="101" spans="1:3">
       <c r="A101" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="B101" t="s">
-        <v>1336</v>
+        <v>1334</v>
       </c>
       <c r="C101" t="s">
-        <v>1337</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="B102" t="s">
-        <v>1338</v>
+        <v>1336</v>
       </c>
       <c r="C102" t="s">
-        <v>1339</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="103" spans="1:3">
       <c r="A103" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="B103" t="s">
-        <v>1340</v>
+        <v>1338</v>
       </c>
       <c r="C103" t="s">
-        <v>1341</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="104" spans="1:3">
       <c r="A104" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="B104" t="s">
-        <v>1342</v>
+        <v>1340</v>
       </c>
       <c r="C104" t="s">
-        <v>1343</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="105" spans="1:3">
       <c r="A105" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="B105" t="s">
-        <v>1344</v>
+        <v>1342</v>
       </c>
       <c r="C105" t="s">
-        <v>1345</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="106" spans="1:3">
       <c r="A106" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="B106" t="s">
-        <v>1346</v>
+        <v>1344</v>
       </c>
       <c r="C106" t="s">
-        <v>1347</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="107" spans="1:3">
       <c r="A107" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="B107" t="s">
-        <v>1348</v>
+        <v>1346</v>
       </c>
       <c r="C107" t="s">
-        <v>1349</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="108" spans="1:3">
       <c r="A108" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="B108" t="s">
-        <v>1350</v>
+        <v>1348</v>
       </c>
       <c r="C108" t="s">
-        <v>1351</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="109" spans="1:3">
       <c r="A109" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="B109" t="s">
-        <v>1352</v>
+        <v>1350</v>
       </c>
       <c r="C109" t="s">
-        <v>1353</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="110" spans="1:3">
       <c r="A110" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="B110" t="s">
-        <v>1354</v>
+        <v>1352</v>
       </c>
       <c r="C110" t="s">
-        <v>1355</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="111" spans="1:3">
       <c r="A111" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="B111" t="s">
-        <v>1356</v>
+        <v>1354</v>
       </c>
       <c r="C111" t="s">
-        <v>1357</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="112" spans="1:3">
       <c r="A112" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="B112" t="s">
-        <v>1358</v>
+        <v>1356</v>
       </c>
       <c r="C112" t="s">
-        <v>1359</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="113" spans="1:3">
       <c r="A113" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="B113" t="s">
-        <v>1360</v>
+        <v>1358</v>
       </c>
       <c r="C113" t="s">
-        <v>1361</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="114" spans="1:3">
       <c r="A114" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="B114" t="s">
-        <v>1362</v>
+        <v>1360</v>
       </c>
       <c r="C114" t="s">
-        <v>1363</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="115" spans="1:3">
       <c r="A115" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="B115" t="s">
-        <v>1364</v>
+        <v>1362</v>
       </c>
       <c r="C115" t="s">
-        <v>1365</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="116" spans="1:3">
       <c r="A116" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="B116" t="s">
-        <v>1366</v>
+        <v>1364</v>
       </c>
       <c r="C116" t="s">
-        <v>1367</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="117" spans="1:3">
       <c r="A117" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="B117" t="s">
-        <v>1368</v>
+        <v>1366</v>
       </c>
       <c r="C117" t="s">
-        <v>1369</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="118" spans="1:3">
       <c r="A118" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="B118" t="s">
-        <v>1370</v>
+        <v>1368</v>
       </c>
       <c r="C118" t="s">
-        <v>1371</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="119" spans="1:3">
       <c r="A119" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="B119" t="s">
-        <v>1372</v>
+        <v>1370</v>
       </c>
       <c r="C119" t="s">
-        <v>1373</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="120" spans="1:3">
       <c r="A120" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="B120" t="s">
-        <v>1374</v>
+        <v>1372</v>
       </c>
       <c r="C120" t="s">
-        <v>1375</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="121" spans="1:3">
       <c r="A121" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="B121" t="s">
-        <v>1376</v>
+        <v>1374</v>
       </c>
       <c r="C121" t="s">
-        <v>1377</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="122" spans="1:3">
       <c r="A122" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="B122" t="s">
-        <v>1378</v>
+        <v>1376</v>
       </c>
       <c r="C122" t="s">
-        <v>1379</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="123" spans="1:3">
       <c r="A123" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="B123" t="s">
-        <v>1380</v>
+        <v>1378</v>
       </c>
       <c r="C123" t="s">
-        <v>1381</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="124" spans="1:3">
       <c r="A124" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="B124" t="s">
-        <v>1382</v>
+        <v>1380</v>
       </c>
       <c r="C124" t="s">
-        <v>1383</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="125" spans="1:3">
       <c r="A125" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="B125" t="s">
-        <v>1384</v>
+        <v>1382</v>
       </c>
       <c r="C125" t="s">
-        <v>1385</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="126" spans="1:3">
       <c r="A126" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="B126" t="s">
-        <v>1386</v>
+        <v>1384</v>
       </c>
       <c r="C126" t="s">
-        <v>1387</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="127" spans="1:3">
       <c r="A127" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="B127" t="s">
-        <v>1388</v>
+        <v>1386</v>
       </c>
       <c r="C127" t="s">
-        <v>1389</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="128" spans="1:3">
       <c r="A128" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="B128" t="s">
-        <v>1390</v>
+        <v>1388</v>
       </c>
       <c r="C128" t="s">
-        <v>1391</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="129" spans="1:3">
       <c r="A129" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="B129" t="s">
-        <v>1392</v>
+        <v>1390</v>
       </c>
       <c r="C129" t="s">
-        <v>1393</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="130" spans="1:3">
       <c r="A130" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="B130" t="s">
-        <v>1394</v>
+        <v>1392</v>
       </c>
       <c r="C130" t="s">
-        <v>1395</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="131" spans="1:3">
       <c r="A131" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="B131" t="s">
-        <v>1396</v>
+        <v>1394</v>
       </c>
       <c r="C131" t="s">
-        <v>1397</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="132" spans="1:3">
       <c r="A132" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="B132" t="s">
-        <v>1398</v>
+        <v>1396</v>
       </c>
       <c r="C132" t="s">
-        <v>1399</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="133" spans="1:3">
       <c r="A133" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="B133" t="s">
-        <v>1400</v>
+        <v>1398</v>
       </c>
       <c r="C133" t="s">
-        <v>1401</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="134" spans="1:3">
       <c r="A134" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="B134" t="s">
-        <v>1402</v>
+        <v>1400</v>
       </c>
       <c r="C134" t="s">
-        <v>1403</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="135" spans="1:3">
       <c r="A135" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="B135" t="s">
-        <v>1404</v>
+        <v>1402</v>
       </c>
       <c r="C135" t="s">
-        <v>1405</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="136" spans="1:3">
       <c r="A136" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="B136" t="s">
-        <v>1406</v>
+        <v>1404</v>
       </c>
       <c r="C136" t="s">
-        <v>1407</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="137" spans="1:3">
       <c r="A137" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="B137" t="s">
-        <v>1408</v>
+        <v>1406</v>
       </c>
       <c r="C137" t="s">
-        <v>1409</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="138" spans="1:3">
       <c r="A138" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="B138" t="s">
-        <v>1410</v>
+        <v>1408</v>
       </c>
       <c r="C138" t="s">
-        <v>1411</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="139" spans="1:3">
       <c r="A139" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="B139" t="s">
-        <v>1412</v>
+        <v>1410</v>
       </c>
       <c r="C139" t="s">
-        <v>1413</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="140" spans="1:3">
       <c r="A140" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="B140" t="s">
-        <v>1414</v>
+        <v>1412</v>
       </c>
       <c r="C140" t="s">
-        <v>1415</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="141" spans="1:3">
       <c r="A141" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="B141" t="s">
-        <v>1416</v>
+        <v>1414</v>
       </c>
       <c r="C141" t="s">
-        <v>1417</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="142" spans="1:3">
       <c r="A142" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="B142" t="s">
-        <v>1418</v>
+        <v>1416</v>
       </c>
       <c r="C142" t="s">
-        <v>1419</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="143" spans="1:3">
       <c r="A143" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="B143" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="C143" t="s">
-        <v>1421</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="144" spans="1:3">
       <c r="A144" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="B144" t="s">
-        <v>1422</v>
+        <v>1420</v>
       </c>
       <c r="C144" t="s">
-        <v>1423</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="145" spans="1:3">
       <c r="A145" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="B145" t="s">
-        <v>1424</v>
+        <v>1422</v>
       </c>
       <c r="C145" t="s">
-        <v>1425</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="146" spans="1:3">
       <c r="A146" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="B146" t="s">
-        <v>1426</v>
+        <v>1424</v>
       </c>
       <c r="C146" t="s">
-        <v>1427</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="147" spans="1:3">
       <c r="A147" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="B147" t="s">
-        <v>1428</v>
+        <v>1426</v>
       </c>
       <c r="C147" t="s">
-        <v>1429</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="148" spans="1:3">
       <c r="A148" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="B148" t="s">
-        <v>1430</v>
+        <v>1428</v>
       </c>
       <c r="C148" t="s">
-        <v>1431</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="149" spans="1:3">
       <c r="A149" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="B149" t="s">
-        <v>1432</v>
+        <v>1430</v>
       </c>
       <c r="C149" t="s">
-        <v>1433</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="150" spans="1:3">
       <c r="A150" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="B150" t="s">
-        <v>1434</v>
+        <v>1432</v>
       </c>
       <c r="C150" t="s">
-        <v>1435</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="151" spans="1:3">
       <c r="A151" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="B151" t="s">
-        <v>1436</v>
+        <v>1434</v>
       </c>
       <c r="C151" t="s">
-        <v>1437</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="152" spans="1:3">
       <c r="A152" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="B152" t="s">
-        <v>1438</v>
+        <v>1436</v>
       </c>
       <c r="C152" t="s">
-        <v>1439</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="153" spans="1:3">
       <c r="A153" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="B153" t="s">
-        <v>1440</v>
+        <v>1438</v>
       </c>
       <c r="C153" t="s">
-        <v>1441</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="154" spans="1:3">
       <c r="A154" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="B154" t="s">
-        <v>1442</v>
+        <v>1440</v>
       </c>
       <c r="C154" t="s">
-        <v>1443</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="155" spans="1:3">
       <c r="A155" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="B155" t="s">
-        <v>1444</v>
+        <v>1442</v>
       </c>
       <c r="C155" t="s">
-        <v>1445</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="156" spans="1:3">
       <c r="A156" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="B156" t="s">
-        <v>1446</v>
+        <v>1444</v>
       </c>
       <c r="C156" t="s">
-        <v>1447</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="157" spans="1:3">
       <c r="A157" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="B157" t="s">
-        <v>1448</v>
+        <v>1446</v>
       </c>
       <c r="C157" t="s">
-        <v>1449</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="158" spans="1:3">
       <c r="A158" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="B158" t="s">
-        <v>1450</v>
+        <v>1448</v>
       </c>
       <c r="C158" t="s">
-        <v>1451</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="159" spans="1:3">
       <c r="A159" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="B159" t="s">
-        <v>1452</v>
+        <v>1450</v>
       </c>
       <c r="C159" t="s">
-        <v>1453</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="160" spans="1:3">
       <c r="A160" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="B160" t="s">
-        <v>1454</v>
+        <v>1452</v>
       </c>
       <c r="C160" t="s">
-        <v>1455</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="161" spans="1:3">
       <c r="A161" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="B161" t="s">
-        <v>1456</v>
+        <v>1454</v>
       </c>
       <c r="C161" t="s">
-        <v>1457</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="162" spans="1:3">
       <c r="A162" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="B162" t="s">
-        <v>1458</v>
+        <v>1456</v>
       </c>
       <c r="C162" t="s">
-        <v>1459</v>
+        <v>1457</v>
       </c>
     </row>
   </sheetData>
@@ -29182,10 +29182,10 @@
         <v>77</v>
       </c>
       <c r="B8" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
       <c r="C8" t="s">
-        <v>1242</v>
+        <v>1240</v>
       </c>
       <c r="D8">
         <v>1000</v>
@@ -29196,7 +29196,7 @@
         <v>77</v>
       </c>
       <c r="B9" t="s">
-        <v>1243</v>
+        <v>1241</v>
       </c>
       <c r="C9" t="s">
         <v>104</v>
@@ -36212,7 +36212,7 @@
         <v>1103</v>
       </c>
       <c r="X5" t="s">
-        <v>1239</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="6" spans="2:31">
@@ -47785,7 +47785,7 @@
         <v>140</v>
       </c>
       <c r="N6" t="s">
-        <v>1244</v>
+        <v>1242</v>
       </c>
       <c r="T6" s="3"/>
       <c r="U6" s="3"/>
@@ -47799,7 +47799,7 @@
       </c>
       <c r="D7" s="2"/>
       <c r="F7" s="2" t="s">
-        <v>1461</v>
+        <v>1459</v>
       </c>
       <c r="H7" t="s">
         <v>25</v>
@@ -47828,7 +47828,7 @@
       </c>
       <c r="D8" s="2"/>
       <c r="F8" t="s">
-        <v>1462</v>
+        <v>1460</v>
       </c>
       <c r="H8" t="s">
         <v>25</v>
@@ -47843,7 +47843,7 @@
         <v>37</v>
       </c>
       <c r="Q8" t="s">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="T8" s="3"/>
       <c r="U8" s="3"/>
@@ -48022,7 +48022,7 @@
         <v>288</v>
       </c>
       <c r="N18" t="s">
-        <v>1237</v>
+        <v>1235</v>
       </c>
       <c r="P18" t="s">
         <v>40</v>
@@ -48056,16 +48056,19 @@
         <v>50</v>
       </c>
       <c r="H20" t="s">
-        <v>1235</v>
+        <v>25</v>
       </c>
       <c r="I20" t="s">
-        <v>1236</v>
+        <v>1462</v>
       </c>
       <c r="K20" t="s">
         <v>288</v>
       </c>
       <c r="N20" t="s">
-        <v>1238</v>
+        <v>1236</v>
+      </c>
+      <c r="P20" t="s">
+        <v>1463</v>
       </c>
       <c r="Q20" t="s">
         <v>110</v>
@@ -48352,10 +48355,10 @@
         <v>74</v>
       </c>
       <c r="E4" t="s">
-        <v>1240</v>
+        <v>1238</v>
       </c>
       <c r="F4" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
       <c r="I4" t="s">
         <v>103</v>
@@ -48369,13 +48372,13 @@
         <v>74</v>
       </c>
       <c r="D5" t="s">
-        <v>1244</v>
+        <v>1242</v>
       </c>
       <c r="E5" t="s">
+        <v>1239</v>
+      </c>
+      <c r="F5" t="s">
         <v>1241</v>
-      </c>
-      <c r="F5" t="s">
-        <v>1243</v>
       </c>
       <c r="I5" t="s">
         <v>103</v>
